--- a/prix/prix.xlsx
+++ b/prix/prix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\robinetterie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9572EE1-A484-42E3-BBAB-3F376FFEE3E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA670DF4-9488-4F3C-A5AA-B616600FAE31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="315">
   <si>
     <t>path</t>
   </si>
@@ -852,6 +852,135 @@
   </si>
   <si>
     <t>79161</t>
+  </si>
+  <si>
+    <t>schutte/24556.png</t>
+  </si>
+  <si>
+    <t>schutte/60170.png</t>
+  </si>
+  <si>
+    <t>schutte/60046.png</t>
+  </si>
+  <si>
+    <t>schutte/60531.png</t>
+  </si>
+  <si>
+    <t>schutte/60690.png</t>
+  </si>
+  <si>
+    <t>schutte/60096.png</t>
+  </si>
+  <si>
+    <t>schutte/60090.png</t>
+  </si>
+  <si>
+    <t>schutte/77440.png</t>
+  </si>
+  <si>
+    <t>schutte/77430.png</t>
+  </si>
+  <si>
+    <t>schutte/44406.png</t>
+  </si>
+  <si>
+    <t>schutte/44306.png</t>
+  </si>
+  <si>
+    <t>schutte/52445.png</t>
+  </si>
+  <si>
+    <t>schutte/33180.png</t>
+  </si>
+  <si>
+    <t>schutte/33186.png</t>
+  </si>
+  <si>
+    <t>schutte/54250.png</t>
+  </si>
+  <si>
+    <t>schutte/33190.png</t>
+  </si>
+  <si>
+    <t>schutte/33196.png</t>
+  </si>
+  <si>
+    <t>schutte/33100.png</t>
+  </si>
+  <si>
+    <t>schutte/33106.png</t>
+  </si>
+  <si>
+    <t>schutte/33120.png</t>
+  </si>
+  <si>
+    <t>schutte/33126.png</t>
+  </si>
+  <si>
+    <t>schutte/33110.png</t>
+  </si>
+  <si>
+    <t>schutte/33116.png</t>
+  </si>
+  <si>
+    <t>schutte/77410.png</t>
+  </si>
+  <si>
+    <t>schutte/44106.png</t>
+  </si>
+  <si>
+    <t>schutte/32210.png</t>
+  </si>
+  <si>
+    <t>schutte/46951.png</t>
+  </si>
+  <si>
+    <t>schutte/37955.png</t>
+  </si>
+  <si>
+    <t>schutte/37965.png</t>
+  </si>
+  <si>
+    <t>schutte/79116.png</t>
+  </si>
+  <si>
+    <t>schutte/79126.png</t>
+  </si>
+  <si>
+    <t>schutte/79760.png</t>
+  </si>
+  <si>
+    <t>schutte/79770.png</t>
+  </si>
+  <si>
+    <t>schutte/79142.png</t>
+  </si>
+  <si>
+    <t>schutte/79147.png</t>
+  </si>
+  <si>
+    <t>schutte/77266.png</t>
+  </si>
+  <si>
+    <t>schutte/35676.png</t>
+  </si>
+  <si>
+    <t>schutte/79616.png</t>
+  </si>
+  <si>
+    <t>schutte/79966.png</t>
+  </si>
+  <si>
+    <t>schutte/79586.png</t>
+  </si>
+  <si>
+    <t>schutte/79162.png</t>
+  </si>
+  <si>
+    <t>schutte/79166.png</t>
+  </si>
+  <si>
+    <t>schutte/79161.png</t>
   </si>
 </sst>
 </file>
@@ -2462,7 +2591,9 @@
       <c r="F52" s="76"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="5"/>
+      <c r="A53" s="5" t="s">
+        <v>273</v>
+      </c>
       <c r="B53" s="79" t="s">
         <v>188</v>
       </c>
@@ -2486,6 +2617,9 @@
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54" s="4" t="s">
+        <v>274</v>
+      </c>
       <c r="B54" s="79" t="s">
         <v>189</v>
       </c>
@@ -2509,6 +2643,9 @@
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A55" s="4" t="s">
+        <v>275</v>
+      </c>
       <c r="B55" s="79" t="s">
         <v>190</v>
       </c>
@@ -2532,6 +2669,9 @@
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A56" s="4" t="s">
+        <v>276</v>
+      </c>
       <c r="B56" s="79" t="s">
         <v>191</v>
       </c>
@@ -2555,7 +2695,9 @@
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A57" s="5"/>
+      <c r="A57" s="5" t="s">
+        <v>277</v>
+      </c>
       <c r="B57" s="79" t="s">
         <v>192</v>
       </c>
@@ -2579,7 +2721,9 @@
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" s="5"/>
+      <c r="A58" s="5" t="s">
+        <v>278</v>
+      </c>
       <c r="B58" s="79" t="s">
         <v>193</v>
       </c>
@@ -2603,7 +2747,9 @@
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="5"/>
+      <c r="A59" s="5" t="s">
+        <v>279</v>
+      </c>
       <c r="B59" s="79" t="s">
         <v>194</v>
       </c>
@@ -2627,7 +2773,9 @@
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="5"/>
+      <c r="A60" s="5" t="s">
+        <v>280</v>
+      </c>
       <c r="B60" s="79" t="s">
         <v>195</v>
       </c>
@@ -2652,7 +2800,9 @@
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="5"/>
+      <c r="A61" s="5" t="s">
+        <v>281</v>
+      </c>
       <c r="B61" s="79" t="s">
         <v>196</v>
       </c>
@@ -2677,7 +2827,9 @@
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="5"/>
+      <c r="A62" s="5" t="s">
+        <v>282</v>
+      </c>
       <c r="B62" s="79" t="s">
         <v>197</v>
       </c>
@@ -2702,7 +2854,9 @@
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A63" s="5"/>
+      <c r="A63" s="5" t="s">
+        <v>283</v>
+      </c>
       <c r="B63" s="79" t="s">
         <v>198</v>
       </c>
@@ -2726,7 +2880,9 @@
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A64" s="5"/>
+      <c r="A64" s="5" t="s">
+        <v>284</v>
+      </c>
       <c r="B64" s="79" t="s">
         <v>199</v>
       </c>
@@ -2750,7 +2906,9 @@
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A65" s="5"/>
+      <c r="A65" s="5" t="s">
+        <v>285</v>
+      </c>
       <c r="B65" s="79" t="s">
         <v>200</v>
       </c>
@@ -2774,7 +2932,9 @@
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A66" s="5"/>
+      <c r="A66" s="5" t="s">
+        <v>286</v>
+      </c>
       <c r="B66" s="79" t="s">
         <v>201</v>
       </c>
@@ -2798,7 +2958,9 @@
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A67" s="5"/>
+      <c r="A67" s="5" t="s">
+        <v>287</v>
+      </c>
       <c r="B67" s="79" t="s">
         <v>202</v>
       </c>
@@ -2822,7 +2984,9 @@
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A68" s="5"/>
+      <c r="A68" s="5" t="s">
+        <v>288</v>
+      </c>
       <c r="B68" s="79" t="s">
         <v>203</v>
       </c>
@@ -2846,7 +3010,9 @@
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A69" s="5"/>
+      <c r="A69" s="5" t="s">
+        <v>289</v>
+      </c>
       <c r="B69" s="79" t="s">
         <v>204</v>
       </c>
@@ -2870,7 +3036,9 @@
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A70" s="5"/>
+      <c r="A70" s="5" t="s">
+        <v>290</v>
+      </c>
       <c r="B70" s="79" t="s">
         <v>205</v>
       </c>
@@ -2894,7 +3062,9 @@
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A71" s="5"/>
+      <c r="A71" s="5" t="s">
+        <v>291</v>
+      </c>
       <c r="B71" s="79" t="s">
         <v>204</v>
       </c>
@@ -2918,7 +3088,9 @@
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A72" s="5"/>
+      <c r="A72" s="5" t="s">
+        <v>292</v>
+      </c>
       <c r="B72" s="79" t="s">
         <v>205</v>
       </c>
@@ -2942,7 +3114,9 @@
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A73" s="5"/>
+      <c r="A73" s="5" t="s">
+        <v>293</v>
+      </c>
       <c r="B73" s="79" t="s">
         <v>206</v>
       </c>
@@ -2966,7 +3140,9 @@
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A74" s="5"/>
+      <c r="A74" s="5" t="s">
+        <v>294</v>
+      </c>
       <c r="B74" s="79" t="s">
         <v>207</v>
       </c>
@@ -2990,7 +3166,9 @@
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A75" s="5"/>
+      <c r="A75" s="5" t="s">
+        <v>295</v>
+      </c>
       <c r="B75" s="79" t="s">
         <v>208</v>
       </c>
@@ -3014,7 +3192,9 @@
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A76" s="5"/>
+      <c r="A76" s="5" t="s">
+        <v>296</v>
+      </c>
       <c r="B76" s="79" t="s">
         <v>209</v>
       </c>
@@ -3038,7 +3218,9 @@
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A77" s="5"/>
+      <c r="A77" s="5" t="s">
+        <v>297</v>
+      </c>
       <c r="B77" s="79" t="s">
         <v>210</v>
       </c>
@@ -3062,7 +3244,9 @@
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A78" s="5"/>
+      <c r="A78" s="5" t="s">
+        <v>298</v>
+      </c>
       <c r="B78" s="79" t="s">
         <v>211</v>
       </c>
@@ -3086,7 +3270,9 @@
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A79" s="5"/>
+      <c r="A79" s="5" t="s">
+        <v>299</v>
+      </c>
       <c r="B79" s="79" t="s">
         <v>212</v>
       </c>
@@ -3110,7 +3296,9 @@
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A80" s="5"/>
+      <c r="A80" s="5" t="s">
+        <v>300</v>
+      </c>
       <c r="B80" s="79" t="s">
         <v>213</v>
       </c>
@@ -3134,7 +3322,9 @@
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A81" s="5"/>
+      <c r="A81" s="5" t="s">
+        <v>301</v>
+      </c>
       <c r="B81" s="79" t="s">
         <v>214</v>
       </c>
@@ -3158,7 +3348,9 @@
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A82" s="5"/>
+      <c r="A82" s="5" t="s">
+        <v>302</v>
+      </c>
       <c r="B82" s="79" t="s">
         <v>215</v>
       </c>
@@ -3182,7 +3374,9 @@
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A83" s="5"/>
+      <c r="A83" s="5" t="s">
+        <v>303</v>
+      </c>
       <c r="B83" s="79" t="s">
         <v>216</v>
       </c>
@@ -3207,7 +3401,9 @@
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A84" s="5"/>
+      <c r="A84" s="5" t="s">
+        <v>304</v>
+      </c>
       <c r="B84" s="79" t="s">
         <v>217</v>
       </c>
@@ -3232,7 +3428,9 @@
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A85" s="5"/>
+      <c r="A85" s="5" t="s">
+        <v>305</v>
+      </c>
       <c r="B85" s="79" t="s">
         <v>218</v>
       </c>
@@ -3257,7 +3455,9 @@
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A86" s="5"/>
+      <c r="A86" s="5" t="s">
+        <v>306</v>
+      </c>
       <c r="B86" s="79" t="s">
         <v>219</v>
       </c>
@@ -3282,7 +3482,9 @@
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A87" s="5"/>
+      <c r="A87" s="5" t="s">
+        <v>307</v>
+      </c>
       <c r="B87" s="79" t="s">
         <v>220</v>
       </c>
@@ -3307,7 +3509,9 @@
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A88" s="5"/>
+      <c r="A88" s="5" t="s">
+        <v>308</v>
+      </c>
       <c r="B88" s="79" t="s">
         <v>221</v>
       </c>
@@ -3332,7 +3536,9 @@
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A89" s="5"/>
+      <c r="A89" s="5" t="s">
+        <v>309</v>
+      </c>
       <c r="B89" s="79" t="s">
         <v>222</v>
       </c>
@@ -3357,7 +3563,9 @@
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A90" s="5"/>
+      <c r="A90" s="5" t="s">
+        <v>272</v>
+      </c>
       <c r="B90" s="79" t="s">
         <v>223</v>
       </c>
@@ -3382,7 +3590,9 @@
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A91" s="5"/>
+      <c r="A91" s="5" t="s">
+        <v>310</v>
+      </c>
       <c r="B91" s="79" t="s">
         <v>224</v>
       </c>
@@ -3407,7 +3617,9 @@
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A92" s="5"/>
+      <c r="A92" s="5" t="s">
+        <v>311</v>
+      </c>
       <c r="B92" s="79" t="s">
         <v>225</v>
       </c>
@@ -3432,7 +3644,9 @@
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A93" s="5"/>
+      <c r="A93" s="5" t="s">
+        <v>312</v>
+      </c>
       <c r="B93" s="79" t="s">
         <v>226</v>
       </c>
@@ -3457,7 +3671,9 @@
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A94" s="5"/>
+      <c r="A94" s="5" t="s">
+        <v>313</v>
+      </c>
       <c r="B94" s="79" t="s">
         <v>227</v>
       </c>
@@ -3482,7 +3698,9 @@
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A95" s="5"/>
+      <c r="A95" s="5" t="s">
+        <v>314</v>
+      </c>
       <c r="B95" s="79" t="s">
         <v>228</v>
       </c>

--- a/prix/prix.xlsx
+++ b/prix/prix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\robinetterie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA670DF4-9488-4F3C-A5AA-B616600FAE31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B05A7376-D66E-45A1-975D-66F12586B168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="338">
   <si>
     <t>path</t>
   </si>
@@ -981,6 +981,75 @@
   </si>
   <si>
     <t>schutte/79161.png</t>
+  </si>
+  <si>
+    <t>427110</t>
+  </si>
+  <si>
+    <t>paffoni/sk180cr.png</t>
+  </si>
+  <si>
+    <t>paffoni/sk168cr.png</t>
+  </si>
+  <si>
+    <t>paffoni/red183cr.png</t>
+  </si>
+  <si>
+    <t>paffoni/ca071hcr.png</t>
+  </si>
+  <si>
+    <t>paffoni/elo75cr.png</t>
+  </si>
+  <si>
+    <t>paffoni/lig077cr.png</t>
+  </si>
+  <si>
+    <t>paffoni/427110.png</t>
+  </si>
+  <si>
+    <t>paffoni/sk075hcrews.png</t>
+  </si>
+  <si>
+    <t>paffoni/eqs168crnew.png</t>
+  </si>
+  <si>
+    <t>paffoni/eqs022crnew.png</t>
+  </si>
+  <si>
+    <t>paffoni/sk023cr.png</t>
+  </si>
+  <si>
+    <t>paffoni/bl182cr.png</t>
+  </si>
+  <si>
+    <t>paffoni/blu180cr.png</t>
+  </si>
+  <si>
+    <t>paffoni/liq022cr.png</t>
+  </si>
+  <si>
+    <t>paffoni/eqs22crnewliq022cr.png</t>
+  </si>
+  <si>
+    <t>paffoni/rin180cr.png</t>
+  </si>
+  <si>
+    <t>paffoni/lig075no.png</t>
+  </si>
+  <si>
+    <t>paffoni/elo75no.png</t>
+  </si>
+  <si>
+    <t>paffoni/red071no.png</t>
+  </si>
+  <si>
+    <t>paffoni/zsal210cr.png</t>
+  </si>
+  <si>
+    <t>paffoni/zflo031ag.png</t>
+  </si>
+  <si>
+    <t>paffoni/zflo062ag.png</t>
   </si>
 </sst>
 </file>
@@ -1070,7 +1139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1305,6 +1374,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1641,7 +1713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{065E4AF0-A4F8-4CE3-9E23-EDCEACB756BD}">
-  <dimension ref="A1:I452"/>
+  <dimension ref="A1:J452"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.88671875" style="4" bestFit="1" customWidth="1"/>
@@ -1652,9 +1724,11 @@
     <col min="6" max="6" width="9.88671875" style="78" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26.77734375" style="26" customWidth="1"/>
     <col min="8" max="8" width="36.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="39.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1675,7 +1749,7 @@
       </c>
       <c r="G1" s="26"/>
     </row>
-    <row r="2" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>68</v>
       </c>
@@ -1685,8 +1759,10 @@
       <c r="F2" s="8"/>
       <c r="G2" s="26"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>316</v>
+      </c>
       <c r="B3" s="17" t="s">
         <v>6</v>
       </c>
@@ -1703,9 +1779,12 @@
       <c r="G3" s="26" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
+      <c r="J3" s="26"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>317</v>
+      </c>
       <c r="B4" s="17" t="s">
         <v>7</v>
       </c>
@@ -1722,9 +1801,12 @@
       <c r="G4" s="26" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
+      <c r="J4" s="26"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>318</v>
+      </c>
       <c r="B5" s="17" t="s">
         <v>8</v>
       </c>
@@ -1741,9 +1823,12 @@
       <c r="G5" s="26" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
+      <c r="J5" s="26"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>319</v>
+      </c>
       <c r="B6" s="17" t="s">
         <v>9</v>
       </c>
@@ -1760,9 +1845,12 @@
       <c r="G6" s="26" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
+      <c r="J6" s="26"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>320</v>
+      </c>
       <c r="B7" s="17" t="s">
         <v>10</v>
       </c>
@@ -1779,9 +1867,12 @@
       <c r="G7" s="26" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="5"/>
+      <c r="J7" s="26"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>321</v>
+      </c>
       <c r="B8" s="17" t="s">
         <v>11</v>
       </c>
@@ -1798,9 +1889,12 @@
       <c r="G8" s="26" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
+      <c r="J8" s="26"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>322</v>
+      </c>
       <c r="B9" s="14" t="s">
         <v>36</v>
       </c>
@@ -1814,12 +1908,15 @@
       <c r="F9" s="76">
         <v>3</v>
       </c>
-      <c r="G9" s="26">
-        <v>427110</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
+      <c r="G9" s="26" t="s">
+        <v>315</v>
+      </c>
+      <c r="J9" s="26"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>323</v>
+      </c>
       <c r="B10" s="20" t="s">
         <v>21</v>
       </c>
@@ -1836,9 +1933,12 @@
       <c r="G10" s="26" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
+      <c r="J10" s="26"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>324</v>
+      </c>
       <c r="B11" s="20" t="s">
         <v>22</v>
       </c>
@@ -1855,9 +1955,12 @@
       <c r="G11" s="26" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
+      <c r="J11" s="26"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>325</v>
+      </c>
       <c r="B12" s="24" t="s">
         <v>23</v>
       </c>
@@ -1874,9 +1977,12 @@
       <c r="G12" s="26" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
+      <c r="J12" s="26"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>326</v>
+      </c>
       <c r="B13" s="20" t="s">
         <v>24</v>
       </c>
@@ -1893,9 +1999,12 @@
       <c r="G13" s="26" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
+      <c r="J13" s="26"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>327</v>
+      </c>
       <c r="B14" s="20" t="s">
         <v>25</v>
       </c>
@@ -1912,9 +2021,12 @@
       <c r="G14" s="26" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
+      <c r="J14" s="26"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>328</v>
+      </c>
       <c r="B15" s="20" t="s">
         <v>26</v>
       </c>
@@ -1931,9 +2043,12 @@
       <c r="G15" s="26" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
+      <c r="J15" s="26"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>329</v>
+      </c>
       <c r="B16" s="20" t="s">
         <v>27</v>
       </c>
@@ -1950,9 +2065,12 @@
       <c r="G16" s="26" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
+      <c r="J16" s="26"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>330</v>
+      </c>
       <c r="B17" s="20" t="s">
         <v>28</v>
       </c>
@@ -1969,9 +2087,12 @@
       <c r="G17" s="26" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
+      <c r="J17" s="26"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>331</v>
+      </c>
       <c r="B18" s="20" t="s">
         <v>29</v>
       </c>
@@ -1988,9 +2109,12 @@
       <c r="G18" s="26" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="5"/>
+      <c r="J18" s="26"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
+        <v>332</v>
+      </c>
       <c r="B19" s="20" t="s">
         <v>30</v>
       </c>
@@ -2007,9 +2131,12 @@
       <c r="G19" s="26" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
+      <c r="J19" s="26"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>333</v>
+      </c>
       <c r="B20" s="20" t="s">
         <v>31</v>
       </c>
@@ -2026,9 +2153,12 @@
       <c r="G20" s="26" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="5"/>
+      <c r="J20" s="26"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>334</v>
+      </c>
       <c r="B21" s="20" t="s">
         <v>32</v>
       </c>
@@ -2045,10 +2175,11 @@
       <c r="G21" s="26" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="J21" s="26"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="80" t="s">
         <v>33</v>
       </c>
       <c r="C22" s="21"/>
@@ -2064,9 +2195,12 @@
       <c r="G22" s="26" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="5"/>
+      <c r="J22" s="26"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
+        <v>335</v>
+      </c>
       <c r="B23" s="14" t="s">
         <v>70</v>
       </c>
@@ -2083,9 +2217,13 @@
       <c r="G23" s="26" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="5"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="26"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
+        <v>336</v>
+      </c>
       <c r="B24" s="14" t="s">
         <v>74</v>
       </c>
@@ -2102,9 +2240,13 @@
       <c r="G24" s="26" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="5"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="26"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
+        <v>337</v>
+      </c>
       <c r="B25" s="14" t="s">
         <v>72</v>
       </c>
@@ -2121,8 +2263,10 @@
       <c r="G25" s="26" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I25" s="14"/>
+      <c r="J25" s="26"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="23" t="s">
         <v>75</v>
       </c>
@@ -2131,7 +2275,7 @@
       <c r="E26" s="10"/>
       <c r="F26" s="76"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="9" t="s">
         <v>14</v>
@@ -2149,7 +2293,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
       <c r="B28" s="9" t="s">
         <v>35</v>
@@ -2167,7 +2311,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="9" t="s">
         <v>12</v>
@@ -2185,7 +2329,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
       <c r="B30" s="9" t="s">
         <v>102</v>
@@ -2203,7 +2347,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="5"/>
       <c r="B31" s="9" t="s">
         <v>16</v>
@@ -2221,7 +2365,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
       <c r="B32" s="9" t="s">
         <v>13</v>
@@ -2527,7 +2671,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="5"/>
       <c r="B49" s="63" t="s">
         <v>139</v>
@@ -2545,7 +2689,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="5"/>
       <c r="B50" s="67" t="s">
         <v>142</v>
@@ -2563,7 +2707,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="5"/>
       <c r="B51" s="71" t="s">
         <v>121</v>
@@ -2581,7 +2725,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="75" t="s">
         <v>144</v>
       </c>
@@ -2590,7 +2734,7 @@
       <c r="E52" s="9"/>
       <c r="F52" s="76"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>273</v>
       </c>
@@ -2609,14 +2753,8 @@
       <c r="G53" s="73" t="s">
         <v>229</v>
       </c>
-      <c r="H53" s="79" t="s">
-        <v>188</v>
-      </c>
-      <c r="I53" s="73" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>274</v>
       </c>
@@ -2635,14 +2773,8 @@
       <c r="G54" s="73" t="s">
         <v>230</v>
       </c>
-      <c r="H54" s="79" t="s">
-        <v>189</v>
-      </c>
-      <c r="I54" s="73" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>275</v>
       </c>
@@ -2661,14 +2793,8 @@
       <c r="G55" s="73" t="s">
         <v>231</v>
       </c>
-      <c r="H55" s="79" t="s">
-        <v>190</v>
-      </c>
-      <c r="I55" s="73" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>276</v>
       </c>
@@ -2687,14 +2813,8 @@
       <c r="G56" s="73" t="s">
         <v>232</v>
       </c>
-      <c r="H56" s="79" t="s">
-        <v>191</v>
-      </c>
-      <c r="I56" s="73" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>277</v>
       </c>
@@ -2713,14 +2833,8 @@
       <c r="G57" s="73" t="s">
         <v>233</v>
       </c>
-      <c r="H57" s="79" t="s">
-        <v>192</v>
-      </c>
-      <c r="I57" s="73" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>278</v>
       </c>
@@ -2739,14 +2853,8 @@
       <c r="G58" s="73" t="s">
         <v>234</v>
       </c>
-      <c r="H58" s="79" t="s">
-        <v>193</v>
-      </c>
-      <c r="I58" s="73" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>279</v>
       </c>
@@ -2765,14 +2873,8 @@
       <c r="G59" s="73" t="s">
         <v>235</v>
       </c>
-      <c r="H59" s="79" t="s">
-        <v>194</v>
-      </c>
-      <c r="I59" s="73" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>280</v>
       </c>
@@ -2792,14 +2894,8 @@
       <c r="G60" s="73" t="s">
         <v>236</v>
       </c>
-      <c r="H60" s="79" t="s">
-        <v>195</v>
-      </c>
-      <c r="I60" s="73" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>281</v>
       </c>
@@ -2819,14 +2915,8 @@
       <c r="G61" s="73" t="s">
         <v>237</v>
       </c>
-      <c r="H61" s="79" t="s">
-        <v>196</v>
-      </c>
-      <c r="I61" s="73" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
         <v>282</v>
       </c>
@@ -2846,14 +2936,8 @@
       <c r="G62" s="73" t="s">
         <v>238</v>
       </c>
-      <c r="H62" s="79" t="s">
-        <v>197</v>
-      </c>
-      <c r="I62" s="73" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
         <v>283</v>
       </c>
@@ -2872,14 +2956,8 @@
       <c r="G63" s="73" t="s">
         <v>239</v>
       </c>
-      <c r="H63" s="79" t="s">
-        <v>198</v>
-      </c>
-      <c r="I63" s="73" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
         <v>284</v>
       </c>
@@ -2898,14 +2976,8 @@
       <c r="G64" s="73" t="s">
         <v>240</v>
       </c>
-      <c r="H64" s="79" t="s">
-        <v>199</v>
-      </c>
-      <c r="I64" s="73" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
         <v>285</v>
       </c>
@@ -2924,14 +2996,8 @@
       <c r="G65" s="73" t="s">
         <v>241</v>
       </c>
-      <c r="H65" s="79" t="s">
-        <v>200</v>
-      </c>
-      <c r="I65" s="73" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
         <v>286</v>
       </c>
@@ -2950,14 +3016,8 @@
       <c r="G66" s="73" t="s">
         <v>242</v>
       </c>
-      <c r="H66" s="79" t="s">
-        <v>201</v>
-      </c>
-      <c r="I66" s="73" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
         <v>287</v>
       </c>
@@ -2976,14 +3036,8 @@
       <c r="G67" s="73" t="s">
         <v>243</v>
       </c>
-      <c r="H67" s="79" t="s">
-        <v>202</v>
-      </c>
-      <c r="I67" s="73" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>288</v>
       </c>
@@ -3002,14 +3056,8 @@
       <c r="G68" s="73" t="s">
         <v>244</v>
       </c>
-      <c r="H68" s="79" t="s">
-        <v>203</v>
-      </c>
-      <c r="I68" s="73" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>289</v>
       </c>
@@ -3028,14 +3076,8 @@
       <c r="G69" s="73" t="s">
         <v>245</v>
       </c>
-      <c r="H69" s="79" t="s">
-        <v>204</v>
-      </c>
-      <c r="I69" s="73" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
         <v>290</v>
       </c>
@@ -3054,14 +3096,8 @@
       <c r="G70" s="73" t="s">
         <v>246</v>
       </c>
-      <c r="H70" s="79" t="s">
-        <v>205</v>
-      </c>
-      <c r="I70" s="73" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>291</v>
       </c>
@@ -3080,14 +3116,8 @@
       <c r="G71" s="73" t="s">
         <v>247</v>
       </c>
-      <c r="H71" s="79" t="s">
-        <v>204</v>
-      </c>
-      <c r="I71" s="73" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
         <v>292</v>
       </c>
@@ -3106,14 +3136,8 @@
       <c r="G72" s="73" t="s">
         <v>248</v>
       </c>
-      <c r="H72" s="79" t="s">
-        <v>205</v>
-      </c>
-      <c r="I72" s="73" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
         <v>293</v>
       </c>
@@ -3132,14 +3156,8 @@
       <c r="G73" s="73" t="s">
         <v>249</v>
       </c>
-      <c r="H73" s="79" t="s">
-        <v>206</v>
-      </c>
-      <c r="I73" s="73" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
         <v>294</v>
       </c>
@@ -3158,14 +3176,8 @@
       <c r="G74" s="73" t="s">
         <v>250</v>
       </c>
-      <c r="H74" s="79" t="s">
-        <v>207</v>
-      </c>
-      <c r="I74" s="73" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
         <v>295</v>
       </c>
@@ -3184,14 +3196,8 @@
       <c r="G75" s="73" t="s">
         <v>251</v>
       </c>
-      <c r="H75" s="79" t="s">
-        <v>208</v>
-      </c>
-      <c r="I75" s="73" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
         <v>296</v>
       </c>
@@ -3210,14 +3216,8 @@
       <c r="G76" s="73" t="s">
         <v>252</v>
       </c>
-      <c r="H76" s="79" t="s">
-        <v>209</v>
-      </c>
-      <c r="I76" s="73" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
         <v>297</v>
       </c>
@@ -3236,14 +3236,8 @@
       <c r="G77" s="73" t="s">
         <v>253</v>
       </c>
-      <c r="H77" s="79" t="s">
-        <v>210</v>
-      </c>
-      <c r="I77" s="73" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>298</v>
       </c>
@@ -3262,14 +3256,8 @@
       <c r="G78" s="73" t="s">
         <v>254</v>
       </c>
-      <c r="H78" s="79" t="s">
-        <v>211</v>
-      </c>
-      <c r="I78" s="73" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
         <v>299</v>
       </c>
@@ -3288,14 +3276,8 @@
       <c r="G79" s="73" t="s">
         <v>255</v>
       </c>
-      <c r="H79" s="79" t="s">
-        <v>212</v>
-      </c>
-      <c r="I79" s="73" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
         <v>300</v>
       </c>
@@ -3314,14 +3296,8 @@
       <c r="G80" s="73" t="s">
         <v>256</v>
       </c>
-      <c r="H80" s="79" t="s">
-        <v>213</v>
-      </c>
-      <c r="I80" s="73" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>301</v>
       </c>
@@ -3340,14 +3316,8 @@
       <c r="G81" s="73" t="s">
         <v>257</v>
       </c>
-      <c r="H81" s="79" t="s">
-        <v>214</v>
-      </c>
-      <c r="I81" s="73" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
         <v>302</v>
       </c>
@@ -3366,14 +3336,8 @@
       <c r="G82" s="73" t="s">
         <v>258</v>
       </c>
-      <c r="H82" s="79" t="s">
-        <v>215</v>
-      </c>
-      <c r="I82" s="73" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
         <v>303</v>
       </c>
@@ -3393,14 +3357,8 @@
       <c r="G83" s="73" t="s">
         <v>259</v>
       </c>
-      <c r="H83" s="79" t="s">
-        <v>216</v>
-      </c>
-      <c r="I83" s="73" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
         <v>304</v>
       </c>
@@ -3420,14 +3378,8 @@
       <c r="G84" s="73" t="s">
         <v>260</v>
       </c>
-      <c r="H84" s="79" t="s">
-        <v>217</v>
-      </c>
-      <c r="I84" s="73" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
         <v>305</v>
       </c>
@@ -3447,14 +3399,8 @@
       <c r="G85" s="73" t="s">
         <v>261</v>
       </c>
-      <c r="H85" s="79" t="s">
-        <v>218</v>
-      </c>
-      <c r="I85" s="73" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
         <v>306</v>
       </c>
@@ -3474,14 +3420,8 @@
       <c r="G86" s="73" t="s">
         <v>262</v>
       </c>
-      <c r="H86" s="79" t="s">
-        <v>219</v>
-      </c>
-      <c r="I86" s="73" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
         <v>307</v>
       </c>
@@ -3501,14 +3441,8 @@
       <c r="G87" s="73" t="s">
         <v>263</v>
       </c>
-      <c r="H87" s="79" t="s">
-        <v>220</v>
-      </c>
-      <c r="I87" s="73" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
         <v>308</v>
       </c>
@@ -3528,14 +3462,8 @@
       <c r="G88" s="73" t="s">
         <v>264</v>
       </c>
-      <c r="H88" s="79" t="s">
-        <v>221</v>
-      </c>
-      <c r="I88" s="73" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
         <v>309</v>
       </c>
@@ -3555,14 +3483,8 @@
       <c r="G89" s="73" t="s">
         <v>265</v>
       </c>
-      <c r="H89" s="79" t="s">
-        <v>222</v>
-      </c>
-      <c r="I89" s="73" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
         <v>272</v>
       </c>
@@ -3582,14 +3504,8 @@
       <c r="G90" s="73" t="s">
         <v>266</v>
       </c>
-      <c r="H90" s="79" t="s">
-        <v>223</v>
-      </c>
-      <c r="I90" s="73" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
         <v>310</v>
       </c>
@@ -3609,14 +3525,8 @@
       <c r="G91" s="73" t="s">
         <v>267</v>
       </c>
-      <c r="H91" s="79" t="s">
-        <v>224</v>
-      </c>
-      <c r="I91" s="73" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
         <v>311</v>
       </c>
@@ -3636,14 +3546,8 @@
       <c r="G92" s="73" t="s">
         <v>268</v>
       </c>
-      <c r="H92" s="79" t="s">
-        <v>225</v>
-      </c>
-      <c r="I92" s="73" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
         <v>312</v>
       </c>
@@ -3663,14 +3567,8 @@
       <c r="G93" s="73" t="s">
         <v>269</v>
       </c>
-      <c r="H93" s="79" t="s">
-        <v>226</v>
-      </c>
-      <c r="I93" s="73" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
         <v>313</v>
       </c>
@@ -3690,14 +3588,8 @@
       <c r="G94" s="73" t="s">
         <v>270</v>
       </c>
-      <c r="H94" s="79" t="s">
-        <v>227</v>
-      </c>
-      <c r="I94" s="73" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
         <v>314</v>
       </c>
@@ -3717,14 +3609,8 @@
       <c r="G95" s="73" t="s">
         <v>271</v>
       </c>
-      <c r="H95" s="79" t="s">
-        <v>228</v>
-      </c>
-      <c r="I95" s="73" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="5"/>
       <c r="B96" s="10"/>
       <c r="C96" s="5"/>
@@ -6567,5 +6453,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/prix/prix.xlsx
+++ b/prix/prix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\robinetterie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B05A7376-D66E-45A1-975D-66F12586B168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E4B27F-5C0F-4408-9365-1FDF983745BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="359">
   <si>
     <t>path</t>
   </si>
@@ -1050,6 +1050,69 @@
   </si>
   <si>
     <t>paffoni/zflo062ag.png</t>
+  </si>
+  <si>
+    <t>23764001</t>
+  </si>
+  <si>
+    <t>grohe/32667001.png</t>
+  </si>
+  <si>
+    <t>grohe/32482002.png</t>
+  </si>
+  <si>
+    <t>grohe/30484.png</t>
+  </si>
+  <si>
+    <t>grohe/31191.png</t>
+  </si>
+  <si>
+    <t>grohe/23335.png</t>
+  </si>
+  <si>
+    <t>grohe/3282500e.png</t>
+  </si>
+  <si>
+    <t>grohe/20201.png</t>
+  </si>
+  <si>
+    <t>grohe/20422.png</t>
+  </si>
+  <si>
+    <t>grohe/33265003.png</t>
+  </si>
+  <si>
+    <t>grohe/33281003.png</t>
+  </si>
+  <si>
+    <t>grohe/31368001.png</t>
+  </si>
+  <si>
+    <t>grohe/33786.png</t>
+  </si>
+  <si>
+    <t>grohe/33202.png</t>
+  </si>
+  <si>
+    <t>grohe/31481.png</t>
+  </si>
+  <si>
+    <t>grohe/34827000.png</t>
+  </si>
+  <si>
+    <t>grohe/28154.png</t>
+  </si>
+  <si>
+    <t>grohe/28151.png</t>
+  </si>
+  <si>
+    <t>grohe/28150.png</t>
+  </si>
+  <si>
+    <t>grohe/26696000.png</t>
+  </si>
+  <si>
+    <t>grohe/26677000.png</t>
   </si>
 </sst>
 </file>
@@ -1059,7 +1122,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1090,6 +1153,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="-0.249977111117893"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1139,7 +1209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1232,6 +1302,9 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1313,54 +1386,9 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1377,6 +1405,27 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1721,7 +1770,7 @@
     <col min="3" max="3" width="20.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.88671875" style="78" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" style="64" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26.77734375" style="26" customWidth="1"/>
     <col min="8" max="8" width="36.109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="39.88671875" bestFit="1" customWidth="1"/>
@@ -1773,7 +1822,7 @@
       <c r="E3" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="76">
+      <c r="F3" s="62">
         <v>1</v>
       </c>
       <c r="G3" s="26" t="s">
@@ -1795,7 +1844,7 @@
       <c r="E4" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="76">
+      <c r="F4" s="62">
         <v>1</v>
       </c>
       <c r="G4" s="26" t="s">
@@ -1817,7 +1866,7 @@
       <c r="E5" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="76">
+      <c r="F5" s="62">
         <v>0</v>
       </c>
       <c r="G5" s="26" t="s">
@@ -1839,7 +1888,7 @@
       <c r="E6" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="76">
+      <c r="F6" s="62">
         <v>2</v>
       </c>
       <c r="G6" s="26" t="s">
@@ -1861,7 +1910,7 @@
       <c r="E7" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="F7" s="76">
+      <c r="F7" s="62">
         <v>3</v>
       </c>
       <c r="G7" s="26" t="s">
@@ -1883,7 +1932,7 @@
       <c r="E8" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="76">
+      <c r="F8" s="62">
         <v>3</v>
       </c>
       <c r="G8" s="26" t="s">
@@ -1905,7 +1954,7 @@
       <c r="E9" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="F9" s="76">
+      <c r="F9" s="62">
         <v>3</v>
       </c>
       <c r="G9" s="26" t="s">
@@ -1927,7 +1976,7 @@
       <c r="E10" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="76">
+      <c r="F10" s="62">
         <v>3</v>
       </c>
       <c r="G10" s="26" t="s">
@@ -1949,7 +1998,7 @@
       <c r="E11" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="76">
+      <c r="F11" s="62">
         <v>3</v>
       </c>
       <c r="G11" s="26" t="s">
@@ -1971,7 +2020,7 @@
       <c r="E12" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="F12" s="76">
+      <c r="F12" s="62">
         <v>0</v>
       </c>
       <c r="G12" s="26" t="s">
@@ -1993,7 +2042,7 @@
       <c r="E13" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="76">
+      <c r="F13" s="62">
         <v>2</v>
       </c>
       <c r="G13" s="26" t="s">
@@ -2015,7 +2064,7 @@
       <c r="E14" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="F14" s="76">
+      <c r="F14" s="62">
         <v>2</v>
       </c>
       <c r="G14" s="26" t="s">
@@ -2037,7 +2086,7 @@
       <c r="E15" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="F15" s="76">
+      <c r="F15" s="62">
         <v>1</v>
       </c>
       <c r="G15" s="26" t="s">
@@ -2059,7 +2108,7 @@
       <c r="E16" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="F16" s="76">
+      <c r="F16" s="62">
         <v>1</v>
       </c>
       <c r="G16" s="26" t="s">
@@ -2081,7 +2130,7 @@
       <c r="E17" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="76">
+      <c r="F17" s="62">
         <v>1</v>
       </c>
       <c r="G17" s="26" t="s">
@@ -2103,7 +2152,7 @@
       <c r="E18" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="76">
+      <c r="F18" s="62">
         <v>1</v>
       </c>
       <c r="G18" s="26" t="s">
@@ -2125,7 +2174,7 @@
       <c r="E19" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="76">
+      <c r="F19" s="62">
         <v>1</v>
       </c>
       <c r="G19" s="26" t="s">
@@ -2147,7 +2196,7 @@
       <c r="E20" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="F20" s="76">
+      <c r="F20" s="62">
         <v>4</v>
       </c>
       <c r="G20" s="26" t="s">
@@ -2169,7 +2218,7 @@
       <c r="E21" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="F21" s="76">
+      <c r="F21" s="62">
         <v>0</v>
       </c>
       <c r="G21" s="26" t="s">
@@ -2179,7 +2228,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
-      <c r="B22" s="80" t="s">
+      <c r="B22" s="66" t="s">
         <v>33</v>
       </c>
       <c r="C22" s="21"/>
@@ -2189,7 +2238,7 @@
       <c r="E22" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="F22" s="76">
+      <c r="F22" s="62">
         <v>2</v>
       </c>
       <c r="G22" s="26" t="s">
@@ -2211,7 +2260,7 @@
       <c r="E23" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="F23" s="76">
+      <c r="F23" s="62">
         <v>1</v>
       </c>
       <c r="G23" s="26" t="s">
@@ -2234,7 +2283,7 @@
       <c r="E24" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="F24" s="76">
+      <c r="F24" s="62">
         <v>4</v>
       </c>
       <c r="G24" s="26" t="s">
@@ -2257,7 +2306,7 @@
       <c r="E25" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="F25" s="76">
+      <c r="F25" s="62">
         <v>1</v>
       </c>
       <c r="G25" s="26" t="s">
@@ -2273,10 +2322,12 @@
       <c r="B26" s="10"/>
       <c r="D26" s="12"/>
       <c r="E26" s="10"/>
-      <c r="F26" s="76"/>
+      <c r="F26" s="62"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="5"/>
+      <c r="A27" s="5" t="s">
+        <v>339</v>
+      </c>
       <c r="B27" s="9" t="s">
         <v>14</v>
       </c>
@@ -2286,7 +2337,7 @@
       <c r="E27" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="F27" s="76">
+      <c r="F27" s="62">
         <v>1</v>
       </c>
       <c r="G27" s="26" t="s">
@@ -2294,7 +2345,9 @@
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="5"/>
+      <c r="A28" s="5" t="s">
+        <v>340</v>
+      </c>
       <c r="B28" s="9" t="s">
         <v>35</v>
       </c>
@@ -2304,7 +2357,7 @@
       <c r="E28" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="F28" s="76">
+      <c r="F28" s="62">
         <v>1</v>
       </c>
       <c r="G28" s="26" t="s">
@@ -2312,7 +2365,9 @@
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="5"/>
+      <c r="A29" s="5" t="s">
+        <v>341</v>
+      </c>
       <c r="B29" s="9" t="s">
         <v>12</v>
       </c>
@@ -2322,7 +2377,7 @@
       <c r="E29" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F29" s="76">
+      <c r="F29" s="62">
         <v>2</v>
       </c>
       <c r="G29" s="26" t="s">
@@ -2330,7 +2385,9 @@
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="5"/>
+      <c r="A30" s="5" t="s">
+        <v>342</v>
+      </c>
       <c r="B30" s="9" t="s">
         <v>102</v>
       </c>
@@ -2340,7 +2397,7 @@
       <c r="E30" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="F30" s="76">
+      <c r="F30" s="62">
         <v>1</v>
       </c>
       <c r="G30" s="26" t="s">
@@ -2348,7 +2405,9 @@
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="5"/>
+      <c r="A31" s="5" t="s">
+        <v>343</v>
+      </c>
       <c r="B31" s="9" t="s">
         <v>16</v>
       </c>
@@ -2358,7 +2417,7 @@
       <c r="E31" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F31" s="76">
+      <c r="F31" s="62">
         <v>7</v>
       </c>
       <c r="G31" s="26" t="s">
@@ -2366,7 +2425,9 @@
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="5"/>
+      <c r="A32" s="5" t="s">
+        <v>344</v>
+      </c>
       <c r="B32" s="9" t="s">
         <v>13</v>
       </c>
@@ -2376,7 +2437,7 @@
       <c r="E32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F32" s="76">
+      <c r="F32" s="62">
         <v>2</v>
       </c>
       <c r="G32" s="26" t="s">
@@ -2384,7 +2445,9 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="5"/>
+      <c r="A33" s="5" t="s">
+        <v>345</v>
+      </c>
       <c r="B33" s="9" t="s">
         <v>17</v>
       </c>
@@ -2394,7 +2457,7 @@
       <c r="E33" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F33" s="76">
+      <c r="F33" s="62">
         <v>3</v>
       </c>
       <c r="G33" s="26" t="s">
@@ -2402,25 +2465,27 @@
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="5"/>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D34" s="11">
+      <c r="C34" s="67"/>
+      <c r="D34" s="12">
         <v>134.22999999999999</v>
       </c>
-      <c r="E34" s="9" t="s">
+      <c r="E34" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F34" s="76">
+      <c r="F34" s="68">
         <v>2</v>
       </c>
-      <c r="G34" s="26" t="s">
+      <c r="G34" s="69" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="5"/>
+      <c r="A35" s="5" t="s">
+        <v>346</v>
+      </c>
       <c r="B35" s="9" t="s">
         <v>15</v>
       </c>
@@ -2430,7 +2495,7 @@
       <c r="E35" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F35" s="76">
+      <c r="F35" s="62">
         <v>2</v>
       </c>
       <c r="G35" s="26" t="s">
@@ -2438,7 +2503,9 @@
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="5"/>
+      <c r="A36" s="5" t="s">
+        <v>347</v>
+      </c>
       <c r="B36" s="9" t="s">
         <v>18</v>
       </c>
@@ -2448,7 +2515,7 @@
       <c r="E36" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="F36" s="76">
+      <c r="F36" s="62">
         <v>3</v>
       </c>
       <c r="G36" s="26" t="s">
@@ -2456,7 +2523,9 @@
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="5"/>
+      <c r="A37" s="5" t="s">
+        <v>348</v>
+      </c>
       <c r="B37" s="9" t="s">
         <v>19</v>
       </c>
@@ -2466,7 +2535,7 @@
       <c r="E37" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F37" s="76">
+      <c r="F37" s="62">
         <v>3</v>
       </c>
       <c r="G37" s="26" t="s">
@@ -2474,7 +2543,9 @@
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="5"/>
+      <c r="A38" s="5" t="s">
+        <v>349</v>
+      </c>
       <c r="B38" s="9" t="s">
         <v>20</v>
       </c>
@@ -2484,7 +2555,7 @@
       <c r="E38" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="F38" s="76">
+      <c r="F38" s="62">
         <v>10</v>
       </c>
       <c r="G38" s="26" t="s">
@@ -2492,7 +2563,9 @@
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="5"/>
+      <c r="A39" s="5" t="s">
+        <v>350</v>
+      </c>
       <c r="B39" s="9" t="s">
         <v>34</v>
       </c>
@@ -2502,7 +2575,7 @@
       <c r="E39" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F39" s="76">
+      <c r="F39" s="62">
         <v>1</v>
       </c>
       <c r="G39" s="26" t="s">
@@ -2510,247 +2583,265 @@
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="5"/>
-      <c r="B40" s="28" t="s">
+      <c r="B40" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="D40" s="29">
+      <c r="C40" s="67"/>
+      <c r="D40" s="12">
         <v>182.9</v>
       </c>
-      <c r="E40" s="27" t="s">
+      <c r="E40" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="F40" s="76">
+      <c r="F40" s="68">
         <v>0</v>
       </c>
-      <c r="G40" s="26">
-        <v>23764001</v>
+      <c r="G40" s="69" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="5"/>
-      <c r="B41" s="31" t="s">
+      <c r="A41" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="B41" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="D41" s="32">
+      <c r="D41" s="29">
         <v>188.49</v>
       </c>
-      <c r="E41" s="30" t="s">
+      <c r="E41" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="F41" s="76">
+      <c r="F41" s="62">
         <v>4</v>
       </c>
-      <c r="G41" s="33" t="s">
+      <c r="G41" s="30" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="5"/>
-      <c r="B42" s="35" t="s">
+      <c r="A42" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="B42" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="D42" s="36">
+      <c r="D42" s="33">
         <v>298.25</v>
       </c>
-      <c r="E42" s="34" t="s">
+      <c r="E42" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="F42" s="76">
+      <c r="F42" s="62">
         <v>2</v>
       </c>
-      <c r="G42" s="37" t="s">
+      <c r="G42" s="34" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="5"/>
-      <c r="B43" s="39" t="s">
+      <c r="A43" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="B43" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="D43" s="40">
+      <c r="D43" s="37">
         <v>302.5</v>
       </c>
-      <c r="E43" s="38" t="s">
+      <c r="E43" s="35" t="s">
         <v>120</v>
       </c>
-      <c r="F43" s="76">
+      <c r="F43" s="62">
         <v>2</v>
       </c>
-      <c r="G43" s="41" t="s">
+      <c r="G43" s="38" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="5"/>
-      <c r="B44" s="43" t="s">
+      <c r="A44" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="B44" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="D44" s="44">
+      <c r="D44" s="41">
         <v>22.740000000000002</v>
       </c>
-      <c r="E44" s="42" t="s">
+      <c r="E44" s="39" t="s">
         <v>123</v>
       </c>
-      <c r="F44" s="76">
+      <c r="F44" s="62">
         <v>4</v>
       </c>
-      <c r="G44" s="45" t="s">
+      <c r="G44" s="42" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="5"/>
-      <c r="B45" s="47" t="s">
+      <c r="A45" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="B45" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="D45" s="48">
+      <c r="D45" s="45">
         <v>19.5</v>
       </c>
-      <c r="E45" s="46" t="s">
+      <c r="E45" s="43" t="s">
         <v>126</v>
       </c>
-      <c r="F45" s="76">
+      <c r="F45" s="62">
         <v>3</v>
       </c>
-      <c r="G45" s="49" t="s">
+      <c r="G45" s="46" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="5"/>
-      <c r="B46" s="51" t="s">
+      <c r="A46" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="B46" s="48" t="s">
         <v>130</v>
       </c>
-      <c r="D46" s="52">
+      <c r="D46" s="49">
         <v>16.7</v>
       </c>
-      <c r="E46" s="50" t="s">
+      <c r="E46" s="47" t="s">
         <v>129</v>
       </c>
-      <c r="F46" s="76">
+      <c r="F46" s="62">
         <v>6</v>
       </c>
-      <c r="G46" s="53" t="s">
+      <c r="G46" s="50" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="5"/>
-      <c r="B47" s="55" t="s">
+      <c r="A47" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="B47" s="52" t="s">
         <v>133</v>
       </c>
-      <c r="D47" s="56">
+      <c r="D47" s="53">
         <v>490</v>
       </c>
-      <c r="E47" s="54" t="s">
+      <c r="E47" s="51" t="s">
         <v>132</v>
       </c>
-      <c r="F47" s="76">
+      <c r="F47" s="62">
         <v>3</v>
       </c>
-      <c r="G47" s="57" t="s">
+      <c r="G47" s="54" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="5"/>
-      <c r="B48" s="59" t="s">
+      <c r="A48" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="B48" s="56" t="s">
         <v>136</v>
       </c>
-      <c r="D48" s="60">
+      <c r="D48" s="57">
         <v>490</v>
       </c>
-      <c r="E48" s="58" t="s">
+      <c r="E48" s="55" t="s">
         <v>135</v>
       </c>
-      <c r="F48" s="76">
+      <c r="F48" s="62">
         <v>5</v>
       </c>
-      <c r="G48" s="61" t="s">
+      <c r="G48" s="58" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="5"/>
-      <c r="B49" s="63" t="s">
+      <c r="B49" s="70" t="s">
         <v>139</v>
       </c>
-      <c r="D49" s="64">
+      <c r="C49" s="71"/>
+      <c r="D49" s="72">
         <v>550</v>
       </c>
-      <c r="E49" s="62" t="s">
+      <c r="E49" s="70" t="s">
         <v>138</v>
       </c>
-      <c r="F49" s="76">
+      <c r="F49" s="73">
         <v>3</v>
       </c>
-      <c r="G49" s="65" t="s">
+      <c r="G49" s="70" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="5"/>
-      <c r="B50" s="67" t="s">
+      <c r="B50" s="70" t="s">
         <v>142</v>
       </c>
-      <c r="D50" s="68">
+      <c r="C50" s="71"/>
+      <c r="D50" s="72">
         <v>550</v>
       </c>
-      <c r="E50" s="66" t="s">
+      <c r="E50" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="F50" s="76">
+      <c r="F50" s="73">
         <v>1</v>
       </c>
-      <c r="G50" s="69" t="s">
+      <c r="G50" s="70" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="5"/>
-      <c r="B51" s="71" t="s">
+      <c r="B51" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="D51" s="72">
+      <c r="C51" s="67"/>
+      <c r="D51" s="12">
         <v>302.5</v>
       </c>
-      <c r="E51" s="70" t="s">
+      <c r="E51" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="F51" s="76">
+      <c r="F51" s="68">
         <v>2</v>
       </c>
-      <c r="G51" s="73" t="s">
+      <c r="G51" s="10" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="75" t="s">
+      <c r="A52" s="61" t="s">
         <v>144</v>
       </c>
       <c r="B52" s="9"/>
       <c r="D52" s="11"/>
       <c r="E52" s="9"/>
-      <c r="F52" s="76"/>
+      <c r="F52" s="62"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="B53" s="79" t="s">
+      <c r="B53" s="65" t="s">
         <v>188</v>
       </c>
-      <c r="D53" s="74">
+      <c r="D53" s="60">
         <v>363</v>
       </c>
-      <c r="E53" s="73" t="s">
+      <c r="E53" s="59" t="s">
         <v>145</v>
       </c>
-      <c r="F53" s="76">
+      <c r="F53" s="62">
         <v>1</v>
       </c>
-      <c r="G53" s="73" t="s">
+      <c r="G53" s="59" t="s">
         <v>229</v>
       </c>
     </row>
@@ -2758,19 +2849,19 @@
       <c r="A54" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="B54" s="79" t="s">
+      <c r="B54" s="65" t="s">
         <v>189</v>
       </c>
-      <c r="D54" s="74">
+      <c r="D54" s="60">
         <v>217.8</v>
       </c>
-      <c r="E54" s="73" t="s">
+      <c r="E54" s="59" t="s">
         <v>146</v>
       </c>
-      <c r="F54" s="76">
+      <c r="F54" s="62">
         <v>1</v>
       </c>
-      <c r="G54" s="73" t="s">
+      <c r="G54" s="59" t="s">
         <v>230</v>
       </c>
     </row>
@@ -2778,19 +2869,19 @@
       <c r="A55" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="B55" s="79" t="s">
+      <c r="B55" s="65" t="s">
         <v>190</v>
       </c>
-      <c r="D55" s="74">
+      <c r="D55" s="60">
         <v>411.40000000000003</v>
       </c>
-      <c r="E55" s="73" t="s">
+      <c r="E55" s="59" t="s">
         <v>147</v>
       </c>
-      <c r="F55" s="76">
+      <c r="F55" s="62">
         <v>1</v>
       </c>
-      <c r="G55" s="73" t="s">
+      <c r="G55" s="59" t="s">
         <v>231</v>
       </c>
     </row>
@@ -2798,19 +2889,19 @@
       <c r="A56" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="B56" s="79" t="s">
+      <c r="B56" s="65" t="s">
         <v>191</v>
       </c>
-      <c r="D56" s="74">
+      <c r="D56" s="60">
         <v>96.8</v>
       </c>
-      <c r="E56" s="73" t="s">
+      <c r="E56" s="59" t="s">
         <v>148</v>
       </c>
-      <c r="F56" s="76">
+      <c r="F56" s="62">
         <v>1</v>
       </c>
-      <c r="G56" s="73" t="s">
+      <c r="G56" s="59" t="s">
         <v>232</v>
       </c>
     </row>
@@ -2818,19 +2909,19 @@
       <c r="A57" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="B57" s="79" t="s">
+      <c r="B57" s="65" t="s">
         <v>192</v>
       </c>
-      <c r="D57" s="74">
+      <c r="D57" s="60">
         <v>96.8</v>
       </c>
-      <c r="E57" s="73" t="s">
+      <c r="E57" s="59" t="s">
         <v>149</v>
       </c>
-      <c r="F57" s="76">
+      <c r="F57" s="62">
         <v>1</v>
       </c>
-      <c r="G57" s="73" t="s">
+      <c r="G57" s="59" t="s">
         <v>233</v>
       </c>
     </row>
@@ -2838,19 +2929,19 @@
       <c r="A58" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="B58" s="79" t="s">
+      <c r="B58" s="65" t="s">
         <v>193</v>
       </c>
-      <c r="D58" s="74">
+      <c r="D58" s="60">
         <v>84.7</v>
       </c>
-      <c r="E58" s="73" t="s">
+      <c r="E58" s="59" t="s">
         <v>150</v>
       </c>
-      <c r="F58" s="76">
+      <c r="F58" s="62">
         <v>1</v>
       </c>
-      <c r="G58" s="73" t="s">
+      <c r="G58" s="59" t="s">
         <v>234</v>
       </c>
     </row>
@@ -2858,19 +2949,19 @@
       <c r="A59" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="B59" s="79" t="s">
+      <c r="B59" s="65" t="s">
         <v>194</v>
       </c>
-      <c r="D59" s="74">
+      <c r="D59" s="60">
         <v>53.24</v>
       </c>
-      <c r="E59" s="73" t="s">
+      <c r="E59" s="59" t="s">
         <v>151</v>
       </c>
-      <c r="F59" s="76">
+      <c r="F59" s="62">
         <v>1</v>
       </c>
-      <c r="G59" s="73" t="s">
+      <c r="G59" s="59" t="s">
         <v>235</v>
       </c>
     </row>
@@ -2878,20 +2969,20 @@
       <c r="A60" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="B60" s="79" t="s">
+      <c r="B60" s="65" t="s">
         <v>195</v>
       </c>
       <c r="C60" s="5"/>
-      <c r="D60" s="74">
+      <c r="D60" s="60">
         <v>66.55</v>
       </c>
-      <c r="E60" s="73" t="s">
+      <c r="E60" s="59" t="s">
         <v>152</v>
       </c>
-      <c r="F60" s="76">
+      <c r="F60" s="62">
         <v>1</v>
       </c>
-      <c r="G60" s="73" t="s">
+      <c r="G60" s="59" t="s">
         <v>236</v>
       </c>
     </row>
@@ -2899,20 +2990,20 @@
       <c r="A61" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="B61" s="79" t="s">
+      <c r="B61" s="65" t="s">
         <v>196</v>
       </c>
       <c r="C61" s="5"/>
-      <c r="D61" s="74">
+      <c r="D61" s="60">
         <v>84.7</v>
       </c>
-      <c r="E61" s="73" t="s">
+      <c r="E61" s="59" t="s">
         <v>153</v>
       </c>
-      <c r="F61" s="76">
+      <c r="F61" s="62">
         <v>1</v>
       </c>
-      <c r="G61" s="73" t="s">
+      <c r="G61" s="59" t="s">
         <v>237</v>
       </c>
     </row>
@@ -2920,20 +3011,20 @@
       <c r="A62" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="B62" s="79" t="s">
+      <c r="B62" s="65" t="s">
         <v>197</v>
       </c>
       <c r="C62" s="5"/>
-      <c r="D62" s="74">
+      <c r="D62" s="60">
         <v>96.8</v>
       </c>
-      <c r="E62" s="73" t="s">
+      <c r="E62" s="59" t="s">
         <v>154</v>
       </c>
-      <c r="F62" s="76">
+      <c r="F62" s="62">
         <v>1</v>
       </c>
-      <c r="G62" s="73" t="s">
+      <c r="G62" s="59" t="s">
         <v>238</v>
       </c>
     </row>
@@ -2941,19 +3032,19 @@
       <c r="A63" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="B63" s="79" t="s">
+      <c r="B63" s="65" t="s">
         <v>198</v>
       </c>
-      <c r="D63" s="74">
+      <c r="D63" s="60">
         <v>78.650000000000006</v>
       </c>
-      <c r="E63" s="73" t="s">
+      <c r="E63" s="59" t="s">
         <v>155</v>
       </c>
-      <c r="F63" s="76">
+      <c r="F63" s="62">
         <v>1</v>
       </c>
-      <c r="G63" s="73" t="s">
+      <c r="G63" s="59" t="s">
         <v>239</v>
       </c>
     </row>
@@ -2961,19 +3052,19 @@
       <c r="A64" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="B64" s="79" t="s">
+      <c r="B64" s="65" t="s">
         <v>199</v>
       </c>
-      <c r="D64" s="74">
+      <c r="D64" s="60">
         <v>133.1</v>
       </c>
-      <c r="E64" s="73" t="s">
+      <c r="E64" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="F64" s="76">
+      <c r="F64" s="62">
         <v>1</v>
       </c>
-      <c r="G64" s="73" t="s">
+      <c r="G64" s="59" t="s">
         <v>240</v>
       </c>
     </row>
@@ -2981,19 +3072,19 @@
       <c r="A65" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="B65" s="79" t="s">
+      <c r="B65" s="65" t="s">
         <v>200</v>
       </c>
-      <c r="D65" s="74">
+      <c r="D65" s="60">
         <v>145.20000000000002</v>
       </c>
-      <c r="E65" s="73" t="s">
+      <c r="E65" s="59" t="s">
         <v>157</v>
       </c>
-      <c r="F65" s="76">
+      <c r="F65" s="62">
         <v>1</v>
       </c>
-      <c r="G65" s="73" t="s">
+      <c r="G65" s="59" t="s">
         <v>241</v>
       </c>
     </row>
@@ -3001,19 +3092,19 @@
       <c r="A66" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="B66" s="79" t="s">
+      <c r="B66" s="65" t="s">
         <v>201</v>
       </c>
-      <c r="D66" s="74">
+      <c r="D66" s="60">
         <v>102.85000000000001</v>
       </c>
-      <c r="E66" s="73" t="s">
+      <c r="E66" s="59" t="s">
         <v>158</v>
       </c>
-      <c r="F66" s="76">
+      <c r="F66" s="62">
         <v>1</v>
       </c>
-      <c r="G66" s="73" t="s">
+      <c r="G66" s="59" t="s">
         <v>242</v>
       </c>
     </row>
@@ -3021,19 +3112,19 @@
       <c r="A67" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="B67" s="79" t="s">
+      <c r="B67" s="65" t="s">
         <v>202</v>
       </c>
-      <c r="D67" s="74">
+      <c r="D67" s="60">
         <v>169.4</v>
       </c>
-      <c r="E67" s="73" t="s">
+      <c r="E67" s="59" t="s">
         <v>159</v>
       </c>
-      <c r="F67" s="76">
+      <c r="F67" s="62">
         <v>1</v>
       </c>
-      <c r="G67" s="73" t="s">
+      <c r="G67" s="59" t="s">
         <v>243</v>
       </c>
     </row>
@@ -3041,19 +3132,19 @@
       <c r="A68" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="B68" s="79" t="s">
+      <c r="B68" s="65" t="s">
         <v>203</v>
       </c>
-      <c r="D68" s="74">
+      <c r="D68" s="60">
         <v>181.5</v>
       </c>
-      <c r="E68" s="73" t="s">
+      <c r="E68" s="59" t="s">
         <v>160</v>
       </c>
-      <c r="F68" s="76">
+      <c r="F68" s="62">
         <v>1</v>
       </c>
-      <c r="G68" s="73" t="s">
+      <c r="G68" s="59" t="s">
         <v>244</v>
       </c>
     </row>
@@ -3061,19 +3152,19 @@
       <c r="A69" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="B69" s="79" t="s">
+      <c r="B69" s="65" t="s">
         <v>204</v>
       </c>
-      <c r="D69" s="74">
+      <c r="D69" s="60">
         <v>121</v>
       </c>
-      <c r="E69" s="73" t="s">
+      <c r="E69" s="59" t="s">
         <v>161</v>
       </c>
-      <c r="F69" s="76">
+      <c r="F69" s="62">
         <v>1</v>
       </c>
-      <c r="G69" s="73" t="s">
+      <c r="G69" s="59" t="s">
         <v>245</v>
       </c>
     </row>
@@ -3081,19 +3172,19 @@
       <c r="A70" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="B70" s="79" t="s">
+      <c r="B70" s="65" t="s">
         <v>205</v>
       </c>
-      <c r="D70" s="74">
+      <c r="D70" s="60">
         <v>133.1</v>
       </c>
-      <c r="E70" s="73" t="s">
+      <c r="E70" s="59" t="s">
         <v>162</v>
       </c>
-      <c r="F70" s="76">
+      <c r="F70" s="62">
         <v>1</v>
       </c>
-      <c r="G70" s="73" t="s">
+      <c r="G70" s="59" t="s">
         <v>246</v>
       </c>
     </row>
@@ -3101,19 +3192,19 @@
       <c r="A71" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="B71" s="79" t="s">
+      <c r="B71" s="65" t="s">
         <v>204</v>
       </c>
-      <c r="D71" s="74">
+      <c r="D71" s="60">
         <v>121</v>
       </c>
-      <c r="E71" s="73" t="s">
+      <c r="E71" s="59" t="s">
         <v>163</v>
       </c>
-      <c r="F71" s="76">
+      <c r="F71" s="62">
         <v>1</v>
       </c>
-      <c r="G71" s="73" t="s">
+      <c r="G71" s="59" t="s">
         <v>247</v>
       </c>
     </row>
@@ -3121,19 +3212,19 @@
       <c r="A72" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="B72" s="79" t="s">
+      <c r="B72" s="65" t="s">
         <v>205</v>
       </c>
-      <c r="D72" s="74">
+      <c r="D72" s="60">
         <v>133.1</v>
       </c>
-      <c r="E72" s="73" t="s">
+      <c r="E72" s="59" t="s">
         <v>164</v>
       </c>
-      <c r="F72" s="76">
+      <c r="F72" s="62">
         <v>1</v>
       </c>
-      <c r="G72" s="73" t="s">
+      <c r="G72" s="59" t="s">
         <v>248</v>
       </c>
     </row>
@@ -3141,19 +3232,19 @@
       <c r="A73" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="B73" s="79" t="s">
+      <c r="B73" s="65" t="s">
         <v>206</v>
       </c>
-      <c r="D73" s="74">
+      <c r="D73" s="60">
         <v>145.20000000000002</v>
       </c>
-      <c r="E73" s="73" t="s">
+      <c r="E73" s="59" t="s">
         <v>165</v>
       </c>
-      <c r="F73" s="76">
+      <c r="F73" s="62">
         <v>1</v>
       </c>
-      <c r="G73" s="73" t="s">
+      <c r="G73" s="59" t="s">
         <v>249</v>
       </c>
     </row>
@@ -3161,19 +3252,19 @@
       <c r="A74" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="B74" s="79" t="s">
+      <c r="B74" s="65" t="s">
         <v>207</v>
       </c>
-      <c r="D74" s="74">
+      <c r="D74" s="60">
         <v>157.30000000000001</v>
       </c>
-      <c r="E74" s="73" t="s">
+      <c r="E74" s="59" t="s">
         <v>166</v>
       </c>
-      <c r="F74" s="76">
+      <c r="F74" s="62">
         <v>1</v>
       </c>
-      <c r="G74" s="73" t="s">
+      <c r="G74" s="59" t="s">
         <v>250</v>
       </c>
     </row>
@@ -3181,19 +3272,19 @@
       <c r="A75" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="B75" s="79" t="s">
+      <c r="B75" s="65" t="s">
         <v>208</v>
       </c>
-      <c r="D75" s="74">
+      <c r="D75" s="60">
         <v>53.24</v>
       </c>
-      <c r="E75" s="73" t="s">
+      <c r="E75" s="59" t="s">
         <v>167</v>
       </c>
-      <c r="F75" s="76">
+      <c r="F75" s="62">
         <v>1</v>
       </c>
-      <c r="G75" s="73" t="s">
+      <c r="G75" s="59" t="s">
         <v>251</v>
       </c>
     </row>
@@ -3201,19 +3292,19 @@
       <c r="A76" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="B76" s="79" t="s">
+      <c r="B76" s="65" t="s">
         <v>209</v>
       </c>
-      <c r="D76" s="74">
+      <c r="D76" s="60">
         <v>84.7</v>
       </c>
-      <c r="E76" s="73" t="s">
+      <c r="E76" s="59" t="s">
         <v>168</v>
       </c>
-      <c r="F76" s="76">
+      <c r="F76" s="62">
         <v>1</v>
       </c>
-      <c r="G76" s="73" t="s">
+      <c r="G76" s="59" t="s">
         <v>252</v>
       </c>
     </row>
@@ -3221,19 +3312,19 @@
       <c r="A77" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="B77" s="79" t="s">
+      <c r="B77" s="65" t="s">
         <v>210</v>
       </c>
-      <c r="D77" s="74">
+      <c r="D77" s="60">
         <v>72.600000000000009</v>
       </c>
-      <c r="E77" s="73" t="s">
+      <c r="E77" s="59" t="s">
         <v>169</v>
       </c>
-      <c r="F77" s="76">
+      <c r="F77" s="62">
         <v>1</v>
       </c>
-      <c r="G77" s="73" t="s">
+      <c r="G77" s="59" t="s">
         <v>253</v>
       </c>
     </row>
@@ -3241,19 +3332,19 @@
       <c r="A78" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="B78" s="79" t="s">
+      <c r="B78" s="65" t="s">
         <v>211</v>
       </c>
-      <c r="D78" s="74">
+      <c r="D78" s="60">
         <v>53.24</v>
       </c>
-      <c r="E78" s="73" t="s">
+      <c r="E78" s="59" t="s">
         <v>170</v>
       </c>
-      <c r="F78" s="76">
+      <c r="F78" s="62">
         <v>1</v>
       </c>
-      <c r="G78" s="73" t="s">
+      <c r="G78" s="59" t="s">
         <v>254</v>
       </c>
     </row>
@@ -3261,19 +3352,19 @@
       <c r="A79" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="B79" s="79" t="s">
+      <c r="B79" s="65" t="s">
         <v>212</v>
       </c>
-      <c r="D79" s="74">
+      <c r="D79" s="60">
         <v>60.5</v>
       </c>
-      <c r="E79" s="73" t="s">
+      <c r="E79" s="59" t="s">
         <v>171</v>
       </c>
-      <c r="F79" s="76">
+      <c r="F79" s="62">
         <v>1</v>
       </c>
-      <c r="G79" s="73" t="s">
+      <c r="G79" s="59" t="s">
         <v>255</v>
       </c>
     </row>
@@ -3281,19 +3372,19 @@
       <c r="A80" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="B80" s="79" t="s">
+      <c r="B80" s="65" t="s">
         <v>213</v>
       </c>
-      <c r="D80" s="74">
+      <c r="D80" s="60">
         <v>66.55</v>
       </c>
-      <c r="E80" s="73" t="s">
+      <c r="E80" s="59" t="s">
         <v>172</v>
       </c>
-      <c r="F80" s="76">
+      <c r="F80" s="62">
         <v>1</v>
       </c>
-      <c r="G80" s="73" t="s">
+      <c r="G80" s="59" t="s">
         <v>256</v>
       </c>
     </row>
@@ -3301,19 +3392,19 @@
       <c r="A81" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="B81" s="79" t="s">
+      <c r="B81" s="65" t="s">
         <v>214</v>
       </c>
-      <c r="D81" s="74">
+      <c r="D81" s="60">
         <v>90.75</v>
       </c>
-      <c r="E81" s="73" t="s">
+      <c r="E81" s="59" t="s">
         <v>173</v>
       </c>
-      <c r="F81" s="76">
+      <c r="F81" s="62">
         <v>1</v>
       </c>
-      <c r="G81" s="73" t="s">
+      <c r="G81" s="59" t="s">
         <v>257</v>
       </c>
     </row>
@@ -3321,19 +3412,19 @@
       <c r="A82" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="B82" s="79" t="s">
+      <c r="B82" s="65" t="s">
         <v>215</v>
       </c>
-      <c r="D82" s="74">
+      <c r="D82" s="60">
         <v>102.85000000000001</v>
       </c>
-      <c r="E82" s="73" t="s">
+      <c r="E82" s="59" t="s">
         <v>174</v>
       </c>
-      <c r="F82" s="76">
+      <c r="F82" s="62">
         <v>1</v>
       </c>
-      <c r="G82" s="73" t="s">
+      <c r="G82" s="59" t="s">
         <v>258</v>
       </c>
     </row>
@@ -3341,20 +3432,20 @@
       <c r="A83" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="B83" s="79" t="s">
+      <c r="B83" s="65" t="s">
         <v>216</v>
       </c>
       <c r="C83" s="5"/>
-      <c r="D83" s="74">
+      <c r="D83" s="60">
         <v>133.1</v>
       </c>
-      <c r="E83" s="73" t="s">
+      <c r="E83" s="59" t="s">
         <v>175</v>
       </c>
-      <c r="F83" s="76">
+      <c r="F83" s="62">
         <v>1</v>
       </c>
-      <c r="G83" s="73" t="s">
+      <c r="G83" s="59" t="s">
         <v>259</v>
       </c>
     </row>
@@ -3362,20 +3453,20 @@
       <c r="A84" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="B84" s="79" t="s">
+      <c r="B84" s="65" t="s">
         <v>217</v>
       </c>
       <c r="C84" s="5"/>
-      <c r="D84" s="74">
+      <c r="D84" s="60">
         <v>133.1</v>
       </c>
-      <c r="E84" s="73" t="s">
+      <c r="E84" s="59" t="s">
         <v>176</v>
       </c>
-      <c r="F84" s="76">
+      <c r="F84" s="62">
         <v>1</v>
       </c>
-      <c r="G84" s="73" t="s">
+      <c r="G84" s="59" t="s">
         <v>260</v>
       </c>
     </row>
@@ -3383,20 +3474,20 @@
       <c r="A85" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="B85" s="79" t="s">
+      <c r="B85" s="65" t="s">
         <v>218</v>
       </c>
       <c r="C85" s="5"/>
-      <c r="D85" s="74">
+      <c r="D85" s="60">
         <v>193.6</v>
       </c>
-      <c r="E85" s="73" t="s">
+      <c r="E85" s="59" t="s">
         <v>177</v>
       </c>
-      <c r="F85" s="76">
+      <c r="F85" s="62">
         <v>1</v>
       </c>
-      <c r="G85" s="73" t="s">
+      <c r="G85" s="59" t="s">
         <v>261</v>
       </c>
     </row>
@@ -3404,20 +3495,20 @@
       <c r="A86" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="B86" s="79" t="s">
+      <c r="B86" s="65" t="s">
         <v>219</v>
       </c>
       <c r="C86" s="5"/>
-      <c r="D86" s="74">
+      <c r="D86" s="60">
         <v>157.30000000000001</v>
       </c>
-      <c r="E86" s="73" t="s">
+      <c r="E86" s="59" t="s">
         <v>178</v>
       </c>
-      <c r="F86" s="76">
+      <c r="F86" s="62">
         <v>1</v>
       </c>
-      <c r="G86" s="73" t="s">
+      <c r="G86" s="59" t="s">
         <v>262</v>
       </c>
     </row>
@@ -3425,20 +3516,20 @@
       <c r="A87" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="B87" s="79" t="s">
+      <c r="B87" s="65" t="s">
         <v>220</v>
       </c>
       <c r="C87" s="5"/>
-      <c r="D87" s="74">
+      <c r="D87" s="60">
         <v>114.95</v>
       </c>
-      <c r="E87" s="73" t="s">
+      <c r="E87" s="59" t="s">
         <v>179</v>
       </c>
-      <c r="F87" s="76">
+      <c r="F87" s="62">
         <v>1</v>
       </c>
-      <c r="G87" s="73" t="s">
+      <c r="G87" s="59" t="s">
         <v>263</v>
       </c>
     </row>
@@ -3446,20 +3537,20 @@
       <c r="A88" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="B88" s="79" t="s">
+      <c r="B88" s="65" t="s">
         <v>221</v>
       </c>
       <c r="C88" s="5"/>
-      <c r="D88" s="74">
+      <c r="D88" s="60">
         <v>90.75</v>
       </c>
-      <c r="E88" s="73" t="s">
+      <c r="E88" s="59" t="s">
         <v>180</v>
       </c>
-      <c r="F88" s="76">
+      <c r="F88" s="62">
         <v>1</v>
       </c>
-      <c r="G88" s="73" t="s">
+      <c r="G88" s="59" t="s">
         <v>264</v>
       </c>
     </row>
@@ -3467,20 +3558,20 @@
       <c r="A89" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="B89" s="79" t="s">
+      <c r="B89" s="65" t="s">
         <v>222</v>
       </c>
       <c r="C89" s="5"/>
-      <c r="D89" s="74">
+      <c r="D89" s="60">
         <v>96.8</v>
       </c>
-      <c r="E89" s="73" t="s">
+      <c r="E89" s="59" t="s">
         <v>181</v>
       </c>
-      <c r="F89" s="76">
+      <c r="F89" s="62">
         <v>1</v>
       </c>
-      <c r="G89" s="73" t="s">
+      <c r="G89" s="59" t="s">
         <v>265</v>
       </c>
     </row>
@@ -3488,20 +3579,20 @@
       <c r="A90" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="B90" s="79" t="s">
+      <c r="B90" s="65" t="s">
         <v>223</v>
       </c>
       <c r="C90" s="5"/>
-      <c r="D90" s="74">
+      <c r="D90" s="60">
         <v>133.1</v>
       </c>
-      <c r="E90" s="73" t="s">
+      <c r="E90" s="59" t="s">
         <v>182</v>
       </c>
-      <c r="F90" s="76">
+      <c r="F90" s="62">
         <v>1</v>
       </c>
-      <c r="G90" s="73" t="s">
+      <c r="G90" s="59" t="s">
         <v>266</v>
       </c>
     </row>
@@ -3509,20 +3600,20 @@
       <c r="A91" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="B91" s="79" t="s">
+      <c r="B91" s="65" t="s">
         <v>224</v>
       </c>
       <c r="C91" s="5"/>
-      <c r="D91" s="74">
+      <c r="D91" s="60">
         <v>84.7</v>
       </c>
-      <c r="E91" s="73" t="s">
+      <c r="E91" s="59" t="s">
         <v>183</v>
       </c>
-      <c r="F91" s="76">
+      <c r="F91" s="62">
         <v>1</v>
       </c>
-      <c r="G91" s="73" t="s">
+      <c r="G91" s="59" t="s">
         <v>267</v>
       </c>
     </row>
@@ -3530,20 +3621,20 @@
       <c r="A92" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="B92" s="79" t="s">
+      <c r="B92" s="65" t="s">
         <v>225</v>
       </c>
       <c r="C92" s="5"/>
-      <c r="D92" s="74">
+      <c r="D92" s="60">
         <v>84.7</v>
       </c>
-      <c r="E92" s="73" t="s">
+      <c r="E92" s="59" t="s">
         <v>184</v>
       </c>
-      <c r="F92" s="76">
+      <c r="F92" s="62">
         <v>1</v>
       </c>
-      <c r="G92" s="73" t="s">
+      <c r="G92" s="59" t="s">
         <v>268</v>
       </c>
     </row>
@@ -3551,20 +3642,20 @@
       <c r="A93" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="B93" s="79" t="s">
+      <c r="B93" s="65" t="s">
         <v>226</v>
       </c>
       <c r="C93" s="5"/>
-      <c r="D93" s="74">
+      <c r="D93" s="60">
         <v>102.85000000000001</v>
       </c>
-      <c r="E93" s="73" t="s">
+      <c r="E93" s="59" t="s">
         <v>185</v>
       </c>
-      <c r="F93" s="76">
+      <c r="F93" s="62">
         <v>1</v>
       </c>
-      <c r="G93" s="73" t="s">
+      <c r="G93" s="59" t="s">
         <v>269</v>
       </c>
     </row>
@@ -3572,20 +3663,20 @@
       <c r="A94" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="B94" s="79" t="s">
+      <c r="B94" s="65" t="s">
         <v>227</v>
       </c>
       <c r="C94" s="5"/>
-      <c r="D94" s="74">
+      <c r="D94" s="60">
         <v>102.85000000000001</v>
       </c>
-      <c r="E94" s="73" t="s">
+      <c r="E94" s="59" t="s">
         <v>186</v>
       </c>
-      <c r="F94" s="76">
+      <c r="F94" s="62">
         <v>1</v>
       </c>
-      <c r="G94" s="73" t="s">
+      <c r="G94" s="59" t="s">
         <v>270</v>
       </c>
     </row>
@@ -3593,20 +3684,20 @@
       <c r="A95" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="B95" s="79" t="s">
+      <c r="B95" s="65" t="s">
         <v>228</v>
       </c>
       <c r="C95" s="5"/>
-      <c r="D95" s="74">
+      <c r="D95" s="60">
         <v>102.85000000000001</v>
       </c>
-      <c r="E95" s="73" t="s">
+      <c r="E95" s="59" t="s">
         <v>187</v>
       </c>
-      <c r="F95" s="76">
+      <c r="F95" s="62">
         <v>1</v>
       </c>
-      <c r="G95" s="73" t="s">
+      <c r="G95" s="59" t="s">
         <v>271</v>
       </c>
     </row>
@@ -3616,7 +3707,7 @@
       <c r="C96" s="5"/>
       <c r="D96" s="12"/>
       <c r="E96" s="10"/>
-      <c r="F96" s="76"/>
+      <c r="F96" s="62"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="5"/>
@@ -3624,7 +3715,7 @@
       <c r="C97" s="5"/>
       <c r="D97" s="12"/>
       <c r="E97" s="10"/>
-      <c r="F97" s="76"/>
+      <c r="F97" s="62"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="5"/>
@@ -3632,7 +3723,7 @@
       <c r="C98" s="5"/>
       <c r="D98" s="12"/>
       <c r="E98" s="10"/>
-      <c r="F98" s="76"/>
+      <c r="F98" s="62"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="5"/>
@@ -3640,7 +3731,7 @@
       <c r="C99" s="5"/>
       <c r="D99" s="11"/>
       <c r="E99" s="9"/>
-      <c r="F99" s="76"/>
+      <c r="F99" s="62"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="5"/>
@@ -3648,7 +3739,7 @@
       <c r="C100" s="5"/>
       <c r="D100" s="11"/>
       <c r="E100" s="9"/>
-      <c r="F100" s="76"/>
+      <c r="F100" s="62"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="5"/>
@@ -3656,7 +3747,7 @@
       <c r="C101" s="5"/>
       <c r="D101" s="11"/>
       <c r="E101" s="9"/>
-      <c r="F101" s="76"/>
+      <c r="F101" s="62"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="5"/>
@@ -3664,7 +3755,7 @@
       <c r="C102" s="5"/>
       <c r="D102" s="12"/>
       <c r="E102" s="10"/>
-      <c r="F102" s="76"/>
+      <c r="F102" s="62"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="5"/>
@@ -3672,7 +3763,7 @@
       <c r="C103" s="5"/>
       <c r="D103" s="11"/>
       <c r="E103" s="9"/>
-      <c r="F103" s="76"/>
+      <c r="F103" s="62"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="5"/>
@@ -3680,7 +3771,7 @@
       <c r="C104" s="5"/>
       <c r="D104" s="12"/>
       <c r="E104" s="10"/>
-      <c r="F104" s="76"/>
+      <c r="F104" s="62"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="5"/>
@@ -3688,7 +3779,7 @@
       <c r="C105" s="5"/>
       <c r="D105" s="11"/>
       <c r="E105" s="9"/>
-      <c r="F105" s="76"/>
+      <c r="F105" s="62"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="5"/>
@@ -3696,7 +3787,7 @@
       <c r="C106" s="5"/>
       <c r="D106" s="11"/>
       <c r="E106" s="9"/>
-      <c r="F106" s="76"/>
+      <c r="F106" s="62"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="5"/>
@@ -3704,7 +3795,7 @@
       <c r="C107" s="5"/>
       <c r="D107" s="12"/>
       <c r="E107" s="10"/>
-      <c r="F107" s="76"/>
+      <c r="F107" s="62"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="5"/>
@@ -3712,7 +3803,7 @@
       <c r="C108" s="5"/>
       <c r="D108" s="11"/>
       <c r="E108" s="9"/>
-      <c r="F108" s="76"/>
+      <c r="F108" s="62"/>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="5"/>
@@ -3720,7 +3811,7 @@
       <c r="C109" s="5"/>
       <c r="D109" s="11"/>
       <c r="E109" s="9"/>
-      <c r="F109" s="76"/>
+      <c r="F109" s="62"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="5"/>
@@ -3728,7 +3819,7 @@
       <c r="C110" s="5"/>
       <c r="D110" s="12"/>
       <c r="E110" s="10"/>
-      <c r="F110" s="76"/>
+      <c r="F110" s="62"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="5"/>
@@ -3736,7 +3827,7 @@
       <c r="C111" s="5"/>
       <c r="D111" s="12"/>
       <c r="E111" s="10"/>
-      <c r="F111" s="76"/>
+      <c r="F111" s="62"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="5"/>
@@ -3744,7 +3835,7 @@
       <c r="C112" s="5"/>
       <c r="D112" s="12"/>
       <c r="E112" s="10"/>
-      <c r="F112" s="76"/>
+      <c r="F112" s="62"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="5"/>
@@ -3752,7 +3843,7 @@
       <c r="C113" s="5"/>
       <c r="D113" s="12"/>
       <c r="E113" s="10"/>
-      <c r="F113" s="76"/>
+      <c r="F113" s="62"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="5"/>
@@ -3760,7 +3851,7 @@
       <c r="C114" s="5"/>
       <c r="D114" s="12"/>
       <c r="E114" s="10"/>
-      <c r="F114" s="76"/>
+      <c r="F114" s="62"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="5"/>
@@ -3768,7 +3859,7 @@
       <c r="C115" s="5"/>
       <c r="D115" s="11"/>
       <c r="E115" s="9"/>
-      <c r="F115" s="76"/>
+      <c r="F115" s="62"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="5"/>
@@ -3776,7 +3867,7 @@
       <c r="C116" s="5"/>
       <c r="D116" s="12"/>
       <c r="E116" s="10"/>
-      <c r="F116" s="76"/>
+      <c r="F116" s="62"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="5"/>
@@ -3784,7 +3875,7 @@
       <c r="C117" s="5"/>
       <c r="D117" s="12"/>
       <c r="E117" s="10"/>
-      <c r="F117" s="76"/>
+      <c r="F117" s="62"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="5"/>
@@ -3792,7 +3883,7 @@
       <c r="C118" s="5"/>
       <c r="D118" s="11"/>
       <c r="E118" s="9"/>
-      <c r="F118" s="76"/>
+      <c r="F118" s="62"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="5"/>
@@ -3800,7 +3891,7 @@
       <c r="C119" s="5"/>
       <c r="D119" s="12"/>
       <c r="E119" s="10"/>
-      <c r="F119" s="76"/>
+      <c r="F119" s="62"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="5"/>
@@ -3808,7 +3899,7 @@
       <c r="C120" s="5"/>
       <c r="D120" s="12"/>
       <c r="E120" s="10"/>
-      <c r="F120" s="76"/>
+      <c r="F120" s="62"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="5"/>
@@ -3816,7 +3907,7 @@
       <c r="C121" s="5"/>
       <c r="D121" s="11"/>
       <c r="E121" s="9"/>
-      <c r="F121" s="76"/>
+      <c r="F121" s="62"/>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="5"/>
@@ -3824,7 +3915,7 @@
       <c r="C122" s="5"/>
       <c r="D122" s="11"/>
       <c r="E122" s="9"/>
-      <c r="F122" s="76"/>
+      <c r="F122" s="62"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="5"/>
@@ -3832,7 +3923,7 @@
       <c r="C123" s="5"/>
       <c r="D123" s="12"/>
       <c r="E123" s="10"/>
-      <c r="F123" s="76"/>
+      <c r="F123" s="62"/>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="5"/>
@@ -3840,7 +3931,7 @@
       <c r="C124" s="5"/>
       <c r="D124" s="12"/>
       <c r="E124" s="10"/>
-      <c r="F124" s="76"/>
+      <c r="F124" s="62"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="5"/>
@@ -3848,7 +3939,7 @@
       <c r="C125" s="5"/>
       <c r="D125" s="11"/>
       <c r="E125" s="9"/>
-      <c r="F125" s="76"/>
+      <c r="F125" s="62"/>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="5"/>
@@ -3856,7 +3947,7 @@
       <c r="C126" s="5"/>
       <c r="D126" s="11"/>
       <c r="E126" s="9"/>
-      <c r="F126" s="76"/>
+      <c r="F126" s="62"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="5"/>
@@ -3864,7 +3955,7 @@
       <c r="C127" s="5"/>
       <c r="D127" s="12"/>
       <c r="E127" s="10"/>
-      <c r="F127" s="76"/>
+      <c r="F127" s="62"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="5"/>
@@ -3872,7 +3963,7 @@
       <c r="C128" s="5"/>
       <c r="D128" s="11"/>
       <c r="E128" s="9"/>
-      <c r="F128" s="76"/>
+      <c r="F128" s="62"/>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="5"/>
@@ -3880,7 +3971,7 @@
       <c r="C129" s="5"/>
       <c r="D129" s="11"/>
       <c r="E129" s="9"/>
-      <c r="F129" s="76"/>
+      <c r="F129" s="62"/>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="5"/>
@@ -3888,7 +3979,7 @@
       <c r="C130" s="5"/>
       <c r="D130" s="11"/>
       <c r="E130" s="9"/>
-      <c r="F130" s="76"/>
+      <c r="F130" s="62"/>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="5"/>
@@ -3896,7 +3987,7 @@
       <c r="C131" s="5"/>
       <c r="D131" s="11"/>
       <c r="E131" s="9"/>
-      <c r="F131" s="76"/>
+      <c r="F131" s="62"/>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="5"/>
@@ -3904,7 +3995,7 @@
       <c r="C132" s="5"/>
       <c r="D132" s="11"/>
       <c r="E132" s="9"/>
-      <c r="F132" s="76"/>
+      <c r="F132" s="62"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="5"/>
@@ -3912,7 +4003,7 @@
       <c r="C133" s="5"/>
       <c r="D133" s="11"/>
       <c r="E133" s="9"/>
-      <c r="F133" s="76"/>
+      <c r="F133" s="62"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="5"/>
@@ -3920,7 +4011,7 @@
       <c r="C134" s="5"/>
       <c r="D134" s="11"/>
       <c r="E134" s="9"/>
-      <c r="F134" s="76"/>
+      <c r="F134" s="62"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="5"/>
@@ -3928,7 +4019,7 @@
       <c r="C135" s="5"/>
       <c r="D135" s="11"/>
       <c r="E135" s="9"/>
-      <c r="F135" s="76"/>
+      <c r="F135" s="62"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="5"/>
@@ -3936,7 +4027,7 @@
       <c r="C136" s="5"/>
       <c r="D136" s="12"/>
       <c r="E136" s="10"/>
-      <c r="F136" s="76"/>
+      <c r="F136" s="62"/>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="5"/>
@@ -3944,7 +4035,7 @@
       <c r="C137" s="5"/>
       <c r="D137" s="11"/>
       <c r="E137" s="9"/>
-      <c r="F137" s="76"/>
+      <c r="F137" s="62"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="5"/>
@@ -3952,7 +4043,7 @@
       <c r="C138" s="5"/>
       <c r="D138" s="12"/>
       <c r="E138" s="10"/>
-      <c r="F138" s="76"/>
+      <c r="F138" s="62"/>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="5"/>
@@ -3960,7 +4051,7 @@
       <c r="C139" s="5"/>
       <c r="D139" s="12"/>
       <c r="E139" s="10"/>
-      <c r="F139" s="76"/>
+      <c r="F139" s="62"/>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="5"/>
@@ -3968,7 +4059,7 @@
       <c r="C140" s="5"/>
       <c r="D140" s="12"/>
       <c r="E140" s="10"/>
-      <c r="F140" s="76"/>
+      <c r="F140" s="62"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="5"/>
@@ -3976,7 +4067,7 @@
       <c r="C141" s="5"/>
       <c r="D141" s="12"/>
       <c r="E141" s="10"/>
-      <c r="F141" s="76"/>
+      <c r="F141" s="62"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="5"/>
@@ -3984,7 +4075,7 @@
       <c r="C142" s="5"/>
       <c r="D142" s="11"/>
       <c r="E142" s="9"/>
-      <c r="F142" s="76"/>
+      <c r="F142" s="62"/>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="5"/>
@@ -3992,7 +4083,7 @@
       <c r="C143" s="5"/>
       <c r="D143" s="12"/>
       <c r="E143" s="10"/>
-      <c r="F143" s="76"/>
+      <c r="F143" s="62"/>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" s="5"/>
@@ -4000,7 +4091,7 @@
       <c r="C144" s="5"/>
       <c r="D144" s="11"/>
       <c r="E144" s="9"/>
-      <c r="F144" s="76"/>
+      <c r="F144" s="62"/>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="5"/>
@@ -4008,7 +4099,7 @@
       <c r="C145" s="5"/>
       <c r="D145" s="12"/>
       <c r="E145" s="10"/>
-      <c r="F145" s="76"/>
+      <c r="F145" s="62"/>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="5"/>
@@ -4016,7 +4107,7 @@
       <c r="C146" s="5"/>
       <c r="D146" s="11"/>
       <c r="E146" s="9"/>
-      <c r="F146" s="76"/>
+      <c r="F146" s="62"/>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="5"/>
@@ -4024,7 +4115,7 @@
       <c r="C147" s="5"/>
       <c r="D147" s="11"/>
       <c r="E147" s="9"/>
-      <c r="F147" s="76"/>
+      <c r="F147" s="62"/>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="5"/>
@@ -4032,7 +4123,7 @@
       <c r="C148" s="5"/>
       <c r="D148" s="12"/>
       <c r="E148" s="10"/>
-      <c r="F148" s="76"/>
+      <c r="F148" s="62"/>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="5"/>
@@ -4040,7 +4131,7 @@
       <c r="C149" s="5"/>
       <c r="D149" s="11"/>
       <c r="E149" s="9"/>
-      <c r="F149" s="76"/>
+      <c r="F149" s="62"/>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" s="5"/>
@@ -4048,7 +4139,7 @@
       <c r="C150" s="5"/>
       <c r="D150" s="12"/>
       <c r="E150" s="10"/>
-      <c r="F150" s="76"/>
+      <c r="F150" s="62"/>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="5"/>
@@ -4056,7 +4147,7 @@
       <c r="C151" s="5"/>
       <c r="D151" s="12"/>
       <c r="E151" s="10"/>
-      <c r="F151" s="76"/>
+      <c r="F151" s="62"/>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" s="5"/>
@@ -4064,7 +4155,7 @@
       <c r="C152" s="5"/>
       <c r="D152" s="12"/>
       <c r="E152" s="10"/>
-      <c r="F152" s="76"/>
+      <c r="F152" s="62"/>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" s="5"/>
@@ -4072,7 +4163,7 @@
       <c r="C153" s="5"/>
       <c r="D153" s="12"/>
       <c r="E153" s="10"/>
-      <c r="F153" s="76"/>
+      <c r="F153" s="62"/>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" s="5"/>
@@ -4080,7 +4171,7 @@
       <c r="C154" s="5"/>
       <c r="D154" s="12"/>
       <c r="E154" s="10"/>
-      <c r="F154" s="76"/>
+      <c r="F154" s="62"/>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" s="5"/>
@@ -4088,7 +4179,7 @@
       <c r="C155" s="5"/>
       <c r="D155" s="12"/>
       <c r="E155" s="10"/>
-      <c r="F155" s="76"/>
+      <c r="F155" s="62"/>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" s="5"/>
@@ -4096,7 +4187,7 @@
       <c r="C156" s="5"/>
       <c r="D156" s="11"/>
       <c r="E156" s="9"/>
-      <c r="F156" s="76"/>
+      <c r="F156" s="62"/>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" s="5"/>
@@ -4104,7 +4195,7 @@
       <c r="C157" s="5"/>
       <c r="D157" s="12"/>
       <c r="E157" s="10"/>
-      <c r="F157" s="76"/>
+      <c r="F157" s="62"/>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" s="5"/>
@@ -4112,7 +4203,7 @@
       <c r="C158" s="5"/>
       <c r="D158" s="12"/>
       <c r="E158" s="10"/>
-      <c r="F158" s="76"/>
+      <c r="F158" s="62"/>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" s="5"/>
@@ -4120,7 +4211,7 @@
       <c r="C159" s="5"/>
       <c r="D159" s="12"/>
       <c r="E159" s="10"/>
-      <c r="F159" s="76"/>
+      <c r="F159" s="62"/>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" s="5"/>
@@ -4128,7 +4219,7 @@
       <c r="C160" s="5"/>
       <c r="D160" s="11"/>
       <c r="E160" s="9"/>
-      <c r="F160" s="76"/>
+      <c r="F160" s="62"/>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" s="5"/>
@@ -4136,7 +4227,7 @@
       <c r="C161" s="5"/>
       <c r="D161" s="11"/>
       <c r="E161" s="9"/>
-      <c r="F161" s="76"/>
+      <c r="F161" s="62"/>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" s="5"/>
@@ -4144,7 +4235,7 @@
       <c r="C162" s="5"/>
       <c r="D162" s="11"/>
       <c r="E162" s="9"/>
-      <c r="F162" s="76"/>
+      <c r="F162" s="62"/>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" s="5"/>
@@ -4152,7 +4243,7 @@
       <c r="C163" s="5"/>
       <c r="D163" s="12"/>
       <c r="E163" s="10"/>
-      <c r="F163" s="76"/>
+      <c r="F163" s="62"/>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" s="5"/>
@@ -4160,7 +4251,7 @@
       <c r="C164" s="5"/>
       <c r="D164" s="12"/>
       <c r="E164" s="10"/>
-      <c r="F164" s="76"/>
+      <c r="F164" s="62"/>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" s="5"/>
@@ -4168,7 +4259,7 @@
       <c r="C165" s="5"/>
       <c r="D165" s="12"/>
       <c r="E165" s="10"/>
-      <c r="F165" s="76"/>
+      <c r="F165" s="62"/>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" s="5"/>
@@ -4176,7 +4267,7 @@
       <c r="C166" s="5"/>
       <c r="D166" s="12"/>
       <c r="E166" s="10"/>
-      <c r="F166" s="76"/>
+      <c r="F166" s="62"/>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" s="5"/>
@@ -4184,7 +4275,7 @@
       <c r="C167" s="5"/>
       <c r="D167" s="12"/>
       <c r="E167" s="10"/>
-      <c r="F167" s="76"/>
+      <c r="F167" s="62"/>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" s="5"/>
@@ -4192,7 +4283,7 @@
       <c r="C168" s="5"/>
       <c r="D168" s="12"/>
       <c r="E168" s="10"/>
-      <c r="F168" s="76"/>
+      <c r="F168" s="62"/>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" s="5"/>
@@ -4200,7 +4291,7 @@
       <c r="C169" s="5"/>
       <c r="D169" s="12"/>
       <c r="E169" s="10"/>
-      <c r="F169" s="76"/>
+      <c r="F169" s="62"/>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" s="5"/>
@@ -4208,7 +4299,7 @@
       <c r="C170" s="5"/>
       <c r="D170" s="12"/>
       <c r="E170" s="10"/>
-      <c r="F170" s="76"/>
+      <c r="F170" s="62"/>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" s="5"/>
@@ -4216,7 +4307,7 @@
       <c r="C171" s="5"/>
       <c r="D171" s="12"/>
       <c r="E171" s="10"/>
-      <c r="F171" s="76"/>
+      <c r="F171" s="62"/>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" s="5"/>
@@ -4224,7 +4315,7 @@
       <c r="C172" s="5"/>
       <c r="D172" s="12"/>
       <c r="E172" s="10"/>
-      <c r="F172" s="76"/>
+      <c r="F172" s="62"/>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" s="5"/>
@@ -4232,7 +4323,7 @@
       <c r="C173" s="5"/>
       <c r="D173" s="12"/>
       <c r="E173" s="10"/>
-      <c r="F173" s="76"/>
+      <c r="F173" s="62"/>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" s="5"/>
@@ -4240,7 +4331,7 @@
       <c r="C174" s="5"/>
       <c r="D174" s="11"/>
       <c r="E174" s="9"/>
-      <c r="F174" s="76"/>
+      <c r="F174" s="62"/>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" s="5"/>
@@ -4248,7 +4339,7 @@
       <c r="C175" s="5"/>
       <c r="D175" s="5"/>
       <c r="E175" s="5"/>
-      <c r="F175" s="77"/>
+      <c r="F175" s="63"/>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" s="5"/>
@@ -4256,7 +4347,7 @@
       <c r="C176" s="5"/>
       <c r="D176" s="5"/>
       <c r="E176" s="5"/>
-      <c r="F176" s="77"/>
+      <c r="F176" s="63"/>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" s="5"/>
@@ -4264,7 +4355,7 @@
       <c r="C177" s="5"/>
       <c r="D177" s="5"/>
       <c r="E177" s="5"/>
-      <c r="F177" s="77"/>
+      <c r="F177" s="63"/>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" s="5"/>
@@ -4272,7 +4363,7 @@
       <c r="C178" s="5"/>
       <c r="D178" s="5"/>
       <c r="E178" s="5"/>
-      <c r="F178" s="77"/>
+      <c r="F178" s="63"/>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" s="5"/>
@@ -4280,7 +4371,7 @@
       <c r="C179" s="5"/>
       <c r="D179" s="5"/>
       <c r="E179" s="5"/>
-      <c r="F179" s="77"/>
+      <c r="F179" s="63"/>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" s="5"/>
@@ -4288,7 +4379,7 @@
       <c r="C180" s="5"/>
       <c r="D180" s="5"/>
       <c r="E180" s="5"/>
-      <c r="F180" s="77"/>
+      <c r="F180" s="63"/>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" s="5"/>
@@ -4296,7 +4387,7 @@
       <c r="C181" s="5"/>
       <c r="D181" s="5"/>
       <c r="E181" s="5"/>
-      <c r="F181" s="77"/>
+      <c r="F181" s="63"/>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" s="5"/>
@@ -4304,7 +4395,7 @@
       <c r="C182" s="5"/>
       <c r="D182" s="5"/>
       <c r="E182" s="5"/>
-      <c r="F182" s="77"/>
+      <c r="F182" s="63"/>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" s="5"/>
@@ -4312,7 +4403,7 @@
       <c r="C183" s="5"/>
       <c r="D183" s="5"/>
       <c r="E183" s="5"/>
-      <c r="F183" s="77"/>
+      <c r="F183" s="63"/>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" s="5"/>
@@ -4320,7 +4411,7 @@
       <c r="C184" s="5"/>
       <c r="D184" s="5"/>
       <c r="E184" s="5"/>
-      <c r="F184" s="77"/>
+      <c r="F184" s="63"/>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" s="5"/>
@@ -4328,7 +4419,7 @@
       <c r="C185" s="5"/>
       <c r="D185" s="5"/>
       <c r="E185" s="5"/>
-      <c r="F185" s="77"/>
+      <c r="F185" s="63"/>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" s="5"/>
@@ -4336,7 +4427,7 @@
       <c r="C186" s="5"/>
       <c r="D186" s="5"/>
       <c r="E186" s="5"/>
-      <c r="F186" s="77"/>
+      <c r="F186" s="63"/>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187" s="5"/>
@@ -4344,7 +4435,7 @@
       <c r="C187" s="5"/>
       <c r="D187" s="5"/>
       <c r="E187" s="5"/>
-      <c r="F187" s="77"/>
+      <c r="F187" s="63"/>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" s="5"/>
@@ -4352,7 +4443,7 @@
       <c r="C188" s="5"/>
       <c r="D188" s="5"/>
       <c r="E188" s="5"/>
-      <c r="F188" s="77"/>
+      <c r="F188" s="63"/>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" s="5"/>
@@ -4360,7 +4451,7 @@
       <c r="C189" s="5"/>
       <c r="D189" s="5"/>
       <c r="E189" s="5"/>
-      <c r="F189" s="77"/>
+      <c r="F189" s="63"/>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" s="5"/>
@@ -4368,7 +4459,7 @@
       <c r="C190" s="5"/>
       <c r="D190" s="5"/>
       <c r="E190" s="5"/>
-      <c r="F190" s="77"/>
+      <c r="F190" s="63"/>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" s="5"/>
@@ -4376,7 +4467,7 @@
       <c r="C191" s="5"/>
       <c r="D191" s="5"/>
       <c r="E191" s="5"/>
-      <c r="F191" s="77"/>
+      <c r="F191" s="63"/>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" s="5"/>
@@ -4384,7 +4475,7 @@
       <c r="C192" s="5"/>
       <c r="D192" s="5"/>
       <c r="E192" s="5"/>
-      <c r="F192" s="77"/>
+      <c r="F192" s="63"/>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193" s="5"/>
@@ -4392,7 +4483,7 @@
       <c r="C193" s="5"/>
       <c r="D193" s="5"/>
       <c r="E193" s="5"/>
-      <c r="F193" s="77"/>
+      <c r="F193" s="63"/>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194" s="5"/>
@@ -4400,7 +4491,7 @@
       <c r="C194" s="5"/>
       <c r="D194" s="5"/>
       <c r="E194" s="5"/>
-      <c r="F194" s="77"/>
+      <c r="F194" s="63"/>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195" s="5"/>
@@ -4408,7 +4499,7 @@
       <c r="C195" s="5"/>
       <c r="D195" s="5"/>
       <c r="E195" s="5"/>
-      <c r="F195" s="77"/>
+      <c r="F195" s="63"/>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A196" s="5"/>
@@ -4416,7 +4507,7 @@
       <c r="C196" s="5"/>
       <c r="D196" s="5"/>
       <c r="E196" s="5"/>
-      <c r="F196" s="77"/>
+      <c r="F196" s="63"/>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A197" s="5"/>
@@ -4424,7 +4515,7 @@
       <c r="C197" s="5"/>
       <c r="D197" s="5"/>
       <c r="E197" s="5"/>
-      <c r="F197" s="77"/>
+      <c r="F197" s="63"/>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A198" s="5"/>
@@ -4432,7 +4523,7 @@
       <c r="C198" s="5"/>
       <c r="D198" s="5"/>
       <c r="E198" s="5"/>
-      <c r="F198" s="77"/>
+      <c r="F198" s="63"/>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A199" s="5"/>
@@ -4440,7 +4531,7 @@
       <c r="C199" s="5"/>
       <c r="D199" s="5"/>
       <c r="E199" s="5"/>
-      <c r="F199" s="77"/>
+      <c r="F199" s="63"/>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A200" s="5"/>
@@ -4448,7 +4539,7 @@
       <c r="C200" s="5"/>
       <c r="D200" s="5"/>
       <c r="E200" s="5"/>
-      <c r="F200" s="77"/>
+      <c r="F200" s="63"/>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201" s="5"/>
@@ -4456,7 +4547,7 @@
       <c r="C201" s="5"/>
       <c r="D201" s="5"/>
       <c r="E201" s="5"/>
-      <c r="F201" s="77"/>
+      <c r="F201" s="63"/>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202" s="5"/>
@@ -4464,7 +4555,7 @@
       <c r="C202" s="5"/>
       <c r="D202" s="5"/>
       <c r="E202" s="5"/>
-      <c r="F202" s="77"/>
+      <c r="F202" s="63"/>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203" s="5"/>
@@ -4472,7 +4563,7 @@
       <c r="C203" s="5"/>
       <c r="D203" s="5"/>
       <c r="E203" s="5"/>
-      <c r="F203" s="77"/>
+      <c r="F203" s="63"/>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204" s="5"/>
@@ -4480,7 +4571,7 @@
       <c r="C204" s="5"/>
       <c r="D204" s="5"/>
       <c r="E204" s="5"/>
-      <c r="F204" s="77"/>
+      <c r="F204" s="63"/>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205" s="5"/>
@@ -4488,7 +4579,7 @@
       <c r="C205" s="5"/>
       <c r="D205" s="5"/>
       <c r="E205" s="5"/>
-      <c r="F205" s="77"/>
+      <c r="F205" s="63"/>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206" s="5"/>
@@ -4496,7 +4587,7 @@
       <c r="C206" s="5"/>
       <c r="D206" s="5"/>
       <c r="E206" s="5"/>
-      <c r="F206" s="77"/>
+      <c r="F206" s="63"/>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A207" s="5"/>
@@ -4504,7 +4595,7 @@
       <c r="C207" s="5"/>
       <c r="D207" s="5"/>
       <c r="E207" s="5"/>
-      <c r="F207" s="77"/>
+      <c r="F207" s="63"/>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A208" s="5"/>
@@ -4512,7 +4603,7 @@
       <c r="C208" s="5"/>
       <c r="D208" s="5"/>
       <c r="E208" s="5"/>
-      <c r="F208" s="77"/>
+      <c r="F208" s="63"/>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209" s="5"/>
@@ -4520,7 +4611,7 @@
       <c r="C209" s="5"/>
       <c r="D209" s="5"/>
       <c r="E209" s="5"/>
-      <c r="F209" s="77"/>
+      <c r="F209" s="63"/>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210" s="5"/>
@@ -4528,7 +4619,7 @@
       <c r="C210" s="5"/>
       <c r="D210" s="5"/>
       <c r="E210" s="5"/>
-      <c r="F210" s="77"/>
+      <c r="F210" s="63"/>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211" s="5"/>
@@ -4536,7 +4627,7 @@
       <c r="C211" s="5"/>
       <c r="D211" s="5"/>
       <c r="E211" s="5"/>
-      <c r="F211" s="77"/>
+      <c r="F211" s="63"/>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212" s="5"/>
@@ -4544,7 +4635,7 @@
       <c r="C212" s="5"/>
       <c r="D212" s="5"/>
       <c r="E212" s="5"/>
-      <c r="F212" s="77"/>
+      <c r="F212" s="63"/>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213" s="5"/>
@@ -4552,7 +4643,7 @@
       <c r="C213" s="5"/>
       <c r="D213" s="5"/>
       <c r="E213" s="5"/>
-      <c r="F213" s="77"/>
+      <c r="F213" s="63"/>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214" s="5"/>
@@ -4560,7 +4651,7 @@
       <c r="C214" s="5"/>
       <c r="D214" s="5"/>
       <c r="E214" s="5"/>
-      <c r="F214" s="77"/>
+      <c r="F214" s="63"/>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215" s="5"/>
@@ -4568,7 +4659,7 @@
       <c r="C215" s="5"/>
       <c r="D215" s="5"/>
       <c r="E215" s="5"/>
-      <c r="F215" s="77"/>
+      <c r="F215" s="63"/>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216" s="5"/>
@@ -4576,7 +4667,7 @@
       <c r="C216" s="5"/>
       <c r="D216" s="5"/>
       <c r="E216" s="5"/>
-      <c r="F216" s="77"/>
+      <c r="F216" s="63"/>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217" s="5"/>
@@ -4584,7 +4675,7 @@
       <c r="C217" s="5"/>
       <c r="D217" s="5"/>
       <c r="E217" s="5"/>
-      <c r="F217" s="77"/>
+      <c r="F217" s="63"/>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218" s="5"/>
@@ -4592,7 +4683,7 @@
       <c r="C218" s="5"/>
       <c r="D218" s="5"/>
       <c r="E218" s="5"/>
-      <c r="F218" s="77"/>
+      <c r="F218" s="63"/>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A219" s="5"/>
@@ -4600,7 +4691,7 @@
       <c r="C219" s="5"/>
       <c r="D219" s="5"/>
       <c r="E219" s="5"/>
-      <c r="F219" s="77"/>
+      <c r="F219" s="63"/>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A220" s="5"/>
@@ -4608,7 +4699,7 @@
       <c r="C220" s="5"/>
       <c r="D220" s="5"/>
       <c r="E220" s="5"/>
-      <c r="F220" s="77"/>
+      <c r="F220" s="63"/>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A221" s="5"/>
@@ -4616,7 +4707,7 @@
       <c r="C221" s="5"/>
       <c r="D221" s="5"/>
       <c r="E221" s="5"/>
-      <c r="F221" s="77"/>
+      <c r="F221" s="63"/>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A222" s="5"/>
@@ -4624,7 +4715,7 @@
       <c r="C222" s="5"/>
       <c r="D222" s="5"/>
       <c r="E222" s="5"/>
-      <c r="F222" s="77"/>
+      <c r="F222" s="63"/>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A223" s="5"/>
@@ -4632,7 +4723,7 @@
       <c r="C223" s="5"/>
       <c r="D223" s="5"/>
       <c r="E223" s="5"/>
-      <c r="F223" s="77"/>
+      <c r="F223" s="63"/>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A224" s="5"/>
@@ -4640,7 +4731,7 @@
       <c r="C224" s="5"/>
       <c r="D224" s="5"/>
       <c r="E224" s="5"/>
-      <c r="F224" s="77"/>
+      <c r="F224" s="63"/>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" s="5"/>
@@ -4648,7 +4739,7 @@
       <c r="C225" s="5"/>
       <c r="D225" s="5"/>
       <c r="E225" s="5"/>
-      <c r="F225" s="77"/>
+      <c r="F225" s="63"/>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226" s="5"/>
@@ -4656,7 +4747,7 @@
       <c r="C226" s="5"/>
       <c r="D226" s="5"/>
       <c r="E226" s="5"/>
-      <c r="F226" s="77"/>
+      <c r="F226" s="63"/>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227" s="5"/>
@@ -4664,7 +4755,7 @@
       <c r="C227" s="5"/>
       <c r="D227" s="5"/>
       <c r="E227" s="5"/>
-      <c r="F227" s="77"/>
+      <c r="F227" s="63"/>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228" s="5"/>
@@ -4672,7 +4763,7 @@
       <c r="C228" s="5"/>
       <c r="D228" s="5"/>
       <c r="E228" s="5"/>
-      <c r="F228" s="77"/>
+      <c r="F228" s="63"/>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229" s="5"/>
@@ -4680,7 +4771,7 @@
       <c r="C229" s="5"/>
       <c r="D229" s="5"/>
       <c r="E229" s="5"/>
-      <c r="F229" s="77"/>
+      <c r="F229" s="63"/>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230" s="5"/>
@@ -4688,7 +4779,7 @@
       <c r="C230" s="5"/>
       <c r="D230" s="5"/>
       <c r="E230" s="5"/>
-      <c r="F230" s="77"/>
+      <c r="F230" s="63"/>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231" s="5"/>
@@ -4696,7 +4787,7 @@
       <c r="C231" s="5"/>
       <c r="D231" s="5"/>
       <c r="E231" s="5"/>
-      <c r="F231" s="77"/>
+      <c r="F231" s="63"/>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" s="5"/>
@@ -4704,7 +4795,7 @@
       <c r="C232" s="5"/>
       <c r="D232" s="5"/>
       <c r="E232" s="5"/>
-      <c r="F232" s="77"/>
+      <c r="F232" s="63"/>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233" s="5"/>
@@ -4712,7 +4803,7 @@
       <c r="C233" s="5"/>
       <c r="D233" s="5"/>
       <c r="E233" s="5"/>
-      <c r="F233" s="77"/>
+      <c r="F233" s="63"/>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234" s="5"/>
@@ -4720,7 +4811,7 @@
       <c r="C234" s="5"/>
       <c r="D234" s="5"/>
       <c r="E234" s="5"/>
-      <c r="F234" s="77"/>
+      <c r="F234" s="63"/>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" s="5"/>
@@ -4728,7 +4819,7 @@
       <c r="C235" s="5"/>
       <c r="D235" s="5"/>
       <c r="E235" s="5"/>
-      <c r="F235" s="77"/>
+      <c r="F235" s="63"/>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" s="5"/>
@@ -4736,7 +4827,7 @@
       <c r="C236" s="5"/>
       <c r="D236" s="5"/>
       <c r="E236" s="5"/>
-      <c r="F236" s="77"/>
+      <c r="F236" s="63"/>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237" s="5"/>
@@ -4744,7 +4835,7 @@
       <c r="C237" s="5"/>
       <c r="D237" s="5"/>
       <c r="E237" s="5"/>
-      <c r="F237" s="77"/>
+      <c r="F237" s="63"/>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238" s="5"/>
@@ -4752,7 +4843,7 @@
       <c r="C238" s="5"/>
       <c r="D238" s="5"/>
       <c r="E238" s="5"/>
-      <c r="F238" s="77"/>
+      <c r="F238" s="63"/>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239" s="5"/>
@@ -4760,7 +4851,7 @@
       <c r="C239" s="5"/>
       <c r="D239" s="5"/>
       <c r="E239" s="5"/>
-      <c r="F239" s="77"/>
+      <c r="F239" s="63"/>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240" s="5"/>
@@ -4768,7 +4859,7 @@
       <c r="C240" s="5"/>
       <c r="D240" s="5"/>
       <c r="E240" s="5"/>
-      <c r="F240" s="77"/>
+      <c r="F240" s="63"/>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241" s="5"/>
@@ -4776,7 +4867,7 @@
       <c r="C241" s="5"/>
       <c r="D241" s="5"/>
       <c r="E241" s="5"/>
-      <c r="F241" s="77"/>
+      <c r="F241" s="63"/>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242" s="5"/>
@@ -4784,7 +4875,7 @@
       <c r="C242" s="5"/>
       <c r="D242" s="5"/>
       <c r="E242" s="5"/>
-      <c r="F242" s="77"/>
+      <c r="F242" s="63"/>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243" s="5"/>
@@ -4792,7 +4883,7 @@
       <c r="C243" s="5"/>
       <c r="D243" s="5"/>
       <c r="E243" s="5"/>
-      <c r="F243" s="77"/>
+      <c r="F243" s="63"/>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244" s="5"/>
@@ -4800,7 +4891,7 @@
       <c r="C244" s="5"/>
       <c r="D244" s="5"/>
       <c r="E244" s="5"/>
-      <c r="F244" s="77"/>
+      <c r="F244" s="63"/>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245" s="5"/>
@@ -4808,7 +4899,7 @@
       <c r="C245" s="5"/>
       <c r="D245" s="5"/>
       <c r="E245" s="5"/>
-      <c r="F245" s="77"/>
+      <c r="F245" s="63"/>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246" s="5"/>
@@ -4816,7 +4907,7 @@
       <c r="C246" s="5"/>
       <c r="D246" s="5"/>
       <c r="E246" s="5"/>
-      <c r="F246" s="77"/>
+      <c r="F246" s="63"/>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247" s="5"/>
@@ -4824,7 +4915,7 @@
       <c r="C247" s="5"/>
       <c r="D247" s="5"/>
       <c r="E247" s="5"/>
-      <c r="F247" s="77"/>
+      <c r="F247" s="63"/>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A248" s="5"/>
@@ -4832,7 +4923,7 @@
       <c r="C248" s="5"/>
       <c r="D248" s="5"/>
       <c r="E248" s="5"/>
-      <c r="F248" s="77"/>
+      <c r="F248" s="63"/>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249" s="5"/>
@@ -4840,7 +4931,7 @@
       <c r="C249" s="5"/>
       <c r="D249" s="5"/>
       <c r="E249" s="5"/>
-      <c r="F249" s="77"/>
+      <c r="F249" s="63"/>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250" s="5"/>
@@ -4848,7 +4939,7 @@
       <c r="C250" s="5"/>
       <c r="D250" s="5"/>
       <c r="E250" s="5"/>
-      <c r="F250" s="77"/>
+      <c r="F250" s="63"/>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251" s="5"/>
@@ -4856,7 +4947,7 @@
       <c r="C251" s="5"/>
       <c r="D251" s="5"/>
       <c r="E251" s="5"/>
-      <c r="F251" s="77"/>
+      <c r="F251" s="63"/>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252" s="5"/>
@@ -4864,7 +4955,7 @@
       <c r="C252" s="5"/>
       <c r="D252" s="5"/>
       <c r="E252" s="5"/>
-      <c r="F252" s="77"/>
+      <c r="F252" s="63"/>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253" s="5"/>
@@ -4872,7 +4963,7 @@
       <c r="C253" s="5"/>
       <c r="D253" s="5"/>
       <c r="E253" s="5"/>
-      <c r="F253" s="77"/>
+      <c r="F253" s="63"/>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254" s="5"/>
@@ -4880,7 +4971,7 @@
       <c r="C254" s="5"/>
       <c r="D254" s="5"/>
       <c r="E254" s="5"/>
-      <c r="F254" s="77"/>
+      <c r="F254" s="63"/>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255" s="5"/>
@@ -4888,7 +4979,7 @@
       <c r="C255" s="5"/>
       <c r="D255" s="5"/>
       <c r="E255" s="5"/>
-      <c r="F255" s="77"/>
+      <c r="F255" s="63"/>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256" s="5"/>
@@ -4896,7 +4987,7 @@
       <c r="C256" s="5"/>
       <c r="D256" s="5"/>
       <c r="E256" s="5"/>
-      <c r="F256" s="77"/>
+      <c r="F256" s="63"/>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A257" s="5"/>
@@ -4904,7 +4995,7 @@
       <c r="C257" s="5"/>
       <c r="D257" s="5"/>
       <c r="E257" s="5"/>
-      <c r="F257" s="77"/>
+      <c r="F257" s="63"/>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A258" s="5"/>
@@ -4912,7 +5003,7 @@
       <c r="C258" s="5"/>
       <c r="D258" s="5"/>
       <c r="E258" s="5"/>
-      <c r="F258" s="77"/>
+      <c r="F258" s="63"/>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A259" s="5"/>
@@ -4920,7 +5011,7 @@
       <c r="C259" s="5"/>
       <c r="D259" s="5"/>
       <c r="E259" s="5"/>
-      <c r="F259" s="77"/>
+      <c r="F259" s="63"/>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A260" s="5"/>
@@ -4928,7 +5019,7 @@
       <c r="C260" s="5"/>
       <c r="D260" s="5"/>
       <c r="E260" s="5"/>
-      <c r="F260" s="77"/>
+      <c r="F260" s="63"/>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A261" s="5"/>
@@ -4936,7 +5027,7 @@
       <c r="C261" s="5"/>
       <c r="D261" s="5"/>
       <c r="E261" s="5"/>
-      <c r="F261" s="77"/>
+      <c r="F261" s="63"/>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262" s="5"/>
@@ -4944,7 +5035,7 @@
       <c r="C262" s="5"/>
       <c r="D262" s="5"/>
       <c r="E262" s="5"/>
-      <c r="F262" s="77"/>
+      <c r="F262" s="63"/>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263" s="5"/>
@@ -4952,7 +5043,7 @@
       <c r="C263" s="5"/>
       <c r="D263" s="5"/>
       <c r="E263" s="5"/>
-      <c r="F263" s="77"/>
+      <c r="F263" s="63"/>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264" s="5"/>
@@ -4960,7 +5051,7 @@
       <c r="C264" s="5"/>
       <c r="D264" s="5"/>
       <c r="E264" s="5"/>
-      <c r="F264" s="77"/>
+      <c r="F264" s="63"/>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265" s="5"/>
@@ -4968,7 +5059,7 @@
       <c r="C265" s="5"/>
       <c r="D265" s="5"/>
       <c r="E265" s="5"/>
-      <c r="F265" s="77"/>
+      <c r="F265" s="63"/>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A266" s="5"/>
@@ -4976,7 +5067,7 @@
       <c r="C266" s="5"/>
       <c r="D266" s="5"/>
       <c r="E266" s="5"/>
-      <c r="F266" s="77"/>
+      <c r="F266" s="63"/>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A267" s="5"/>
@@ -4984,7 +5075,7 @@
       <c r="C267" s="5"/>
       <c r="D267" s="5"/>
       <c r="E267" s="5"/>
-      <c r="F267" s="77"/>
+      <c r="F267" s="63"/>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A268" s="5"/>
@@ -4992,7 +5083,7 @@
       <c r="C268" s="5"/>
       <c r="D268" s="5"/>
       <c r="E268" s="5"/>
-      <c r="F268" s="77"/>
+      <c r="F268" s="63"/>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A269" s="5"/>
@@ -5000,7 +5091,7 @@
       <c r="C269" s="5"/>
       <c r="D269" s="5"/>
       <c r="E269" s="5"/>
-      <c r="F269" s="77"/>
+      <c r="F269" s="63"/>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A270" s="5"/>
@@ -5008,7 +5099,7 @@
       <c r="C270" s="5"/>
       <c r="D270" s="5"/>
       <c r="E270" s="5"/>
-      <c r="F270" s="77"/>
+      <c r="F270" s="63"/>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A271" s="5"/>
@@ -5016,7 +5107,7 @@
       <c r="C271" s="5"/>
       <c r="D271" s="5"/>
       <c r="E271" s="5"/>
-      <c r="F271" s="77"/>
+      <c r="F271" s="63"/>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A272" s="5"/>
@@ -5024,7 +5115,7 @@
       <c r="C272" s="5"/>
       <c r="D272" s="5"/>
       <c r="E272" s="5"/>
-      <c r="F272" s="77"/>
+      <c r="F272" s="63"/>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A273" s="5"/>
@@ -5032,7 +5123,7 @@
       <c r="C273" s="5"/>
       <c r="D273" s="5"/>
       <c r="E273" s="5"/>
-      <c r="F273" s="77"/>
+      <c r="F273" s="63"/>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A274" s="5"/>
@@ -5040,7 +5131,7 @@
       <c r="C274" s="5"/>
       <c r="D274" s="5"/>
       <c r="E274" s="5"/>
-      <c r="F274" s="77"/>
+      <c r="F274" s="63"/>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A275" s="5"/>
@@ -5048,7 +5139,7 @@
       <c r="C275" s="5"/>
       <c r="D275" s="5"/>
       <c r="E275" s="5"/>
-      <c r="F275" s="77"/>
+      <c r="F275" s="63"/>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A276" s="5"/>
@@ -5056,7 +5147,7 @@
       <c r="C276" s="5"/>
       <c r="D276" s="5"/>
       <c r="E276" s="5"/>
-      <c r="F276" s="77"/>
+      <c r="F276" s="63"/>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A277" s="5"/>
@@ -5064,7 +5155,7 @@
       <c r="C277" s="5"/>
       <c r="D277" s="5"/>
       <c r="E277" s="5"/>
-      <c r="F277" s="77"/>
+      <c r="F277" s="63"/>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A278" s="5"/>
@@ -5072,7 +5163,7 @@
       <c r="C278" s="5"/>
       <c r="D278" s="5"/>
       <c r="E278" s="5"/>
-      <c r="F278" s="77"/>
+      <c r="F278" s="63"/>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A279" s="5"/>
@@ -5080,7 +5171,7 @@
       <c r="C279" s="5"/>
       <c r="D279" s="5"/>
       <c r="E279" s="5"/>
-      <c r="F279" s="77"/>
+      <c r="F279" s="63"/>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A280" s="5"/>
@@ -5088,7 +5179,7 @@
       <c r="C280" s="5"/>
       <c r="D280" s="5"/>
       <c r="E280" s="5"/>
-      <c r="F280" s="77"/>
+      <c r="F280" s="63"/>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A281" s="5"/>
@@ -5096,7 +5187,7 @@
       <c r="C281" s="5"/>
       <c r="D281" s="5"/>
       <c r="E281" s="5"/>
-      <c r="F281" s="77"/>
+      <c r="F281" s="63"/>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A282" s="5"/>
@@ -5104,7 +5195,7 @@
       <c r="C282" s="5"/>
       <c r="D282" s="5"/>
       <c r="E282" s="5"/>
-      <c r="F282" s="77"/>
+      <c r="F282" s="63"/>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A283" s="5"/>
@@ -5112,7 +5203,7 @@
       <c r="C283" s="5"/>
       <c r="D283" s="5"/>
       <c r="E283" s="5"/>
-      <c r="F283" s="77"/>
+      <c r="F283" s="63"/>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A284" s="5"/>
@@ -5120,7 +5211,7 @@
       <c r="C284" s="5"/>
       <c r="D284" s="5"/>
       <c r="E284" s="5"/>
-      <c r="F284" s="77"/>
+      <c r="F284" s="63"/>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A285" s="5"/>
@@ -5128,7 +5219,7 @@
       <c r="C285" s="5"/>
       <c r="D285" s="5"/>
       <c r="E285" s="5"/>
-      <c r="F285" s="77"/>
+      <c r="F285" s="63"/>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A286" s="5"/>
@@ -5136,7 +5227,7 @@
       <c r="C286" s="5"/>
       <c r="D286" s="5"/>
       <c r="E286" s="5"/>
-      <c r="F286" s="77"/>
+      <c r="F286" s="63"/>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A287" s="5"/>
@@ -5144,7 +5235,7 @@
       <c r="C287" s="5"/>
       <c r="D287" s="5"/>
       <c r="E287" s="5"/>
-      <c r="F287" s="77"/>
+      <c r="F287" s="63"/>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A288" s="5"/>
@@ -5152,7 +5243,7 @@
       <c r="C288" s="5"/>
       <c r="D288" s="5"/>
       <c r="E288" s="5"/>
-      <c r="F288" s="77"/>
+      <c r="F288" s="63"/>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A289" s="5"/>
@@ -5160,7 +5251,7 @@
       <c r="C289" s="5"/>
       <c r="D289" s="5"/>
       <c r="E289" s="5"/>
-      <c r="F289" s="77"/>
+      <c r="F289" s="63"/>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A290" s="5"/>
@@ -5168,7 +5259,7 @@
       <c r="C290" s="5"/>
       <c r="D290" s="5"/>
       <c r="E290" s="5"/>
-      <c r="F290" s="77"/>
+      <c r="F290" s="63"/>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A291" s="5"/>
@@ -5176,7 +5267,7 @@
       <c r="C291" s="5"/>
       <c r="D291" s="5"/>
       <c r="E291" s="5"/>
-      <c r="F291" s="77"/>
+      <c r="F291" s="63"/>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A292" s="5"/>
@@ -5184,7 +5275,7 @@
       <c r="C292" s="5"/>
       <c r="D292" s="5"/>
       <c r="E292" s="5"/>
-      <c r="F292" s="77"/>
+      <c r="F292" s="63"/>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A293" s="5"/>
@@ -5192,7 +5283,7 @@
       <c r="C293" s="5"/>
       <c r="D293" s="5"/>
       <c r="E293" s="5"/>
-      <c r="F293" s="77"/>
+      <c r="F293" s="63"/>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A294" s="5"/>
@@ -5200,7 +5291,7 @@
       <c r="C294" s="5"/>
       <c r="D294" s="5"/>
       <c r="E294" s="5"/>
-      <c r="F294" s="77"/>
+      <c r="F294" s="63"/>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A295" s="5"/>
@@ -5208,7 +5299,7 @@
       <c r="C295" s="5"/>
       <c r="D295" s="5"/>
       <c r="E295" s="5"/>
-      <c r="F295" s="77"/>
+      <c r="F295" s="63"/>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A296" s="5"/>
@@ -5216,7 +5307,7 @@
       <c r="C296" s="5"/>
       <c r="D296" s="5"/>
       <c r="E296" s="5"/>
-      <c r="F296" s="77"/>
+      <c r="F296" s="63"/>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A297" s="5"/>
@@ -5224,7 +5315,7 @@
       <c r="C297" s="5"/>
       <c r="D297" s="5"/>
       <c r="E297" s="5"/>
-      <c r="F297" s="77"/>
+      <c r="F297" s="63"/>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A298" s="5"/>
@@ -5232,7 +5323,7 @@
       <c r="C298" s="5"/>
       <c r="D298" s="5"/>
       <c r="E298" s="5"/>
-      <c r="F298" s="77"/>
+      <c r="F298" s="63"/>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A299" s="5"/>
@@ -5240,7 +5331,7 @@
       <c r="C299" s="5"/>
       <c r="D299" s="5"/>
       <c r="E299" s="5"/>
-      <c r="F299" s="77"/>
+      <c r="F299" s="63"/>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A300" s="5"/>
@@ -5248,7 +5339,7 @@
       <c r="C300" s="5"/>
       <c r="D300" s="5"/>
       <c r="E300" s="5"/>
-      <c r="F300" s="77"/>
+      <c r="F300" s="63"/>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A301" s="5"/>
@@ -5256,7 +5347,7 @@
       <c r="C301" s="5"/>
       <c r="D301" s="5"/>
       <c r="E301" s="5"/>
-      <c r="F301" s="77"/>
+      <c r="F301" s="63"/>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A302" s="5"/>
@@ -5264,7 +5355,7 @@
       <c r="C302" s="5"/>
       <c r="D302" s="5"/>
       <c r="E302" s="5"/>
-      <c r="F302" s="77"/>
+      <c r="F302" s="63"/>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A303" s="5"/>
@@ -5272,7 +5363,7 @@
       <c r="C303" s="5"/>
       <c r="D303" s="5"/>
       <c r="E303" s="5"/>
-      <c r="F303" s="77"/>
+      <c r="F303" s="63"/>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A304" s="5"/>
@@ -5280,7 +5371,7 @@
       <c r="C304" s="5"/>
       <c r="D304" s="5"/>
       <c r="E304" s="5"/>
-      <c r="F304" s="77"/>
+      <c r="F304" s="63"/>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A305" s="5"/>
@@ -5288,7 +5379,7 @@
       <c r="C305" s="5"/>
       <c r="D305" s="5"/>
       <c r="E305" s="5"/>
-      <c r="F305" s="77"/>
+      <c r="F305" s="63"/>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A306" s="5"/>
@@ -5296,7 +5387,7 @@
       <c r="C306" s="5"/>
       <c r="D306" s="5"/>
       <c r="E306" s="5"/>
-      <c r="F306" s="77"/>
+      <c r="F306" s="63"/>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A307" s="5"/>
@@ -5304,7 +5395,7 @@
       <c r="C307" s="5"/>
       <c r="D307" s="5"/>
       <c r="E307" s="5"/>
-      <c r="F307" s="77"/>
+      <c r="F307" s="63"/>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A308" s="5"/>
@@ -5312,7 +5403,7 @@
       <c r="C308" s="5"/>
       <c r="D308" s="5"/>
       <c r="E308" s="5"/>
-      <c r="F308" s="77"/>
+      <c r="F308" s="63"/>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A309" s="5"/>
@@ -5320,7 +5411,7 @@
       <c r="C309" s="5"/>
       <c r="D309" s="5"/>
       <c r="E309" s="5"/>
-      <c r="F309" s="77"/>
+      <c r="F309" s="63"/>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A310" s="5"/>
@@ -5328,7 +5419,7 @@
       <c r="C310" s="5"/>
       <c r="D310" s="5"/>
       <c r="E310" s="5"/>
-      <c r="F310" s="77"/>
+      <c r="F310" s="63"/>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A311" s="5"/>
@@ -5336,7 +5427,7 @@
       <c r="C311" s="5"/>
       <c r="D311" s="5"/>
       <c r="E311" s="5"/>
-      <c r="F311" s="77"/>
+      <c r="F311" s="63"/>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A312" s="5"/>
@@ -5344,7 +5435,7 @@
       <c r="C312" s="5"/>
       <c r="D312" s="5"/>
       <c r="E312" s="5"/>
-      <c r="F312" s="77"/>
+      <c r="F312" s="63"/>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A313" s="5"/>
@@ -5352,7 +5443,7 @@
       <c r="C313" s="5"/>
       <c r="D313" s="5"/>
       <c r="E313" s="5"/>
-      <c r="F313" s="77"/>
+      <c r="F313" s="63"/>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A314" s="5"/>
@@ -5360,7 +5451,7 @@
       <c r="C314" s="5"/>
       <c r="D314" s="5"/>
       <c r="E314" s="5"/>
-      <c r="F314" s="77"/>
+      <c r="F314" s="63"/>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A315" s="5"/>
@@ -5368,7 +5459,7 @@
       <c r="C315" s="5"/>
       <c r="D315" s="5"/>
       <c r="E315" s="5"/>
-      <c r="F315" s="77"/>
+      <c r="F315" s="63"/>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A316" s="5"/>
@@ -5376,7 +5467,7 @@
       <c r="C316" s="5"/>
       <c r="D316" s="5"/>
       <c r="E316" s="5"/>
-      <c r="F316" s="77"/>
+      <c r="F316" s="63"/>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A317" s="5"/>
@@ -5384,7 +5475,7 @@
       <c r="C317" s="5"/>
       <c r="D317" s="5"/>
       <c r="E317" s="5"/>
-      <c r="F317" s="77"/>
+      <c r="F317" s="63"/>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A318" s="5"/>
@@ -5392,7 +5483,7 @@
       <c r="C318" s="5"/>
       <c r="D318" s="5"/>
       <c r="E318" s="5"/>
-      <c r="F318" s="77"/>
+      <c r="F318" s="63"/>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A319" s="5"/>
@@ -5400,7 +5491,7 @@
       <c r="C319" s="5"/>
       <c r="D319" s="5"/>
       <c r="E319" s="5"/>
-      <c r="F319" s="77"/>
+      <c r="F319" s="63"/>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A320" s="5"/>
@@ -5408,7 +5499,7 @@
       <c r="C320" s="5"/>
       <c r="D320" s="5"/>
       <c r="E320" s="5"/>
-      <c r="F320" s="77"/>
+      <c r="F320" s="63"/>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A321" s="5"/>
@@ -5416,7 +5507,7 @@
       <c r="C321" s="5"/>
       <c r="D321" s="5"/>
       <c r="E321" s="5"/>
-      <c r="F321" s="77"/>
+      <c r="F321" s="63"/>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A322" s="5"/>
@@ -5424,7 +5515,7 @@
       <c r="C322" s="5"/>
       <c r="D322" s="5"/>
       <c r="E322" s="5"/>
-      <c r="F322" s="77"/>
+      <c r="F322" s="63"/>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A323" s="5"/>
@@ -5432,7 +5523,7 @@
       <c r="C323" s="5"/>
       <c r="D323" s="5"/>
       <c r="E323" s="5"/>
-      <c r="F323" s="77"/>
+      <c r="F323" s="63"/>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A324" s="5"/>
@@ -5440,7 +5531,7 @@
       <c r="C324" s="5"/>
       <c r="D324" s="5"/>
       <c r="E324" s="5"/>
-      <c r="F324" s="77"/>
+      <c r="F324" s="63"/>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A325" s="5"/>
@@ -5448,7 +5539,7 @@
       <c r="C325" s="5"/>
       <c r="D325" s="5"/>
       <c r="E325" s="5"/>
-      <c r="F325" s="77"/>
+      <c r="F325" s="63"/>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A326" s="5"/>
@@ -5456,7 +5547,7 @@
       <c r="C326" s="5"/>
       <c r="D326" s="5"/>
       <c r="E326" s="5"/>
-      <c r="F326" s="77"/>
+      <c r="F326" s="63"/>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A327" s="5"/>
@@ -5464,7 +5555,7 @@
       <c r="C327" s="5"/>
       <c r="D327" s="5"/>
       <c r="E327" s="5"/>
-      <c r="F327" s="77"/>
+      <c r="F327" s="63"/>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A328" s="5"/>
@@ -5472,7 +5563,7 @@
       <c r="C328" s="5"/>
       <c r="D328" s="5"/>
       <c r="E328" s="5"/>
-      <c r="F328" s="77"/>
+      <c r="F328" s="63"/>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A329" s="5"/>
@@ -5480,7 +5571,7 @@
       <c r="C329" s="5"/>
       <c r="D329" s="5"/>
       <c r="E329" s="5"/>
-      <c r="F329" s="77"/>
+      <c r="F329" s="63"/>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A330" s="5"/>
@@ -5488,7 +5579,7 @@
       <c r="C330" s="5"/>
       <c r="D330" s="5"/>
       <c r="E330" s="5"/>
-      <c r="F330" s="77"/>
+      <c r="F330" s="63"/>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A331" s="5"/>
@@ -5496,7 +5587,7 @@
       <c r="C331" s="5"/>
       <c r="D331" s="5"/>
       <c r="E331" s="5"/>
-      <c r="F331" s="77"/>
+      <c r="F331" s="63"/>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A332" s="5"/>
@@ -5504,7 +5595,7 @@
       <c r="C332" s="5"/>
       <c r="D332" s="5"/>
       <c r="E332" s="5"/>
-      <c r="F332" s="77"/>
+      <c r="F332" s="63"/>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A333" s="5"/>
@@ -5512,7 +5603,7 @@
       <c r="C333" s="5"/>
       <c r="D333" s="5"/>
       <c r="E333" s="5"/>
-      <c r="F333" s="77"/>
+      <c r="F333" s="63"/>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A334" s="5"/>
@@ -5520,7 +5611,7 @@
       <c r="C334" s="5"/>
       <c r="D334" s="5"/>
       <c r="E334" s="5"/>
-      <c r="F334" s="77"/>
+      <c r="F334" s="63"/>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A335" s="5"/>
@@ -5528,7 +5619,7 @@
       <c r="C335" s="5"/>
       <c r="D335" s="5"/>
       <c r="E335" s="5"/>
-      <c r="F335" s="77"/>
+      <c r="F335" s="63"/>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A336" s="5"/>
@@ -5536,7 +5627,7 @@
       <c r="C336" s="5"/>
       <c r="D336" s="5"/>
       <c r="E336" s="5"/>
-      <c r="F336" s="77"/>
+      <c r="F336" s="63"/>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A337" s="5"/>
@@ -5544,7 +5635,7 @@
       <c r="C337" s="5"/>
       <c r="D337" s="5"/>
       <c r="E337" s="5"/>
-      <c r="F337" s="77"/>
+      <c r="F337" s="63"/>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A338" s="5"/>
@@ -5552,7 +5643,7 @@
       <c r="C338" s="5"/>
       <c r="D338" s="5"/>
       <c r="E338" s="5"/>
-      <c r="F338" s="77"/>
+      <c r="F338" s="63"/>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A339" s="5"/>
@@ -5560,7 +5651,7 @@
       <c r="C339" s="5"/>
       <c r="D339" s="5"/>
       <c r="E339" s="5"/>
-      <c r="F339" s="77"/>
+      <c r="F339" s="63"/>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A340" s="5"/>
@@ -5568,7 +5659,7 @@
       <c r="C340" s="5"/>
       <c r="D340" s="5"/>
       <c r="E340" s="5"/>
-      <c r="F340" s="77"/>
+      <c r="F340" s="63"/>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A341" s="5"/>
@@ -5576,7 +5667,7 @@
       <c r="C341" s="5"/>
       <c r="D341" s="5"/>
       <c r="E341" s="5"/>
-      <c r="F341" s="77"/>
+      <c r="F341" s="63"/>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A342" s="5"/>
@@ -5584,7 +5675,7 @@
       <c r="C342" s="5"/>
       <c r="D342" s="5"/>
       <c r="E342" s="5"/>
-      <c r="F342" s="77"/>
+      <c r="F342" s="63"/>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A343" s="5"/>
@@ -5592,7 +5683,7 @@
       <c r="C343" s="5"/>
       <c r="D343" s="5"/>
       <c r="E343" s="5"/>
-      <c r="F343" s="77"/>
+      <c r="F343" s="63"/>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A344" s="5"/>
@@ -5600,7 +5691,7 @@
       <c r="C344" s="5"/>
       <c r="D344" s="5"/>
       <c r="E344" s="5"/>
-      <c r="F344" s="77"/>
+      <c r="F344" s="63"/>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A345" s="5"/>
@@ -5608,7 +5699,7 @@
       <c r="C345" s="5"/>
       <c r="D345" s="5"/>
       <c r="E345" s="5"/>
-      <c r="F345" s="77"/>
+      <c r="F345" s="63"/>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A346" s="5"/>
@@ -5616,7 +5707,7 @@
       <c r="C346" s="5"/>
       <c r="D346" s="5"/>
       <c r="E346" s="5"/>
-      <c r="F346" s="77"/>
+      <c r="F346" s="63"/>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A347" s="5"/>
@@ -5624,7 +5715,7 @@
       <c r="C347" s="5"/>
       <c r="D347" s="5"/>
       <c r="E347" s="5"/>
-      <c r="F347" s="77"/>
+      <c r="F347" s="63"/>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A348" s="5"/>
@@ -5632,7 +5723,7 @@
       <c r="C348" s="5"/>
       <c r="D348" s="5"/>
       <c r="E348" s="5"/>
-      <c r="F348" s="77"/>
+      <c r="F348" s="63"/>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A349" s="5"/>
@@ -5640,7 +5731,7 @@
       <c r="C349" s="5"/>
       <c r="D349" s="5"/>
       <c r="E349" s="5"/>
-      <c r="F349" s="77"/>
+      <c r="F349" s="63"/>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A350" s="5"/>
@@ -5648,7 +5739,7 @@
       <c r="C350" s="5"/>
       <c r="D350" s="5"/>
       <c r="E350" s="5"/>
-      <c r="F350" s="77"/>
+      <c r="F350" s="63"/>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A351" s="5"/>
@@ -5656,7 +5747,7 @@
       <c r="C351" s="5"/>
       <c r="D351" s="5"/>
       <c r="E351" s="5"/>
-      <c r="F351" s="77"/>
+      <c r="F351" s="63"/>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A352" s="5"/>
@@ -5664,7 +5755,7 @@
       <c r="C352" s="5"/>
       <c r="D352" s="5"/>
       <c r="E352" s="5"/>
-      <c r="F352" s="77"/>
+      <c r="F352" s="63"/>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A353" s="5"/>
@@ -5672,7 +5763,7 @@
       <c r="C353" s="5"/>
       <c r="D353" s="5"/>
       <c r="E353" s="5"/>
-      <c r="F353" s="77"/>
+      <c r="F353" s="63"/>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A354" s="5"/>
@@ -5680,7 +5771,7 @@
       <c r="C354" s="5"/>
       <c r="D354" s="5"/>
       <c r="E354" s="5"/>
-      <c r="F354" s="77"/>
+      <c r="F354" s="63"/>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A355" s="5"/>
@@ -5688,7 +5779,7 @@
       <c r="C355" s="5"/>
       <c r="D355" s="5"/>
       <c r="E355" s="5"/>
-      <c r="F355" s="77"/>
+      <c r="F355" s="63"/>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A356" s="5"/>
@@ -5696,7 +5787,7 @@
       <c r="C356" s="5"/>
       <c r="D356" s="5"/>
       <c r="E356" s="5"/>
-      <c r="F356" s="77"/>
+      <c r="F356" s="63"/>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A357" s="5"/>
@@ -5704,7 +5795,7 @@
       <c r="C357" s="5"/>
       <c r="D357" s="5"/>
       <c r="E357" s="5"/>
-      <c r="F357" s="77"/>
+      <c r="F357" s="63"/>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A358" s="5"/>
@@ -5712,7 +5803,7 @@
       <c r="C358" s="5"/>
       <c r="D358" s="5"/>
       <c r="E358" s="5"/>
-      <c r="F358" s="77"/>
+      <c r="F358" s="63"/>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A359" s="5"/>
@@ -5720,7 +5811,7 @@
       <c r="C359" s="5"/>
       <c r="D359" s="5"/>
       <c r="E359" s="5"/>
-      <c r="F359" s="77"/>
+      <c r="F359" s="63"/>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A360" s="5"/>
@@ -5728,7 +5819,7 @@
       <c r="C360" s="5"/>
       <c r="D360" s="5"/>
       <c r="E360" s="5"/>
-      <c r="F360" s="77"/>
+      <c r="F360" s="63"/>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A361" s="5"/>
@@ -5736,7 +5827,7 @@
       <c r="C361" s="5"/>
       <c r="D361" s="5"/>
       <c r="E361" s="5"/>
-      <c r="F361" s="77"/>
+      <c r="F361" s="63"/>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A362" s="5"/>
@@ -5744,7 +5835,7 @@
       <c r="C362" s="5"/>
       <c r="D362" s="5"/>
       <c r="E362" s="5"/>
-      <c r="F362" s="77"/>
+      <c r="F362" s="63"/>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A363" s="5"/>
@@ -5752,7 +5843,7 @@
       <c r="C363" s="5"/>
       <c r="D363" s="5"/>
       <c r="E363" s="5"/>
-      <c r="F363" s="77"/>
+      <c r="F363" s="63"/>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A364" s="5"/>
@@ -5760,7 +5851,7 @@
       <c r="C364" s="5"/>
       <c r="D364" s="5"/>
       <c r="E364" s="5"/>
-      <c r="F364" s="77"/>
+      <c r="F364" s="63"/>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A365" s="5"/>
@@ -5768,7 +5859,7 @@
       <c r="C365" s="5"/>
       <c r="D365" s="5"/>
       <c r="E365" s="5"/>
-      <c r="F365" s="77"/>
+      <c r="F365" s="63"/>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A366" s="5"/>
@@ -5776,7 +5867,7 @@
       <c r="C366" s="5"/>
       <c r="D366" s="5"/>
       <c r="E366" s="5"/>
-      <c r="F366" s="77"/>
+      <c r="F366" s="63"/>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A367" s="5"/>
@@ -5784,7 +5875,7 @@
       <c r="C367" s="5"/>
       <c r="D367" s="5"/>
       <c r="E367" s="5"/>
-      <c r="F367" s="77"/>
+      <c r="F367" s="63"/>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A368" s="5"/>
@@ -5792,7 +5883,7 @@
       <c r="C368" s="5"/>
       <c r="D368" s="5"/>
       <c r="E368" s="5"/>
-      <c r="F368" s="77"/>
+      <c r="F368" s="63"/>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A369" s="5"/>
@@ -5800,7 +5891,7 @@
       <c r="C369" s="5"/>
       <c r="D369" s="5"/>
       <c r="E369" s="5"/>
-      <c r="F369" s="77"/>
+      <c r="F369" s="63"/>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A370" s="5"/>
@@ -5808,7 +5899,7 @@
       <c r="C370" s="5"/>
       <c r="D370" s="5"/>
       <c r="E370" s="5"/>
-      <c r="F370" s="77"/>
+      <c r="F370" s="63"/>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A371" s="5"/>
@@ -5816,7 +5907,7 @@
       <c r="C371" s="5"/>
       <c r="D371" s="5"/>
       <c r="E371" s="5"/>
-      <c r="F371" s="77"/>
+      <c r="F371" s="63"/>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A372" s="5"/>
@@ -5824,7 +5915,7 @@
       <c r="C372" s="5"/>
       <c r="D372" s="5"/>
       <c r="E372" s="5"/>
-      <c r="F372" s="77"/>
+      <c r="F372" s="63"/>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A373" s="5"/>
@@ -5832,7 +5923,7 @@
       <c r="C373" s="5"/>
       <c r="D373" s="5"/>
       <c r="E373" s="5"/>
-      <c r="F373" s="77"/>
+      <c r="F373" s="63"/>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A374" s="5"/>
@@ -5840,7 +5931,7 @@
       <c r="C374" s="5"/>
       <c r="D374" s="5"/>
       <c r="E374" s="5"/>
-      <c r="F374" s="77"/>
+      <c r="F374" s="63"/>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A375" s="5"/>
@@ -5848,7 +5939,7 @@
       <c r="C375" s="5"/>
       <c r="D375" s="5"/>
       <c r="E375" s="5"/>
-      <c r="F375" s="77"/>
+      <c r="F375" s="63"/>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A376" s="5"/>
@@ -5856,7 +5947,7 @@
       <c r="C376" s="5"/>
       <c r="D376" s="5"/>
       <c r="E376" s="5"/>
-      <c r="F376" s="77"/>
+      <c r="F376" s="63"/>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A377" s="5"/>
@@ -5864,7 +5955,7 @@
       <c r="C377" s="5"/>
       <c r="D377" s="5"/>
       <c r="E377" s="5"/>
-      <c r="F377" s="77"/>
+      <c r="F377" s="63"/>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A378" s="5"/>
@@ -5872,7 +5963,7 @@
       <c r="C378" s="5"/>
       <c r="D378" s="5"/>
       <c r="E378" s="5"/>
-      <c r="F378" s="77"/>
+      <c r="F378" s="63"/>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A379" s="5"/>
@@ -5880,7 +5971,7 @@
       <c r="C379" s="5"/>
       <c r="D379" s="5"/>
       <c r="E379" s="5"/>
-      <c r="F379" s="77"/>
+      <c r="F379" s="63"/>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A380" s="5"/>
@@ -5888,7 +5979,7 @@
       <c r="C380" s="5"/>
       <c r="D380" s="5"/>
       <c r="E380" s="5"/>
-      <c r="F380" s="77"/>
+      <c r="F380" s="63"/>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A381" s="5"/>
@@ -5896,7 +5987,7 @@
       <c r="C381" s="5"/>
       <c r="D381" s="5"/>
       <c r="E381" s="5"/>
-      <c r="F381" s="77"/>
+      <c r="F381" s="63"/>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A382" s="5"/>
@@ -5904,7 +5995,7 @@
       <c r="C382" s="5"/>
       <c r="D382" s="5"/>
       <c r="E382" s="5"/>
-      <c r="F382" s="77"/>
+      <c r="F382" s="63"/>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A383" s="5"/>
@@ -5912,7 +6003,7 @@
       <c r="C383" s="5"/>
       <c r="D383" s="5"/>
       <c r="E383" s="5"/>
-      <c r="F383" s="77"/>
+      <c r="F383" s="63"/>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A384" s="5"/>
@@ -5920,7 +6011,7 @@
       <c r="C384" s="5"/>
       <c r="D384" s="5"/>
       <c r="E384" s="5"/>
-      <c r="F384" s="77"/>
+      <c r="F384" s="63"/>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A385" s="5"/>
@@ -5928,7 +6019,7 @@
       <c r="C385" s="5"/>
       <c r="D385" s="5"/>
       <c r="E385" s="5"/>
-      <c r="F385" s="77"/>
+      <c r="F385" s="63"/>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A386" s="5"/>
@@ -5936,7 +6027,7 @@
       <c r="C386" s="5"/>
       <c r="D386" s="5"/>
       <c r="E386" s="5"/>
-      <c r="F386" s="77"/>
+      <c r="F386" s="63"/>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A387" s="5"/>
@@ -5944,7 +6035,7 @@
       <c r="C387" s="5"/>
       <c r="D387" s="5"/>
       <c r="E387" s="5"/>
-      <c r="F387" s="77"/>
+      <c r="F387" s="63"/>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A388" s="5"/>
@@ -5952,7 +6043,7 @@
       <c r="C388" s="5"/>
       <c r="D388" s="5"/>
       <c r="E388" s="5"/>
-      <c r="F388" s="77"/>
+      <c r="F388" s="63"/>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A389" s="5"/>
@@ -5960,7 +6051,7 @@
       <c r="C389" s="5"/>
       <c r="D389" s="5"/>
       <c r="E389" s="5"/>
-      <c r="F389" s="77"/>
+      <c r="F389" s="63"/>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A390" s="5"/>
@@ -5968,7 +6059,7 @@
       <c r="C390" s="5"/>
       <c r="D390" s="5"/>
       <c r="E390" s="5"/>
-      <c r="F390" s="77"/>
+      <c r="F390" s="63"/>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A391" s="5"/>
@@ -5976,7 +6067,7 @@
       <c r="C391" s="5"/>
       <c r="D391" s="5"/>
       <c r="E391" s="5"/>
-      <c r="F391" s="77"/>
+      <c r="F391" s="63"/>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A392" s="5"/>
@@ -5984,7 +6075,7 @@
       <c r="C392" s="5"/>
       <c r="D392" s="5"/>
       <c r="E392" s="5"/>
-      <c r="F392" s="77"/>
+      <c r="F392" s="63"/>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A393" s="5"/>
@@ -5992,7 +6083,7 @@
       <c r="C393" s="5"/>
       <c r="D393" s="5"/>
       <c r="E393" s="5"/>
-      <c r="F393" s="77"/>
+      <c r="F393" s="63"/>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A394" s="5"/>
@@ -6000,7 +6091,7 @@
       <c r="C394" s="5"/>
       <c r="D394" s="5"/>
       <c r="E394" s="5"/>
-      <c r="F394" s="77"/>
+      <c r="F394" s="63"/>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A395" s="5"/>
@@ -6008,7 +6099,7 @@
       <c r="C395" s="5"/>
       <c r="D395" s="5"/>
       <c r="E395" s="5"/>
-      <c r="F395" s="77"/>
+      <c r="F395" s="63"/>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A396" s="5"/>
@@ -6016,7 +6107,7 @@
       <c r="C396" s="5"/>
       <c r="D396" s="5"/>
       <c r="E396" s="5"/>
-      <c r="F396" s="77"/>
+      <c r="F396" s="63"/>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A397" s="5"/>
@@ -6024,7 +6115,7 @@
       <c r="C397" s="5"/>
       <c r="D397" s="5"/>
       <c r="E397" s="5"/>
-      <c r="F397" s="77"/>
+      <c r="F397" s="63"/>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A398" s="5"/>
@@ -6032,7 +6123,7 @@
       <c r="C398" s="5"/>
       <c r="D398" s="5"/>
       <c r="E398" s="5"/>
-      <c r="F398" s="77"/>
+      <c r="F398" s="63"/>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A399" s="5"/>
@@ -6040,7 +6131,7 @@
       <c r="C399" s="5"/>
       <c r="D399" s="5"/>
       <c r="E399" s="5"/>
-      <c r="F399" s="77"/>
+      <c r="F399" s="63"/>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A400" s="5"/>
@@ -6048,7 +6139,7 @@
       <c r="C400" s="5"/>
       <c r="D400" s="5"/>
       <c r="E400" s="5"/>
-      <c r="F400" s="77"/>
+      <c r="F400" s="63"/>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A401" s="5"/>
@@ -6056,7 +6147,7 @@
       <c r="C401" s="5"/>
       <c r="D401" s="5"/>
       <c r="E401" s="5"/>
-      <c r="F401" s="77"/>
+      <c r="F401" s="63"/>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A402" s="5"/>
@@ -6064,7 +6155,7 @@
       <c r="C402" s="5"/>
       <c r="D402" s="5"/>
       <c r="E402" s="5"/>
-      <c r="F402" s="77"/>
+      <c r="F402" s="63"/>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A403" s="5"/>
@@ -6072,7 +6163,7 @@
       <c r="C403" s="5"/>
       <c r="D403" s="5"/>
       <c r="E403" s="5"/>
-      <c r="F403" s="77"/>
+      <c r="F403" s="63"/>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A404" s="5"/>
@@ -6080,7 +6171,7 @@
       <c r="C404" s="5"/>
       <c r="D404" s="5"/>
       <c r="E404" s="5"/>
-      <c r="F404" s="77"/>
+      <c r="F404" s="63"/>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A405" s="5"/>
@@ -6088,7 +6179,7 @@
       <c r="C405" s="5"/>
       <c r="D405" s="5"/>
       <c r="E405" s="5"/>
-      <c r="F405" s="77"/>
+      <c r="F405" s="63"/>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A406" s="5"/>
@@ -6096,7 +6187,7 @@
       <c r="C406" s="5"/>
       <c r="D406" s="5"/>
       <c r="E406" s="5"/>
-      <c r="F406" s="77"/>
+      <c r="F406" s="63"/>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A407" s="5"/>
@@ -6104,7 +6195,7 @@
       <c r="C407" s="5"/>
       <c r="D407" s="5"/>
       <c r="E407" s="5"/>
-      <c r="F407" s="77"/>
+      <c r="F407" s="63"/>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A408" s="5"/>
@@ -6112,7 +6203,7 @@
       <c r="C408" s="5"/>
       <c r="D408" s="5"/>
       <c r="E408" s="5"/>
-      <c r="F408" s="77"/>
+      <c r="F408" s="63"/>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A409" s="5"/>
@@ -6120,7 +6211,7 @@
       <c r="C409" s="5"/>
       <c r="D409" s="5"/>
       <c r="E409" s="5"/>
-      <c r="F409" s="77"/>
+      <c r="F409" s="63"/>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A410" s="5"/>
@@ -6128,7 +6219,7 @@
       <c r="C410" s="5"/>
       <c r="D410" s="5"/>
       <c r="E410" s="5"/>
-      <c r="F410" s="77"/>
+      <c r="F410" s="63"/>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A411" s="5"/>
@@ -6136,7 +6227,7 @@
       <c r="C411" s="5"/>
       <c r="D411" s="5"/>
       <c r="E411" s="5"/>
-      <c r="F411" s="77"/>
+      <c r="F411" s="63"/>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A412" s="5"/>
@@ -6144,7 +6235,7 @@
       <c r="C412" s="5"/>
       <c r="D412" s="5"/>
       <c r="E412" s="5"/>
-      <c r="F412" s="77"/>
+      <c r="F412" s="63"/>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A413" s="5"/>
@@ -6152,7 +6243,7 @@
       <c r="C413" s="5"/>
       <c r="D413" s="5"/>
       <c r="E413" s="5"/>
-      <c r="F413" s="77"/>
+      <c r="F413" s="63"/>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A414" s="5"/>
@@ -6160,7 +6251,7 @@
       <c r="C414" s="5"/>
       <c r="D414" s="5"/>
       <c r="E414" s="5"/>
-      <c r="F414" s="77"/>
+      <c r="F414" s="63"/>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A415" s="5"/>
@@ -6168,7 +6259,7 @@
       <c r="C415" s="5"/>
       <c r="D415" s="5"/>
       <c r="E415" s="5"/>
-      <c r="F415" s="77"/>
+      <c r="F415" s="63"/>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A416" s="5"/>
@@ -6176,7 +6267,7 @@
       <c r="C416" s="5"/>
       <c r="D416" s="5"/>
       <c r="E416" s="5"/>
-      <c r="F416" s="77"/>
+      <c r="F416" s="63"/>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A417" s="5"/>
@@ -6184,7 +6275,7 @@
       <c r="C417" s="5"/>
       <c r="D417" s="5"/>
       <c r="E417" s="5"/>
-      <c r="F417" s="77"/>
+      <c r="F417" s="63"/>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A418" s="5"/>
@@ -6192,7 +6283,7 @@
       <c r="C418" s="5"/>
       <c r="D418" s="5"/>
       <c r="E418" s="5"/>
-      <c r="F418" s="77"/>
+      <c r="F418" s="63"/>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A419" s="5"/>
@@ -6200,7 +6291,7 @@
       <c r="C419" s="5"/>
       <c r="D419" s="5"/>
       <c r="E419" s="5"/>
-      <c r="F419" s="77"/>
+      <c r="F419" s="63"/>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A420" s="5"/>
@@ -6208,7 +6299,7 @@
       <c r="C420" s="5"/>
       <c r="D420" s="5"/>
       <c r="E420" s="5"/>
-      <c r="F420" s="77"/>
+      <c r="F420" s="63"/>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A421" s="5"/>
@@ -6216,7 +6307,7 @@
       <c r="C421" s="5"/>
       <c r="D421" s="5"/>
       <c r="E421" s="5"/>
-      <c r="F421" s="77"/>
+      <c r="F421" s="63"/>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A422" s="5"/>
@@ -6224,7 +6315,7 @@
       <c r="C422" s="5"/>
       <c r="D422" s="5"/>
       <c r="E422" s="5"/>
-      <c r="F422" s="77"/>
+      <c r="F422" s="63"/>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A423" s="5"/>
@@ -6232,7 +6323,7 @@
       <c r="C423" s="5"/>
       <c r="D423" s="5"/>
       <c r="E423" s="5"/>
-      <c r="F423" s="77"/>
+      <c r="F423" s="63"/>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A424" s="5"/>
@@ -6240,7 +6331,7 @@
       <c r="C424" s="5"/>
       <c r="D424" s="5"/>
       <c r="E424" s="5"/>
-      <c r="F424" s="77"/>
+      <c r="F424" s="63"/>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A425" s="5"/>
@@ -6248,7 +6339,7 @@
       <c r="C425" s="5"/>
       <c r="D425" s="5"/>
       <c r="E425" s="5"/>
-      <c r="F425" s="77"/>
+      <c r="F425" s="63"/>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A426" s="5"/>
@@ -6256,7 +6347,7 @@
       <c r="C426" s="5"/>
       <c r="D426" s="5"/>
       <c r="E426" s="5"/>
-      <c r="F426" s="77"/>
+      <c r="F426" s="63"/>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A427" s="5"/>
@@ -6264,7 +6355,7 @@
       <c r="C427" s="5"/>
       <c r="D427" s="5"/>
       <c r="E427" s="5"/>
-      <c r="F427" s="77"/>
+      <c r="F427" s="63"/>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A428" s="5"/>
@@ -6272,7 +6363,7 @@
       <c r="C428" s="5"/>
       <c r="D428" s="5"/>
       <c r="E428" s="5"/>
-      <c r="F428" s="77"/>
+      <c r="F428" s="63"/>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A429" s="5"/>
@@ -6280,7 +6371,7 @@
       <c r="C429" s="5"/>
       <c r="D429" s="5"/>
       <c r="E429" s="5"/>
-      <c r="F429" s="77"/>
+      <c r="F429" s="63"/>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A430" s="5"/>
@@ -6288,7 +6379,7 @@
       <c r="C430" s="5"/>
       <c r="D430" s="5"/>
       <c r="E430" s="5"/>
-      <c r="F430" s="77"/>
+      <c r="F430" s="63"/>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A431" s="5"/>
@@ -6296,7 +6387,7 @@
       <c r="C431" s="5"/>
       <c r="D431" s="5"/>
       <c r="E431" s="5"/>
-      <c r="F431" s="77"/>
+      <c r="F431" s="63"/>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A432" s="5"/>
@@ -6304,7 +6395,7 @@
       <c r="C432" s="5"/>
       <c r="D432" s="5"/>
       <c r="E432" s="5"/>
-      <c r="F432" s="77"/>
+      <c r="F432" s="63"/>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A433" s="5"/>
@@ -6312,7 +6403,7 @@
       <c r="C433" s="5"/>
       <c r="D433" s="5"/>
       <c r="E433" s="5"/>
-      <c r="F433" s="77"/>
+      <c r="F433" s="63"/>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A434" s="5"/>
@@ -6320,7 +6411,7 @@
       <c r="C434" s="5"/>
       <c r="D434" s="5"/>
       <c r="E434" s="5"/>
-      <c r="F434" s="77"/>
+      <c r="F434" s="63"/>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A435" s="5"/>
@@ -6328,7 +6419,7 @@
       <c r="C435" s="5"/>
       <c r="D435" s="5"/>
       <c r="E435" s="5"/>
-      <c r="F435" s="77"/>
+      <c r="F435" s="63"/>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A436" s="5"/>
@@ -6336,7 +6427,7 @@
       <c r="C436" s="5"/>
       <c r="D436" s="5"/>
       <c r="E436" s="5"/>
-      <c r="F436" s="77"/>
+      <c r="F436" s="63"/>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A437" s="5"/>
@@ -6344,7 +6435,7 @@
       <c r="C437" s="5"/>
       <c r="D437" s="5"/>
       <c r="E437" s="5"/>
-      <c r="F437" s="77"/>
+      <c r="F437" s="63"/>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A438" s="5"/>
@@ -6352,7 +6443,7 @@
       <c r="C438" s="5"/>
       <c r="D438" s="5"/>
       <c r="E438" s="5"/>
-      <c r="F438" s="77"/>
+      <c r="F438" s="63"/>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A439" s="5"/>
@@ -6360,7 +6451,7 @@
       <c r="C439" s="5"/>
       <c r="D439" s="5"/>
       <c r="E439" s="5"/>
-      <c r="F439" s="77"/>
+      <c r="F439" s="63"/>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A440" s="5"/>
@@ -6368,7 +6459,7 @@
       <c r="C440" s="5"/>
       <c r="D440" s="5"/>
       <c r="E440" s="5"/>
-      <c r="F440" s="77"/>
+      <c r="F440" s="63"/>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A441" s="5"/>
@@ -6376,7 +6467,7 @@
       <c r="C441" s="5"/>
       <c r="D441" s="5"/>
       <c r="E441" s="5"/>
-      <c r="F441" s="77"/>
+      <c r="F441" s="63"/>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A442" s="5"/>
@@ -6384,7 +6475,7 @@
       <c r="C442" s="5"/>
       <c r="D442" s="5"/>
       <c r="E442" s="5"/>
-      <c r="F442" s="77"/>
+      <c r="F442" s="63"/>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A443" s="5"/>
@@ -6392,7 +6483,7 @@
       <c r="C443" s="5"/>
       <c r="D443" s="5"/>
       <c r="E443" s="5"/>
-      <c r="F443" s="77"/>
+      <c r="F443" s="63"/>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A444" s="5"/>
@@ -6400,7 +6491,7 @@
       <c r="C444" s="5"/>
       <c r="D444" s="5"/>
       <c r="E444" s="5"/>
-      <c r="F444" s="77"/>
+      <c r="F444" s="63"/>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A445" s="5"/>
@@ -6408,7 +6499,7 @@
       <c r="C445" s="5"/>
       <c r="D445" s="5"/>
       <c r="E445" s="5"/>
-      <c r="F445" s="77"/>
+      <c r="F445" s="63"/>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A446" s="5"/>
@@ -6416,7 +6507,7 @@
       <c r="C446" s="5"/>
       <c r="D446" s="5"/>
       <c r="E446" s="5"/>
-      <c r="F446" s="77"/>
+      <c r="F446" s="63"/>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A447" s="5"/>
@@ -6424,7 +6515,7 @@
       <c r="C447" s="5"/>
       <c r="D447" s="5"/>
       <c r="E447" s="5"/>
-      <c r="F447" s="77"/>
+      <c r="F447" s="63"/>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A448" s="5"/>
@@ -6432,7 +6523,7 @@
       <c r="C448" s="5"/>
       <c r="D448" s="5"/>
       <c r="E448" s="5"/>
-      <c r="F448" s="77"/>
+      <c r="F448" s="63"/>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A449" s="5"/>
@@ -6440,7 +6531,7 @@
       <c r="C449" s="5"/>
       <c r="D449" s="5"/>
       <c r="E449" s="5"/>
-      <c r="F449" s="77"/>
+      <c r="F449" s="63"/>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A450" s="2"/>

--- a/prix/prix.xlsx
+++ b/prix/prix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\robinetterie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E4B27F-5C0F-4408-9365-1FDF983745BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00888863-6ACF-4845-989D-ACCEF6926FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>

--- a/prix/prix.xlsx
+++ b/prix/prix.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\robinetterie\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\robinetterie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00888863-6ACF-4845-989D-ACCEF6926FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10D42F5D-4B24-4341-A64B-1FC74BD10BD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
+    <workbookView xWindow="23124" yWindow="12" windowWidth="19116" windowHeight="10884" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="530">
   <si>
     <t>path</t>
   </si>
@@ -1113,6 +1113,519 @@
   </si>
   <si>
     <t>grohe/26677000.png</t>
+  </si>
+  <si>
+    <t>42170648</t>
+  </si>
+  <si>
+    <t>42170649</t>
+  </si>
+  <si>
+    <t>42170650</t>
+  </si>
+  <si>
+    <t>42170655</t>
+  </si>
+  <si>
+    <t>42170656</t>
+  </si>
+  <si>
+    <t>42170657</t>
+  </si>
+  <si>
+    <t>42170658</t>
+  </si>
+  <si>
+    <t>42170659</t>
+  </si>
+  <si>
+    <t>42170660</t>
+  </si>
+  <si>
+    <t>42170661</t>
+  </si>
+  <si>
+    <t>42170662</t>
+  </si>
+  <si>
+    <t>42170663</t>
+  </si>
+  <si>
+    <t>42170664</t>
+  </si>
+  <si>
+    <t>42170665</t>
+  </si>
+  <si>
+    <t>42170666</t>
+  </si>
+  <si>
+    <t>42170667</t>
+  </si>
+  <si>
+    <t>42170668</t>
+  </si>
+  <si>
+    <t>42170669</t>
+  </si>
+  <si>
+    <t>42170670</t>
+  </si>
+  <si>
+    <t>42170671</t>
+  </si>
+  <si>
+    <t>42170672</t>
+  </si>
+  <si>
+    <t>42170673</t>
+  </si>
+  <si>
+    <t>42170674</t>
+  </si>
+  <si>
+    <t>42170675</t>
+  </si>
+  <si>
+    <t>42170676</t>
+  </si>
+  <si>
+    <t>42170677</t>
+  </si>
+  <si>
+    <t>42170678</t>
+  </si>
+  <si>
+    <t>42170680</t>
+  </si>
+  <si>
+    <t>42170681</t>
+  </si>
+  <si>
+    <t>42170682</t>
+  </si>
+  <si>
+    <t>42170683</t>
+  </si>
+  <si>
+    <t>42170684</t>
+  </si>
+  <si>
+    <t>42170685</t>
+  </si>
+  <si>
+    <t>42170686</t>
+  </si>
+  <si>
+    <t>42170687</t>
+  </si>
+  <si>
+    <t>42170688</t>
+  </si>
+  <si>
+    <t>42170689</t>
+  </si>
+  <si>
+    <t>42170690</t>
+  </si>
+  <si>
+    <t>42170691</t>
+  </si>
+  <si>
+    <t>42170692</t>
+  </si>
+  <si>
+    <t>42170693</t>
+  </si>
+  <si>
+    <t>42170694</t>
+  </si>
+  <si>
+    <t>42170695</t>
+  </si>
+  <si>
+    <t>Mitigeur evier CORNWALL or</t>
+  </si>
+  <si>
+    <t>Mitigeur evier LONDON chromé+douchette</t>
+  </si>
+  <si>
+    <t>Mitigeur evier LONDON inox+douchette</t>
+  </si>
+  <si>
+    <t>Douchette à main KARIBIK chromé.3jets</t>
+  </si>
+  <si>
+    <t>Douchette à main KARIBIK graphite.3jets</t>
+  </si>
+  <si>
+    <t>Douchette à main KARIBIK noire.3jets</t>
+  </si>
+  <si>
+    <t>Douchette à main HAWAII chromé 3jets</t>
+  </si>
+  <si>
+    <t>Douchette à main HAWAII graphite 3 jets</t>
+  </si>
+  <si>
+    <t>Douchette à main HAWAII noire 3 jets</t>
+  </si>
+  <si>
+    <t>Douchette à main SUMATRA chromé 3jets</t>
+  </si>
+  <si>
+    <t>Douchette à main BARI chromé 3jets</t>
+  </si>
+  <si>
+    <t>Douchette à main aqua2save chromé</t>
+  </si>
+  <si>
+    <t>Douchette à main BELLAQUA chromé</t>
+  </si>
+  <si>
+    <t>Set de douche pour lavabo chromé</t>
+  </si>
+  <si>
+    <t>Set de douchette chromé</t>
+  </si>
+  <si>
+    <t>Douche de tête MADURA chromé</t>
+  </si>
+  <si>
+    <t>Flexible douche 80cm chromé</t>
+  </si>
+  <si>
+    <t>Flexible douche 80cm noir</t>
+  </si>
+  <si>
+    <t>Support de douchette pour barre chromé</t>
+  </si>
+  <si>
+    <t>Curseur pour barre de douche</t>
+  </si>
+  <si>
+    <t>Support de douchette chromé</t>
+  </si>
+  <si>
+    <t>Support de douchette noir</t>
+  </si>
+  <si>
+    <t>Pieces articulée chromée</t>
+  </si>
+  <si>
+    <t>Inverseur 3 voies chromé</t>
+  </si>
+  <si>
+    <t>Flexible de douche 125cm chromé</t>
+  </si>
+  <si>
+    <t>Flexible de douche 150cm chromé</t>
+  </si>
+  <si>
+    <t>Flexible de douche 150cm chromé/noir</t>
+  </si>
+  <si>
+    <t>Flexible de douche 200 argent</t>
+  </si>
+  <si>
+    <t>Flexible de douche 150 noir</t>
+  </si>
+  <si>
+    <t>Flexible de douche 175 chromé</t>
+  </si>
+  <si>
+    <t>Flexible de douche 200 chromé</t>
+  </si>
+  <si>
+    <t>Flexible de douche 200 noir chromé</t>
+  </si>
+  <si>
+    <t>Flexible de douche 150 blanc</t>
+  </si>
+  <si>
+    <t>Flexible de douche 150 graphite</t>
+  </si>
+  <si>
+    <t>Barre de douche chromé STELLA</t>
+  </si>
+  <si>
+    <t>Set bare de douche chromé NAPOLI</t>
+  </si>
+  <si>
+    <t>Barre de douche chromée réglable SIGNO</t>
+  </si>
+  <si>
+    <t>Set de douche chromée réglable FRESH</t>
+  </si>
+  <si>
+    <t>Set de douche chromée ADRIA</t>
+  </si>
+  <si>
+    <t>Set de douche chromée FLORENZ</t>
+  </si>
+  <si>
+    <t>Set de douche noir RAVEN</t>
+  </si>
+  <si>
+    <t>Douchette NAPOLI chromée</t>
+  </si>
+  <si>
+    <t>79167</t>
+  </si>
+  <si>
+    <t>79700</t>
+  </si>
+  <si>
+    <t>79705</t>
+  </si>
+  <si>
+    <t>60200</t>
+  </si>
+  <si>
+    <t>60202</t>
+  </si>
+  <si>
+    <t>60203</t>
+  </si>
+  <si>
+    <t>60220</t>
+  </si>
+  <si>
+    <t>60222</t>
+  </si>
+  <si>
+    <t>60226</t>
+  </si>
+  <si>
+    <t>60230</t>
+  </si>
+  <si>
+    <t>60811</t>
+  </si>
+  <si>
+    <t>60791</t>
+  </si>
+  <si>
+    <t>60700</t>
+  </si>
+  <si>
+    <t>78016</t>
+  </si>
+  <si>
+    <t>61861</t>
+  </si>
+  <si>
+    <t>60947</t>
+  </si>
+  <si>
+    <t>63431</t>
+  </si>
+  <si>
+    <t>63867</t>
+  </si>
+  <si>
+    <t>66340</t>
+  </si>
+  <si>
+    <t>66410</t>
+  </si>
+  <si>
+    <t>66121</t>
+  </si>
+  <si>
+    <t>66111</t>
+  </si>
+  <si>
+    <t>66116</t>
+  </si>
+  <si>
+    <t>66421</t>
+  </si>
+  <si>
+    <t>69511</t>
+  </si>
+  <si>
+    <t>63441</t>
+  </si>
+  <si>
+    <t>63451</t>
+  </si>
+  <si>
+    <t>63852</t>
+  </si>
+  <si>
+    <t>63961</t>
+  </si>
+  <si>
+    <t>63877</t>
+  </si>
+  <si>
+    <t>63471</t>
+  </si>
+  <si>
+    <t>63461</t>
+  </si>
+  <si>
+    <t>63861</t>
+  </si>
+  <si>
+    <t>63878</t>
+  </si>
+  <si>
+    <t>63872</t>
+  </si>
+  <si>
+    <t>67111</t>
+  </si>
+  <si>
+    <t>64830</t>
+  </si>
+  <si>
+    <t>67131</t>
+  </si>
+  <si>
+    <t>64160</t>
+  </si>
+  <si>
+    <t>64860</t>
+  </si>
+  <si>
+    <t>64870</t>
+  </si>
+  <si>
+    <t>64926</t>
+  </si>
+  <si>
+    <t>60740</t>
+  </si>
+  <si>
+    <t>schutte/79167.png</t>
+  </si>
+  <si>
+    <t>schutte/79700.png</t>
+  </si>
+  <si>
+    <t>schutte/79705.png</t>
+  </si>
+  <si>
+    <t>schutte/60200.png</t>
+  </si>
+  <si>
+    <t>schutte/60202.png</t>
+  </si>
+  <si>
+    <t>schutte/60203.png</t>
+  </si>
+  <si>
+    <t>schutte/60220.png</t>
+  </si>
+  <si>
+    <t>schutte/60222.png</t>
+  </si>
+  <si>
+    <t>schutte/60226.png</t>
+  </si>
+  <si>
+    <t>schutte/60230.png</t>
+  </si>
+  <si>
+    <t>schutte/60811.png</t>
+  </si>
+  <si>
+    <t>schutte/60791.png</t>
+  </si>
+  <si>
+    <t>schutte/60700.png</t>
+  </si>
+  <si>
+    <t>schutte/78016.png</t>
+  </si>
+  <si>
+    <t>schutte/61861.png</t>
+  </si>
+  <si>
+    <t>schutte/60947.png</t>
+  </si>
+  <si>
+    <t>schutte/63431.png</t>
+  </si>
+  <si>
+    <t>schutte/63867.png</t>
+  </si>
+  <si>
+    <t>schutte/66340.png</t>
+  </si>
+  <si>
+    <t>schutte/66410.png</t>
+  </si>
+  <si>
+    <t>schutte/66121.png</t>
+  </si>
+  <si>
+    <t>schutte/66111.png</t>
+  </si>
+  <si>
+    <t>schutte/66116.png</t>
+  </si>
+  <si>
+    <t>schutte/66421.png</t>
+  </si>
+  <si>
+    <t>schutte/69511.png</t>
+  </si>
+  <si>
+    <t>schutte/63441.png</t>
+  </si>
+  <si>
+    <t>schutte/63451.png</t>
+  </si>
+  <si>
+    <t>schutte/63852.png</t>
+  </si>
+  <si>
+    <t>schutte/63961.png</t>
+  </si>
+  <si>
+    <t>schutte/63877.png</t>
+  </si>
+  <si>
+    <t>schutte/63471.png</t>
+  </si>
+  <si>
+    <t>schutte/63461.png</t>
+  </si>
+  <si>
+    <t>schutte/63861.png</t>
+  </si>
+  <si>
+    <t>schutte/63878.png</t>
+  </si>
+  <si>
+    <t>schutte/63872.png</t>
+  </si>
+  <si>
+    <t>schutte/67111.png</t>
+  </si>
+  <si>
+    <t>schutte/64830.png</t>
+  </si>
+  <si>
+    <t>schutte/67131.png</t>
+  </si>
+  <si>
+    <t>schutte/64160.png</t>
+  </si>
+  <si>
+    <t>schutte/64860.png</t>
+  </si>
+  <si>
+    <t>schutte/64870.png</t>
+  </si>
+  <si>
+    <t>schutte/64926.png</t>
+  </si>
+  <si>
+    <t>schutte/60740.png</t>
   </si>
 </sst>
 </file>
@@ -1209,7 +1722,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1287,119 +1800,11 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1770,7 +2175,7 @@
     <col min="3" max="3" width="20.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.88671875" style="64" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26.77734375" style="26" customWidth="1"/>
     <col min="8" max="8" width="36.109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="39.88671875" bestFit="1" customWidth="1"/>
@@ -1822,7 +2227,7 @@
       <c r="E3" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="62">
+      <c r="F3" s="28">
         <v>1</v>
       </c>
       <c r="G3" s="26" t="s">
@@ -1844,7 +2249,7 @@
       <c r="E4" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="62">
+      <c r="F4" s="28">
         <v>1</v>
       </c>
       <c r="G4" s="26" t="s">
@@ -1866,7 +2271,7 @@
       <c r="E5" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="62">
+      <c r="F5" s="28">
         <v>0</v>
       </c>
       <c r="G5" s="26" t="s">
@@ -1888,7 +2293,7 @@
       <c r="E6" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="62">
+      <c r="F6" s="28">
         <v>2</v>
       </c>
       <c r="G6" s="26" t="s">
@@ -1910,7 +2315,7 @@
       <c r="E7" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="F7" s="62">
+      <c r="F7" s="28">
         <v>3</v>
       </c>
       <c r="G7" s="26" t="s">
@@ -1932,7 +2337,7 @@
       <c r="E8" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="62">
+      <c r="F8" s="28">
         <v>3</v>
       </c>
       <c r="G8" s="26" t="s">
@@ -1954,7 +2359,7 @@
       <c r="E9" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="F9" s="62">
+      <c r="F9" s="28">
         <v>3</v>
       </c>
       <c r="G9" s="26" t="s">
@@ -1976,7 +2381,7 @@
       <c r="E10" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="62">
+      <c r="F10" s="28">
         <v>3</v>
       </c>
       <c r="G10" s="26" t="s">
@@ -1998,7 +2403,7 @@
       <c r="E11" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="62">
+      <c r="F11" s="28">
         <v>3</v>
       </c>
       <c r="G11" s="26" t="s">
@@ -2020,7 +2425,7 @@
       <c r="E12" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="F12" s="62">
+      <c r="F12" s="28">
         <v>0</v>
       </c>
       <c r="G12" s="26" t="s">
@@ -2042,7 +2447,7 @@
       <c r="E13" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="62">
+      <c r="F13" s="28">
         <v>2</v>
       </c>
       <c r="G13" s="26" t="s">
@@ -2064,7 +2469,7 @@
       <c r="E14" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="F14" s="62">
+      <c r="F14" s="28">
         <v>2</v>
       </c>
       <c r="G14" s="26" t="s">
@@ -2086,7 +2491,7 @@
       <c r="E15" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="F15" s="62">
+      <c r="F15" s="28">
         <v>1</v>
       </c>
       <c r="G15" s="26" t="s">
@@ -2108,7 +2513,7 @@
       <c r="E16" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="F16" s="62">
+      <c r="F16" s="28">
         <v>1</v>
       </c>
       <c r="G16" s="26" t="s">
@@ -2130,7 +2535,7 @@
       <c r="E17" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="62">
+      <c r="F17" s="28">
         <v>1</v>
       </c>
       <c r="G17" s="26" t="s">
@@ -2152,7 +2557,7 @@
       <c r="E18" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="62">
+      <c r="F18" s="28">
         <v>1</v>
       </c>
       <c r="G18" s="26" t="s">
@@ -2174,7 +2579,7 @@
       <c r="E19" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="62">
+      <c r="F19" s="28">
         <v>1</v>
       </c>
       <c r="G19" s="26" t="s">
@@ -2196,7 +2601,7 @@
       <c r="E20" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="F20" s="62">
+      <c r="F20" s="28">
         <v>4</v>
       </c>
       <c r="G20" s="26" t="s">
@@ -2218,7 +2623,7 @@
       <c r="E21" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="F21" s="62">
+      <c r="F21" s="28">
         <v>0</v>
       </c>
       <c r="G21" s="26" t="s">
@@ -2228,7 +2633,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
-      <c r="B22" s="66" t="s">
+      <c r="B22" s="30" t="s">
         <v>33</v>
       </c>
       <c r="C22" s="21"/>
@@ -2238,7 +2643,7 @@
       <c r="E22" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="F22" s="62">
+      <c r="F22" s="28">
         <v>2</v>
       </c>
       <c r="G22" s="26" t="s">
@@ -2260,7 +2665,7 @@
       <c r="E23" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="F23" s="62">
+      <c r="F23" s="28">
         <v>1</v>
       </c>
       <c r="G23" s="26" t="s">
@@ -2283,7 +2688,7 @@
       <c r="E24" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="F24" s="62">
+      <c r="F24" s="28">
         <v>4</v>
       </c>
       <c r="G24" s="26" t="s">
@@ -2306,7 +2711,7 @@
       <c r="E25" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="F25" s="62">
+      <c r="F25" s="28">
         <v>1</v>
       </c>
       <c r="G25" s="26" t="s">
@@ -2322,7 +2727,7 @@
       <c r="B26" s="10"/>
       <c r="D26" s="12"/>
       <c r="E26" s="10"/>
-      <c r="F26" s="62"/>
+      <c r="F26" s="28"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
@@ -2337,7 +2742,7 @@
       <c r="E27" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="F27" s="62">
+      <c r="F27" s="28">
         <v>1</v>
       </c>
       <c r="G27" s="26" t="s">
@@ -2357,7 +2762,7 @@
       <c r="E28" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="F28" s="62">
+      <c r="F28" s="28">
         <v>1</v>
       </c>
       <c r="G28" s="26" t="s">
@@ -2377,7 +2782,7 @@
       <c r="E29" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F29" s="62">
+      <c r="F29" s="28">
         <v>2</v>
       </c>
       <c r="G29" s="26" t="s">
@@ -2397,7 +2802,7 @@
       <c r="E30" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="F30" s="62">
+      <c r="F30" s="28">
         <v>1</v>
       </c>
       <c r="G30" s="26" t="s">
@@ -2417,7 +2822,7 @@
       <c r="E31" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F31" s="62">
+      <c r="F31" s="28">
         <v>7</v>
       </c>
       <c r="G31" s="26" t="s">
@@ -2437,7 +2842,7 @@
       <c r="E32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F32" s="62">
+      <c r="F32" s="28">
         <v>2</v>
       </c>
       <c r="G32" s="26" t="s">
@@ -2457,7 +2862,7 @@
       <c r="E33" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F33" s="62">
+      <c r="F33" s="28">
         <v>3</v>
       </c>
       <c r="G33" s="26" t="s">
@@ -2468,17 +2873,17 @@
       <c r="B34" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C34" s="67"/>
+      <c r="C34" s="31"/>
       <c r="D34" s="12">
         <v>134.22999999999999</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F34" s="68">
+      <c r="F34" s="32">
         <v>2</v>
       </c>
-      <c r="G34" s="69" t="s">
+      <c r="G34" s="33" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2495,7 +2900,7 @@
       <c r="E35" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F35" s="62">
+      <c r="F35" s="28">
         <v>2</v>
       </c>
       <c r="G35" s="26" t="s">
@@ -2515,7 +2920,7 @@
       <c r="E36" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="F36" s="62">
+      <c r="F36" s="28">
         <v>3</v>
       </c>
       <c r="G36" s="26" t="s">
@@ -2535,7 +2940,7 @@
       <c r="E37" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F37" s="62">
+      <c r="F37" s="28">
         <v>3</v>
       </c>
       <c r="G37" s="26" t="s">
@@ -2555,7 +2960,7 @@
       <c r="E38" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="F38" s="62">
+      <c r="F38" s="28">
         <v>10</v>
       </c>
       <c r="G38" s="26" t="s">
@@ -2575,7 +2980,7 @@
       <c r="E39" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F39" s="62">
+      <c r="F39" s="28">
         <v>1</v>
       </c>
       <c r="G39" s="26" t="s">
@@ -2586,17 +2991,17 @@
       <c r="B40" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="C40" s="67"/>
+      <c r="C40" s="31"/>
       <c r="D40" s="12">
         <v>182.9</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="F40" s="68">
+      <c r="F40" s="32">
         <v>0</v>
       </c>
-      <c r="G40" s="69" t="s">
+      <c r="G40" s="33" t="s">
         <v>338</v>
       </c>
     </row>
@@ -2604,19 +3009,19 @@
       <c r="A41" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="B41" s="28" t="s">
+      <c r="B41" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="D41" s="29">
+      <c r="D41" s="11">
         <v>188.49</v>
       </c>
-      <c r="E41" s="27" t="s">
+      <c r="E41" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="F41" s="62">
+      <c r="F41" s="28">
         <v>4</v>
       </c>
-      <c r="G41" s="30" t="s">
+      <c r="G41" s="9" t="s">
         <v>116</v>
       </c>
     </row>
@@ -2624,19 +3029,19 @@
       <c r="A42" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="B42" s="32" t="s">
+      <c r="B42" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="D42" s="33">
+      <c r="D42" s="11">
         <v>298.25</v>
       </c>
-      <c r="E42" s="31" t="s">
+      <c r="E42" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="F42" s="62">
+      <c r="F42" s="28">
         <v>2</v>
       </c>
-      <c r="G42" s="34" t="s">
+      <c r="G42" s="9" t="s">
         <v>119</v>
       </c>
     </row>
@@ -2644,19 +3049,19 @@
       <c r="A43" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="B43" s="36" t="s">
+      <c r="B43" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="D43" s="37">
+      <c r="D43" s="11">
         <v>302.5</v>
       </c>
-      <c r="E43" s="35" t="s">
+      <c r="E43" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="F43" s="62">
+      <c r="F43" s="28">
         <v>2</v>
       </c>
-      <c r="G43" s="38" t="s">
+      <c r="G43" s="9" t="s">
         <v>122</v>
       </c>
     </row>
@@ -2664,19 +3069,19 @@
       <c r="A44" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="B44" s="40" t="s">
+      <c r="B44" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="D44" s="41">
+      <c r="D44" s="11">
         <v>22.740000000000002</v>
       </c>
-      <c r="E44" s="39" t="s">
+      <c r="E44" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="F44" s="62">
+      <c r="F44" s="28">
         <v>4</v>
       </c>
-      <c r="G44" s="42" t="s">
+      <c r="G44" s="9" t="s">
         <v>125</v>
       </c>
     </row>
@@ -2684,19 +3089,19 @@
       <c r="A45" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="B45" s="44" t="s">
+      <c r="B45" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="D45" s="45">
+      <c r="D45" s="11">
         <v>19.5</v>
       </c>
-      <c r="E45" s="43" t="s">
+      <c r="E45" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="F45" s="62">
+      <c r="F45" s="28">
         <v>3</v>
       </c>
-      <c r="G45" s="46" t="s">
+      <c r="G45" s="9" t="s">
         <v>128</v>
       </c>
     </row>
@@ -2704,19 +3109,19 @@
       <c r="A46" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="B46" s="48" t="s">
+      <c r="B46" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="D46" s="49">
+      <c r="D46" s="11">
         <v>16.7</v>
       </c>
-      <c r="E46" s="47" t="s">
+      <c r="E46" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="F46" s="62">
+      <c r="F46" s="28">
         <v>6</v>
       </c>
-      <c r="G46" s="50" t="s">
+      <c r="G46" s="9" t="s">
         <v>131</v>
       </c>
     </row>
@@ -2724,19 +3129,19 @@
       <c r="A47" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="B47" s="52" t="s">
+      <c r="B47" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="D47" s="53">
+      <c r="D47" s="11">
         <v>490</v>
       </c>
-      <c r="E47" s="51" t="s">
+      <c r="E47" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="F47" s="62">
+      <c r="F47" s="28">
         <v>3</v>
       </c>
-      <c r="G47" s="54" t="s">
+      <c r="G47" s="9" t="s">
         <v>134</v>
       </c>
     </row>
@@ -2744,56 +3149,56 @@
       <c r="A48" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="B48" s="56" t="s">
+      <c r="B48" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="D48" s="57">
+      <c r="D48" s="11">
         <v>490</v>
       </c>
-      <c r="E48" s="55" t="s">
+      <c r="E48" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="F48" s="62">
+      <c r="F48" s="28">
         <v>5</v>
       </c>
-      <c r="G48" s="58" t="s">
+      <c r="G48" s="9" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B49" s="70" t="s">
+      <c r="B49" s="34" t="s">
         <v>139</v>
       </c>
-      <c r="C49" s="71"/>
-      <c r="D49" s="72">
+      <c r="C49" s="35"/>
+      <c r="D49" s="36">
         <v>550</v>
       </c>
-      <c r="E49" s="70" t="s">
+      <c r="E49" s="34" t="s">
         <v>138</v>
       </c>
-      <c r="F49" s="73">
+      <c r="F49" s="37">
         <v>3</v>
       </c>
-      <c r="G49" s="70" t="s">
+      <c r="G49" s="34" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="5"/>
-      <c r="B50" s="70" t="s">
+      <c r="B50" s="34" t="s">
         <v>142</v>
       </c>
-      <c r="C50" s="71"/>
-      <c r="D50" s="72">
+      <c r="C50" s="35"/>
+      <c r="D50" s="36">
         <v>550</v>
       </c>
-      <c r="E50" s="70" t="s">
+      <c r="E50" s="34" t="s">
         <v>141</v>
       </c>
-      <c r="F50" s="73">
-        <v>1</v>
-      </c>
-      <c r="G50" s="70" t="s">
+      <c r="F50" s="37">
+        <v>1</v>
+      </c>
+      <c r="G50" s="34" t="s">
         <v>143</v>
       </c>
     </row>
@@ -2802,14 +3207,14 @@
       <c r="B51" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="C51" s="67"/>
+      <c r="C51" s="31"/>
       <c r="D51" s="12">
         <v>302.5</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="F51" s="68">
+      <c r="F51" s="32">
         <v>2</v>
       </c>
       <c r="G51" s="10" t="s">
@@ -2817,31 +3222,31 @@
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="61" t="s">
+      <c r="A52" s="27" t="s">
         <v>144</v>
       </c>
       <c r="B52" s="9"/>
       <c r="D52" s="11"/>
       <c r="E52" s="9"/>
-      <c r="F52" s="62"/>
+      <c r="F52" s="28"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="B53" s="65" t="s">
+      <c r="B53" s="29" t="s">
         <v>188</v>
       </c>
-      <c r="D53" s="60">
+      <c r="D53" s="11">
         <v>363</v>
       </c>
-      <c r="E53" s="59" t="s">
+      <c r="E53" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="F53" s="62">
-        <v>1</v>
-      </c>
-      <c r="G53" s="59" t="s">
+      <c r="F53" s="28">
+        <v>1</v>
+      </c>
+      <c r="G53" s="9" t="s">
         <v>229</v>
       </c>
     </row>
@@ -2849,19 +3254,19 @@
       <c r="A54" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="B54" s="65" t="s">
+      <c r="B54" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="D54" s="60">
+      <c r="D54" s="11">
         <v>217.8</v>
       </c>
-      <c r="E54" s="59" t="s">
+      <c r="E54" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="F54" s="62">
-        <v>1</v>
-      </c>
-      <c r="G54" s="59" t="s">
+      <c r="F54" s="28">
+        <v>1</v>
+      </c>
+      <c r="G54" s="9" t="s">
         <v>230</v>
       </c>
     </row>
@@ -2869,19 +3274,19 @@
       <c r="A55" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="B55" s="65" t="s">
+      <c r="B55" s="29" t="s">
         <v>190</v>
       </c>
-      <c r="D55" s="60">
+      <c r="D55" s="11">
         <v>411.40000000000003</v>
       </c>
-      <c r="E55" s="59" t="s">
+      <c r="E55" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="F55" s="62">
-        <v>1</v>
-      </c>
-      <c r="G55" s="59" t="s">
+      <c r="F55" s="28">
+        <v>1</v>
+      </c>
+      <c r="G55" s="9" t="s">
         <v>231</v>
       </c>
     </row>
@@ -2889,19 +3294,19 @@
       <c r="A56" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="B56" s="65" t="s">
+      <c r="B56" s="29" t="s">
         <v>191</v>
       </c>
-      <c r="D56" s="60">
+      <c r="D56" s="11">
         <v>96.8</v>
       </c>
-      <c r="E56" s="59" t="s">
+      <c r="E56" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="F56" s="62">
-        <v>1</v>
-      </c>
-      <c r="G56" s="59" t="s">
+      <c r="F56" s="28">
+        <v>1</v>
+      </c>
+      <c r="G56" s="9" t="s">
         <v>232</v>
       </c>
     </row>
@@ -2909,19 +3314,19 @@
       <c r="A57" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="B57" s="65" t="s">
+      <c r="B57" s="29" t="s">
         <v>192</v>
       </c>
-      <c r="D57" s="60">
+      <c r="D57" s="11">
         <v>96.8</v>
       </c>
-      <c r="E57" s="59" t="s">
+      <c r="E57" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="F57" s="62">
-        <v>1</v>
-      </c>
-      <c r="G57" s="59" t="s">
+      <c r="F57" s="28">
+        <v>1</v>
+      </c>
+      <c r="G57" s="9" t="s">
         <v>233</v>
       </c>
     </row>
@@ -2929,19 +3334,19 @@
       <c r="A58" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="B58" s="65" t="s">
+      <c r="B58" s="29" t="s">
         <v>193</v>
       </c>
-      <c r="D58" s="60">
+      <c r="D58" s="11">
         <v>84.7</v>
       </c>
-      <c r="E58" s="59" t="s">
+      <c r="E58" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="F58" s="62">
-        <v>1</v>
-      </c>
-      <c r="G58" s="59" t="s">
+      <c r="F58" s="28">
+        <v>1</v>
+      </c>
+      <c r="G58" s="9" t="s">
         <v>234</v>
       </c>
     </row>
@@ -2949,19 +3354,19 @@
       <c r="A59" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="B59" s="65" t="s">
+      <c r="B59" s="29" t="s">
         <v>194</v>
       </c>
-      <c r="D59" s="60">
+      <c r="D59" s="11">
         <v>53.24</v>
       </c>
-      <c r="E59" s="59" t="s">
+      <c r="E59" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="F59" s="62">
-        <v>1</v>
-      </c>
-      <c r="G59" s="59" t="s">
+      <c r="F59" s="28">
+        <v>1</v>
+      </c>
+      <c r="G59" s="9" t="s">
         <v>235</v>
       </c>
     </row>
@@ -2969,20 +3374,20 @@
       <c r="A60" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="B60" s="65" t="s">
+      <c r="B60" s="29" t="s">
         <v>195</v>
       </c>
       <c r="C60" s="5"/>
-      <c r="D60" s="60">
+      <c r="D60" s="11">
         <v>66.55</v>
       </c>
-      <c r="E60" s="59" t="s">
+      <c r="E60" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="F60" s="62">
-        <v>1</v>
-      </c>
-      <c r="G60" s="59" t="s">
+      <c r="F60" s="28">
+        <v>1</v>
+      </c>
+      <c r="G60" s="9" t="s">
         <v>236</v>
       </c>
     </row>
@@ -2990,20 +3395,20 @@
       <c r="A61" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="B61" s="65" t="s">
+      <c r="B61" s="29" t="s">
         <v>196</v>
       </c>
       <c r="C61" s="5"/>
-      <c r="D61" s="60">
+      <c r="D61" s="11">
         <v>84.7</v>
       </c>
-      <c r="E61" s="59" t="s">
+      <c r="E61" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="F61" s="62">
-        <v>1</v>
-      </c>
-      <c r="G61" s="59" t="s">
+      <c r="F61" s="28">
+        <v>1</v>
+      </c>
+      <c r="G61" s="9" t="s">
         <v>237</v>
       </c>
     </row>
@@ -3011,20 +3416,20 @@
       <c r="A62" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="B62" s="65" t="s">
+      <c r="B62" s="29" t="s">
         <v>197</v>
       </c>
       <c r="C62" s="5"/>
-      <c r="D62" s="60">
+      <c r="D62" s="11">
         <v>96.8</v>
       </c>
-      <c r="E62" s="59" t="s">
+      <c r="E62" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="F62" s="62">
-        <v>1</v>
-      </c>
-      <c r="G62" s="59" t="s">
+      <c r="F62" s="28">
+        <v>1</v>
+      </c>
+      <c r="G62" s="9" t="s">
         <v>238</v>
       </c>
     </row>
@@ -3032,19 +3437,19 @@
       <c r="A63" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="B63" s="65" t="s">
+      <c r="B63" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="D63" s="60">
+      <c r="D63" s="11">
         <v>78.650000000000006</v>
       </c>
-      <c r="E63" s="59" t="s">
+      <c r="E63" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="F63" s="62">
-        <v>1</v>
-      </c>
-      <c r="G63" s="59" t="s">
+      <c r="F63" s="28">
+        <v>1</v>
+      </c>
+      <c r="G63" s="9" t="s">
         <v>239</v>
       </c>
     </row>
@@ -3052,19 +3457,19 @@
       <c r="A64" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="B64" s="65" t="s">
+      <c r="B64" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="D64" s="60">
+      <c r="D64" s="11">
         <v>133.1</v>
       </c>
-      <c r="E64" s="59" t="s">
+      <c r="E64" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="F64" s="62">
-        <v>1</v>
-      </c>
-      <c r="G64" s="59" t="s">
+      <c r="F64" s="28">
+        <v>1</v>
+      </c>
+      <c r="G64" s="9" t="s">
         <v>240</v>
       </c>
     </row>
@@ -3072,19 +3477,19 @@
       <c r="A65" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="B65" s="65" t="s">
+      <c r="B65" s="29" t="s">
         <v>200</v>
       </c>
-      <c r="D65" s="60">
+      <c r="D65" s="11">
         <v>145.20000000000002</v>
       </c>
-      <c r="E65" s="59" t="s">
+      <c r="E65" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="F65" s="62">
-        <v>1</v>
-      </c>
-      <c r="G65" s="59" t="s">
+      <c r="F65" s="28">
+        <v>1</v>
+      </c>
+      <c r="G65" s="9" t="s">
         <v>241</v>
       </c>
     </row>
@@ -3092,19 +3497,19 @@
       <c r="A66" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="B66" s="65" t="s">
+      <c r="B66" s="29" t="s">
         <v>201</v>
       </c>
-      <c r="D66" s="60">
+      <c r="D66" s="11">
         <v>102.85000000000001</v>
       </c>
-      <c r="E66" s="59" t="s">
+      <c r="E66" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="F66" s="62">
-        <v>1</v>
-      </c>
-      <c r="G66" s="59" t="s">
+      <c r="F66" s="28">
+        <v>1</v>
+      </c>
+      <c r="G66" s="9" t="s">
         <v>242</v>
       </c>
     </row>
@@ -3112,19 +3517,19 @@
       <c r="A67" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="B67" s="65" t="s">
+      <c r="B67" s="29" t="s">
         <v>202</v>
       </c>
-      <c r="D67" s="60">
+      <c r="D67" s="11">
         <v>169.4</v>
       </c>
-      <c r="E67" s="59" t="s">
+      <c r="E67" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="F67" s="62">
-        <v>1</v>
-      </c>
-      <c r="G67" s="59" t="s">
+      <c r="F67" s="28">
+        <v>1</v>
+      </c>
+      <c r="G67" s="9" t="s">
         <v>243</v>
       </c>
     </row>
@@ -3132,19 +3537,19 @@
       <c r="A68" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="B68" s="65" t="s">
+      <c r="B68" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="D68" s="60">
+      <c r="D68" s="11">
         <v>181.5</v>
       </c>
-      <c r="E68" s="59" t="s">
+      <c r="E68" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="F68" s="62">
-        <v>1</v>
-      </c>
-      <c r="G68" s="59" t="s">
+      <c r="F68" s="28">
+        <v>1</v>
+      </c>
+      <c r="G68" s="9" t="s">
         <v>244</v>
       </c>
     </row>
@@ -3152,19 +3557,19 @@
       <c r="A69" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="B69" s="65" t="s">
+      <c r="B69" s="29" t="s">
         <v>204</v>
       </c>
-      <c r="D69" s="60">
+      <c r="D69" s="11">
         <v>121</v>
       </c>
-      <c r="E69" s="59" t="s">
+      <c r="E69" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="F69" s="62">
-        <v>1</v>
-      </c>
-      <c r="G69" s="59" t="s">
+      <c r="F69" s="28">
+        <v>1</v>
+      </c>
+      <c r="G69" s="9" t="s">
         <v>245</v>
       </c>
     </row>
@@ -3172,19 +3577,19 @@
       <c r="A70" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="B70" s="65" t="s">
+      <c r="B70" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="D70" s="60">
+      <c r="D70" s="11">
         <v>133.1</v>
       </c>
-      <c r="E70" s="59" t="s">
+      <c r="E70" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="F70" s="62">
-        <v>1</v>
-      </c>
-      <c r="G70" s="59" t="s">
+      <c r="F70" s="28">
+        <v>1</v>
+      </c>
+      <c r="G70" s="9" t="s">
         <v>246</v>
       </c>
     </row>
@@ -3192,19 +3597,19 @@
       <c r="A71" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="B71" s="65" t="s">
+      <c r="B71" s="29" t="s">
         <v>204</v>
       </c>
-      <c r="D71" s="60">
+      <c r="D71" s="11">
         <v>121</v>
       </c>
-      <c r="E71" s="59" t="s">
+      <c r="E71" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="F71" s="62">
-        <v>1</v>
-      </c>
-      <c r="G71" s="59" t="s">
+      <c r="F71" s="28">
+        <v>1</v>
+      </c>
+      <c r="G71" s="9" t="s">
         <v>247</v>
       </c>
     </row>
@@ -3212,19 +3617,19 @@
       <c r="A72" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="B72" s="65" t="s">
+      <c r="B72" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="D72" s="60">
+      <c r="D72" s="11">
         <v>133.1</v>
       </c>
-      <c r="E72" s="59" t="s">
+      <c r="E72" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="F72" s="62">
-        <v>1</v>
-      </c>
-      <c r="G72" s="59" t="s">
+      <c r="F72" s="28">
+        <v>1</v>
+      </c>
+      <c r="G72" s="9" t="s">
         <v>248</v>
       </c>
     </row>
@@ -3232,19 +3637,19 @@
       <c r="A73" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="B73" s="65" t="s">
+      <c r="B73" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="D73" s="60">
+      <c r="D73" s="11">
         <v>145.20000000000002</v>
       </c>
-      <c r="E73" s="59" t="s">
+      <c r="E73" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="F73" s="62">
-        <v>1</v>
-      </c>
-      <c r="G73" s="59" t="s">
+      <c r="F73" s="28">
+        <v>1</v>
+      </c>
+      <c r="G73" s="9" t="s">
         <v>249</v>
       </c>
     </row>
@@ -3252,19 +3657,19 @@
       <c r="A74" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="B74" s="65" t="s">
+      <c r="B74" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D74" s="60">
+      <c r="D74" s="11">
         <v>157.30000000000001</v>
       </c>
-      <c r="E74" s="59" t="s">
+      <c r="E74" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="F74" s="62">
-        <v>1</v>
-      </c>
-      <c r="G74" s="59" t="s">
+      <c r="F74" s="28">
+        <v>1</v>
+      </c>
+      <c r="G74" s="9" t="s">
         <v>250</v>
       </c>
     </row>
@@ -3272,19 +3677,19 @@
       <c r="A75" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="B75" s="65" t="s">
+      <c r="B75" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="D75" s="60">
+      <c r="D75" s="11">
         <v>53.24</v>
       </c>
-      <c r="E75" s="59" t="s">
+      <c r="E75" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="F75" s="62">
-        <v>1</v>
-      </c>
-      <c r="G75" s="59" t="s">
+      <c r="F75" s="28">
+        <v>1</v>
+      </c>
+      <c r="G75" s="9" t="s">
         <v>251</v>
       </c>
     </row>
@@ -3292,19 +3697,19 @@
       <c r="A76" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="B76" s="65" t="s">
+      <c r="B76" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="D76" s="60">
+      <c r="D76" s="11">
         <v>84.7</v>
       </c>
-      <c r="E76" s="59" t="s">
+      <c r="E76" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="F76" s="62">
-        <v>1</v>
-      </c>
-      <c r="G76" s="59" t="s">
+      <c r="F76" s="28">
+        <v>1</v>
+      </c>
+      <c r="G76" s="9" t="s">
         <v>252</v>
       </c>
     </row>
@@ -3312,19 +3717,19 @@
       <c r="A77" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="B77" s="65" t="s">
+      <c r="B77" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="D77" s="60">
+      <c r="D77" s="11">
         <v>72.600000000000009</v>
       </c>
-      <c r="E77" s="59" t="s">
+      <c r="E77" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="F77" s="62">
-        <v>1</v>
-      </c>
-      <c r="G77" s="59" t="s">
+      <c r="F77" s="28">
+        <v>1</v>
+      </c>
+      <c r="G77" s="9" t="s">
         <v>253</v>
       </c>
     </row>
@@ -3332,19 +3737,19 @@
       <c r="A78" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="B78" s="65" t="s">
+      <c r="B78" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="D78" s="60">
+      <c r="D78" s="11">
         <v>53.24</v>
       </c>
-      <c r="E78" s="59" t="s">
+      <c r="E78" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="F78" s="62">
-        <v>1</v>
-      </c>
-      <c r="G78" s="59" t="s">
+      <c r="F78" s="28">
+        <v>1</v>
+      </c>
+      <c r="G78" s="9" t="s">
         <v>254</v>
       </c>
     </row>
@@ -3352,19 +3757,19 @@
       <c r="A79" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="B79" s="65" t="s">
+      <c r="B79" s="29" t="s">
         <v>212</v>
       </c>
-      <c r="D79" s="60">
+      <c r="D79" s="11">
         <v>60.5</v>
       </c>
-      <c r="E79" s="59" t="s">
+      <c r="E79" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="F79" s="62">
-        <v>1</v>
-      </c>
-      <c r="G79" s="59" t="s">
+      <c r="F79" s="28">
+        <v>1</v>
+      </c>
+      <c r="G79" s="9" t="s">
         <v>255</v>
       </c>
     </row>
@@ -3372,726 +3777,1414 @@
       <c r="A80" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="B80" s="65" t="s">
+      <c r="B80" s="29" t="s">
         <v>213</v>
       </c>
-      <c r="D80" s="60">
+      <c r="D80" s="11">
         <v>66.55</v>
       </c>
-      <c r="E80" s="59" t="s">
+      <c r="E80" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="F80" s="62">
-        <v>1</v>
-      </c>
-      <c r="G80" s="59" t="s">
+      <c r="F80" s="28">
+        <v>1</v>
+      </c>
+      <c r="G80" s="9" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="B81" s="65" t="s">
+      <c r="B81" s="29" t="s">
         <v>214</v>
       </c>
-      <c r="D81" s="60">
+      <c r="D81" s="11">
         <v>90.75</v>
       </c>
-      <c r="E81" s="59" t="s">
+      <c r="E81" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="F81" s="62">
-        <v>1</v>
-      </c>
-      <c r="G81" s="59" t="s">
+      <c r="F81" s="28">
+        <v>1</v>
+      </c>
+      <c r="G81" s="9" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="B82" s="65" t="s">
+      <c r="B82" s="29" t="s">
         <v>215</v>
       </c>
-      <c r="D82" s="60">
+      <c r="D82" s="11">
         <v>102.85000000000001</v>
       </c>
-      <c r="E82" s="59" t="s">
+      <c r="E82" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="F82" s="62">
-        <v>1</v>
-      </c>
-      <c r="G82" s="59" t="s">
+      <c r="F82" s="28">
+        <v>1</v>
+      </c>
+      <c r="G82" s="9" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="B83" s="65" t="s">
+      <c r="B83" s="29" t="s">
         <v>216</v>
       </c>
       <c r="C83" s="5"/>
-      <c r="D83" s="60">
+      <c r="D83" s="11">
         <v>133.1</v>
       </c>
-      <c r="E83" s="59" t="s">
+      <c r="E83" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="F83" s="62">
-        <v>1</v>
-      </c>
-      <c r="G83" s="59" t="s">
+      <c r="F83" s="28">
+        <v>1</v>
+      </c>
+      <c r="G83" s="9" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="B84" s="65" t="s">
+      <c r="B84" s="29" t="s">
         <v>217</v>
       </c>
       <c r="C84" s="5"/>
-      <c r="D84" s="60">
+      <c r="D84" s="11">
         <v>133.1</v>
       </c>
-      <c r="E84" s="59" t="s">
+      <c r="E84" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="F84" s="62">
-        <v>1</v>
-      </c>
-      <c r="G84" s="59" t="s">
+      <c r="F84" s="28">
+        <v>1</v>
+      </c>
+      <c r="G84" s="9" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="B85" s="65" t="s">
+      <c r="B85" s="29" t="s">
         <v>218</v>
       </c>
       <c r="C85" s="5"/>
-      <c r="D85" s="60">
+      <c r="D85" s="11">
         <v>193.6</v>
       </c>
-      <c r="E85" s="59" t="s">
+      <c r="E85" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="F85" s="62">
-        <v>1</v>
-      </c>
-      <c r="G85" s="59" t="s">
+      <c r="F85" s="28">
+        <v>1</v>
+      </c>
+      <c r="G85" s="9" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="B86" s="65" t="s">
+      <c r="B86" s="29" t="s">
         <v>219</v>
       </c>
       <c r="C86" s="5"/>
-      <c r="D86" s="60">
+      <c r="D86" s="11">
         <v>157.30000000000001</v>
       </c>
-      <c r="E86" s="59" t="s">
+      <c r="E86" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="F86" s="62">
-        <v>1</v>
-      </c>
-      <c r="G86" s="59" t="s">
+      <c r="F86" s="28">
+        <v>1</v>
+      </c>
+      <c r="G86" s="9" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="B87" s="65" t="s">
+      <c r="B87" s="29" t="s">
         <v>220</v>
       </c>
       <c r="C87" s="5"/>
-      <c r="D87" s="60">
+      <c r="D87" s="11">
         <v>114.95</v>
       </c>
-      <c r="E87" s="59" t="s">
+      <c r="E87" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="F87" s="62">
-        <v>1</v>
-      </c>
-      <c r="G87" s="59" t="s">
+      <c r="F87" s="28">
+        <v>1</v>
+      </c>
+      <c r="G87" s="9" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="B88" s="65" t="s">
+      <c r="B88" s="29" t="s">
         <v>221</v>
       </c>
       <c r="C88" s="5"/>
-      <c r="D88" s="60">
+      <c r="D88" s="11">
         <v>90.75</v>
       </c>
-      <c r="E88" s="59" t="s">
+      <c r="E88" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="F88" s="62">
-        <v>1</v>
-      </c>
-      <c r="G88" s="59" t="s">
+      <c r="F88" s="28">
+        <v>1</v>
+      </c>
+      <c r="G88" s="9" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="B89" s="65" t="s">
+      <c r="B89" s="29" t="s">
         <v>222</v>
       </c>
       <c r="C89" s="5"/>
-      <c r="D89" s="60">
+      <c r="D89" s="11">
         <v>96.8</v>
       </c>
-      <c r="E89" s="59" t="s">
+      <c r="E89" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F89" s="62">
-        <v>1</v>
-      </c>
-      <c r="G89" s="59" t="s">
+      <c r="F89" s="28">
+        <v>1</v>
+      </c>
+      <c r="G89" s="9" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="B90" s="65" t="s">
+      <c r="B90" s="29" t="s">
         <v>223</v>
       </c>
       <c r="C90" s="5"/>
-      <c r="D90" s="60">
+      <c r="D90" s="11">
         <v>133.1</v>
       </c>
-      <c r="E90" s="59" t="s">
+      <c r="E90" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="F90" s="62">
-        <v>1</v>
-      </c>
-      <c r="G90" s="59" t="s">
+      <c r="F90" s="28">
+        <v>1</v>
+      </c>
+      <c r="G90" s="9" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="B91" s="65" t="s">
+      <c r="B91" s="29" t="s">
         <v>224</v>
       </c>
       <c r="C91" s="5"/>
-      <c r="D91" s="60">
+      <c r="D91" s="11">
         <v>84.7</v>
       </c>
-      <c r="E91" s="59" t="s">
+      <c r="E91" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="F91" s="62">
-        <v>1</v>
-      </c>
-      <c r="G91" s="59" t="s">
+      <c r="F91" s="28">
+        <v>1</v>
+      </c>
+      <c r="G91" s="9" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="B92" s="65" t="s">
+      <c r="B92" s="29" t="s">
         <v>225</v>
       </c>
       <c r="C92" s="5"/>
-      <c r="D92" s="60">
+      <c r="D92" s="11">
         <v>84.7</v>
       </c>
-      <c r="E92" s="59" t="s">
+      <c r="E92" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="F92" s="62">
-        <v>1</v>
-      </c>
-      <c r="G92" s="59" t="s">
+      <c r="F92" s="28">
+        <v>1</v>
+      </c>
+      <c r="G92" s="9" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="B93" s="65" t="s">
+      <c r="B93" s="29" t="s">
         <v>226</v>
       </c>
       <c r="C93" s="5"/>
-      <c r="D93" s="60">
+      <c r="D93" s="11">
         <v>102.85000000000001</v>
       </c>
-      <c r="E93" s="59" t="s">
+      <c r="E93" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="F93" s="62">
-        <v>1</v>
-      </c>
-      <c r="G93" s="59" t="s">
+      <c r="F93" s="28">
+        <v>1</v>
+      </c>
+      <c r="G93" s="9" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="B94" s="65" t="s">
+      <c r="B94" s="29" t="s">
         <v>227</v>
       </c>
       <c r="C94" s="5"/>
-      <c r="D94" s="60">
+      <c r="D94" s="11">
         <v>102.85000000000001</v>
       </c>
-      <c r="E94" s="59" t="s">
+      <c r="E94" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="F94" s="62">
-        <v>1</v>
-      </c>
-      <c r="G94" s="59" t="s">
+      <c r="F94" s="28">
+        <v>1</v>
+      </c>
+      <c r="G94" s="9" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="B95" s="65" t="s">
+      <c r="B95" s="29" t="s">
         <v>228</v>
       </c>
       <c r="C95" s="5"/>
-      <c r="D95" s="60">
+      <c r="D95" s="11">
         <v>102.85000000000001</v>
       </c>
-      <c r="E95" s="59" t="s">
+      <c r="E95" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="F95" s="62">
-        <v>1</v>
-      </c>
-      <c r="G95" s="59" t="s">
+      <c r="F95" s="28">
+        <v>1</v>
+      </c>
+      <c r="G95" s="9" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A96" s="5"/>
-      <c r="B96" s="10"/>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A96" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="B96" s="9" t="s">
+        <v>402</v>
+      </c>
       <c r="C96" s="5"/>
-      <c r="D96" s="12"/>
-      <c r="E96" s="10"/>
-      <c r="F96" s="62"/>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="5"/>
-      <c r="B97" s="10"/>
+      <c r="D96" s="11">
+        <v>102.85000000000001</v>
+      </c>
+      <c r="E96" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="F96" s="28">
+        <v>1</v>
+      </c>
+      <c r="G96" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="H96" s="9" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A97" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="B97" s="9" t="s">
+        <v>403</v>
+      </c>
       <c r="C97" s="5"/>
-      <c r="D97" s="12"/>
-      <c r="E97" s="10"/>
-      <c r="F97" s="62"/>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="5"/>
-      <c r="B98" s="10"/>
+      <c r="D97" s="11">
+        <v>108.9</v>
+      </c>
+      <c r="E97" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="F97" s="28">
+        <v>1</v>
+      </c>
+      <c r="G97" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="H97" s="9" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A98" s="5" t="s">
+        <v>489</v>
+      </c>
+      <c r="B98" s="9" t="s">
+        <v>404</v>
+      </c>
       <c r="C98" s="5"/>
-      <c r="D98" s="12"/>
-      <c r="E98" s="10"/>
-      <c r="F98" s="62"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="5"/>
-      <c r="B99" s="9"/>
+      <c r="D98" s="11">
+        <v>121</v>
+      </c>
+      <c r="E98" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="F98" s="28">
+        <v>1</v>
+      </c>
+      <c r="G98" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="H98" s="9" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A99" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="B99" s="9" t="s">
+        <v>405</v>
+      </c>
       <c r="C99" s="5"/>
-      <c r="D99" s="11"/>
-      <c r="E99" s="9"/>
-      <c r="F99" s="62"/>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="5"/>
-      <c r="B100" s="9"/>
+      <c r="D99" s="11">
+        <v>41.14</v>
+      </c>
+      <c r="E99" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="F99" s="28">
+        <v>1</v>
+      </c>
+      <c r="G99" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="H99" s="9" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A100" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="B100" s="9" t="s">
+        <v>406</v>
+      </c>
       <c r="C100" s="5"/>
-      <c r="D100" s="11"/>
-      <c r="E100" s="9"/>
-      <c r="F100" s="62"/>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="5"/>
-      <c r="B101" s="9"/>
+      <c r="D100" s="11">
+        <v>43.56</v>
+      </c>
+      <c r="E100" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="F100" s="28">
+        <v>1</v>
+      </c>
+      <c r="G100" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="H100" s="9" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A101" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="B101" s="9" t="s">
+        <v>407</v>
+      </c>
       <c r="C101" s="5"/>
-      <c r="D101" s="11"/>
-      <c r="E101" s="9"/>
-      <c r="F101" s="62"/>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="5"/>
-      <c r="B102" s="10"/>
+      <c r="D101" s="11">
+        <v>43.56</v>
+      </c>
+      <c r="E101" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="F101" s="28">
+        <v>1</v>
+      </c>
+      <c r="G101" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="H101" s="9" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A102" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="B102" s="9" t="s">
+        <v>408</v>
+      </c>
       <c r="C102" s="5"/>
-      <c r="D102" s="12"/>
-      <c r="E102" s="10"/>
-      <c r="F102" s="62"/>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="5"/>
-      <c r="B103" s="9"/>
+      <c r="D102" s="11">
+        <v>43.56</v>
+      </c>
+      <c r="E102" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="F102" s="28">
+        <v>1</v>
+      </c>
+      <c r="G102" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="H102" s="9" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A103" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="B103" s="9" t="s">
+        <v>409</v>
+      </c>
       <c r="C103" s="5"/>
-      <c r="D103" s="11"/>
-      <c r="E103" s="9"/>
-      <c r="F103" s="62"/>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="5"/>
-      <c r="B104" s="10"/>
+      <c r="D103" s="11">
+        <v>45.980000000000004</v>
+      </c>
+      <c r="E103" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="F103" s="28">
+        <v>1</v>
+      </c>
+      <c r="G103" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="H103" s="9" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A104" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="B104" s="9" t="s">
+        <v>410</v>
+      </c>
       <c r="C104" s="5"/>
-      <c r="D104" s="12"/>
-      <c r="E104" s="10"/>
-      <c r="F104" s="62"/>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="5"/>
-      <c r="B105" s="9"/>
+      <c r="D104" s="11">
+        <v>45.980000000000004</v>
+      </c>
+      <c r="E104" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="F104" s="28">
+        <v>1</v>
+      </c>
+      <c r="G104" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="H104" s="9" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A105" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="B105" s="9" t="s">
+        <v>411</v>
+      </c>
       <c r="C105" s="5"/>
-      <c r="D105" s="11"/>
-      <c r="E105" s="9"/>
-      <c r="F105" s="62"/>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="5"/>
-      <c r="B106" s="9"/>
+      <c r="D105" s="11">
+        <v>38.72</v>
+      </c>
+      <c r="E105" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="F105" s="28">
+        <v>1</v>
+      </c>
+      <c r="G105" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="H105" s="9" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A106" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="B106" s="9" t="s">
+        <v>412</v>
+      </c>
       <c r="C106" s="5"/>
-      <c r="D106" s="11"/>
-      <c r="E106" s="9"/>
-      <c r="F106" s="62"/>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="5"/>
-      <c r="B107" s="10"/>
+      <c r="D106" s="11">
+        <v>11.5</v>
+      </c>
+      <c r="E106" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="F106" s="28">
+        <v>1</v>
+      </c>
+      <c r="G106" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="H106" s="9" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A107" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="B107" s="9" t="s">
+        <v>413</v>
+      </c>
       <c r="C107" s="5"/>
-      <c r="D107" s="12"/>
-      <c r="E107" s="10"/>
-      <c r="F107" s="62"/>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="5"/>
-      <c r="B108" s="9"/>
+      <c r="D107" s="11">
+        <v>15.73</v>
+      </c>
+      <c r="E107" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="F107" s="28">
+        <v>1</v>
+      </c>
+      <c r="G107" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="H107" s="9" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A108" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="B108" s="9" t="s">
+        <v>414</v>
+      </c>
       <c r="C108" s="5"/>
-      <c r="D108" s="11"/>
-      <c r="E108" s="9"/>
-      <c r="F108" s="62"/>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="5"/>
-      <c r="B109" s="9"/>
+      <c r="D108" s="11">
+        <v>24.2</v>
+      </c>
+      <c r="E108" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="F108" s="28">
+        <v>1</v>
+      </c>
+      <c r="G108" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="H108" s="9" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A109" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="B109" s="9" t="s">
+        <v>415</v>
+      </c>
       <c r="C109" s="5"/>
-      <c r="D109" s="11"/>
-      <c r="E109" s="9"/>
-      <c r="F109" s="62"/>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="5"/>
-      <c r="B110" s="10"/>
+      <c r="D109" s="11">
+        <v>24.2</v>
+      </c>
+      <c r="E109" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="F109" s="28">
+        <v>1</v>
+      </c>
+      <c r="G109" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="H109" s="9" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A110" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="B110" s="9" t="s">
+        <v>416</v>
+      </c>
       <c r="C110" s="5"/>
-      <c r="D110" s="12"/>
-      <c r="E110" s="10"/>
-      <c r="F110" s="62"/>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="5"/>
-      <c r="B111" s="10"/>
+      <c r="D110" s="11">
+        <v>30.25</v>
+      </c>
+      <c r="E110" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="F110" s="28">
+        <v>1</v>
+      </c>
+      <c r="G110" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="H110" s="9" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A111" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="B111" s="9" t="s">
+        <v>417</v>
+      </c>
       <c r="C111" s="5"/>
-      <c r="D111" s="12"/>
-      <c r="E111" s="10"/>
-      <c r="F111" s="62"/>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="5"/>
-      <c r="B112" s="10"/>
+      <c r="D111" s="11">
+        <v>26.62</v>
+      </c>
+      <c r="E111" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="F111" s="28">
+        <v>1</v>
+      </c>
+      <c r="G111" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="H111" s="9" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A112" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="B112" s="9" t="s">
+        <v>418</v>
+      </c>
       <c r="C112" s="5"/>
-      <c r="D112" s="12"/>
-      <c r="E112" s="10"/>
-      <c r="F112" s="62"/>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="5"/>
-      <c r="B113" s="10"/>
+      <c r="D112" s="11">
+        <v>12.1</v>
+      </c>
+      <c r="E112" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="F112" s="28">
+        <v>1</v>
+      </c>
+      <c r="G112" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="H112" s="9" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A113" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="B113" s="9" t="s">
+        <v>419</v>
+      </c>
       <c r="C113" s="5"/>
-      <c r="D113" s="12"/>
-      <c r="E113" s="10"/>
-      <c r="F113" s="62"/>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="5"/>
-      <c r="B114" s="10"/>
+      <c r="D113" s="11">
+        <v>14.52</v>
+      </c>
+      <c r="E113" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="F113" s="28">
+        <v>1</v>
+      </c>
+      <c r="G113" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="H113" s="9" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A114" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="B114" s="9" t="s">
+        <v>420</v>
+      </c>
       <c r="C114" s="5"/>
-      <c r="D114" s="12"/>
-      <c r="E114" s="10"/>
-      <c r="F114" s="62"/>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="5"/>
-      <c r="B115" s="9"/>
+      <c r="D114" s="11">
+        <v>12.1</v>
+      </c>
+      <c r="E114" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="F114" s="28">
+        <v>1</v>
+      </c>
+      <c r="G114" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="H114" s="9" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A115" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="B115" s="9" t="s">
+        <v>421</v>
+      </c>
       <c r="C115" s="5"/>
-      <c r="D115" s="11"/>
-      <c r="E115" s="9"/>
-      <c r="F115" s="62"/>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="5"/>
-      <c r="B116" s="10"/>
+      <c r="D115" s="11">
+        <v>8.4700000000000006</v>
+      </c>
+      <c r="E115" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="F115" s="28">
+        <v>1</v>
+      </c>
+      <c r="G115" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="H115" s="9" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A116" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="B116" s="9" t="s">
+        <v>422</v>
+      </c>
       <c r="C116" s="5"/>
-      <c r="D116" s="12"/>
-      <c r="E116" s="10"/>
-      <c r="F116" s="62"/>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="5"/>
-      <c r="B117" s="10"/>
+      <c r="D116" s="11">
+        <v>4.84</v>
+      </c>
+      <c r="E116" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="F116" s="28">
+        <v>1</v>
+      </c>
+      <c r="G116" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="H116" s="9" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A117" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="B117" s="9" t="s">
+        <v>422</v>
+      </c>
       <c r="C117" s="5"/>
-      <c r="D117" s="12"/>
-      <c r="E117" s="10"/>
-      <c r="F117" s="62"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="5"/>
-      <c r="B118" s="9"/>
+      <c r="D117" s="11">
+        <v>8.4700000000000006</v>
+      </c>
+      <c r="E117" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="F117" s="28">
+        <v>1</v>
+      </c>
+      <c r="G117" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="H117" s="9" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A118" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="B118" s="9" t="s">
+        <v>423</v>
+      </c>
       <c r="C118" s="5"/>
-      <c r="D118" s="11"/>
-      <c r="E118" s="9"/>
-      <c r="F118" s="62"/>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="5"/>
-      <c r="B119" s="10"/>
+      <c r="D118" s="11">
+        <v>12.1</v>
+      </c>
+      <c r="E118" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="F118" s="28">
+        <v>1</v>
+      </c>
+      <c r="G118" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="H118" s="9" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A119" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="B119" s="9" t="s">
+        <v>424</v>
+      </c>
       <c r="C119" s="5"/>
-      <c r="D119" s="12"/>
-      <c r="E119" s="10"/>
-      <c r="F119" s="62"/>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="5"/>
-      <c r="B120" s="10"/>
+      <c r="D119" s="11">
+        <v>8.4700000000000006</v>
+      </c>
+      <c r="E119" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="F119" s="28">
+        <v>1</v>
+      </c>
+      <c r="G119" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="H119" s="9" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A120" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="B120" s="9" t="s">
+        <v>425</v>
+      </c>
       <c r="C120" s="5"/>
-      <c r="D120" s="12"/>
-      <c r="E120" s="10"/>
-      <c r="F120" s="62"/>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="5"/>
-      <c r="B121" s="9"/>
+      <c r="D120" s="11">
+        <v>18.150000000000002</v>
+      </c>
+      <c r="E120" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="F120" s="28">
+        <v>1</v>
+      </c>
+      <c r="G120" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="H120" s="9" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A121" s="5" t="s">
+        <v>512</v>
+      </c>
+      <c r="B121" s="9" t="s">
+        <v>426</v>
+      </c>
       <c r="C121" s="5"/>
-      <c r="D121" s="11"/>
-      <c r="E121" s="9"/>
-      <c r="F121" s="62"/>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="5"/>
-      <c r="B122" s="9"/>
+      <c r="D121" s="11">
+        <v>12.1</v>
+      </c>
+      <c r="E121" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="F121" s="28">
+        <v>1</v>
+      </c>
+      <c r="G121" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="H121" s="9" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A122" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="B122" s="9" t="s">
+        <v>427</v>
+      </c>
       <c r="C122" s="5"/>
-      <c r="D122" s="11"/>
-      <c r="E122" s="9"/>
-      <c r="F122" s="62"/>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="5"/>
-      <c r="B123" s="10"/>
+      <c r="D122" s="11">
+        <v>13.31</v>
+      </c>
+      <c r="E122" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="F122" s="28">
+        <v>1</v>
+      </c>
+      <c r="G122" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="H122" s="9" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A123" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="B123" s="9" t="s">
+        <v>428</v>
+      </c>
       <c r="C123" s="5"/>
-      <c r="D123" s="12"/>
-      <c r="E123" s="10"/>
-      <c r="F123" s="62"/>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="5"/>
-      <c r="B124" s="10"/>
+      <c r="D123" s="11">
+        <v>12.1</v>
+      </c>
+      <c r="E123" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="F123" s="28">
+        <v>1</v>
+      </c>
+      <c r="G123" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="H123" s="9" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A124" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="B124" s="9" t="s">
+        <v>429</v>
+      </c>
       <c r="C124" s="5"/>
-      <c r="D124" s="12"/>
-      <c r="E124" s="10"/>
-      <c r="F124" s="62"/>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="5"/>
-      <c r="B125" s="9"/>
+      <c r="D124" s="11">
+        <v>15.73</v>
+      </c>
+      <c r="E124" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="F124" s="28">
+        <v>1</v>
+      </c>
+      <c r="G124" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="H124" s="9" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A125" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="B125" s="9" t="s">
+        <v>430</v>
+      </c>
       <c r="C125" s="5"/>
-      <c r="D125" s="11"/>
-      <c r="E125" s="9"/>
-      <c r="F125" s="62"/>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="5"/>
-      <c r="B126" s="9"/>
+      <c r="D125" s="11">
+        <v>15.73</v>
+      </c>
+      <c r="E125" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="F125" s="28">
+        <v>1</v>
+      </c>
+      <c r="G125" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="H125" s="9" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A126" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="B126" s="9" t="s">
+        <v>431</v>
+      </c>
       <c r="C126" s="5"/>
-      <c r="D126" s="11"/>
-      <c r="E126" s="9"/>
-      <c r="F126" s="62"/>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="5"/>
-      <c r="B127" s="10"/>
+      <c r="D126" s="11">
+        <v>14.52</v>
+      </c>
+      <c r="E126" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="F126" s="28">
+        <v>1</v>
+      </c>
+      <c r="G126" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="H126" s="9" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A127" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="B127" s="9" t="s">
+        <v>432</v>
+      </c>
       <c r="C127" s="5"/>
-      <c r="D127" s="12"/>
-      <c r="E127" s="10"/>
-      <c r="F127" s="62"/>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="5"/>
-      <c r="B128" s="9"/>
+      <c r="D127" s="11">
+        <v>15.73</v>
+      </c>
+      <c r="E127" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="F127" s="28">
+        <v>1</v>
+      </c>
+      <c r="G127" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="H127" s="9" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A128" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="B128" s="9" t="s">
+        <v>433</v>
+      </c>
       <c r="C128" s="5"/>
-      <c r="D128" s="11"/>
-      <c r="E128" s="9"/>
-      <c r="F128" s="62"/>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="5"/>
-      <c r="B129" s="9"/>
+      <c r="D128" s="11">
+        <v>15.73</v>
+      </c>
+      <c r="E128" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="F128" s="28">
+        <v>1</v>
+      </c>
+      <c r="G128" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="H128" s="9" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A129" s="5" t="s">
+        <v>520</v>
+      </c>
+      <c r="B129" s="9" t="s">
+        <v>434</v>
+      </c>
       <c r="C129" s="5"/>
-      <c r="D129" s="11"/>
-      <c r="E129" s="9"/>
-      <c r="F129" s="62"/>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="5"/>
-      <c r="B130" s="9"/>
+      <c r="D129" s="11">
+        <v>15.73</v>
+      </c>
+      <c r="E129" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="F129" s="28">
+        <v>1</v>
+      </c>
+      <c r="G129" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="H129" s="9" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A130" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="B130" s="9" t="s">
+        <v>435</v>
+      </c>
       <c r="C130" s="5"/>
-      <c r="D130" s="11"/>
-      <c r="E130" s="9"/>
-      <c r="F130" s="62"/>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="5"/>
-      <c r="B131" s="9"/>
+      <c r="D130" s="11">
+        <v>19.36</v>
+      </c>
+      <c r="E130" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="F130" s="28">
+        <v>1</v>
+      </c>
+      <c r="G130" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="H130" s="9" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A131" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="B131" s="9" t="s">
+        <v>436</v>
+      </c>
       <c r="C131" s="5"/>
-      <c r="D131" s="11"/>
-      <c r="E131" s="9"/>
-      <c r="F131" s="62"/>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="5"/>
-      <c r="B132" s="9"/>
+      <c r="D131" s="11">
+        <v>18.150000000000002</v>
+      </c>
+      <c r="E131" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="F131" s="28">
+        <v>1</v>
+      </c>
+      <c r="G131" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="H131" s="9" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A132" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="B132" s="9" t="s">
+        <v>437</v>
+      </c>
       <c r="C132" s="5"/>
-      <c r="D132" s="11"/>
-      <c r="E132" s="9"/>
-      <c r="F132" s="62"/>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="5"/>
-      <c r="B133" s="9"/>
+      <c r="D132" s="11">
+        <v>21.78</v>
+      </c>
+      <c r="E132" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="F132" s="28">
+        <v>1</v>
+      </c>
+      <c r="G132" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="H132" s="9" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A133" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="B133" s="9" t="s">
+        <v>438</v>
+      </c>
       <c r="C133" s="5"/>
-      <c r="D133" s="11"/>
-      <c r="E133" s="9"/>
-      <c r="F133" s="62"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="5"/>
-      <c r="B134" s="9"/>
+      <c r="D133" s="11">
+        <v>25.41</v>
+      </c>
+      <c r="E133" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="F133" s="28">
+        <v>1</v>
+      </c>
+      <c r="G133" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="H133" s="9" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A134" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="B134" s="9" t="s">
+        <v>439</v>
+      </c>
       <c r="C134" s="5"/>
-      <c r="D134" s="11"/>
-      <c r="E134" s="9"/>
-      <c r="F134" s="62"/>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="5"/>
-      <c r="B135" s="9"/>
+      <c r="D134" s="11">
+        <v>36.300000000000004</v>
+      </c>
+      <c r="E134" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="F134" s="28">
+        <v>1</v>
+      </c>
+      <c r="G134" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="H134" s="9" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A135" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="B135" s="9" t="s">
+        <v>440</v>
+      </c>
       <c r="C135" s="5"/>
-      <c r="D135" s="11"/>
-      <c r="E135" s="9"/>
-      <c r="F135" s="62"/>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="5"/>
-      <c r="B136" s="10"/>
+      <c r="D135" s="11">
+        <v>43.56</v>
+      </c>
+      <c r="E135" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="F135" s="28">
+        <v>1</v>
+      </c>
+      <c r="G135" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="H135" s="9" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A136" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="B136" s="9" t="s">
+        <v>441</v>
+      </c>
       <c r="C136" s="5"/>
-      <c r="D136" s="12"/>
-      <c r="E136" s="10"/>
-      <c r="F136" s="62"/>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="5"/>
-      <c r="B137" s="9"/>
+      <c r="D136" s="11">
+        <v>42.35</v>
+      </c>
+      <c r="E136" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="F136" s="28">
+        <v>1</v>
+      </c>
+      <c r="G136" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="H136" s="9" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A137" s="5" t="s">
+        <v>528</v>
+      </c>
+      <c r="B137" s="9" t="s">
+        <v>442</v>
+      </c>
       <c r="C137" s="5"/>
-      <c r="D137" s="11"/>
-      <c r="E137" s="9"/>
-      <c r="F137" s="62"/>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="5"/>
-      <c r="B138" s="10"/>
+      <c r="D137" s="11">
+        <v>54.45</v>
+      </c>
+      <c r="E137" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="F137" s="28">
+        <v>1</v>
+      </c>
+      <c r="G137" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="H137" s="9" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A138" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="B138" s="9" t="s">
+        <v>443</v>
+      </c>
       <c r="C138" s="5"/>
-      <c r="D138" s="12"/>
-      <c r="E138" s="10"/>
-      <c r="F138" s="62"/>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D138" s="11">
+        <v>8.4700000000000006</v>
+      </c>
+      <c r="E138" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="F138" s="28">
+        <v>1</v>
+      </c>
+      <c r="G138" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="H138" s="9" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" s="5"/>
       <c r="B139" s="10"/>
       <c r="C139" s="5"/>
       <c r="D139" s="12"/>
       <c r="E139" s="10"/>
-      <c r="F139" s="62"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F139" s="28"/>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" s="5"/>
       <c r="B140" s="10"/>
       <c r="C140" s="5"/>
       <c r="D140" s="12"/>
       <c r="E140" s="10"/>
-      <c r="F140" s="62"/>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F140" s="28"/>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" s="5"/>
       <c r="B141" s="10"/>
       <c r="C141" s="5"/>
       <c r="D141" s="12"/>
       <c r="E141" s="10"/>
-      <c r="F141" s="62"/>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F141" s="28"/>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" s="5"/>
       <c r="B142" s="9"/>
       <c r="C142" s="5"/>
       <c r="D142" s="11"/>
       <c r="E142" s="9"/>
-      <c r="F142" s="62"/>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F142" s="28"/>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" s="5"/>
       <c r="B143" s="10"/>
       <c r="C143" s="5"/>
       <c r="D143" s="12"/>
       <c r="E143" s="10"/>
-      <c r="F143" s="62"/>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F143" s="28"/>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" s="5"/>
       <c r="B144" s="9"/>
       <c r="C144" s="5"/>
       <c r="D144" s="11"/>
       <c r="E144" s="9"/>
-      <c r="F144" s="62"/>
+      <c r="F144" s="28"/>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="5"/>
@@ -4099,7 +5192,7 @@
       <c r="C145" s="5"/>
       <c r="D145" s="12"/>
       <c r="E145" s="10"/>
-      <c r="F145" s="62"/>
+      <c r="F145" s="28"/>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="5"/>
@@ -4107,7 +5200,7 @@
       <c r="C146" s="5"/>
       <c r="D146" s="11"/>
       <c r="E146" s="9"/>
-      <c r="F146" s="62"/>
+      <c r="F146" s="28"/>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="5"/>
@@ -4115,7 +5208,7 @@
       <c r="C147" s="5"/>
       <c r="D147" s="11"/>
       <c r="E147" s="9"/>
-      <c r="F147" s="62"/>
+      <c r="F147" s="28"/>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="5"/>
@@ -4123,7 +5216,7 @@
       <c r="C148" s="5"/>
       <c r="D148" s="12"/>
       <c r="E148" s="10"/>
-      <c r="F148" s="62"/>
+      <c r="F148" s="28"/>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="5"/>
@@ -4131,7 +5224,7 @@
       <c r="C149" s="5"/>
       <c r="D149" s="11"/>
       <c r="E149" s="9"/>
-      <c r="F149" s="62"/>
+      <c r="F149" s="28"/>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" s="5"/>
@@ -4139,7 +5232,7 @@
       <c r="C150" s="5"/>
       <c r="D150" s="12"/>
       <c r="E150" s="10"/>
-      <c r="F150" s="62"/>
+      <c r="F150" s="28"/>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="5"/>
@@ -4147,7 +5240,7 @@
       <c r="C151" s="5"/>
       <c r="D151" s="12"/>
       <c r="E151" s="10"/>
-      <c r="F151" s="62"/>
+      <c r="F151" s="28"/>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" s="5"/>
@@ -4155,7 +5248,7 @@
       <c r="C152" s="5"/>
       <c r="D152" s="12"/>
       <c r="E152" s="10"/>
-      <c r="F152" s="62"/>
+      <c r="F152" s="28"/>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" s="5"/>
@@ -4163,7 +5256,7 @@
       <c r="C153" s="5"/>
       <c r="D153" s="12"/>
       <c r="E153" s="10"/>
-      <c r="F153" s="62"/>
+      <c r="F153" s="28"/>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" s="5"/>
@@ -4171,7 +5264,7 @@
       <c r="C154" s="5"/>
       <c r="D154" s="12"/>
       <c r="E154" s="10"/>
-      <c r="F154" s="62"/>
+      <c r="F154" s="28"/>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" s="5"/>
@@ -4179,7 +5272,7 @@
       <c r="C155" s="5"/>
       <c r="D155" s="12"/>
       <c r="E155" s="10"/>
-      <c r="F155" s="62"/>
+      <c r="F155" s="28"/>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" s="5"/>
@@ -4187,7 +5280,7 @@
       <c r="C156" s="5"/>
       <c r="D156" s="11"/>
       <c r="E156" s="9"/>
-      <c r="F156" s="62"/>
+      <c r="F156" s="28"/>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" s="5"/>
@@ -4195,7 +5288,7 @@
       <c r="C157" s="5"/>
       <c r="D157" s="12"/>
       <c r="E157" s="10"/>
-      <c r="F157" s="62"/>
+      <c r="F157" s="28"/>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" s="5"/>
@@ -4203,7 +5296,7 @@
       <c r="C158" s="5"/>
       <c r="D158" s="12"/>
       <c r="E158" s="10"/>
-      <c r="F158" s="62"/>
+      <c r="F158" s="28"/>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" s="5"/>
@@ -4211,7 +5304,7 @@
       <c r="C159" s="5"/>
       <c r="D159" s="12"/>
       <c r="E159" s="10"/>
-      <c r="F159" s="62"/>
+      <c r="F159" s="28"/>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" s="5"/>
@@ -4219,7 +5312,7 @@
       <c r="C160" s="5"/>
       <c r="D160" s="11"/>
       <c r="E160" s="9"/>
-      <c r="F160" s="62"/>
+      <c r="F160" s="28"/>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" s="5"/>
@@ -4227,7 +5320,7 @@
       <c r="C161" s="5"/>
       <c r="D161" s="11"/>
       <c r="E161" s="9"/>
-      <c r="F161" s="62"/>
+      <c r="F161" s="28"/>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" s="5"/>
@@ -4235,7 +5328,7 @@
       <c r="C162" s="5"/>
       <c r="D162" s="11"/>
       <c r="E162" s="9"/>
-      <c r="F162" s="62"/>
+      <c r="F162" s="28"/>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" s="5"/>
@@ -4243,7 +5336,7 @@
       <c r="C163" s="5"/>
       <c r="D163" s="12"/>
       <c r="E163" s="10"/>
-      <c r="F163" s="62"/>
+      <c r="F163" s="28"/>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" s="5"/>
@@ -4251,7 +5344,7 @@
       <c r="C164" s="5"/>
       <c r="D164" s="12"/>
       <c r="E164" s="10"/>
-      <c r="F164" s="62"/>
+      <c r="F164" s="28"/>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" s="5"/>
@@ -4259,7 +5352,7 @@
       <c r="C165" s="5"/>
       <c r="D165" s="12"/>
       <c r="E165" s="10"/>
-      <c r="F165" s="62"/>
+      <c r="F165" s="28"/>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" s="5"/>
@@ -4267,7 +5360,7 @@
       <c r="C166" s="5"/>
       <c r="D166" s="12"/>
       <c r="E166" s="10"/>
-      <c r="F166" s="62"/>
+      <c r="F166" s="28"/>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" s="5"/>
@@ -4275,7 +5368,7 @@
       <c r="C167" s="5"/>
       <c r="D167" s="12"/>
       <c r="E167" s="10"/>
-      <c r="F167" s="62"/>
+      <c r="F167" s="28"/>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" s="5"/>
@@ -4283,7 +5376,7 @@
       <c r="C168" s="5"/>
       <c r="D168" s="12"/>
       <c r="E168" s="10"/>
-      <c r="F168" s="62"/>
+      <c r="F168" s="28"/>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" s="5"/>
@@ -4291,7 +5384,7 @@
       <c r="C169" s="5"/>
       <c r="D169" s="12"/>
       <c r="E169" s="10"/>
-      <c r="F169" s="62"/>
+      <c r="F169" s="28"/>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" s="5"/>
@@ -4299,7 +5392,7 @@
       <c r="C170" s="5"/>
       <c r="D170" s="12"/>
       <c r="E170" s="10"/>
-      <c r="F170" s="62"/>
+      <c r="F170" s="28"/>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" s="5"/>
@@ -4307,7 +5400,7 @@
       <c r="C171" s="5"/>
       <c r="D171" s="12"/>
       <c r="E171" s="10"/>
-      <c r="F171" s="62"/>
+      <c r="F171" s="28"/>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" s="5"/>
@@ -4315,7 +5408,7 @@
       <c r="C172" s="5"/>
       <c r="D172" s="12"/>
       <c r="E172" s="10"/>
-      <c r="F172" s="62"/>
+      <c r="F172" s="28"/>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" s="5"/>
@@ -4323,7 +5416,7 @@
       <c r="C173" s="5"/>
       <c r="D173" s="12"/>
       <c r="E173" s="10"/>
-      <c r="F173" s="62"/>
+      <c r="F173" s="28"/>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" s="5"/>
@@ -4331,7 +5424,7 @@
       <c r="C174" s="5"/>
       <c r="D174" s="11"/>
       <c r="E174" s="9"/>
-      <c r="F174" s="62"/>
+      <c r="F174" s="28"/>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" s="5"/>
@@ -4339,7 +5432,7 @@
       <c r="C175" s="5"/>
       <c r="D175" s="5"/>
       <c r="E175" s="5"/>
-      <c r="F175" s="63"/>
+      <c r="F175" s="5"/>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" s="5"/>
@@ -4347,7 +5440,7 @@
       <c r="C176" s="5"/>
       <c r="D176" s="5"/>
       <c r="E176" s="5"/>
-      <c r="F176" s="63"/>
+      <c r="F176" s="5"/>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" s="5"/>
@@ -4355,7 +5448,7 @@
       <c r="C177" s="5"/>
       <c r="D177" s="5"/>
       <c r="E177" s="5"/>
-      <c r="F177" s="63"/>
+      <c r="F177" s="5"/>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" s="5"/>
@@ -4363,7 +5456,7 @@
       <c r="C178" s="5"/>
       <c r="D178" s="5"/>
       <c r="E178" s="5"/>
-      <c r="F178" s="63"/>
+      <c r="F178" s="5"/>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" s="5"/>
@@ -4371,7 +5464,7 @@
       <c r="C179" s="5"/>
       <c r="D179" s="5"/>
       <c r="E179" s="5"/>
-      <c r="F179" s="63"/>
+      <c r="F179" s="5"/>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" s="5"/>
@@ -4379,7 +5472,7 @@
       <c r="C180" s="5"/>
       <c r="D180" s="5"/>
       <c r="E180" s="5"/>
-      <c r="F180" s="63"/>
+      <c r="F180" s="5"/>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" s="5"/>
@@ -4387,7 +5480,7 @@
       <c r="C181" s="5"/>
       <c r="D181" s="5"/>
       <c r="E181" s="5"/>
-      <c r="F181" s="63"/>
+      <c r="F181" s="5"/>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" s="5"/>
@@ -4395,7 +5488,7 @@
       <c r="C182" s="5"/>
       <c r="D182" s="5"/>
       <c r="E182" s="5"/>
-      <c r="F182" s="63"/>
+      <c r="F182" s="5"/>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" s="5"/>
@@ -4403,7 +5496,7 @@
       <c r="C183" s="5"/>
       <c r="D183" s="5"/>
       <c r="E183" s="5"/>
-      <c r="F183" s="63"/>
+      <c r="F183" s="5"/>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" s="5"/>
@@ -4411,7 +5504,7 @@
       <c r="C184" s="5"/>
       <c r="D184" s="5"/>
       <c r="E184" s="5"/>
-      <c r="F184" s="63"/>
+      <c r="F184" s="5"/>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" s="5"/>
@@ -4419,7 +5512,7 @@
       <c r="C185" s="5"/>
       <c r="D185" s="5"/>
       <c r="E185" s="5"/>
-      <c r="F185" s="63"/>
+      <c r="F185" s="5"/>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" s="5"/>
@@ -4427,7 +5520,7 @@
       <c r="C186" s="5"/>
       <c r="D186" s="5"/>
       <c r="E186" s="5"/>
-      <c r="F186" s="63"/>
+      <c r="F186" s="5"/>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187" s="5"/>
@@ -4435,7 +5528,7 @@
       <c r="C187" s="5"/>
       <c r="D187" s="5"/>
       <c r="E187" s="5"/>
-      <c r="F187" s="63"/>
+      <c r="F187" s="5"/>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" s="5"/>
@@ -4443,7 +5536,7 @@
       <c r="C188" s="5"/>
       <c r="D188" s="5"/>
       <c r="E188" s="5"/>
-      <c r="F188" s="63"/>
+      <c r="F188" s="5"/>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" s="5"/>
@@ -4451,7 +5544,7 @@
       <c r="C189" s="5"/>
       <c r="D189" s="5"/>
       <c r="E189" s="5"/>
-      <c r="F189" s="63"/>
+      <c r="F189" s="5"/>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" s="5"/>
@@ -4459,7 +5552,7 @@
       <c r="C190" s="5"/>
       <c r="D190" s="5"/>
       <c r="E190" s="5"/>
-      <c r="F190" s="63"/>
+      <c r="F190" s="5"/>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" s="5"/>
@@ -4467,7 +5560,7 @@
       <c r="C191" s="5"/>
       <c r="D191" s="5"/>
       <c r="E191" s="5"/>
-      <c r="F191" s="63"/>
+      <c r="F191" s="5"/>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" s="5"/>
@@ -4475,7 +5568,7 @@
       <c r="C192" s="5"/>
       <c r="D192" s="5"/>
       <c r="E192" s="5"/>
-      <c r="F192" s="63"/>
+      <c r="F192" s="5"/>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193" s="5"/>
@@ -4483,7 +5576,7 @@
       <c r="C193" s="5"/>
       <c r="D193" s="5"/>
       <c r="E193" s="5"/>
-      <c r="F193" s="63"/>
+      <c r="F193" s="5"/>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194" s="5"/>
@@ -4491,7 +5584,7 @@
       <c r="C194" s="5"/>
       <c r="D194" s="5"/>
       <c r="E194" s="5"/>
-      <c r="F194" s="63"/>
+      <c r="F194" s="5"/>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195" s="5"/>
@@ -4499,7 +5592,7 @@
       <c r="C195" s="5"/>
       <c r="D195" s="5"/>
       <c r="E195" s="5"/>
-      <c r="F195" s="63"/>
+      <c r="F195" s="5"/>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A196" s="5"/>
@@ -4507,7 +5600,7 @@
       <c r="C196" s="5"/>
       <c r="D196" s="5"/>
       <c r="E196" s="5"/>
-      <c r="F196" s="63"/>
+      <c r="F196" s="5"/>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A197" s="5"/>
@@ -4515,7 +5608,7 @@
       <c r="C197" s="5"/>
       <c r="D197" s="5"/>
       <c r="E197" s="5"/>
-      <c r="F197" s="63"/>
+      <c r="F197" s="5"/>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A198" s="5"/>
@@ -4523,7 +5616,7 @@
       <c r="C198" s="5"/>
       <c r="D198" s="5"/>
       <c r="E198" s="5"/>
-      <c r="F198" s="63"/>
+      <c r="F198" s="5"/>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A199" s="5"/>
@@ -4531,7 +5624,7 @@
       <c r="C199" s="5"/>
       <c r="D199" s="5"/>
       <c r="E199" s="5"/>
-      <c r="F199" s="63"/>
+      <c r="F199" s="5"/>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A200" s="5"/>
@@ -4539,7 +5632,7 @@
       <c r="C200" s="5"/>
       <c r="D200" s="5"/>
       <c r="E200" s="5"/>
-      <c r="F200" s="63"/>
+      <c r="F200" s="5"/>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201" s="5"/>
@@ -4547,7 +5640,7 @@
       <c r="C201" s="5"/>
       <c r="D201" s="5"/>
       <c r="E201" s="5"/>
-      <c r="F201" s="63"/>
+      <c r="F201" s="5"/>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202" s="5"/>
@@ -4555,7 +5648,7 @@
       <c r="C202" s="5"/>
       <c r="D202" s="5"/>
       <c r="E202" s="5"/>
-      <c r="F202" s="63"/>
+      <c r="F202" s="5"/>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203" s="5"/>
@@ -4563,7 +5656,7 @@
       <c r="C203" s="5"/>
       <c r="D203" s="5"/>
       <c r="E203" s="5"/>
-      <c r="F203" s="63"/>
+      <c r="F203" s="5"/>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204" s="5"/>
@@ -4571,7 +5664,7 @@
       <c r="C204" s="5"/>
       <c r="D204" s="5"/>
       <c r="E204" s="5"/>
-      <c r="F204" s="63"/>
+      <c r="F204" s="5"/>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205" s="5"/>
@@ -4579,7 +5672,7 @@
       <c r="C205" s="5"/>
       <c r="D205" s="5"/>
       <c r="E205" s="5"/>
-      <c r="F205" s="63"/>
+      <c r="F205" s="5"/>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206" s="5"/>
@@ -4587,7 +5680,7 @@
       <c r="C206" s="5"/>
       <c r="D206" s="5"/>
       <c r="E206" s="5"/>
-      <c r="F206" s="63"/>
+      <c r="F206" s="5"/>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A207" s="5"/>
@@ -4595,7 +5688,7 @@
       <c r="C207" s="5"/>
       <c r="D207" s="5"/>
       <c r="E207" s="5"/>
-      <c r="F207" s="63"/>
+      <c r="F207" s="5"/>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A208" s="5"/>
@@ -4603,7 +5696,7 @@
       <c r="C208" s="5"/>
       <c r="D208" s="5"/>
       <c r="E208" s="5"/>
-      <c r="F208" s="63"/>
+      <c r="F208" s="5"/>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209" s="5"/>
@@ -4611,7 +5704,7 @@
       <c r="C209" s="5"/>
       <c r="D209" s="5"/>
       <c r="E209" s="5"/>
-      <c r="F209" s="63"/>
+      <c r="F209" s="5"/>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210" s="5"/>
@@ -4619,7 +5712,7 @@
       <c r="C210" s="5"/>
       <c r="D210" s="5"/>
       <c r="E210" s="5"/>
-      <c r="F210" s="63"/>
+      <c r="F210" s="5"/>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211" s="5"/>
@@ -4627,7 +5720,7 @@
       <c r="C211" s="5"/>
       <c r="D211" s="5"/>
       <c r="E211" s="5"/>
-      <c r="F211" s="63"/>
+      <c r="F211" s="5"/>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212" s="5"/>
@@ -4635,7 +5728,7 @@
       <c r="C212" s="5"/>
       <c r="D212" s="5"/>
       <c r="E212" s="5"/>
-      <c r="F212" s="63"/>
+      <c r="F212" s="5"/>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213" s="5"/>
@@ -4643,7 +5736,7 @@
       <c r="C213" s="5"/>
       <c r="D213" s="5"/>
       <c r="E213" s="5"/>
-      <c r="F213" s="63"/>
+      <c r="F213" s="5"/>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214" s="5"/>
@@ -4651,7 +5744,7 @@
       <c r="C214" s="5"/>
       <c r="D214" s="5"/>
       <c r="E214" s="5"/>
-      <c r="F214" s="63"/>
+      <c r="F214" s="5"/>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215" s="5"/>
@@ -4659,7 +5752,7 @@
       <c r="C215" s="5"/>
       <c r="D215" s="5"/>
       <c r="E215" s="5"/>
-      <c r="F215" s="63"/>
+      <c r="F215" s="5"/>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216" s="5"/>
@@ -4667,7 +5760,7 @@
       <c r="C216" s="5"/>
       <c r="D216" s="5"/>
       <c r="E216" s="5"/>
-      <c r="F216" s="63"/>
+      <c r="F216" s="5"/>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217" s="5"/>
@@ -4675,7 +5768,7 @@
       <c r="C217" s="5"/>
       <c r="D217" s="5"/>
       <c r="E217" s="5"/>
-      <c r="F217" s="63"/>
+      <c r="F217" s="5"/>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218" s="5"/>
@@ -4683,7 +5776,7 @@
       <c r="C218" s="5"/>
       <c r="D218" s="5"/>
       <c r="E218" s="5"/>
-      <c r="F218" s="63"/>
+      <c r="F218" s="5"/>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A219" s="5"/>
@@ -4691,7 +5784,7 @@
       <c r="C219" s="5"/>
       <c r="D219" s="5"/>
       <c r="E219" s="5"/>
-      <c r="F219" s="63"/>
+      <c r="F219" s="5"/>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A220" s="5"/>
@@ -4699,7 +5792,7 @@
       <c r="C220" s="5"/>
       <c r="D220" s="5"/>
       <c r="E220" s="5"/>
-      <c r="F220" s="63"/>
+      <c r="F220" s="5"/>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A221" s="5"/>
@@ -4707,7 +5800,7 @@
       <c r="C221" s="5"/>
       <c r="D221" s="5"/>
       <c r="E221" s="5"/>
-      <c r="F221" s="63"/>
+      <c r="F221" s="5"/>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A222" s="5"/>
@@ -4715,7 +5808,7 @@
       <c r="C222" s="5"/>
       <c r="D222" s="5"/>
       <c r="E222" s="5"/>
-      <c r="F222" s="63"/>
+      <c r="F222" s="5"/>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A223" s="5"/>
@@ -4723,7 +5816,7 @@
       <c r="C223" s="5"/>
       <c r="D223" s="5"/>
       <c r="E223" s="5"/>
-      <c r="F223" s="63"/>
+      <c r="F223" s="5"/>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A224" s="5"/>
@@ -4731,7 +5824,7 @@
       <c r="C224" s="5"/>
       <c r="D224" s="5"/>
       <c r="E224" s="5"/>
-      <c r="F224" s="63"/>
+      <c r="F224" s="5"/>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" s="5"/>
@@ -4739,7 +5832,7 @@
       <c r="C225" s="5"/>
       <c r="D225" s="5"/>
       <c r="E225" s="5"/>
-      <c r="F225" s="63"/>
+      <c r="F225" s="5"/>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226" s="5"/>
@@ -4747,7 +5840,7 @@
       <c r="C226" s="5"/>
       <c r="D226" s="5"/>
       <c r="E226" s="5"/>
-      <c r="F226" s="63"/>
+      <c r="F226" s="5"/>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227" s="5"/>
@@ -4755,7 +5848,7 @@
       <c r="C227" s="5"/>
       <c r="D227" s="5"/>
       <c r="E227" s="5"/>
-      <c r="F227" s="63"/>
+      <c r="F227" s="5"/>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228" s="5"/>
@@ -4763,7 +5856,7 @@
       <c r="C228" s="5"/>
       <c r="D228" s="5"/>
       <c r="E228" s="5"/>
-      <c r="F228" s="63"/>
+      <c r="F228" s="5"/>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229" s="5"/>
@@ -4771,7 +5864,7 @@
       <c r="C229" s="5"/>
       <c r="D229" s="5"/>
       <c r="E229" s="5"/>
-      <c r="F229" s="63"/>
+      <c r="F229" s="5"/>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230" s="5"/>
@@ -4779,7 +5872,7 @@
       <c r="C230" s="5"/>
       <c r="D230" s="5"/>
       <c r="E230" s="5"/>
-      <c r="F230" s="63"/>
+      <c r="F230" s="5"/>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231" s="5"/>
@@ -4787,7 +5880,7 @@
       <c r="C231" s="5"/>
       <c r="D231" s="5"/>
       <c r="E231" s="5"/>
-      <c r="F231" s="63"/>
+      <c r="F231" s="5"/>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" s="5"/>
@@ -4795,7 +5888,7 @@
       <c r="C232" s="5"/>
       <c r="D232" s="5"/>
       <c r="E232" s="5"/>
-      <c r="F232" s="63"/>
+      <c r="F232" s="5"/>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233" s="5"/>
@@ -4803,7 +5896,7 @@
       <c r="C233" s="5"/>
       <c r="D233" s="5"/>
       <c r="E233" s="5"/>
-      <c r="F233" s="63"/>
+      <c r="F233" s="5"/>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234" s="5"/>
@@ -4811,7 +5904,7 @@
       <c r="C234" s="5"/>
       <c r="D234" s="5"/>
       <c r="E234" s="5"/>
-      <c r="F234" s="63"/>
+      <c r="F234" s="5"/>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" s="5"/>
@@ -4819,7 +5912,7 @@
       <c r="C235" s="5"/>
       <c r="D235" s="5"/>
       <c r="E235" s="5"/>
-      <c r="F235" s="63"/>
+      <c r="F235" s="5"/>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" s="5"/>
@@ -4827,7 +5920,7 @@
       <c r="C236" s="5"/>
       <c r="D236" s="5"/>
       <c r="E236" s="5"/>
-      <c r="F236" s="63"/>
+      <c r="F236" s="5"/>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237" s="5"/>
@@ -4835,7 +5928,7 @@
       <c r="C237" s="5"/>
       <c r="D237" s="5"/>
       <c r="E237" s="5"/>
-      <c r="F237" s="63"/>
+      <c r="F237" s="5"/>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238" s="5"/>
@@ -4843,7 +5936,7 @@
       <c r="C238" s="5"/>
       <c r="D238" s="5"/>
       <c r="E238" s="5"/>
-      <c r="F238" s="63"/>
+      <c r="F238" s="5"/>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239" s="5"/>
@@ -4851,7 +5944,7 @@
       <c r="C239" s="5"/>
       <c r="D239" s="5"/>
       <c r="E239" s="5"/>
-      <c r="F239" s="63"/>
+      <c r="F239" s="5"/>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240" s="5"/>
@@ -4859,7 +5952,7 @@
       <c r="C240" s="5"/>
       <c r="D240" s="5"/>
       <c r="E240" s="5"/>
-      <c r="F240" s="63"/>
+      <c r="F240" s="5"/>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241" s="5"/>
@@ -4867,7 +5960,7 @@
       <c r="C241" s="5"/>
       <c r="D241" s="5"/>
       <c r="E241" s="5"/>
-      <c r="F241" s="63"/>
+      <c r="F241" s="5"/>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242" s="5"/>
@@ -4875,7 +5968,7 @@
       <c r="C242" s="5"/>
       <c r="D242" s="5"/>
       <c r="E242" s="5"/>
-      <c r="F242" s="63"/>
+      <c r="F242" s="5"/>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243" s="5"/>
@@ -4883,7 +5976,7 @@
       <c r="C243" s="5"/>
       <c r="D243" s="5"/>
       <c r="E243" s="5"/>
-      <c r="F243" s="63"/>
+      <c r="F243" s="5"/>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244" s="5"/>
@@ -4891,7 +5984,7 @@
       <c r="C244" s="5"/>
       <c r="D244" s="5"/>
       <c r="E244" s="5"/>
-      <c r="F244" s="63"/>
+      <c r="F244" s="5"/>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245" s="5"/>
@@ -4899,7 +5992,7 @@
       <c r="C245" s="5"/>
       <c r="D245" s="5"/>
       <c r="E245" s="5"/>
-      <c r="F245" s="63"/>
+      <c r="F245" s="5"/>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246" s="5"/>
@@ -4907,7 +6000,7 @@
       <c r="C246" s="5"/>
       <c r="D246" s="5"/>
       <c r="E246" s="5"/>
-      <c r="F246" s="63"/>
+      <c r="F246" s="5"/>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247" s="5"/>
@@ -4915,7 +6008,7 @@
       <c r="C247" s="5"/>
       <c r="D247" s="5"/>
       <c r="E247" s="5"/>
-      <c r="F247" s="63"/>
+      <c r="F247" s="5"/>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A248" s="5"/>
@@ -4923,7 +6016,7 @@
       <c r="C248" s="5"/>
       <c r="D248" s="5"/>
       <c r="E248" s="5"/>
-      <c r="F248" s="63"/>
+      <c r="F248" s="5"/>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249" s="5"/>
@@ -4931,7 +6024,7 @@
       <c r="C249" s="5"/>
       <c r="D249" s="5"/>
       <c r="E249" s="5"/>
-      <c r="F249" s="63"/>
+      <c r="F249" s="5"/>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250" s="5"/>
@@ -4939,7 +6032,7 @@
       <c r="C250" s="5"/>
       <c r="D250" s="5"/>
       <c r="E250" s="5"/>
-      <c r="F250" s="63"/>
+      <c r="F250" s="5"/>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251" s="5"/>
@@ -4947,7 +6040,7 @@
       <c r="C251" s="5"/>
       <c r="D251" s="5"/>
       <c r="E251" s="5"/>
-      <c r="F251" s="63"/>
+      <c r="F251" s="5"/>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252" s="5"/>
@@ -4955,7 +6048,7 @@
       <c r="C252" s="5"/>
       <c r="D252" s="5"/>
       <c r="E252" s="5"/>
-      <c r="F252" s="63"/>
+      <c r="F252" s="5"/>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253" s="5"/>
@@ -4963,7 +6056,7 @@
       <c r="C253" s="5"/>
       <c r="D253" s="5"/>
       <c r="E253" s="5"/>
-      <c r="F253" s="63"/>
+      <c r="F253" s="5"/>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254" s="5"/>
@@ -4971,7 +6064,7 @@
       <c r="C254" s="5"/>
       <c r="D254" s="5"/>
       <c r="E254" s="5"/>
-      <c r="F254" s="63"/>
+      <c r="F254" s="5"/>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255" s="5"/>
@@ -4979,7 +6072,7 @@
       <c r="C255" s="5"/>
       <c r="D255" s="5"/>
       <c r="E255" s="5"/>
-      <c r="F255" s="63"/>
+      <c r="F255" s="5"/>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256" s="5"/>
@@ -4987,7 +6080,7 @@
       <c r="C256" s="5"/>
       <c r="D256" s="5"/>
       <c r="E256" s="5"/>
-      <c r="F256" s="63"/>
+      <c r="F256" s="5"/>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A257" s="5"/>
@@ -4995,7 +6088,7 @@
       <c r="C257" s="5"/>
       <c r="D257" s="5"/>
       <c r="E257" s="5"/>
-      <c r="F257" s="63"/>
+      <c r="F257" s="5"/>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A258" s="5"/>
@@ -5003,7 +6096,7 @@
       <c r="C258" s="5"/>
       <c r="D258" s="5"/>
       <c r="E258" s="5"/>
-      <c r="F258" s="63"/>
+      <c r="F258" s="5"/>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A259" s="5"/>
@@ -5011,7 +6104,7 @@
       <c r="C259" s="5"/>
       <c r="D259" s="5"/>
       <c r="E259" s="5"/>
-      <c r="F259" s="63"/>
+      <c r="F259" s="5"/>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A260" s="5"/>
@@ -5019,7 +6112,7 @@
       <c r="C260" s="5"/>
       <c r="D260" s="5"/>
       <c r="E260" s="5"/>
-      <c r="F260" s="63"/>
+      <c r="F260" s="5"/>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A261" s="5"/>
@@ -5027,7 +6120,7 @@
       <c r="C261" s="5"/>
       <c r="D261" s="5"/>
       <c r="E261" s="5"/>
-      <c r="F261" s="63"/>
+      <c r="F261" s="5"/>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262" s="5"/>
@@ -5035,7 +6128,7 @@
       <c r="C262" s="5"/>
       <c r="D262" s="5"/>
       <c r="E262" s="5"/>
-      <c r="F262" s="63"/>
+      <c r="F262" s="5"/>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263" s="5"/>
@@ -5043,7 +6136,7 @@
       <c r="C263" s="5"/>
       <c r="D263" s="5"/>
       <c r="E263" s="5"/>
-      <c r="F263" s="63"/>
+      <c r="F263" s="5"/>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264" s="5"/>
@@ -5051,7 +6144,7 @@
       <c r="C264" s="5"/>
       <c r="D264" s="5"/>
       <c r="E264" s="5"/>
-      <c r="F264" s="63"/>
+      <c r="F264" s="5"/>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265" s="5"/>
@@ -5059,7 +6152,7 @@
       <c r="C265" s="5"/>
       <c r="D265" s="5"/>
       <c r="E265" s="5"/>
-      <c r="F265" s="63"/>
+      <c r="F265" s="5"/>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A266" s="5"/>
@@ -5067,7 +6160,7 @@
       <c r="C266" s="5"/>
       <c r="D266" s="5"/>
       <c r="E266" s="5"/>
-      <c r="F266" s="63"/>
+      <c r="F266" s="5"/>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A267" s="5"/>
@@ -5075,7 +6168,7 @@
       <c r="C267" s="5"/>
       <c r="D267" s="5"/>
       <c r="E267" s="5"/>
-      <c r="F267" s="63"/>
+      <c r="F267" s="5"/>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A268" s="5"/>
@@ -5083,7 +6176,7 @@
       <c r="C268" s="5"/>
       <c r="D268" s="5"/>
       <c r="E268" s="5"/>
-      <c r="F268" s="63"/>
+      <c r="F268" s="5"/>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A269" s="5"/>
@@ -5091,7 +6184,7 @@
       <c r="C269" s="5"/>
       <c r="D269" s="5"/>
       <c r="E269" s="5"/>
-      <c r="F269" s="63"/>
+      <c r="F269" s="5"/>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A270" s="5"/>
@@ -5099,7 +6192,7 @@
       <c r="C270" s="5"/>
       <c r="D270" s="5"/>
       <c r="E270" s="5"/>
-      <c r="F270" s="63"/>
+      <c r="F270" s="5"/>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A271" s="5"/>
@@ -5107,7 +6200,7 @@
       <c r="C271" s="5"/>
       <c r="D271" s="5"/>
       <c r="E271" s="5"/>
-      <c r="F271" s="63"/>
+      <c r="F271" s="5"/>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A272" s="5"/>
@@ -5115,7 +6208,7 @@
       <c r="C272" s="5"/>
       <c r="D272" s="5"/>
       <c r="E272" s="5"/>
-      <c r="F272" s="63"/>
+      <c r="F272" s="5"/>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A273" s="5"/>
@@ -5123,7 +6216,7 @@
       <c r="C273" s="5"/>
       <c r="D273" s="5"/>
       <c r="E273" s="5"/>
-      <c r="F273" s="63"/>
+      <c r="F273" s="5"/>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A274" s="5"/>
@@ -5131,7 +6224,7 @@
       <c r="C274" s="5"/>
       <c r="D274" s="5"/>
       <c r="E274" s="5"/>
-      <c r="F274" s="63"/>
+      <c r="F274" s="5"/>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A275" s="5"/>
@@ -5139,7 +6232,7 @@
       <c r="C275" s="5"/>
       <c r="D275" s="5"/>
       <c r="E275" s="5"/>
-      <c r="F275" s="63"/>
+      <c r="F275" s="5"/>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A276" s="5"/>
@@ -5147,7 +6240,7 @@
       <c r="C276" s="5"/>
       <c r="D276" s="5"/>
       <c r="E276" s="5"/>
-      <c r="F276" s="63"/>
+      <c r="F276" s="5"/>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A277" s="5"/>
@@ -5155,7 +6248,7 @@
       <c r="C277" s="5"/>
       <c r="D277" s="5"/>
       <c r="E277" s="5"/>
-      <c r="F277" s="63"/>
+      <c r="F277" s="5"/>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A278" s="5"/>
@@ -5163,7 +6256,7 @@
       <c r="C278" s="5"/>
       <c r="D278" s="5"/>
       <c r="E278" s="5"/>
-      <c r="F278" s="63"/>
+      <c r="F278" s="5"/>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A279" s="5"/>
@@ -5171,7 +6264,7 @@
       <c r="C279" s="5"/>
       <c r="D279" s="5"/>
       <c r="E279" s="5"/>
-      <c r="F279" s="63"/>
+      <c r="F279" s="5"/>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A280" s="5"/>
@@ -5179,7 +6272,7 @@
       <c r="C280" s="5"/>
       <c r="D280" s="5"/>
       <c r="E280" s="5"/>
-      <c r="F280" s="63"/>
+      <c r="F280" s="5"/>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A281" s="5"/>
@@ -5187,7 +6280,7 @@
       <c r="C281" s="5"/>
       <c r="D281" s="5"/>
       <c r="E281" s="5"/>
-      <c r="F281" s="63"/>
+      <c r="F281" s="5"/>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A282" s="5"/>
@@ -5195,7 +6288,7 @@
       <c r="C282" s="5"/>
       <c r="D282" s="5"/>
       <c r="E282" s="5"/>
-      <c r="F282" s="63"/>
+      <c r="F282" s="5"/>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A283" s="5"/>
@@ -5203,7 +6296,7 @@
       <c r="C283" s="5"/>
       <c r="D283" s="5"/>
       <c r="E283" s="5"/>
-      <c r="F283" s="63"/>
+      <c r="F283" s="5"/>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A284" s="5"/>
@@ -5211,7 +6304,7 @@
       <c r="C284" s="5"/>
       <c r="D284" s="5"/>
       <c r="E284" s="5"/>
-      <c r="F284" s="63"/>
+      <c r="F284" s="5"/>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A285" s="5"/>
@@ -5219,7 +6312,7 @@
       <c r="C285" s="5"/>
       <c r="D285" s="5"/>
       <c r="E285" s="5"/>
-      <c r="F285" s="63"/>
+      <c r="F285" s="5"/>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A286" s="5"/>
@@ -5227,7 +6320,7 @@
       <c r="C286" s="5"/>
       <c r="D286" s="5"/>
       <c r="E286" s="5"/>
-      <c r="F286" s="63"/>
+      <c r="F286" s="5"/>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A287" s="5"/>
@@ -5235,7 +6328,7 @@
       <c r="C287" s="5"/>
       <c r="D287" s="5"/>
       <c r="E287" s="5"/>
-      <c r="F287" s="63"/>
+      <c r="F287" s="5"/>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A288" s="5"/>
@@ -5243,7 +6336,7 @@
       <c r="C288" s="5"/>
       <c r="D288" s="5"/>
       <c r="E288" s="5"/>
-      <c r="F288" s="63"/>
+      <c r="F288" s="5"/>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A289" s="5"/>
@@ -5251,7 +6344,7 @@
       <c r="C289" s="5"/>
       <c r="D289" s="5"/>
       <c r="E289" s="5"/>
-      <c r="F289" s="63"/>
+      <c r="F289" s="5"/>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A290" s="5"/>
@@ -5259,7 +6352,7 @@
       <c r="C290" s="5"/>
       <c r="D290" s="5"/>
       <c r="E290" s="5"/>
-      <c r="F290" s="63"/>
+      <c r="F290" s="5"/>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A291" s="5"/>
@@ -5267,7 +6360,7 @@
       <c r="C291" s="5"/>
       <c r="D291" s="5"/>
       <c r="E291" s="5"/>
-      <c r="F291" s="63"/>
+      <c r="F291" s="5"/>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A292" s="5"/>
@@ -5275,7 +6368,7 @@
       <c r="C292" s="5"/>
       <c r="D292" s="5"/>
       <c r="E292" s="5"/>
-      <c r="F292" s="63"/>
+      <c r="F292" s="5"/>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A293" s="5"/>
@@ -5283,7 +6376,7 @@
       <c r="C293" s="5"/>
       <c r="D293" s="5"/>
       <c r="E293" s="5"/>
-      <c r="F293" s="63"/>
+      <c r="F293" s="5"/>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A294" s="5"/>
@@ -5291,7 +6384,7 @@
       <c r="C294" s="5"/>
       <c r="D294" s="5"/>
       <c r="E294" s="5"/>
-      <c r="F294" s="63"/>
+      <c r="F294" s="5"/>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A295" s="5"/>
@@ -5299,7 +6392,7 @@
       <c r="C295" s="5"/>
       <c r="D295" s="5"/>
       <c r="E295" s="5"/>
-      <c r="F295" s="63"/>
+      <c r="F295" s="5"/>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A296" s="5"/>
@@ -5307,7 +6400,7 @@
       <c r="C296" s="5"/>
       <c r="D296" s="5"/>
       <c r="E296" s="5"/>
-      <c r="F296" s="63"/>
+      <c r="F296" s="5"/>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A297" s="5"/>
@@ -5315,7 +6408,7 @@
       <c r="C297" s="5"/>
       <c r="D297" s="5"/>
       <c r="E297" s="5"/>
-      <c r="F297" s="63"/>
+      <c r="F297" s="5"/>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A298" s="5"/>
@@ -5323,7 +6416,7 @@
       <c r="C298" s="5"/>
       <c r="D298" s="5"/>
       <c r="E298" s="5"/>
-      <c r="F298" s="63"/>
+      <c r="F298" s="5"/>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A299" s="5"/>
@@ -5331,7 +6424,7 @@
       <c r="C299" s="5"/>
       <c r="D299" s="5"/>
       <c r="E299" s="5"/>
-      <c r="F299" s="63"/>
+      <c r="F299" s="5"/>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A300" s="5"/>
@@ -5339,7 +6432,7 @@
       <c r="C300" s="5"/>
       <c r="D300" s="5"/>
       <c r="E300" s="5"/>
-      <c r="F300" s="63"/>
+      <c r="F300" s="5"/>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A301" s="5"/>
@@ -5347,7 +6440,7 @@
       <c r="C301" s="5"/>
       <c r="D301" s="5"/>
       <c r="E301" s="5"/>
-      <c r="F301" s="63"/>
+      <c r="F301" s="5"/>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A302" s="5"/>
@@ -5355,7 +6448,7 @@
       <c r="C302" s="5"/>
       <c r="D302" s="5"/>
       <c r="E302" s="5"/>
-      <c r="F302" s="63"/>
+      <c r="F302" s="5"/>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A303" s="5"/>
@@ -5363,7 +6456,7 @@
       <c r="C303" s="5"/>
       <c r="D303" s="5"/>
       <c r="E303" s="5"/>
-      <c r="F303" s="63"/>
+      <c r="F303" s="5"/>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A304" s="5"/>
@@ -5371,7 +6464,7 @@
       <c r="C304" s="5"/>
       <c r="D304" s="5"/>
       <c r="E304" s="5"/>
-      <c r="F304" s="63"/>
+      <c r="F304" s="5"/>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A305" s="5"/>
@@ -5379,7 +6472,7 @@
       <c r="C305" s="5"/>
       <c r="D305" s="5"/>
       <c r="E305" s="5"/>
-      <c r="F305" s="63"/>
+      <c r="F305" s="5"/>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A306" s="5"/>
@@ -5387,7 +6480,7 @@
       <c r="C306" s="5"/>
       <c r="D306" s="5"/>
       <c r="E306" s="5"/>
-      <c r="F306" s="63"/>
+      <c r="F306" s="5"/>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A307" s="5"/>
@@ -5395,7 +6488,7 @@
       <c r="C307" s="5"/>
       <c r="D307" s="5"/>
       <c r="E307" s="5"/>
-      <c r="F307" s="63"/>
+      <c r="F307" s="5"/>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A308" s="5"/>
@@ -5403,7 +6496,7 @@
       <c r="C308" s="5"/>
       <c r="D308" s="5"/>
       <c r="E308" s="5"/>
-      <c r="F308" s="63"/>
+      <c r="F308" s="5"/>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A309" s="5"/>
@@ -5411,7 +6504,7 @@
       <c r="C309" s="5"/>
       <c r="D309" s="5"/>
       <c r="E309" s="5"/>
-      <c r="F309" s="63"/>
+      <c r="F309" s="5"/>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A310" s="5"/>
@@ -5419,7 +6512,7 @@
       <c r="C310" s="5"/>
       <c r="D310" s="5"/>
       <c r="E310" s="5"/>
-      <c r="F310" s="63"/>
+      <c r="F310" s="5"/>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A311" s="5"/>
@@ -5427,7 +6520,7 @@
       <c r="C311" s="5"/>
       <c r="D311" s="5"/>
       <c r="E311" s="5"/>
-      <c r="F311" s="63"/>
+      <c r="F311" s="5"/>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A312" s="5"/>
@@ -5435,7 +6528,7 @@
       <c r="C312" s="5"/>
       <c r="D312" s="5"/>
       <c r="E312" s="5"/>
-      <c r="F312" s="63"/>
+      <c r="F312" s="5"/>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A313" s="5"/>
@@ -5443,7 +6536,7 @@
       <c r="C313" s="5"/>
       <c r="D313" s="5"/>
       <c r="E313" s="5"/>
-      <c r="F313" s="63"/>
+      <c r="F313" s="5"/>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A314" s="5"/>
@@ -5451,7 +6544,7 @@
       <c r="C314" s="5"/>
       <c r="D314" s="5"/>
       <c r="E314" s="5"/>
-      <c r="F314" s="63"/>
+      <c r="F314" s="5"/>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A315" s="5"/>
@@ -5459,7 +6552,7 @@
       <c r="C315" s="5"/>
       <c r="D315" s="5"/>
       <c r="E315" s="5"/>
-      <c r="F315" s="63"/>
+      <c r="F315" s="5"/>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A316" s="5"/>
@@ -5467,7 +6560,7 @@
       <c r="C316" s="5"/>
       <c r="D316" s="5"/>
       <c r="E316" s="5"/>
-      <c r="F316" s="63"/>
+      <c r="F316" s="5"/>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A317" s="5"/>
@@ -5475,7 +6568,7 @@
       <c r="C317" s="5"/>
       <c r="D317" s="5"/>
       <c r="E317" s="5"/>
-      <c r="F317" s="63"/>
+      <c r="F317" s="5"/>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A318" s="5"/>
@@ -5483,7 +6576,7 @@
       <c r="C318" s="5"/>
       <c r="D318" s="5"/>
       <c r="E318" s="5"/>
-      <c r="F318" s="63"/>
+      <c r="F318" s="5"/>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A319" s="5"/>
@@ -5491,7 +6584,7 @@
       <c r="C319" s="5"/>
       <c r="D319" s="5"/>
       <c r="E319" s="5"/>
-      <c r="F319" s="63"/>
+      <c r="F319" s="5"/>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A320" s="5"/>
@@ -5499,7 +6592,7 @@
       <c r="C320" s="5"/>
       <c r="D320" s="5"/>
       <c r="E320" s="5"/>
-      <c r="F320" s="63"/>
+      <c r="F320" s="5"/>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A321" s="5"/>
@@ -5507,7 +6600,7 @@
       <c r="C321" s="5"/>
       <c r="D321" s="5"/>
       <c r="E321" s="5"/>
-      <c r="F321" s="63"/>
+      <c r="F321" s="5"/>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A322" s="5"/>
@@ -5515,7 +6608,7 @@
       <c r="C322" s="5"/>
       <c r="D322" s="5"/>
       <c r="E322" s="5"/>
-      <c r="F322" s="63"/>
+      <c r="F322" s="5"/>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A323" s="5"/>
@@ -5523,7 +6616,7 @@
       <c r="C323" s="5"/>
       <c r="D323" s="5"/>
       <c r="E323" s="5"/>
-      <c r="F323" s="63"/>
+      <c r="F323" s="5"/>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A324" s="5"/>
@@ -5531,7 +6624,7 @@
       <c r="C324" s="5"/>
       <c r="D324" s="5"/>
       <c r="E324" s="5"/>
-      <c r="F324" s="63"/>
+      <c r="F324" s="5"/>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A325" s="5"/>
@@ -5539,7 +6632,7 @@
       <c r="C325" s="5"/>
       <c r="D325" s="5"/>
       <c r="E325" s="5"/>
-      <c r="F325" s="63"/>
+      <c r="F325" s="5"/>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A326" s="5"/>
@@ -5547,7 +6640,7 @@
       <c r="C326" s="5"/>
       <c r="D326" s="5"/>
       <c r="E326" s="5"/>
-      <c r="F326" s="63"/>
+      <c r="F326" s="5"/>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A327" s="5"/>
@@ -5555,7 +6648,7 @@
       <c r="C327" s="5"/>
       <c r="D327" s="5"/>
       <c r="E327" s="5"/>
-      <c r="F327" s="63"/>
+      <c r="F327" s="5"/>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A328" s="5"/>
@@ -5563,7 +6656,7 @@
       <c r="C328" s="5"/>
       <c r="D328" s="5"/>
       <c r="E328" s="5"/>
-      <c r="F328" s="63"/>
+      <c r="F328" s="5"/>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A329" s="5"/>
@@ -5571,7 +6664,7 @@
       <c r="C329" s="5"/>
       <c r="D329" s="5"/>
       <c r="E329" s="5"/>
-      <c r="F329" s="63"/>
+      <c r="F329" s="5"/>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A330" s="5"/>
@@ -5579,7 +6672,7 @@
       <c r="C330" s="5"/>
       <c r="D330" s="5"/>
       <c r="E330" s="5"/>
-      <c r="F330" s="63"/>
+      <c r="F330" s="5"/>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A331" s="5"/>
@@ -5587,7 +6680,7 @@
       <c r="C331" s="5"/>
       <c r="D331" s="5"/>
       <c r="E331" s="5"/>
-      <c r="F331" s="63"/>
+      <c r="F331" s="5"/>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A332" s="5"/>
@@ -5595,7 +6688,7 @@
       <c r="C332" s="5"/>
       <c r="D332" s="5"/>
       <c r="E332" s="5"/>
-      <c r="F332" s="63"/>
+      <c r="F332" s="5"/>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A333" s="5"/>
@@ -5603,7 +6696,7 @@
       <c r="C333" s="5"/>
       <c r="D333" s="5"/>
       <c r="E333" s="5"/>
-      <c r="F333" s="63"/>
+      <c r="F333" s="5"/>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A334" s="5"/>
@@ -5611,7 +6704,7 @@
       <c r="C334" s="5"/>
       <c r="D334" s="5"/>
       <c r="E334" s="5"/>
-      <c r="F334" s="63"/>
+      <c r="F334" s="5"/>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A335" s="5"/>
@@ -5619,7 +6712,7 @@
       <c r="C335" s="5"/>
       <c r="D335" s="5"/>
       <c r="E335" s="5"/>
-      <c r="F335" s="63"/>
+      <c r="F335" s="5"/>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A336" s="5"/>
@@ -5627,7 +6720,7 @@
       <c r="C336" s="5"/>
       <c r="D336" s="5"/>
       <c r="E336" s="5"/>
-      <c r="F336" s="63"/>
+      <c r="F336" s="5"/>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A337" s="5"/>
@@ -5635,7 +6728,7 @@
       <c r="C337" s="5"/>
       <c r="D337" s="5"/>
       <c r="E337" s="5"/>
-      <c r="F337" s="63"/>
+      <c r="F337" s="5"/>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A338" s="5"/>
@@ -5643,7 +6736,7 @@
       <c r="C338" s="5"/>
       <c r="D338" s="5"/>
       <c r="E338" s="5"/>
-      <c r="F338" s="63"/>
+      <c r="F338" s="5"/>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A339" s="5"/>
@@ -5651,7 +6744,7 @@
       <c r="C339" s="5"/>
       <c r="D339" s="5"/>
       <c r="E339" s="5"/>
-      <c r="F339" s="63"/>
+      <c r="F339" s="5"/>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A340" s="5"/>
@@ -5659,7 +6752,7 @@
       <c r="C340" s="5"/>
       <c r="D340" s="5"/>
       <c r="E340" s="5"/>
-      <c r="F340" s="63"/>
+      <c r="F340" s="5"/>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A341" s="5"/>
@@ -5667,7 +6760,7 @@
       <c r="C341" s="5"/>
       <c r="D341" s="5"/>
       <c r="E341" s="5"/>
-      <c r="F341" s="63"/>
+      <c r="F341" s="5"/>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A342" s="5"/>
@@ -5675,7 +6768,7 @@
       <c r="C342" s="5"/>
       <c r="D342" s="5"/>
       <c r="E342" s="5"/>
-      <c r="F342" s="63"/>
+      <c r="F342" s="5"/>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A343" s="5"/>
@@ -5683,7 +6776,7 @@
       <c r="C343" s="5"/>
       <c r="D343" s="5"/>
       <c r="E343" s="5"/>
-      <c r="F343" s="63"/>
+      <c r="F343" s="5"/>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A344" s="5"/>
@@ -5691,7 +6784,7 @@
       <c r="C344" s="5"/>
       <c r="D344" s="5"/>
       <c r="E344" s="5"/>
-      <c r="F344" s="63"/>
+      <c r="F344" s="5"/>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A345" s="5"/>
@@ -5699,7 +6792,7 @@
       <c r="C345" s="5"/>
       <c r="D345" s="5"/>
       <c r="E345" s="5"/>
-      <c r="F345" s="63"/>
+      <c r="F345" s="5"/>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A346" s="5"/>
@@ -5707,7 +6800,7 @@
       <c r="C346" s="5"/>
       <c r="D346" s="5"/>
       <c r="E346" s="5"/>
-      <c r="F346" s="63"/>
+      <c r="F346" s="5"/>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A347" s="5"/>
@@ -5715,7 +6808,7 @@
       <c r="C347" s="5"/>
       <c r="D347" s="5"/>
       <c r="E347" s="5"/>
-      <c r="F347" s="63"/>
+      <c r="F347" s="5"/>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A348" s="5"/>
@@ -5723,7 +6816,7 @@
       <c r="C348" s="5"/>
       <c r="D348" s="5"/>
       <c r="E348" s="5"/>
-      <c r="F348" s="63"/>
+      <c r="F348" s="5"/>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A349" s="5"/>
@@ -5731,7 +6824,7 @@
       <c r="C349" s="5"/>
       <c r="D349" s="5"/>
       <c r="E349" s="5"/>
-      <c r="F349" s="63"/>
+      <c r="F349" s="5"/>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A350" s="5"/>
@@ -5739,7 +6832,7 @@
       <c r="C350" s="5"/>
       <c r="D350" s="5"/>
       <c r="E350" s="5"/>
-      <c r="F350" s="63"/>
+      <c r="F350" s="5"/>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A351" s="5"/>
@@ -5747,7 +6840,7 @@
       <c r="C351" s="5"/>
       <c r="D351" s="5"/>
       <c r="E351" s="5"/>
-      <c r="F351" s="63"/>
+      <c r="F351" s="5"/>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A352" s="5"/>
@@ -5755,7 +6848,7 @@
       <c r="C352" s="5"/>
       <c r="D352" s="5"/>
       <c r="E352" s="5"/>
-      <c r="F352" s="63"/>
+      <c r="F352" s="5"/>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A353" s="5"/>
@@ -5763,7 +6856,7 @@
       <c r="C353" s="5"/>
       <c r="D353" s="5"/>
       <c r="E353" s="5"/>
-      <c r="F353" s="63"/>
+      <c r="F353" s="5"/>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A354" s="5"/>
@@ -5771,7 +6864,7 @@
       <c r="C354" s="5"/>
       <c r="D354" s="5"/>
       <c r="E354" s="5"/>
-      <c r="F354" s="63"/>
+      <c r="F354" s="5"/>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A355" s="5"/>
@@ -5779,7 +6872,7 @@
       <c r="C355" s="5"/>
       <c r="D355" s="5"/>
       <c r="E355" s="5"/>
-      <c r="F355" s="63"/>
+      <c r="F355" s="5"/>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A356" s="5"/>
@@ -5787,7 +6880,7 @@
       <c r="C356" s="5"/>
       <c r="D356" s="5"/>
       <c r="E356" s="5"/>
-      <c r="F356" s="63"/>
+      <c r="F356" s="5"/>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A357" s="5"/>
@@ -5795,7 +6888,7 @@
       <c r="C357" s="5"/>
       <c r="D357" s="5"/>
       <c r="E357" s="5"/>
-      <c r="F357" s="63"/>
+      <c r="F357" s="5"/>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A358" s="5"/>
@@ -5803,7 +6896,7 @@
       <c r="C358" s="5"/>
       <c r="D358" s="5"/>
       <c r="E358" s="5"/>
-      <c r="F358" s="63"/>
+      <c r="F358" s="5"/>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A359" s="5"/>
@@ -5811,7 +6904,7 @@
       <c r="C359" s="5"/>
       <c r="D359" s="5"/>
       <c r="E359" s="5"/>
-      <c r="F359" s="63"/>
+      <c r="F359" s="5"/>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A360" s="5"/>
@@ -5819,7 +6912,7 @@
       <c r="C360" s="5"/>
       <c r="D360" s="5"/>
       <c r="E360" s="5"/>
-      <c r="F360" s="63"/>
+      <c r="F360" s="5"/>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A361" s="5"/>
@@ -5827,7 +6920,7 @@
       <c r="C361" s="5"/>
       <c r="D361" s="5"/>
       <c r="E361" s="5"/>
-      <c r="F361" s="63"/>
+      <c r="F361" s="5"/>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A362" s="5"/>
@@ -5835,7 +6928,7 @@
       <c r="C362" s="5"/>
       <c r="D362" s="5"/>
       <c r="E362" s="5"/>
-      <c r="F362" s="63"/>
+      <c r="F362" s="5"/>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A363" s="5"/>
@@ -5843,7 +6936,7 @@
       <c r="C363" s="5"/>
       <c r="D363" s="5"/>
       <c r="E363" s="5"/>
-      <c r="F363" s="63"/>
+      <c r="F363" s="5"/>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A364" s="5"/>
@@ -5851,7 +6944,7 @@
       <c r="C364" s="5"/>
       <c r="D364" s="5"/>
       <c r="E364" s="5"/>
-      <c r="F364" s="63"/>
+      <c r="F364" s="5"/>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A365" s="5"/>
@@ -5859,7 +6952,7 @@
       <c r="C365" s="5"/>
       <c r="D365" s="5"/>
       <c r="E365" s="5"/>
-      <c r="F365" s="63"/>
+      <c r="F365" s="5"/>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A366" s="5"/>
@@ -5867,7 +6960,7 @@
       <c r="C366" s="5"/>
       <c r="D366" s="5"/>
       <c r="E366" s="5"/>
-      <c r="F366" s="63"/>
+      <c r="F366" s="5"/>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A367" s="5"/>
@@ -5875,7 +6968,7 @@
       <c r="C367" s="5"/>
       <c r="D367" s="5"/>
       <c r="E367" s="5"/>
-      <c r="F367" s="63"/>
+      <c r="F367" s="5"/>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A368" s="5"/>
@@ -5883,7 +6976,7 @@
       <c r="C368" s="5"/>
       <c r="D368" s="5"/>
       <c r="E368" s="5"/>
-      <c r="F368" s="63"/>
+      <c r="F368" s="5"/>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A369" s="5"/>
@@ -5891,7 +6984,7 @@
       <c r="C369" s="5"/>
       <c r="D369" s="5"/>
       <c r="E369" s="5"/>
-      <c r="F369" s="63"/>
+      <c r="F369" s="5"/>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A370" s="5"/>
@@ -5899,7 +6992,7 @@
       <c r="C370" s="5"/>
       <c r="D370" s="5"/>
       <c r="E370" s="5"/>
-      <c r="F370" s="63"/>
+      <c r="F370" s="5"/>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A371" s="5"/>
@@ -5907,7 +7000,7 @@
       <c r="C371" s="5"/>
       <c r="D371" s="5"/>
       <c r="E371" s="5"/>
-      <c r="F371" s="63"/>
+      <c r="F371" s="5"/>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A372" s="5"/>
@@ -5915,7 +7008,7 @@
       <c r="C372" s="5"/>
       <c r="D372" s="5"/>
       <c r="E372" s="5"/>
-      <c r="F372" s="63"/>
+      <c r="F372" s="5"/>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A373" s="5"/>
@@ -5923,7 +7016,7 @@
       <c r="C373" s="5"/>
       <c r="D373" s="5"/>
       <c r="E373" s="5"/>
-      <c r="F373" s="63"/>
+      <c r="F373" s="5"/>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A374" s="5"/>
@@ -5931,7 +7024,7 @@
       <c r="C374" s="5"/>
       <c r="D374" s="5"/>
       <c r="E374" s="5"/>
-      <c r="F374" s="63"/>
+      <c r="F374" s="5"/>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A375" s="5"/>
@@ -5939,7 +7032,7 @@
       <c r="C375" s="5"/>
       <c r="D375" s="5"/>
       <c r="E375" s="5"/>
-      <c r="F375" s="63"/>
+      <c r="F375" s="5"/>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A376" s="5"/>
@@ -5947,7 +7040,7 @@
       <c r="C376" s="5"/>
       <c r="D376" s="5"/>
       <c r="E376" s="5"/>
-      <c r="F376" s="63"/>
+      <c r="F376" s="5"/>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A377" s="5"/>
@@ -5955,7 +7048,7 @@
       <c r="C377" s="5"/>
       <c r="D377" s="5"/>
       <c r="E377" s="5"/>
-      <c r="F377" s="63"/>
+      <c r="F377" s="5"/>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A378" s="5"/>
@@ -5963,7 +7056,7 @@
       <c r="C378" s="5"/>
       <c r="D378" s="5"/>
       <c r="E378" s="5"/>
-      <c r="F378" s="63"/>
+      <c r="F378" s="5"/>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A379" s="5"/>
@@ -5971,7 +7064,7 @@
       <c r="C379" s="5"/>
       <c r="D379" s="5"/>
       <c r="E379" s="5"/>
-      <c r="F379" s="63"/>
+      <c r="F379" s="5"/>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A380" s="5"/>
@@ -5979,7 +7072,7 @@
       <c r="C380" s="5"/>
       <c r="D380" s="5"/>
       <c r="E380" s="5"/>
-      <c r="F380" s="63"/>
+      <c r="F380" s="5"/>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A381" s="5"/>
@@ -5987,7 +7080,7 @@
       <c r="C381" s="5"/>
       <c r="D381" s="5"/>
       <c r="E381" s="5"/>
-      <c r="F381" s="63"/>
+      <c r="F381" s="5"/>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A382" s="5"/>
@@ -5995,7 +7088,7 @@
       <c r="C382" s="5"/>
       <c r="D382" s="5"/>
       <c r="E382" s="5"/>
-      <c r="F382" s="63"/>
+      <c r="F382" s="5"/>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A383" s="5"/>
@@ -6003,7 +7096,7 @@
       <c r="C383" s="5"/>
       <c r="D383" s="5"/>
       <c r="E383" s="5"/>
-      <c r="F383" s="63"/>
+      <c r="F383" s="5"/>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A384" s="5"/>
@@ -6011,7 +7104,7 @@
       <c r="C384" s="5"/>
       <c r="D384" s="5"/>
       <c r="E384" s="5"/>
-      <c r="F384" s="63"/>
+      <c r="F384" s="5"/>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A385" s="5"/>
@@ -6019,7 +7112,7 @@
       <c r="C385" s="5"/>
       <c r="D385" s="5"/>
       <c r="E385" s="5"/>
-      <c r="F385" s="63"/>
+      <c r="F385" s="5"/>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A386" s="5"/>
@@ -6027,7 +7120,7 @@
       <c r="C386" s="5"/>
       <c r="D386" s="5"/>
       <c r="E386" s="5"/>
-      <c r="F386" s="63"/>
+      <c r="F386" s="5"/>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A387" s="5"/>
@@ -6035,7 +7128,7 @@
       <c r="C387" s="5"/>
       <c r="D387" s="5"/>
       <c r="E387" s="5"/>
-      <c r="F387" s="63"/>
+      <c r="F387" s="5"/>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A388" s="5"/>
@@ -6043,7 +7136,7 @@
       <c r="C388" s="5"/>
       <c r="D388" s="5"/>
       <c r="E388" s="5"/>
-      <c r="F388" s="63"/>
+      <c r="F388" s="5"/>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A389" s="5"/>
@@ -6051,7 +7144,7 @@
       <c r="C389" s="5"/>
       <c r="D389" s="5"/>
       <c r="E389" s="5"/>
-      <c r="F389" s="63"/>
+      <c r="F389" s="5"/>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A390" s="5"/>
@@ -6059,7 +7152,7 @@
       <c r="C390" s="5"/>
       <c r="D390" s="5"/>
       <c r="E390" s="5"/>
-      <c r="F390" s="63"/>
+      <c r="F390" s="5"/>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A391" s="5"/>
@@ -6067,7 +7160,7 @@
       <c r="C391" s="5"/>
       <c r="D391" s="5"/>
       <c r="E391" s="5"/>
-      <c r="F391" s="63"/>
+      <c r="F391" s="5"/>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A392" s="5"/>
@@ -6075,7 +7168,7 @@
       <c r="C392" s="5"/>
       <c r="D392" s="5"/>
       <c r="E392" s="5"/>
-      <c r="F392" s="63"/>
+      <c r="F392" s="5"/>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A393" s="5"/>
@@ -6083,7 +7176,7 @@
       <c r="C393" s="5"/>
       <c r="D393" s="5"/>
       <c r="E393" s="5"/>
-      <c r="F393" s="63"/>
+      <c r="F393" s="5"/>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A394" s="5"/>
@@ -6091,7 +7184,7 @@
       <c r="C394" s="5"/>
       <c r="D394" s="5"/>
       <c r="E394" s="5"/>
-      <c r="F394" s="63"/>
+      <c r="F394" s="5"/>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A395" s="5"/>
@@ -6099,7 +7192,7 @@
       <c r="C395" s="5"/>
       <c r="D395" s="5"/>
       <c r="E395" s="5"/>
-      <c r="F395" s="63"/>
+      <c r="F395" s="5"/>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A396" s="5"/>
@@ -6107,7 +7200,7 @@
       <c r="C396" s="5"/>
       <c r="D396" s="5"/>
       <c r="E396" s="5"/>
-      <c r="F396" s="63"/>
+      <c r="F396" s="5"/>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A397" s="5"/>
@@ -6115,7 +7208,7 @@
       <c r="C397" s="5"/>
       <c r="D397" s="5"/>
       <c r="E397" s="5"/>
-      <c r="F397" s="63"/>
+      <c r="F397" s="5"/>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A398" s="5"/>
@@ -6123,7 +7216,7 @@
       <c r="C398" s="5"/>
       <c r="D398" s="5"/>
       <c r="E398" s="5"/>
-      <c r="F398" s="63"/>
+      <c r="F398" s="5"/>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A399" s="5"/>
@@ -6131,7 +7224,7 @@
       <c r="C399" s="5"/>
       <c r="D399" s="5"/>
       <c r="E399" s="5"/>
-      <c r="F399" s="63"/>
+      <c r="F399" s="5"/>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A400" s="5"/>
@@ -6139,7 +7232,7 @@
       <c r="C400" s="5"/>
       <c r="D400" s="5"/>
       <c r="E400" s="5"/>
-      <c r="F400" s="63"/>
+      <c r="F400" s="5"/>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A401" s="5"/>
@@ -6147,7 +7240,7 @@
       <c r="C401" s="5"/>
       <c r="D401" s="5"/>
       <c r="E401" s="5"/>
-      <c r="F401" s="63"/>
+      <c r="F401" s="5"/>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A402" s="5"/>
@@ -6155,7 +7248,7 @@
       <c r="C402" s="5"/>
       <c r="D402" s="5"/>
       <c r="E402" s="5"/>
-      <c r="F402" s="63"/>
+      <c r="F402" s="5"/>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A403" s="5"/>
@@ -6163,7 +7256,7 @@
       <c r="C403" s="5"/>
       <c r="D403" s="5"/>
       <c r="E403" s="5"/>
-      <c r="F403" s="63"/>
+      <c r="F403" s="5"/>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A404" s="5"/>
@@ -6171,7 +7264,7 @@
       <c r="C404" s="5"/>
       <c r="D404" s="5"/>
       <c r="E404" s="5"/>
-      <c r="F404" s="63"/>
+      <c r="F404" s="5"/>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A405" s="5"/>
@@ -6179,7 +7272,7 @@
       <c r="C405" s="5"/>
       <c r="D405" s="5"/>
       <c r="E405" s="5"/>
-      <c r="F405" s="63"/>
+      <c r="F405" s="5"/>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A406" s="5"/>
@@ -6187,7 +7280,7 @@
       <c r="C406" s="5"/>
       <c r="D406" s="5"/>
       <c r="E406" s="5"/>
-      <c r="F406" s="63"/>
+      <c r="F406" s="5"/>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A407" s="5"/>
@@ -6195,7 +7288,7 @@
       <c r="C407" s="5"/>
       <c r="D407" s="5"/>
       <c r="E407" s="5"/>
-      <c r="F407" s="63"/>
+      <c r="F407" s="5"/>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A408" s="5"/>
@@ -6203,7 +7296,7 @@
       <c r="C408" s="5"/>
       <c r="D408" s="5"/>
       <c r="E408" s="5"/>
-      <c r="F408" s="63"/>
+      <c r="F408" s="5"/>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A409" s="5"/>
@@ -6211,7 +7304,7 @@
       <c r="C409" s="5"/>
       <c r="D409" s="5"/>
       <c r="E409" s="5"/>
-      <c r="F409" s="63"/>
+      <c r="F409" s="5"/>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A410" s="5"/>
@@ -6219,7 +7312,7 @@
       <c r="C410" s="5"/>
       <c r="D410" s="5"/>
       <c r="E410" s="5"/>
-      <c r="F410" s="63"/>
+      <c r="F410" s="5"/>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A411" s="5"/>
@@ -6227,7 +7320,7 @@
       <c r="C411" s="5"/>
       <c r="D411" s="5"/>
       <c r="E411" s="5"/>
-      <c r="F411" s="63"/>
+      <c r="F411" s="5"/>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A412" s="5"/>
@@ -6235,7 +7328,7 @@
       <c r="C412" s="5"/>
       <c r="D412" s="5"/>
       <c r="E412" s="5"/>
-      <c r="F412" s="63"/>
+      <c r="F412" s="5"/>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A413" s="5"/>
@@ -6243,7 +7336,7 @@
       <c r="C413" s="5"/>
       <c r="D413" s="5"/>
       <c r="E413" s="5"/>
-      <c r="F413" s="63"/>
+      <c r="F413" s="5"/>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A414" s="5"/>
@@ -6251,7 +7344,7 @@
       <c r="C414" s="5"/>
       <c r="D414" s="5"/>
       <c r="E414" s="5"/>
-      <c r="F414" s="63"/>
+      <c r="F414" s="5"/>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A415" s="5"/>
@@ -6259,7 +7352,7 @@
       <c r="C415" s="5"/>
       <c r="D415" s="5"/>
       <c r="E415" s="5"/>
-      <c r="F415" s="63"/>
+      <c r="F415" s="5"/>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A416" s="5"/>
@@ -6267,7 +7360,7 @@
       <c r="C416" s="5"/>
       <c r="D416" s="5"/>
       <c r="E416" s="5"/>
-      <c r="F416" s="63"/>
+      <c r="F416" s="5"/>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A417" s="5"/>
@@ -6275,7 +7368,7 @@
       <c r="C417" s="5"/>
       <c r="D417" s="5"/>
       <c r="E417" s="5"/>
-      <c r="F417" s="63"/>
+      <c r="F417" s="5"/>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A418" s="5"/>
@@ -6283,7 +7376,7 @@
       <c r="C418" s="5"/>
       <c r="D418" s="5"/>
       <c r="E418" s="5"/>
-      <c r="F418" s="63"/>
+      <c r="F418" s="5"/>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A419" s="5"/>
@@ -6291,7 +7384,7 @@
       <c r="C419" s="5"/>
       <c r="D419" s="5"/>
       <c r="E419" s="5"/>
-      <c r="F419" s="63"/>
+      <c r="F419" s="5"/>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A420" s="5"/>
@@ -6299,7 +7392,7 @@
       <c r="C420" s="5"/>
       <c r="D420" s="5"/>
       <c r="E420" s="5"/>
-      <c r="F420" s="63"/>
+      <c r="F420" s="5"/>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A421" s="5"/>
@@ -6307,7 +7400,7 @@
       <c r="C421" s="5"/>
       <c r="D421" s="5"/>
       <c r="E421" s="5"/>
-      <c r="F421" s="63"/>
+      <c r="F421" s="5"/>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A422" s="5"/>
@@ -6315,7 +7408,7 @@
       <c r="C422" s="5"/>
       <c r="D422" s="5"/>
       <c r="E422" s="5"/>
-      <c r="F422" s="63"/>
+      <c r="F422" s="5"/>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A423" s="5"/>
@@ -6323,7 +7416,7 @@
       <c r="C423" s="5"/>
       <c r="D423" s="5"/>
       <c r="E423" s="5"/>
-      <c r="F423" s="63"/>
+      <c r="F423" s="5"/>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A424" s="5"/>
@@ -6331,7 +7424,7 @@
       <c r="C424" s="5"/>
       <c r="D424" s="5"/>
       <c r="E424" s="5"/>
-      <c r="F424" s="63"/>
+      <c r="F424" s="5"/>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A425" s="5"/>
@@ -6339,7 +7432,7 @@
       <c r="C425" s="5"/>
       <c r="D425" s="5"/>
       <c r="E425" s="5"/>
-      <c r="F425" s="63"/>
+      <c r="F425" s="5"/>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A426" s="5"/>
@@ -6347,7 +7440,7 @@
       <c r="C426" s="5"/>
       <c r="D426" s="5"/>
       <c r="E426" s="5"/>
-      <c r="F426" s="63"/>
+      <c r="F426" s="5"/>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A427" s="5"/>
@@ -6355,7 +7448,7 @@
       <c r="C427" s="5"/>
       <c r="D427" s="5"/>
       <c r="E427" s="5"/>
-      <c r="F427" s="63"/>
+      <c r="F427" s="5"/>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A428" s="5"/>
@@ -6363,7 +7456,7 @@
       <c r="C428" s="5"/>
       <c r="D428" s="5"/>
       <c r="E428" s="5"/>
-      <c r="F428" s="63"/>
+      <c r="F428" s="5"/>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A429" s="5"/>
@@ -6371,7 +7464,7 @@
       <c r="C429" s="5"/>
       <c r="D429" s="5"/>
       <c r="E429" s="5"/>
-      <c r="F429" s="63"/>
+      <c r="F429" s="5"/>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A430" s="5"/>
@@ -6379,7 +7472,7 @@
       <c r="C430" s="5"/>
       <c r="D430" s="5"/>
       <c r="E430" s="5"/>
-      <c r="F430" s="63"/>
+      <c r="F430" s="5"/>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A431" s="5"/>
@@ -6387,7 +7480,7 @@
       <c r="C431" s="5"/>
       <c r="D431" s="5"/>
       <c r="E431" s="5"/>
-      <c r="F431" s="63"/>
+      <c r="F431" s="5"/>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A432" s="5"/>
@@ -6395,7 +7488,7 @@
       <c r="C432" s="5"/>
       <c r="D432" s="5"/>
       <c r="E432" s="5"/>
-      <c r="F432" s="63"/>
+      <c r="F432" s="5"/>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A433" s="5"/>
@@ -6403,7 +7496,7 @@
       <c r="C433" s="5"/>
       <c r="D433" s="5"/>
       <c r="E433" s="5"/>
-      <c r="F433" s="63"/>
+      <c r="F433" s="5"/>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A434" s="5"/>
@@ -6411,7 +7504,7 @@
       <c r="C434" s="5"/>
       <c r="D434" s="5"/>
       <c r="E434" s="5"/>
-      <c r="F434" s="63"/>
+      <c r="F434" s="5"/>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A435" s="5"/>
@@ -6419,7 +7512,7 @@
       <c r="C435" s="5"/>
       <c r="D435" s="5"/>
       <c r="E435" s="5"/>
-      <c r="F435" s="63"/>
+      <c r="F435" s="5"/>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A436" s="5"/>
@@ -6427,7 +7520,7 @@
       <c r="C436" s="5"/>
       <c r="D436" s="5"/>
       <c r="E436" s="5"/>
-      <c r="F436" s="63"/>
+      <c r="F436" s="5"/>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A437" s="5"/>
@@ -6435,7 +7528,7 @@
       <c r="C437" s="5"/>
       <c r="D437" s="5"/>
       <c r="E437" s="5"/>
-      <c r="F437" s="63"/>
+      <c r="F437" s="5"/>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A438" s="5"/>
@@ -6443,7 +7536,7 @@
       <c r="C438" s="5"/>
       <c r="D438" s="5"/>
       <c r="E438" s="5"/>
-      <c r="F438" s="63"/>
+      <c r="F438" s="5"/>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A439" s="5"/>
@@ -6451,7 +7544,7 @@
       <c r="C439" s="5"/>
       <c r="D439" s="5"/>
       <c r="E439" s="5"/>
-      <c r="F439" s="63"/>
+      <c r="F439" s="5"/>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A440" s="5"/>
@@ -6459,7 +7552,7 @@
       <c r="C440" s="5"/>
       <c r="D440" s="5"/>
       <c r="E440" s="5"/>
-      <c r="F440" s="63"/>
+      <c r="F440" s="5"/>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A441" s="5"/>
@@ -6467,7 +7560,7 @@
       <c r="C441" s="5"/>
       <c r="D441" s="5"/>
       <c r="E441" s="5"/>
-      <c r="F441" s="63"/>
+      <c r="F441" s="5"/>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A442" s="5"/>
@@ -6475,7 +7568,7 @@
       <c r="C442" s="5"/>
       <c r="D442" s="5"/>
       <c r="E442" s="5"/>
-      <c r="F442" s="63"/>
+      <c r="F442" s="5"/>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A443" s="5"/>
@@ -6483,7 +7576,7 @@
       <c r="C443" s="5"/>
       <c r="D443" s="5"/>
       <c r="E443" s="5"/>
-      <c r="F443" s="63"/>
+      <c r="F443" s="5"/>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A444" s="5"/>
@@ -6491,7 +7584,7 @@
       <c r="C444" s="5"/>
       <c r="D444" s="5"/>
       <c r="E444" s="5"/>
-      <c r="F444" s="63"/>
+      <c r="F444" s="5"/>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A445" s="5"/>
@@ -6499,7 +7592,7 @@
       <c r="C445" s="5"/>
       <c r="D445" s="5"/>
       <c r="E445" s="5"/>
-      <c r="F445" s="63"/>
+      <c r="F445" s="5"/>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A446" s="5"/>
@@ -6507,7 +7600,7 @@
       <c r="C446" s="5"/>
       <c r="D446" s="5"/>
       <c r="E446" s="5"/>
-      <c r="F446" s="63"/>
+      <c r="F446" s="5"/>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A447" s="5"/>
@@ -6515,7 +7608,7 @@
       <c r="C447" s="5"/>
       <c r="D447" s="5"/>
       <c r="E447" s="5"/>
-      <c r="F447" s="63"/>
+      <c r="F447" s="5"/>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A448" s="5"/>
@@ -6523,7 +7616,7 @@
       <c r="C448" s="5"/>
       <c r="D448" s="5"/>
       <c r="E448" s="5"/>
-      <c r="F448" s="63"/>
+      <c r="F448" s="5"/>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A449" s="5"/>
@@ -6531,7 +7624,7 @@
       <c r="C449" s="5"/>
       <c r="D449" s="5"/>
       <c r="E449" s="5"/>
-      <c r="F449" s="63"/>
+      <c r="F449" s="5"/>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A450" s="2"/>

--- a/prix/prix.xlsx
+++ b/prix/prix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\robinetterie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10D42F5D-4B24-4341-A64B-1FC74BD10BD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{205706CF-B90B-4D88-BCE1-E9F2439B2F52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="23124" yWindow="12" windowWidth="19116" windowHeight="10884" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -1722,7 +1722,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1831,6 +1831,12 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -3237,14 +3243,14 @@
       <c r="B53" s="29" t="s">
         <v>188</v>
       </c>
-      <c r="D53" s="11">
+      <c r="D53" s="38">
         <v>363</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="F53" s="28">
-        <v>1</v>
+      <c r="F53" s="39">
+        <v>3</v>
       </c>
       <c r="G53" s="9" t="s">
         <v>229</v>
@@ -3257,14 +3263,14 @@
       <c r="B54" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="D54" s="11">
+      <c r="D54" s="38">
         <v>217.8</v>
       </c>
       <c r="E54" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="F54" s="28">
-        <v>1</v>
+      <c r="F54" s="39">
+        <v>3</v>
       </c>
       <c r="G54" s="9" t="s">
         <v>230</v>
@@ -3277,14 +3283,14 @@
       <c r="B55" s="29" t="s">
         <v>190</v>
       </c>
-      <c r="D55" s="11">
+      <c r="D55" s="38">
         <v>411.40000000000003</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="F55" s="28">
-        <v>1</v>
+      <c r="F55" s="39">
+        <v>3</v>
       </c>
       <c r="G55" s="9" t="s">
         <v>231</v>
@@ -3297,14 +3303,14 @@
       <c r="B56" s="29" t="s">
         <v>191</v>
       </c>
-      <c r="D56" s="11">
+      <c r="D56" s="38">
         <v>96.8</v>
       </c>
       <c r="E56" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="F56" s="28">
-        <v>1</v>
+      <c r="F56" s="39">
+        <v>3</v>
       </c>
       <c r="G56" s="9" t="s">
         <v>232</v>
@@ -3317,14 +3323,14 @@
       <c r="B57" s="29" t="s">
         <v>192</v>
       </c>
-      <c r="D57" s="11">
+      <c r="D57" s="38">
         <v>96.8</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="F57" s="28">
-        <v>1</v>
+      <c r="F57" s="39">
+        <v>3</v>
       </c>
       <c r="G57" s="9" t="s">
         <v>233</v>
@@ -3337,14 +3343,14 @@
       <c r="B58" s="29" t="s">
         <v>193</v>
       </c>
-      <c r="D58" s="11">
+      <c r="D58" s="38">
         <v>84.7</v>
       </c>
       <c r="E58" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="F58" s="28">
-        <v>1</v>
+      <c r="F58" s="39">
+        <v>3</v>
       </c>
       <c r="G58" s="9" t="s">
         <v>234</v>
@@ -3357,13 +3363,13 @@
       <c r="B59" s="29" t="s">
         <v>194</v>
       </c>
-      <c r="D59" s="11">
-        <v>53.24</v>
+      <c r="D59" s="38">
+        <v>411.40000000000003</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="F59" s="28">
+      <c r="F59" s="39">
         <v>1</v>
       </c>
       <c r="G59" s="9" t="s">
@@ -3378,14 +3384,14 @@
         <v>195</v>
       </c>
       <c r="C60" s="5"/>
-      <c r="D60" s="11">
-        <v>66.55</v>
+      <c r="D60" s="38">
+        <v>53.24</v>
       </c>
       <c r="E60" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="F60" s="28">
-        <v>1</v>
+      <c r="F60" s="39">
+        <v>3</v>
       </c>
       <c r="G60" s="9" t="s">
         <v>236</v>
@@ -3399,14 +3405,14 @@
         <v>196</v>
       </c>
       <c r="C61" s="5"/>
-      <c r="D61" s="11">
-        <v>84.7</v>
+      <c r="D61" s="38">
+        <v>66.55</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="F61" s="28">
-        <v>1</v>
+      <c r="F61" s="39">
+        <v>3</v>
       </c>
       <c r="G61" s="9" t="s">
         <v>237</v>
@@ -3420,14 +3426,14 @@
         <v>197</v>
       </c>
       <c r="C62" s="5"/>
-      <c r="D62" s="11">
-        <v>96.8</v>
+      <c r="D62" s="38">
+        <v>84.7</v>
       </c>
       <c r="E62" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="F62" s="28">
-        <v>1</v>
+      <c r="F62" s="39">
+        <v>3</v>
       </c>
       <c r="G62" s="9" t="s">
         <v>238</v>
@@ -3440,14 +3446,14 @@
       <c r="B63" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="D63" s="11">
-        <v>78.650000000000006</v>
+      <c r="D63" s="38">
+        <v>96.8</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="F63" s="28">
-        <v>1</v>
+      <c r="F63" s="39">
+        <v>3</v>
       </c>
       <c r="G63" s="9" t="s">
         <v>239</v>
@@ -3460,14 +3466,14 @@
       <c r="B64" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="D64" s="11">
-        <v>133.1</v>
+      <c r="D64" s="38">
+        <v>78.650000000000006</v>
       </c>
       <c r="E64" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="F64" s="28">
-        <v>1</v>
+      <c r="F64" s="39">
+        <v>3</v>
       </c>
       <c r="G64" s="9" t="s">
         <v>240</v>
@@ -3480,14 +3486,14 @@
       <c r="B65" s="29" t="s">
         <v>200</v>
       </c>
-      <c r="D65" s="11">
-        <v>145.20000000000002</v>
+      <c r="D65" s="38">
+        <v>133.1</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="F65" s="28">
-        <v>1</v>
+      <c r="F65" s="39">
+        <v>3</v>
       </c>
       <c r="G65" s="9" t="s">
         <v>241</v>
@@ -3500,14 +3506,14 @@
       <c r="B66" s="29" t="s">
         <v>201</v>
       </c>
-      <c r="D66" s="11">
-        <v>102.85000000000001</v>
+      <c r="D66" s="38">
+        <v>145.20000000000002</v>
       </c>
       <c r="E66" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="F66" s="28">
-        <v>1</v>
+      <c r="F66" s="39">
+        <v>3</v>
       </c>
       <c r="G66" s="9" t="s">
         <v>242</v>
@@ -3520,14 +3526,14 @@
       <c r="B67" s="29" t="s">
         <v>202</v>
       </c>
-      <c r="D67" s="11">
-        <v>169.4</v>
+      <c r="D67" s="38">
+        <v>102.85000000000001</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="F67" s="28">
-        <v>1</v>
+      <c r="F67" s="39">
+        <v>3</v>
       </c>
       <c r="G67" s="9" t="s">
         <v>243</v>
@@ -3540,14 +3546,14 @@
       <c r="B68" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="D68" s="11">
-        <v>181.5</v>
+      <c r="D68" s="38">
+        <v>169.4</v>
       </c>
       <c r="E68" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="F68" s="28">
-        <v>1</v>
+      <c r="F68" s="39">
+        <v>3</v>
       </c>
       <c r="G68" s="9" t="s">
         <v>244</v>
@@ -3560,14 +3566,14 @@
       <c r="B69" s="29" t="s">
         <v>204</v>
       </c>
-      <c r="D69" s="11">
-        <v>121</v>
+      <c r="D69" s="38">
+        <v>181.5</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="F69" s="28">
-        <v>1</v>
+      <c r="F69" s="39">
+        <v>3</v>
       </c>
       <c r="G69" s="9" t="s">
         <v>245</v>
@@ -3580,14 +3586,14 @@
       <c r="B70" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="D70" s="11">
-        <v>133.1</v>
+      <c r="D70" s="38">
+        <v>121</v>
       </c>
       <c r="E70" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="F70" s="28">
-        <v>1</v>
+      <c r="F70" s="39">
+        <v>3</v>
       </c>
       <c r="G70" s="9" t="s">
         <v>246</v>
@@ -3600,14 +3606,14 @@
       <c r="B71" s="29" t="s">
         <v>204</v>
       </c>
-      <c r="D71" s="11">
-        <v>121</v>
+      <c r="D71" s="38">
+        <v>133.1</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="F71" s="28">
-        <v>1</v>
+      <c r="F71" s="39">
+        <v>3</v>
       </c>
       <c r="G71" s="9" t="s">
         <v>247</v>
@@ -3620,14 +3626,14 @@
       <c r="B72" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="D72" s="11">
-        <v>133.1</v>
+      <c r="D72" s="38">
+        <v>121</v>
       </c>
       <c r="E72" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="F72" s="28">
-        <v>1</v>
+      <c r="F72" s="39">
+        <v>3</v>
       </c>
       <c r="G72" s="9" t="s">
         <v>248</v>
@@ -3640,14 +3646,14 @@
       <c r="B73" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="D73" s="11">
-        <v>145.20000000000002</v>
+      <c r="D73" s="38">
+        <v>133.1</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="F73" s="28">
-        <v>1</v>
+      <c r="F73" s="39">
+        <v>3</v>
       </c>
       <c r="G73" s="9" t="s">
         <v>249</v>
@@ -3660,13 +3666,13 @@
       <c r="B74" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D74" s="11">
-        <v>157.30000000000001</v>
+      <c r="D74" s="38">
+        <v>145.20000000000002</v>
       </c>
       <c r="E74" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="F74" s="28">
+      <c r="F74" s="39">
         <v>1</v>
       </c>
       <c r="G74" s="9" t="s">
@@ -3680,14 +3686,14 @@
       <c r="B75" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="D75" s="11">
-        <v>53.24</v>
+      <c r="D75" s="38">
+        <v>157.30000000000001</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="F75" s="28">
-        <v>1</v>
+      <c r="F75" s="39">
+        <v>3</v>
       </c>
       <c r="G75" s="9" t="s">
         <v>251</v>
@@ -3700,14 +3706,14 @@
       <c r="B76" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="D76" s="11">
-        <v>84.7</v>
+      <c r="D76" s="38">
+        <v>53.24</v>
       </c>
       <c r="E76" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="F76" s="28">
-        <v>1</v>
+      <c r="F76" s="39">
+        <v>3</v>
       </c>
       <c r="G76" s="9" t="s">
         <v>252</v>
@@ -3720,14 +3726,14 @@
       <c r="B77" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="D77" s="11">
-        <v>72.600000000000009</v>
+      <c r="D77" s="38">
+        <v>84.7</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="F77" s="28">
-        <v>1</v>
+      <c r="F77" s="39">
+        <v>3</v>
       </c>
       <c r="G77" s="9" t="s">
         <v>253</v>
@@ -3740,14 +3746,14 @@
       <c r="B78" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="D78" s="11">
-        <v>53.24</v>
+      <c r="D78" s="38">
+        <v>72.600000000000009</v>
       </c>
       <c r="E78" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="F78" s="28">
-        <v>1</v>
+      <c r="F78" s="39">
+        <v>3</v>
       </c>
       <c r="G78" s="9" t="s">
         <v>254</v>
@@ -3760,14 +3766,14 @@
       <c r="B79" s="29" t="s">
         <v>212</v>
       </c>
-      <c r="D79" s="11">
-        <v>60.5</v>
+      <c r="D79" s="38">
+        <v>53.24</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="F79" s="28">
-        <v>1</v>
+      <c r="F79" s="39">
+        <v>3</v>
       </c>
       <c r="G79" s="9" t="s">
         <v>255</v>
@@ -3780,14 +3786,14 @@
       <c r="B80" s="29" t="s">
         <v>213</v>
       </c>
-      <c r="D80" s="11">
-        <v>66.55</v>
+      <c r="D80" s="38">
+        <v>60.5</v>
       </c>
       <c r="E80" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="F80" s="28">
-        <v>1</v>
+      <c r="F80" s="39">
+        <v>3</v>
       </c>
       <c r="G80" s="9" t="s">
         <v>256</v>
@@ -3800,14 +3806,14 @@
       <c r="B81" s="29" t="s">
         <v>214</v>
       </c>
-      <c r="D81" s="11">
-        <v>90.75</v>
+      <c r="D81" s="38">
+        <v>66.55</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="F81" s="28">
-        <v>1</v>
+      <c r="F81" s="39">
+        <v>3</v>
       </c>
       <c r="G81" s="9" t="s">
         <v>257</v>
@@ -3820,14 +3826,14 @@
       <c r="B82" s="29" t="s">
         <v>215</v>
       </c>
-      <c r="D82" s="11">
-        <v>102.85000000000001</v>
+      <c r="D82" s="38">
+        <v>90.75</v>
       </c>
       <c r="E82" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="F82" s="28">
-        <v>1</v>
+      <c r="F82" s="39">
+        <v>3</v>
       </c>
       <c r="G82" s="9" t="s">
         <v>258</v>
@@ -3841,14 +3847,14 @@
         <v>216</v>
       </c>
       <c r="C83" s="5"/>
-      <c r="D83" s="11">
-        <v>133.1</v>
+      <c r="D83" s="38">
+        <v>102.85000000000001</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="F83" s="28">
-        <v>1</v>
+      <c r="F83" s="39">
+        <v>3</v>
       </c>
       <c r="G83" s="9" t="s">
         <v>259</v>
@@ -3862,14 +3868,14 @@
         <v>217</v>
       </c>
       <c r="C84" s="5"/>
-      <c r="D84" s="11">
+      <c r="D84" s="38">
         <v>133.1</v>
       </c>
       <c r="E84" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="F84" s="28">
-        <v>1</v>
+      <c r="F84" s="39">
+        <v>3</v>
       </c>
       <c r="G84" s="9" t="s">
         <v>260</v>
@@ -3883,14 +3889,14 @@
         <v>218</v>
       </c>
       <c r="C85" s="5"/>
-      <c r="D85" s="11">
-        <v>193.6</v>
+      <c r="D85" s="38">
+        <v>133.1</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="F85" s="28">
-        <v>1</v>
+      <c r="F85" s="39">
+        <v>3</v>
       </c>
       <c r="G85" s="9" t="s">
         <v>261</v>
@@ -3904,14 +3910,14 @@
         <v>219</v>
       </c>
       <c r="C86" s="5"/>
-      <c r="D86" s="11">
-        <v>157.30000000000001</v>
+      <c r="D86" s="38">
+        <v>193.6</v>
       </c>
       <c r="E86" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="F86" s="28">
-        <v>1</v>
+      <c r="F86" s="39">
+        <v>3</v>
       </c>
       <c r="G86" s="9" t="s">
         <v>262</v>
@@ -3925,14 +3931,14 @@
         <v>220</v>
       </c>
       <c r="C87" s="5"/>
-      <c r="D87" s="11">
-        <v>114.95</v>
+      <c r="D87" s="38">
+        <v>157.30000000000001</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="F87" s="28">
-        <v>1</v>
+      <c r="F87" s="39">
+        <v>3</v>
       </c>
       <c r="G87" s="9" t="s">
         <v>263</v>
@@ -3946,14 +3952,14 @@
         <v>221</v>
       </c>
       <c r="C88" s="5"/>
-      <c r="D88" s="11">
-        <v>90.75</v>
+      <c r="D88" s="38">
+        <v>114.95</v>
       </c>
       <c r="E88" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="F88" s="28">
-        <v>1</v>
+      <c r="F88" s="39">
+        <v>3</v>
       </c>
       <c r="G88" s="9" t="s">
         <v>264</v>
@@ -3967,14 +3973,14 @@
         <v>222</v>
       </c>
       <c r="C89" s="5"/>
-      <c r="D89" s="11">
-        <v>96.8</v>
+      <c r="D89" s="38">
+        <v>90.75</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F89" s="28">
-        <v>1</v>
+      <c r="F89" s="39">
+        <v>3</v>
       </c>
       <c r="G89" s="9" t="s">
         <v>265</v>
@@ -3988,14 +3994,14 @@
         <v>223</v>
       </c>
       <c r="C90" s="5"/>
-      <c r="D90" s="11">
-        <v>133.1</v>
+      <c r="D90" s="38">
+        <v>96.8</v>
       </c>
       <c r="E90" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="F90" s="28">
-        <v>1</v>
+      <c r="F90" s="39">
+        <v>3</v>
       </c>
       <c r="G90" s="9" t="s">
         <v>266</v>
@@ -4009,14 +4015,14 @@
         <v>224</v>
       </c>
       <c r="C91" s="5"/>
-      <c r="D91" s="11">
-        <v>84.7</v>
+      <c r="D91" s="38">
+        <v>133.1</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="F91" s="28">
-        <v>1</v>
+      <c r="F91" s="39">
+        <v>3</v>
       </c>
       <c r="G91" s="9" t="s">
         <v>267</v>
@@ -4030,14 +4036,14 @@
         <v>225</v>
       </c>
       <c r="C92" s="5"/>
-      <c r="D92" s="11">
+      <c r="D92" s="38">
         <v>84.7</v>
       </c>
       <c r="E92" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="F92" s="28">
-        <v>1</v>
+      <c r="F92" s="39">
+        <v>3</v>
       </c>
       <c r="G92" s="9" t="s">
         <v>268</v>
@@ -4051,14 +4057,14 @@
         <v>226</v>
       </c>
       <c r="C93" s="5"/>
-      <c r="D93" s="11">
-        <v>102.85000000000001</v>
+      <c r="D93" s="38">
+        <v>84.7</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="F93" s="28">
-        <v>1</v>
+      <c r="F93" s="39">
+        <v>3</v>
       </c>
       <c r="G93" s="9" t="s">
         <v>269</v>
@@ -4072,14 +4078,14 @@
         <v>227</v>
       </c>
       <c r="C94" s="5"/>
-      <c r="D94" s="11">
+      <c r="D94" s="38">
         <v>102.85000000000001</v>
       </c>
       <c r="E94" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="F94" s="28">
-        <v>1</v>
+      <c r="F94" s="39">
+        <v>3</v>
       </c>
       <c r="G94" s="9" t="s">
         <v>270</v>
@@ -4093,14 +4099,14 @@
         <v>228</v>
       </c>
       <c r="C95" s="5"/>
-      <c r="D95" s="11">
+      <c r="D95" s="38">
         <v>102.85000000000001</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="F95" s="28">
-        <v>1</v>
+      <c r="F95" s="39">
+        <v>3</v>
       </c>
       <c r="G95" s="9" t="s">
         <v>271</v>
@@ -4114,14 +4120,14 @@
         <v>402</v>
       </c>
       <c r="C96" s="5"/>
-      <c r="D96" s="11">
+      <c r="D96" s="38">
         <v>102.85000000000001</v>
       </c>
       <c r="E96" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="F96" s="28">
-        <v>1</v>
+      <c r="F96" s="39">
+        <v>3</v>
       </c>
       <c r="G96" s="9" t="s">
         <v>444</v>
@@ -4138,14 +4144,14 @@
         <v>403</v>
       </c>
       <c r="C97" s="5"/>
-      <c r="D97" s="11">
-        <v>108.9</v>
+      <c r="D97" s="38">
+        <v>102.85000000000001</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>360</v>
       </c>
-      <c r="F97" s="28">
-        <v>1</v>
+      <c r="F97" s="39">
+        <v>3</v>
       </c>
       <c r="G97" s="9" t="s">
         <v>445</v>
@@ -4162,14 +4168,14 @@
         <v>404</v>
       </c>
       <c r="C98" s="5"/>
-      <c r="D98" s="11">
-        <v>121</v>
+      <c r="D98" s="38">
+        <v>108.9</v>
       </c>
       <c r="E98" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="F98" s="28">
-        <v>1</v>
+      <c r="F98" s="39">
+        <v>2</v>
       </c>
       <c r="G98" s="9" t="s">
         <v>446</v>
@@ -4186,14 +4192,14 @@
         <v>405</v>
       </c>
       <c r="C99" s="5"/>
-      <c r="D99" s="11">
-        <v>41.14</v>
+      <c r="D99" s="38">
+        <v>121</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="F99" s="28">
-        <v>1</v>
+      <c r="F99" s="39">
+        <v>3</v>
       </c>
       <c r="G99" s="9" t="s">
         <v>447</v>
@@ -4210,14 +4216,14 @@
         <v>406</v>
       </c>
       <c r="C100" s="5"/>
-      <c r="D100" s="11">
-        <v>43.56</v>
+      <c r="D100" s="38">
+        <v>41.14</v>
       </c>
       <c r="E100" s="9" t="s">
         <v>363</v>
       </c>
-      <c r="F100" s="28">
-        <v>1</v>
+      <c r="F100" s="39">
+        <v>6</v>
       </c>
       <c r="G100" s="9" t="s">
         <v>448</v>
@@ -4234,14 +4240,14 @@
         <v>407</v>
       </c>
       <c r="C101" s="5"/>
-      <c r="D101" s="11">
+      <c r="D101" s="38">
         <v>43.56</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>364</v>
       </c>
-      <c r="F101" s="28">
-        <v>1</v>
+      <c r="F101" s="39">
+        <v>3</v>
       </c>
       <c r="G101" s="9" t="s">
         <v>449</v>
@@ -4258,14 +4264,14 @@
         <v>408</v>
       </c>
       <c r="C102" s="5"/>
-      <c r="D102" s="11">
+      <c r="D102" s="38">
         <v>43.56</v>
       </c>
       <c r="E102" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="F102" s="28">
-        <v>1</v>
+      <c r="F102" s="39">
+        <v>3</v>
       </c>
       <c r="G102" s="9" t="s">
         <v>450</v>
@@ -4282,14 +4288,14 @@
         <v>409</v>
       </c>
       <c r="C103" s="5"/>
-      <c r="D103" s="11">
-        <v>45.980000000000004</v>
+      <c r="D103" s="38">
+        <v>43.56</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>366</v>
       </c>
-      <c r="F103" s="28">
-        <v>1</v>
+      <c r="F103" s="39">
+        <v>3</v>
       </c>
       <c r="G103" s="9" t="s">
         <v>451</v>
@@ -4306,14 +4312,14 @@
         <v>410</v>
       </c>
       <c r="C104" s="5"/>
-      <c r="D104" s="11">
+      <c r="D104" s="38">
         <v>45.980000000000004</v>
       </c>
       <c r="E104" s="9" t="s">
         <v>367</v>
       </c>
-      <c r="F104" s="28">
-        <v>1</v>
+      <c r="F104" s="39">
+        <v>3</v>
       </c>
       <c r="G104" s="9" t="s">
         <v>452</v>
@@ -4330,14 +4336,14 @@
         <v>411</v>
       </c>
       <c r="C105" s="5"/>
-      <c r="D105" s="11">
-        <v>38.72</v>
+      <c r="D105" s="38">
+        <v>45.980000000000004</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>368</v>
       </c>
-      <c r="F105" s="28">
-        <v>1</v>
+      <c r="F105" s="39">
+        <v>3</v>
       </c>
       <c r="G105" s="9" t="s">
         <v>453</v>
@@ -4354,14 +4360,14 @@
         <v>412</v>
       </c>
       <c r="C106" s="5"/>
-      <c r="D106" s="11">
-        <v>11.5</v>
+      <c r="D106" s="38">
+        <v>38.72</v>
       </c>
       <c r="E106" s="9" t="s">
         <v>369</v>
       </c>
-      <c r="F106" s="28">
-        <v>1</v>
+      <c r="F106" s="39">
+        <v>3</v>
       </c>
       <c r="G106" s="9" t="s">
         <v>454</v>
@@ -4378,14 +4384,14 @@
         <v>413</v>
       </c>
       <c r="C107" s="5"/>
-      <c r="D107" s="11">
-        <v>15.73</v>
+      <c r="D107" s="38">
+        <v>11.5</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>370</v>
       </c>
-      <c r="F107" s="28">
-        <v>1</v>
+      <c r="F107" s="39">
+        <v>3</v>
       </c>
       <c r="G107" s="9" t="s">
         <v>455</v>
@@ -4402,14 +4408,14 @@
         <v>414</v>
       </c>
       <c r="C108" s="5"/>
-      <c r="D108" s="11">
-        <v>24.2</v>
+      <c r="D108" s="38">
+        <v>15.73</v>
       </c>
       <c r="E108" s="9" t="s">
         <v>371</v>
       </c>
-      <c r="F108" s="28">
-        <v>1</v>
+      <c r="F108" s="39">
+        <v>3</v>
       </c>
       <c r="G108" s="9" t="s">
         <v>456</v>
@@ -4426,14 +4432,14 @@
         <v>415</v>
       </c>
       <c r="C109" s="5"/>
-      <c r="D109" s="11">
+      <c r="D109" s="38">
         <v>24.2</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>372</v>
       </c>
-      <c r="F109" s="28">
-        <v>1</v>
+      <c r="F109" s="39">
+        <v>3</v>
       </c>
       <c r="G109" s="9" t="s">
         <v>457</v>
@@ -4450,14 +4456,14 @@
         <v>416</v>
       </c>
       <c r="C110" s="5"/>
-      <c r="D110" s="11">
-        <v>30.25</v>
+      <c r="D110" s="38">
+        <v>24.2</v>
       </c>
       <c r="E110" s="9" t="s">
         <v>373</v>
       </c>
-      <c r="F110" s="28">
-        <v>1</v>
+      <c r="F110" s="39">
+        <v>3</v>
       </c>
       <c r="G110" s="9" t="s">
         <v>458</v>
@@ -4474,14 +4480,14 @@
         <v>417</v>
       </c>
       <c r="C111" s="5"/>
-      <c r="D111" s="11">
-        <v>26.62</v>
+      <c r="D111" s="38">
+        <v>30.25</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>374</v>
       </c>
-      <c r="F111" s="28">
-        <v>1</v>
+      <c r="F111" s="39">
+        <v>3</v>
       </c>
       <c r="G111" s="9" t="s">
         <v>459</v>
@@ -4498,14 +4504,14 @@
         <v>418</v>
       </c>
       <c r="C112" s="5"/>
-      <c r="D112" s="11">
-        <v>12.1</v>
+      <c r="D112" s="38">
+        <v>26.62</v>
       </c>
       <c r="E112" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="F112" s="28">
-        <v>1</v>
+      <c r="F112" s="39">
+        <v>3</v>
       </c>
       <c r="G112" s="9" t="s">
         <v>460</v>
@@ -4522,14 +4528,14 @@
         <v>419</v>
       </c>
       <c r="C113" s="5"/>
-      <c r="D113" s="11">
-        <v>14.52</v>
+      <c r="D113" s="38">
+        <v>12.1</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="F113" s="28">
-        <v>1</v>
+      <c r="F113" s="39">
+        <v>3</v>
       </c>
       <c r="G113" s="9" t="s">
         <v>461</v>
@@ -4546,14 +4552,14 @@
         <v>420</v>
       </c>
       <c r="C114" s="5"/>
-      <c r="D114" s="11">
-        <v>12.1</v>
+      <c r="D114" s="38">
+        <v>14.52</v>
       </c>
       <c r="E114" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="F114" s="28">
-        <v>1</v>
+      <c r="F114" s="39">
+        <v>3</v>
       </c>
       <c r="G114" s="9" t="s">
         <v>462</v>
@@ -4570,14 +4576,14 @@
         <v>421</v>
       </c>
       <c r="C115" s="5"/>
-      <c r="D115" s="11">
-        <v>8.4700000000000006</v>
+      <c r="D115" s="38">
+        <v>12.1</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="F115" s="28">
-        <v>1</v>
+      <c r="F115" s="39">
+        <v>3</v>
       </c>
       <c r="G115" s="9" t="s">
         <v>463</v>
@@ -4594,14 +4600,14 @@
         <v>422</v>
       </c>
       <c r="C116" s="5"/>
-      <c r="D116" s="11">
-        <v>4.84</v>
+      <c r="D116" s="38">
+        <v>8.4700000000000006</v>
       </c>
       <c r="E116" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="F116" s="28">
-        <v>1</v>
+      <c r="F116" s="39">
+        <v>3</v>
       </c>
       <c r="G116" s="9" t="s">
         <v>464</v>
@@ -4618,14 +4624,14 @@
         <v>422</v>
       </c>
       <c r="C117" s="5"/>
-      <c r="D117" s="11">
-        <v>8.4700000000000006</v>
+      <c r="D117" s="38">
+        <v>4.84</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>380</v>
       </c>
-      <c r="F117" s="28">
-        <v>1</v>
+      <c r="F117" s="39">
+        <v>3</v>
       </c>
       <c r="G117" s="9" t="s">
         <v>465</v>
@@ -4642,14 +4648,14 @@
         <v>423</v>
       </c>
       <c r="C118" s="5"/>
-      <c r="D118" s="11">
-        <v>12.1</v>
+      <c r="D118" s="38">
+        <v>8.4700000000000006</v>
       </c>
       <c r="E118" s="9" t="s">
         <v>381</v>
       </c>
-      <c r="F118" s="28">
-        <v>1</v>
+      <c r="F118" s="39">
+        <v>3</v>
       </c>
       <c r="G118" s="9" t="s">
         <v>466</v>
@@ -4666,14 +4672,14 @@
         <v>424</v>
       </c>
       <c r="C119" s="5"/>
-      <c r="D119" s="11">
-        <v>8.4700000000000006</v>
+      <c r="D119" s="38">
+        <v>12.1</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>382</v>
       </c>
-      <c r="F119" s="28">
-        <v>1</v>
+      <c r="F119" s="39">
+        <v>3</v>
       </c>
       <c r="G119" s="9" t="s">
         <v>467</v>
@@ -4690,14 +4696,14 @@
         <v>425</v>
       </c>
       <c r="C120" s="5"/>
-      <c r="D120" s="11">
-        <v>18.150000000000002</v>
+      <c r="D120" s="38">
+        <v>8.4700000000000006</v>
       </c>
       <c r="E120" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="F120" s="28">
-        <v>1</v>
+      <c r="F120" s="39">
+        <v>3</v>
       </c>
       <c r="G120" s="9" t="s">
         <v>468</v>
@@ -4714,14 +4720,14 @@
         <v>426</v>
       </c>
       <c r="C121" s="5"/>
-      <c r="D121" s="11">
-        <v>12.1</v>
+      <c r="D121" s="38">
+        <v>18.150000000000002</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>384</v>
       </c>
-      <c r="F121" s="28">
-        <v>1</v>
+      <c r="F121" s="39">
+        <v>3</v>
       </c>
       <c r="G121" s="9" t="s">
         <v>469</v>
@@ -4738,14 +4744,14 @@
         <v>427</v>
       </c>
       <c r="C122" s="5"/>
-      <c r="D122" s="11">
-        <v>13.31</v>
+      <c r="D122" s="38">
+        <v>12.1</v>
       </c>
       <c r="E122" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="F122" s="28">
-        <v>1</v>
+      <c r="F122" s="39">
+        <v>3</v>
       </c>
       <c r="G122" s="9" t="s">
         <v>470</v>
@@ -4762,14 +4768,14 @@
         <v>428</v>
       </c>
       <c r="C123" s="5"/>
-      <c r="D123" s="11">
-        <v>12.1</v>
+      <c r="D123" s="38">
+        <v>13.31</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="F123" s="28">
-        <v>1</v>
+      <c r="F123" s="39">
+        <v>3</v>
       </c>
       <c r="G123" s="9" t="s">
         <v>471</v>
@@ -4786,14 +4792,14 @@
         <v>429</v>
       </c>
       <c r="C124" s="5"/>
-      <c r="D124" s="11">
-        <v>15.73</v>
+      <c r="D124" s="38">
+        <v>12.1</v>
       </c>
       <c r="E124" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="F124" s="28">
-        <v>1</v>
+      <c r="F124" s="39">
+        <v>3</v>
       </c>
       <c r="G124" s="9" t="s">
         <v>472</v>
@@ -4810,14 +4816,14 @@
         <v>430</v>
       </c>
       <c r="C125" s="5"/>
-      <c r="D125" s="11">
+      <c r="D125" s="38">
         <v>15.73</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>388</v>
       </c>
-      <c r="F125" s="28">
-        <v>1</v>
+      <c r="F125" s="39">
+        <v>3</v>
       </c>
       <c r="G125" s="9" t="s">
         <v>473</v>
@@ -4834,14 +4840,14 @@
         <v>431</v>
       </c>
       <c r="C126" s="5"/>
-      <c r="D126" s="11">
-        <v>14.52</v>
+      <c r="D126" s="38">
+        <v>15.73</v>
       </c>
       <c r="E126" s="9" t="s">
         <v>389</v>
       </c>
-      <c r="F126" s="28">
-        <v>1</v>
+      <c r="F126" s="39">
+        <v>3</v>
       </c>
       <c r="G126" s="9" t="s">
         <v>474</v>
@@ -4858,14 +4864,14 @@
         <v>432</v>
       </c>
       <c r="C127" s="5"/>
-      <c r="D127" s="11">
-        <v>15.73</v>
+      <c r="D127" s="38">
+        <v>14.52</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>390</v>
       </c>
-      <c r="F127" s="28">
-        <v>1</v>
+      <c r="F127" s="39">
+        <v>3</v>
       </c>
       <c r="G127" s="9" t="s">
         <v>475</v>
@@ -4882,14 +4888,14 @@
         <v>433</v>
       </c>
       <c r="C128" s="5"/>
-      <c r="D128" s="11">
+      <c r="D128" s="38">
         <v>15.73</v>
       </c>
       <c r="E128" s="9" t="s">
         <v>391</v>
       </c>
-      <c r="F128" s="28">
-        <v>1</v>
+      <c r="F128" s="39">
+        <v>3</v>
       </c>
       <c r="G128" s="9" t="s">
         <v>476</v>
@@ -4906,14 +4912,14 @@
         <v>434</v>
       </c>
       <c r="C129" s="5"/>
-      <c r="D129" s="11">
-        <v>15.73</v>
+      <c r="D129" s="38">
+        <v>13.31</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>392</v>
       </c>
-      <c r="F129" s="28">
-        <v>1</v>
+      <c r="F129" s="39">
+        <v>3</v>
       </c>
       <c r="G129" s="9" t="s">
         <v>477</v>
@@ -4930,14 +4936,14 @@
         <v>435</v>
       </c>
       <c r="C130" s="5"/>
-      <c r="D130" s="11">
-        <v>19.36</v>
+      <c r="D130" s="38">
+        <v>15.73</v>
       </c>
       <c r="E130" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="F130" s="28">
-        <v>1</v>
+      <c r="F130" s="39">
+        <v>3</v>
       </c>
       <c r="G130" s="9" t="s">
         <v>478</v>
@@ -4954,14 +4960,14 @@
         <v>436</v>
       </c>
       <c r="C131" s="5"/>
-      <c r="D131" s="11">
-        <v>18.150000000000002</v>
+      <c r="D131" s="38">
+        <v>19.36</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>394</v>
       </c>
-      <c r="F131" s="28">
-        <v>1</v>
+      <c r="F131" s="39">
+        <v>3</v>
       </c>
       <c r="G131" s="9" t="s">
         <v>479</v>
@@ -4978,14 +4984,14 @@
         <v>437</v>
       </c>
       <c r="C132" s="5"/>
-      <c r="D132" s="11">
-        <v>21.78</v>
+      <c r="D132" s="38">
+        <v>18.150000000000002</v>
       </c>
       <c r="E132" s="9" t="s">
         <v>395</v>
       </c>
-      <c r="F132" s="28">
-        <v>1</v>
+      <c r="F132" s="39">
+        <v>3</v>
       </c>
       <c r="G132" s="9" t="s">
         <v>480</v>
@@ -5002,14 +5008,14 @@
         <v>438</v>
       </c>
       <c r="C133" s="5"/>
-      <c r="D133" s="11">
-        <v>25.41</v>
+      <c r="D133" s="38">
+        <v>21.78</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>396</v>
       </c>
-      <c r="F133" s="28">
-        <v>1</v>
+      <c r="F133" s="39">
+        <v>3</v>
       </c>
       <c r="G133" s="9" t="s">
         <v>481</v>
@@ -5026,14 +5032,14 @@
         <v>439</v>
       </c>
       <c r="C134" s="5"/>
-      <c r="D134" s="11">
-        <v>36.300000000000004</v>
+      <c r="D134" s="38">
+        <v>25.41</v>
       </c>
       <c r="E134" s="9" t="s">
         <v>397</v>
       </c>
-      <c r="F134" s="28">
-        <v>1</v>
+      <c r="F134" s="39">
+        <v>3</v>
       </c>
       <c r="G134" s="9" t="s">
         <v>482</v>
@@ -5050,14 +5056,14 @@
         <v>440</v>
       </c>
       <c r="C135" s="5"/>
-      <c r="D135" s="11">
-        <v>43.56</v>
+      <c r="D135" s="38">
+        <v>36.300000000000004</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>398</v>
       </c>
-      <c r="F135" s="28">
-        <v>1</v>
+      <c r="F135" s="39">
+        <v>3</v>
       </c>
       <c r="G135" s="9" t="s">
         <v>483</v>
@@ -5074,14 +5080,14 @@
         <v>441</v>
       </c>
       <c r="C136" s="5"/>
-      <c r="D136" s="11">
-        <v>42.35</v>
+      <c r="D136" s="38">
+        <v>43.56</v>
       </c>
       <c r="E136" s="9" t="s">
         <v>399</v>
       </c>
-      <c r="F136" s="28">
-        <v>1</v>
+      <c r="F136" s="39">
+        <v>3</v>
       </c>
       <c r="G136" s="9" t="s">
         <v>484</v>
@@ -5098,14 +5104,14 @@
         <v>442</v>
       </c>
       <c r="C137" s="5"/>
-      <c r="D137" s="11">
-        <v>54.45</v>
+      <c r="D137" s="38">
+        <v>42.35</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>400</v>
       </c>
-      <c r="F137" s="28">
-        <v>1</v>
+      <c r="F137" s="39">
+        <v>3</v>
       </c>
       <c r="G137" s="9" t="s">
         <v>485</v>
@@ -5122,14 +5128,14 @@
         <v>443</v>
       </c>
       <c r="C138" s="5"/>
-      <c r="D138" s="11">
-        <v>8.4700000000000006</v>
+      <c r="D138" s="38">
+        <v>54.45</v>
       </c>
       <c r="E138" s="9" t="s">
         <v>401</v>
       </c>
-      <c r="F138" s="28">
-        <v>1</v>
+      <c r="F138" s="39">
+        <v>3</v>
       </c>
       <c r="G138" s="9" t="s">
         <v>486</v>
@@ -5142,9 +5148,13 @@
       <c r="A139" s="5"/>
       <c r="B139" s="10"/>
       <c r="C139" s="5"/>
-      <c r="D139" s="12"/>
+      <c r="D139" s="38">
+        <v>8.4700000000000006</v>
+      </c>
       <c r="E139" s="10"/>
-      <c r="F139" s="28"/>
+      <c r="F139" s="39">
+        <v>3</v>
+      </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" s="5"/>

--- a/prix/prix.xlsx
+++ b/prix/prix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\robinetterie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{205706CF-B90B-4D88-BCE1-E9F2439B2F52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0107EEAD-7EBF-4175-88A4-09F8FBC7573D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23124" yWindow="12" windowWidth="19116" windowHeight="10884" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
+    <workbookView xWindow="1068" yWindow="708" windowWidth="19116" windowHeight="10884" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="532">
   <si>
     <t>path</t>
   </si>
@@ -1626,6 +1626,12 @@
   </si>
   <si>
     <t>schutte/60740.png</t>
+  </si>
+  <si>
+    <t>ideal-standard/black-mat.png</t>
+  </si>
+  <si>
+    <t>ideal-standard/silver.png</t>
   </si>
 </sst>
 </file>
@@ -1722,7 +1728,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1831,12 +1837,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -3172,6 +3172,9 @@
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
+        <v>531</v>
+      </c>
       <c r="B49" s="34" t="s">
         <v>139</v>
       </c>
@@ -3190,7 +3193,9 @@
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="5"/>
+      <c r="A50" s="4" t="s">
+        <v>530</v>
+      </c>
       <c r="B50" s="34" t="s">
         <v>142</v>
       </c>
@@ -3243,13 +3248,13 @@
       <c r="B53" s="29" t="s">
         <v>188</v>
       </c>
-      <c r="D53" s="38">
+      <c r="D53" s="11">
         <v>363</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="F53" s="39">
+      <c r="F53" s="28">
         <v>3</v>
       </c>
       <c r="G53" s="9" t="s">
@@ -3263,13 +3268,13 @@
       <c r="B54" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="D54" s="38">
+      <c r="D54" s="11">
         <v>217.8</v>
       </c>
       <c r="E54" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="F54" s="39">
+      <c r="F54" s="28">
         <v>3</v>
       </c>
       <c r="G54" s="9" t="s">
@@ -3283,13 +3288,13 @@
       <c r="B55" s="29" t="s">
         <v>190</v>
       </c>
-      <c r="D55" s="38">
+      <c r="D55" s="11">
         <v>411.40000000000003</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="F55" s="39">
+      <c r="F55" s="28">
         <v>3</v>
       </c>
       <c r="G55" s="9" t="s">
@@ -3303,13 +3308,13 @@
       <c r="B56" s="29" t="s">
         <v>191</v>
       </c>
-      <c r="D56" s="38">
+      <c r="D56" s="11">
         <v>96.8</v>
       </c>
       <c r="E56" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="F56" s="39">
+      <c r="F56" s="28">
         <v>3</v>
       </c>
       <c r="G56" s="9" t="s">
@@ -3323,13 +3328,13 @@
       <c r="B57" s="29" t="s">
         <v>192</v>
       </c>
-      <c r="D57" s="38">
+      <c r="D57" s="11">
         <v>96.8</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="F57" s="39">
+      <c r="F57" s="28">
         <v>3</v>
       </c>
       <c r="G57" s="9" t="s">
@@ -3343,13 +3348,13 @@
       <c r="B58" s="29" t="s">
         <v>193</v>
       </c>
-      <c r="D58" s="38">
+      <c r="D58" s="11">
         <v>84.7</v>
       </c>
       <c r="E58" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="F58" s="39">
+      <c r="F58" s="28">
         <v>3</v>
       </c>
       <c r="G58" s="9" t="s">
@@ -3363,13 +3368,13 @@
       <c r="B59" s="29" t="s">
         <v>194</v>
       </c>
-      <c r="D59" s="38">
+      <c r="D59" s="11">
         <v>411.40000000000003</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="F59" s="39">
+      <c r="F59" s="28">
         <v>1</v>
       </c>
       <c r="G59" s="9" t="s">
@@ -3384,13 +3389,13 @@
         <v>195</v>
       </c>
       <c r="C60" s="5"/>
-      <c r="D60" s="38">
+      <c r="D60" s="11">
         <v>53.24</v>
       </c>
       <c r="E60" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="F60" s="39">
+      <c r="F60" s="28">
         <v>3</v>
       </c>
       <c r="G60" s="9" t="s">
@@ -3405,13 +3410,13 @@
         <v>196</v>
       </c>
       <c r="C61" s="5"/>
-      <c r="D61" s="38">
+      <c r="D61" s="11">
         <v>66.55</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="F61" s="39">
+      <c r="F61" s="28">
         <v>3</v>
       </c>
       <c r="G61" s="9" t="s">
@@ -3426,13 +3431,13 @@
         <v>197</v>
       </c>
       <c r="C62" s="5"/>
-      <c r="D62" s="38">
+      <c r="D62" s="11">
         <v>84.7</v>
       </c>
       <c r="E62" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="F62" s="39">
+      <c r="F62" s="28">
         <v>3</v>
       </c>
       <c r="G62" s="9" t="s">
@@ -3446,13 +3451,13 @@
       <c r="B63" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="D63" s="38">
+      <c r="D63" s="11">
         <v>96.8</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="F63" s="39">
+      <c r="F63" s="28">
         <v>3</v>
       </c>
       <c r="G63" s="9" t="s">
@@ -3466,13 +3471,13 @@
       <c r="B64" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="D64" s="38">
+      <c r="D64" s="11">
         <v>78.650000000000006</v>
       </c>
       <c r="E64" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="F64" s="39">
+      <c r="F64" s="28">
         <v>3</v>
       </c>
       <c r="G64" s="9" t="s">
@@ -3486,13 +3491,13 @@
       <c r="B65" s="29" t="s">
         <v>200</v>
       </c>
-      <c r="D65" s="38">
+      <c r="D65" s="11">
         <v>133.1</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="F65" s="39">
+      <c r="F65" s="28">
         <v>3</v>
       </c>
       <c r="G65" s="9" t="s">
@@ -3506,13 +3511,13 @@
       <c r="B66" s="29" t="s">
         <v>201</v>
       </c>
-      <c r="D66" s="38">
+      <c r="D66" s="11">
         <v>145.20000000000002</v>
       </c>
       <c r="E66" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="F66" s="39">
+      <c r="F66" s="28">
         <v>3</v>
       </c>
       <c r="G66" s="9" t="s">
@@ -3526,13 +3531,13 @@
       <c r="B67" s="29" t="s">
         <v>202</v>
       </c>
-      <c r="D67" s="38">
+      <c r="D67" s="11">
         <v>102.85000000000001</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="F67" s="39">
+      <c r="F67" s="28">
         <v>3</v>
       </c>
       <c r="G67" s="9" t="s">
@@ -3546,13 +3551,13 @@
       <c r="B68" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="D68" s="38">
+      <c r="D68" s="11">
         <v>169.4</v>
       </c>
       <c r="E68" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="F68" s="39">
+      <c r="F68" s="28">
         <v>3</v>
       </c>
       <c r="G68" s="9" t="s">
@@ -3566,13 +3571,13 @@
       <c r="B69" s="29" t="s">
         <v>204</v>
       </c>
-      <c r="D69" s="38">
+      <c r="D69" s="11">
         <v>181.5</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="F69" s="39">
+      <c r="F69" s="28">
         <v>3</v>
       </c>
       <c r="G69" s="9" t="s">
@@ -3586,13 +3591,13 @@
       <c r="B70" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="D70" s="38">
+      <c r="D70" s="11">
         <v>121</v>
       </c>
       <c r="E70" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="F70" s="39">
+      <c r="F70" s="28">
         <v>3</v>
       </c>
       <c r="G70" s="9" t="s">
@@ -3606,13 +3611,13 @@
       <c r="B71" s="29" t="s">
         <v>204</v>
       </c>
-      <c r="D71" s="38">
+      <c r="D71" s="11">
         <v>133.1</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="F71" s="39">
+      <c r="F71" s="28">
         <v>3</v>
       </c>
       <c r="G71" s="9" t="s">
@@ -3626,13 +3631,13 @@
       <c r="B72" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="D72" s="38">
+      <c r="D72" s="11">
         <v>121</v>
       </c>
       <c r="E72" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="F72" s="39">
+      <c r="F72" s="28">
         <v>3</v>
       </c>
       <c r="G72" s="9" t="s">
@@ -3646,13 +3651,13 @@
       <c r="B73" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="D73" s="38">
+      <c r="D73" s="11">
         <v>133.1</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="F73" s="39">
+      <c r="F73" s="28">
         <v>3</v>
       </c>
       <c r="G73" s="9" t="s">
@@ -3666,13 +3671,13 @@
       <c r="B74" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D74" s="38">
+      <c r="D74" s="11">
         <v>145.20000000000002</v>
       </c>
       <c r="E74" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="F74" s="39">
+      <c r="F74" s="28">
         <v>1</v>
       </c>
       <c r="G74" s="9" t="s">
@@ -3686,13 +3691,13 @@
       <c r="B75" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="D75" s="38">
+      <c r="D75" s="11">
         <v>157.30000000000001</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="F75" s="39">
+      <c r="F75" s="28">
         <v>3</v>
       </c>
       <c r="G75" s="9" t="s">
@@ -3706,13 +3711,13 @@
       <c r="B76" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="D76" s="38">
+      <c r="D76" s="11">
         <v>53.24</v>
       </c>
       <c r="E76" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="F76" s="39">
+      <c r="F76" s="28">
         <v>3</v>
       </c>
       <c r="G76" s="9" t="s">
@@ -3726,13 +3731,13 @@
       <c r="B77" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="D77" s="38">
+      <c r="D77" s="11">
         <v>84.7</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="F77" s="39">
+      <c r="F77" s="28">
         <v>3</v>
       </c>
       <c r="G77" s="9" t="s">
@@ -3746,13 +3751,13 @@
       <c r="B78" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="D78" s="38">
+      <c r="D78" s="11">
         <v>72.600000000000009</v>
       </c>
       <c r="E78" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="F78" s="39">
+      <c r="F78" s="28">
         <v>3</v>
       </c>
       <c r="G78" s="9" t="s">
@@ -3766,13 +3771,13 @@
       <c r="B79" s="29" t="s">
         <v>212</v>
       </c>
-      <c r="D79" s="38">
+      <c r="D79" s="11">
         <v>53.24</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="F79" s="39">
+      <c r="F79" s="28">
         <v>3</v>
       </c>
       <c r="G79" s="9" t="s">
@@ -3786,13 +3791,13 @@
       <c r="B80" s="29" t="s">
         <v>213</v>
       </c>
-      <c r="D80" s="38">
+      <c r="D80" s="11">
         <v>60.5</v>
       </c>
       <c r="E80" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="F80" s="39">
+      <c r="F80" s="28">
         <v>3</v>
       </c>
       <c r="G80" s="9" t="s">
@@ -3806,13 +3811,13 @@
       <c r="B81" s="29" t="s">
         <v>214</v>
       </c>
-      <c r="D81" s="38">
+      <c r="D81" s="11">
         <v>66.55</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="F81" s="39">
+      <c r="F81" s="28">
         <v>3</v>
       </c>
       <c r="G81" s="9" t="s">
@@ -3826,13 +3831,13 @@
       <c r="B82" s="29" t="s">
         <v>215</v>
       </c>
-      <c r="D82" s="38">
+      <c r="D82" s="11">
         <v>90.75</v>
       </c>
       <c r="E82" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="F82" s="39">
+      <c r="F82" s="28">
         <v>3</v>
       </c>
       <c r="G82" s="9" t="s">
@@ -3847,13 +3852,13 @@
         <v>216</v>
       </c>
       <c r="C83" s="5"/>
-      <c r="D83" s="38">
+      <c r="D83" s="11">
         <v>102.85000000000001</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="F83" s="39">
+      <c r="F83" s="28">
         <v>3</v>
       </c>
       <c r="G83" s="9" t="s">
@@ -3868,13 +3873,13 @@
         <v>217</v>
       </c>
       <c r="C84" s="5"/>
-      <c r="D84" s="38">
+      <c r="D84" s="11">
         <v>133.1</v>
       </c>
       <c r="E84" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="F84" s="39">
+      <c r="F84" s="28">
         <v>3</v>
       </c>
       <c r="G84" s="9" t="s">
@@ -3889,13 +3894,13 @@
         <v>218</v>
       </c>
       <c r="C85" s="5"/>
-      <c r="D85" s="38">
+      <c r="D85" s="11">
         <v>133.1</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="F85" s="39">
+      <c r="F85" s="28">
         <v>3</v>
       </c>
       <c r="G85" s="9" t="s">
@@ -3910,13 +3915,13 @@
         <v>219</v>
       </c>
       <c r="C86" s="5"/>
-      <c r="D86" s="38">
+      <c r="D86" s="11">
         <v>193.6</v>
       </c>
       <c r="E86" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="F86" s="39">
+      <c r="F86" s="28">
         <v>3</v>
       </c>
       <c r="G86" s="9" t="s">
@@ -3931,13 +3936,13 @@
         <v>220</v>
       </c>
       <c r="C87" s="5"/>
-      <c r="D87" s="38">
+      <c r="D87" s="11">
         <v>157.30000000000001</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="F87" s="39">
+      <c r="F87" s="28">
         <v>3</v>
       </c>
       <c r="G87" s="9" t="s">
@@ -3952,13 +3957,13 @@
         <v>221</v>
       </c>
       <c r="C88" s="5"/>
-      <c r="D88" s="38">
+      <c r="D88" s="11">
         <v>114.95</v>
       </c>
       <c r="E88" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="F88" s="39">
+      <c r="F88" s="28">
         <v>3</v>
       </c>
       <c r="G88" s="9" t="s">
@@ -3973,13 +3978,13 @@
         <v>222</v>
       </c>
       <c r="C89" s="5"/>
-      <c r="D89" s="38">
+      <c r="D89" s="11">
         <v>90.75</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F89" s="39">
+      <c r="F89" s="28">
         <v>3</v>
       </c>
       <c r="G89" s="9" t="s">
@@ -3994,13 +3999,13 @@
         <v>223</v>
       </c>
       <c r="C90" s="5"/>
-      <c r="D90" s="38">
+      <c r="D90" s="11">
         <v>96.8</v>
       </c>
       <c r="E90" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="F90" s="39">
+      <c r="F90" s="28">
         <v>3</v>
       </c>
       <c r="G90" s="9" t="s">
@@ -4015,13 +4020,13 @@
         <v>224</v>
       </c>
       <c r="C91" s="5"/>
-      <c r="D91" s="38">
+      <c r="D91" s="11">
         <v>133.1</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="F91" s="39">
+      <c r="F91" s="28">
         <v>3</v>
       </c>
       <c r="G91" s="9" t="s">
@@ -4036,13 +4041,13 @@
         <v>225</v>
       </c>
       <c r="C92" s="5"/>
-      <c r="D92" s="38">
+      <c r="D92" s="11">
         <v>84.7</v>
       </c>
       <c r="E92" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="F92" s="39">
+      <c r="F92" s="28">
         <v>3</v>
       </c>
       <c r="G92" s="9" t="s">
@@ -4057,13 +4062,13 @@
         <v>226</v>
       </c>
       <c r="C93" s="5"/>
-      <c r="D93" s="38">
+      <c r="D93" s="11">
         <v>84.7</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="F93" s="39">
+      <c r="F93" s="28">
         <v>3</v>
       </c>
       <c r="G93" s="9" t="s">
@@ -4078,13 +4083,13 @@
         <v>227</v>
       </c>
       <c r="C94" s="5"/>
-      <c r="D94" s="38">
+      <c r="D94" s="11">
         <v>102.85000000000001</v>
       </c>
       <c r="E94" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="F94" s="39">
+      <c r="F94" s="28">
         <v>3</v>
       </c>
       <c r="G94" s="9" t="s">
@@ -4099,13 +4104,13 @@
         <v>228</v>
       </c>
       <c r="C95" s="5"/>
-      <c r="D95" s="38">
+      <c r="D95" s="11">
         <v>102.85000000000001</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="F95" s="39">
+      <c r="F95" s="28">
         <v>3</v>
       </c>
       <c r="G95" s="9" t="s">
@@ -4120,13 +4125,13 @@
         <v>402</v>
       </c>
       <c r="C96" s="5"/>
-      <c r="D96" s="38">
+      <c r="D96" s="11">
         <v>102.85000000000001</v>
       </c>
       <c r="E96" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="F96" s="39">
+      <c r="F96" s="28">
         <v>3</v>
       </c>
       <c r="G96" s="9" t="s">
@@ -4144,13 +4149,13 @@
         <v>403</v>
       </c>
       <c r="C97" s="5"/>
-      <c r="D97" s="38">
+      <c r="D97" s="11">
         <v>102.85000000000001</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>360</v>
       </c>
-      <c r="F97" s="39">
+      <c r="F97" s="28">
         <v>3</v>
       </c>
       <c r="G97" s="9" t="s">
@@ -4168,13 +4173,13 @@
         <v>404</v>
       </c>
       <c r="C98" s="5"/>
-      <c r="D98" s="38">
+      <c r="D98" s="11">
         <v>108.9</v>
       </c>
       <c r="E98" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="F98" s="39">
+      <c r="F98" s="28">
         <v>2</v>
       </c>
       <c r="G98" s="9" t="s">
@@ -4192,13 +4197,13 @@
         <v>405</v>
       </c>
       <c r="C99" s="5"/>
-      <c r="D99" s="38">
+      <c r="D99" s="11">
         <v>121</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="F99" s="39">
+      <c r="F99" s="28">
         <v>3</v>
       </c>
       <c r="G99" s="9" t="s">
@@ -4216,13 +4221,13 @@
         <v>406</v>
       </c>
       <c r="C100" s="5"/>
-      <c r="D100" s="38">
+      <c r="D100" s="11">
         <v>41.14</v>
       </c>
       <c r="E100" s="9" t="s">
         <v>363</v>
       </c>
-      <c r="F100" s="39">
+      <c r="F100" s="28">
         <v>6</v>
       </c>
       <c r="G100" s="9" t="s">
@@ -4240,13 +4245,13 @@
         <v>407</v>
       </c>
       <c r="C101" s="5"/>
-      <c r="D101" s="38">
+      <c r="D101" s="11">
         <v>43.56</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>364</v>
       </c>
-      <c r="F101" s="39">
+      <c r="F101" s="28">
         <v>3</v>
       </c>
       <c r="G101" s="9" t="s">
@@ -4264,13 +4269,13 @@
         <v>408</v>
       </c>
       <c r="C102" s="5"/>
-      <c r="D102" s="38">
+      <c r="D102" s="11">
         <v>43.56</v>
       </c>
       <c r="E102" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="F102" s="39">
+      <c r="F102" s="28">
         <v>3</v>
       </c>
       <c r="G102" s="9" t="s">
@@ -4288,13 +4293,13 @@
         <v>409</v>
       </c>
       <c r="C103" s="5"/>
-      <c r="D103" s="38">
+      <c r="D103" s="11">
         <v>43.56</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>366</v>
       </c>
-      <c r="F103" s="39">
+      <c r="F103" s="28">
         <v>3</v>
       </c>
       <c r="G103" s="9" t="s">
@@ -4312,13 +4317,13 @@
         <v>410</v>
       </c>
       <c r="C104" s="5"/>
-      <c r="D104" s="38">
+      <c r="D104" s="11">
         <v>45.980000000000004</v>
       </c>
       <c r="E104" s="9" t="s">
         <v>367</v>
       </c>
-      <c r="F104" s="39">
+      <c r="F104" s="28">
         <v>3</v>
       </c>
       <c r="G104" s="9" t="s">
@@ -4336,13 +4341,13 @@
         <v>411</v>
       </c>
       <c r="C105" s="5"/>
-      <c r="D105" s="38">
+      <c r="D105" s="11">
         <v>45.980000000000004</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>368</v>
       </c>
-      <c r="F105" s="39">
+      <c r="F105" s="28">
         <v>3</v>
       </c>
       <c r="G105" s="9" t="s">
@@ -4360,13 +4365,13 @@
         <v>412</v>
       </c>
       <c r="C106" s="5"/>
-      <c r="D106" s="38">
+      <c r="D106" s="11">
         <v>38.72</v>
       </c>
       <c r="E106" s="9" t="s">
         <v>369</v>
       </c>
-      <c r="F106" s="39">
+      <c r="F106" s="28">
         <v>3</v>
       </c>
       <c r="G106" s="9" t="s">
@@ -4384,13 +4389,13 @@
         <v>413</v>
       </c>
       <c r="C107" s="5"/>
-      <c r="D107" s="38">
+      <c r="D107" s="11">
         <v>11.5</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>370</v>
       </c>
-      <c r="F107" s="39">
+      <c r="F107" s="28">
         <v>3</v>
       </c>
       <c r="G107" s="9" t="s">
@@ -4408,13 +4413,13 @@
         <v>414</v>
       </c>
       <c r="C108" s="5"/>
-      <c r="D108" s="38">
+      <c r="D108" s="11">
         <v>15.73</v>
       </c>
       <c r="E108" s="9" t="s">
         <v>371</v>
       </c>
-      <c r="F108" s="39">
+      <c r="F108" s="28">
         <v>3</v>
       </c>
       <c r="G108" s="9" t="s">
@@ -4432,13 +4437,13 @@
         <v>415</v>
       </c>
       <c r="C109" s="5"/>
-      <c r="D109" s="38">
+      <c r="D109" s="11">
         <v>24.2</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>372</v>
       </c>
-      <c r="F109" s="39">
+      <c r="F109" s="28">
         <v>3</v>
       </c>
       <c r="G109" s="9" t="s">
@@ -4456,13 +4461,13 @@
         <v>416</v>
       </c>
       <c r="C110" s="5"/>
-      <c r="D110" s="38">
+      <c r="D110" s="11">
         <v>24.2</v>
       </c>
       <c r="E110" s="9" t="s">
         <v>373</v>
       </c>
-      <c r="F110" s="39">
+      <c r="F110" s="28">
         <v>3</v>
       </c>
       <c r="G110" s="9" t="s">
@@ -4480,13 +4485,13 @@
         <v>417</v>
       </c>
       <c r="C111" s="5"/>
-      <c r="D111" s="38">
+      <c r="D111" s="11">
         <v>30.25</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>374</v>
       </c>
-      <c r="F111" s="39">
+      <c r="F111" s="28">
         <v>3</v>
       </c>
       <c r="G111" s="9" t="s">
@@ -4504,13 +4509,13 @@
         <v>418</v>
       </c>
       <c r="C112" s="5"/>
-      <c r="D112" s="38">
+      <c r="D112" s="11">
         <v>26.62</v>
       </c>
       <c r="E112" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="F112" s="39">
+      <c r="F112" s="28">
         <v>3</v>
       </c>
       <c r="G112" s="9" t="s">
@@ -4528,13 +4533,13 @@
         <v>419</v>
       </c>
       <c r="C113" s="5"/>
-      <c r="D113" s="38">
+      <c r="D113" s="11">
         <v>12.1</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="F113" s="39">
+      <c r="F113" s="28">
         <v>3</v>
       </c>
       <c r="G113" s="9" t="s">
@@ -4552,13 +4557,13 @@
         <v>420</v>
       </c>
       <c r="C114" s="5"/>
-      <c r="D114" s="38">
+      <c r="D114" s="11">
         <v>14.52</v>
       </c>
       <c r="E114" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="F114" s="39">
+      <c r="F114" s="28">
         <v>3</v>
       </c>
       <c r="G114" s="9" t="s">
@@ -4576,13 +4581,13 @@
         <v>421</v>
       </c>
       <c r="C115" s="5"/>
-      <c r="D115" s="38">
+      <c r="D115" s="11">
         <v>12.1</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="F115" s="39">
+      <c r="F115" s="28">
         <v>3</v>
       </c>
       <c r="G115" s="9" t="s">
@@ -4600,13 +4605,13 @@
         <v>422</v>
       </c>
       <c r="C116" s="5"/>
-      <c r="D116" s="38">
+      <c r="D116" s="11">
         <v>8.4700000000000006</v>
       </c>
       <c r="E116" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="F116" s="39">
+      <c r="F116" s="28">
         <v>3</v>
       </c>
       <c r="G116" s="9" t="s">
@@ -4624,13 +4629,13 @@
         <v>422</v>
       </c>
       <c r="C117" s="5"/>
-      <c r="D117" s="38">
+      <c r="D117" s="11">
         <v>4.84</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>380</v>
       </c>
-      <c r="F117" s="39">
+      <c r="F117" s="28">
         <v>3</v>
       </c>
       <c r="G117" s="9" t="s">
@@ -4648,13 +4653,13 @@
         <v>423</v>
       </c>
       <c r="C118" s="5"/>
-      <c r="D118" s="38">
+      <c r="D118" s="11">
         <v>8.4700000000000006</v>
       </c>
       <c r="E118" s="9" t="s">
         <v>381</v>
       </c>
-      <c r="F118" s="39">
+      <c r="F118" s="28">
         <v>3</v>
       </c>
       <c r="G118" s="9" t="s">
@@ -4672,13 +4677,13 @@
         <v>424</v>
       </c>
       <c r="C119" s="5"/>
-      <c r="D119" s="38">
+      <c r="D119" s="11">
         <v>12.1</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>382</v>
       </c>
-      <c r="F119" s="39">
+      <c r="F119" s="28">
         <v>3</v>
       </c>
       <c r="G119" s="9" t="s">
@@ -4696,13 +4701,13 @@
         <v>425</v>
       </c>
       <c r="C120" s="5"/>
-      <c r="D120" s="38">
+      <c r="D120" s="11">
         <v>8.4700000000000006</v>
       </c>
       <c r="E120" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="F120" s="39">
+      <c r="F120" s="28">
         <v>3</v>
       </c>
       <c r="G120" s="9" t="s">
@@ -4720,13 +4725,13 @@
         <v>426</v>
       </c>
       <c r="C121" s="5"/>
-      <c r="D121" s="38">
+      <c r="D121" s="11">
         <v>18.150000000000002</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>384</v>
       </c>
-      <c r="F121" s="39">
+      <c r="F121" s="28">
         <v>3</v>
       </c>
       <c r="G121" s="9" t="s">
@@ -4744,13 +4749,13 @@
         <v>427</v>
       </c>
       <c r="C122" s="5"/>
-      <c r="D122" s="38">
+      <c r="D122" s="11">
         <v>12.1</v>
       </c>
       <c r="E122" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="F122" s="39">
+      <c r="F122" s="28">
         <v>3</v>
       </c>
       <c r="G122" s="9" t="s">
@@ -4768,13 +4773,13 @@
         <v>428</v>
       </c>
       <c r="C123" s="5"/>
-      <c r="D123" s="38">
+      <c r="D123" s="11">
         <v>13.31</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="F123" s="39">
+      <c r="F123" s="28">
         <v>3</v>
       </c>
       <c r="G123" s="9" t="s">
@@ -4792,13 +4797,13 @@
         <v>429</v>
       </c>
       <c r="C124" s="5"/>
-      <c r="D124" s="38">
+      <c r="D124" s="11">
         <v>12.1</v>
       </c>
       <c r="E124" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="F124" s="39">
+      <c r="F124" s="28">
         <v>3</v>
       </c>
       <c r="G124" s="9" t="s">
@@ -4816,13 +4821,13 @@
         <v>430</v>
       </c>
       <c r="C125" s="5"/>
-      <c r="D125" s="38">
+      <c r="D125" s="11">
         <v>15.73</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>388</v>
       </c>
-      <c r="F125" s="39">
+      <c r="F125" s="28">
         <v>3</v>
       </c>
       <c r="G125" s="9" t="s">
@@ -4840,13 +4845,13 @@
         <v>431</v>
       </c>
       <c r="C126" s="5"/>
-      <c r="D126" s="38">
+      <c r="D126" s="11">
         <v>15.73</v>
       </c>
       <c r="E126" s="9" t="s">
         <v>389</v>
       </c>
-      <c r="F126" s="39">
+      <c r="F126" s="28">
         <v>3</v>
       </c>
       <c r="G126" s="9" t="s">
@@ -4864,13 +4869,13 @@
         <v>432</v>
       </c>
       <c r="C127" s="5"/>
-      <c r="D127" s="38">
+      <c r="D127" s="11">
         <v>14.52</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>390</v>
       </c>
-      <c r="F127" s="39">
+      <c r="F127" s="28">
         <v>3</v>
       </c>
       <c r="G127" s="9" t="s">
@@ -4888,13 +4893,13 @@
         <v>433</v>
       </c>
       <c r="C128" s="5"/>
-      <c r="D128" s="38">
+      <c r="D128" s="11">
         <v>15.73</v>
       </c>
       <c r="E128" s="9" t="s">
         <v>391</v>
       </c>
-      <c r="F128" s="39">
+      <c r="F128" s="28">
         <v>3</v>
       </c>
       <c r="G128" s="9" t="s">
@@ -4912,13 +4917,13 @@
         <v>434</v>
       </c>
       <c r="C129" s="5"/>
-      <c r="D129" s="38">
+      <c r="D129" s="11">
         <v>13.31</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>392</v>
       </c>
-      <c r="F129" s="39">
+      <c r="F129" s="28">
         <v>3</v>
       </c>
       <c r="G129" s="9" t="s">
@@ -4936,13 +4941,13 @@
         <v>435</v>
       </c>
       <c r="C130" s="5"/>
-      <c r="D130" s="38">
+      <c r="D130" s="11">
         <v>15.73</v>
       </c>
       <c r="E130" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="F130" s="39">
+      <c r="F130" s="28">
         <v>3</v>
       </c>
       <c r="G130" s="9" t="s">
@@ -4960,13 +4965,13 @@
         <v>436</v>
       </c>
       <c r="C131" s="5"/>
-      <c r="D131" s="38">
+      <c r="D131" s="11">
         <v>19.36</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>394</v>
       </c>
-      <c r="F131" s="39">
+      <c r="F131" s="28">
         <v>3</v>
       </c>
       <c r="G131" s="9" t="s">
@@ -4984,13 +4989,13 @@
         <v>437</v>
       </c>
       <c r="C132" s="5"/>
-      <c r="D132" s="38">
+      <c r="D132" s="11">
         <v>18.150000000000002</v>
       </c>
       <c r="E132" s="9" t="s">
         <v>395</v>
       </c>
-      <c r="F132" s="39">
+      <c r="F132" s="28">
         <v>3</v>
       </c>
       <c r="G132" s="9" t="s">
@@ -5008,13 +5013,13 @@
         <v>438</v>
       </c>
       <c r="C133" s="5"/>
-      <c r="D133" s="38">
+      <c r="D133" s="11">
         <v>21.78</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>396</v>
       </c>
-      <c r="F133" s="39">
+      <c r="F133" s="28">
         <v>3</v>
       </c>
       <c r="G133" s="9" t="s">
@@ -5032,13 +5037,13 @@
         <v>439</v>
       </c>
       <c r="C134" s="5"/>
-      <c r="D134" s="38">
+      <c r="D134" s="11">
         <v>25.41</v>
       </c>
       <c r="E134" s="9" t="s">
         <v>397</v>
       </c>
-      <c r="F134" s="39">
+      <c r="F134" s="28">
         <v>3</v>
       </c>
       <c r="G134" s="9" t="s">
@@ -5056,13 +5061,13 @@
         <v>440</v>
       </c>
       <c r="C135" s="5"/>
-      <c r="D135" s="38">
+      <c r="D135" s="11">
         <v>36.300000000000004</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>398</v>
       </c>
-      <c r="F135" s="39">
+      <c r="F135" s="28">
         <v>3</v>
       </c>
       <c r="G135" s="9" t="s">
@@ -5080,13 +5085,13 @@
         <v>441</v>
       </c>
       <c r="C136" s="5"/>
-      <c r="D136" s="38">
+      <c r="D136" s="11">
         <v>43.56</v>
       </c>
       <c r="E136" s="9" t="s">
         <v>399</v>
       </c>
-      <c r="F136" s="39">
+      <c r="F136" s="28">
         <v>3</v>
       </c>
       <c r="G136" s="9" t="s">
@@ -5104,13 +5109,13 @@
         <v>442</v>
       </c>
       <c r="C137" s="5"/>
-      <c r="D137" s="38">
+      <c r="D137" s="11">
         <v>42.35</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>400</v>
       </c>
-      <c r="F137" s="39">
+      <c r="F137" s="28">
         <v>3</v>
       </c>
       <c r="G137" s="9" t="s">
@@ -5128,13 +5133,13 @@
         <v>443</v>
       </c>
       <c r="C138" s="5"/>
-      <c r="D138" s="38">
+      <c r="D138" s="11">
         <v>54.45</v>
       </c>
       <c r="E138" s="9" t="s">
         <v>401</v>
       </c>
-      <c r="F138" s="39">
+      <c r="F138" s="28">
         <v>3</v>
       </c>
       <c r="G138" s="9" t="s">
@@ -5148,11 +5153,11 @@
       <c r="A139" s="5"/>
       <c r="B139" s="10"/>
       <c r="C139" s="5"/>
-      <c r="D139" s="38">
+      <c r="D139" s="11">
         <v>8.4700000000000006</v>
       </c>
       <c r="E139" s="10"/>
-      <c r="F139" s="39">
+      <c r="F139" s="28">
         <v>3</v>
       </c>
     </row>

--- a/prix/prix.xlsx
+++ b/prix/prix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\robinetterie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0107EEAD-7EBF-4175-88A4-09F8FBC7573D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD65C618-4596-4488-ADC2-745945B72FA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1068" yWindow="708" windowWidth="19116" windowHeight="10884" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -1684,7 +1684,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1715,6 +1715,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1728,7 +1734,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1782,25 +1788,16 @@
     <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1837,6 +1834,27 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -2182,7 +2200,7 @@
     <col min="4" max="4" width="8.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.77734375" style="26" customWidth="1"/>
+    <col min="7" max="7" width="26.77734375" style="23" customWidth="1"/>
     <col min="8" max="8" width="36.109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="39.88671875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.88671875" bestFit="1" customWidth="1"/>
@@ -2207,7 +2225,7 @@
       <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="26"/>
+      <c r="G1" s="23"/>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
@@ -2217,7 +2235,7 @@
       <c r="D2" s="7"/>
       <c r="E2" s="6"/>
       <c r="F2" s="8"/>
-      <c r="G2" s="26"/>
+      <c r="G2" s="23"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
@@ -2227,19 +2245,19 @@
         <v>6</v>
       </c>
       <c r="C3" s="18"/>
-      <c r="D3" s="19">
+      <c r="D3" s="36">
         <v>187</v>
       </c>
       <c r="E3" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="28">
+      <c r="F3" s="37">
         <v>1</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="G3" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="J3" s="26"/>
+      <c r="J3" s="23"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
@@ -2249,19 +2267,19 @@
         <v>7</v>
       </c>
       <c r="C4" s="18"/>
-      <c r="D4" s="19">
-        <v>137.44999999999999</v>
+      <c r="D4" s="36">
+        <v>137.45000000000002</v>
       </c>
       <c r="E4" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="37">
         <v>1</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="G4" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="J4" s="26"/>
+      <c r="J4" s="23"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
@@ -2271,19 +2289,19 @@
         <v>8</v>
       </c>
       <c r="C5" s="18"/>
-      <c r="D5" s="19">
+      <c r="D5" s="36">
         <v>184.8</v>
       </c>
       <c r="E5" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="28">
-        <v>0</v>
-      </c>
-      <c r="G5" s="26" t="s">
+      <c r="F5" s="37">
+        <v>3</v>
+      </c>
+      <c r="G5" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="J5" s="26"/>
+      <c r="J5" s="23"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
@@ -2293,19 +2311,19 @@
         <v>9</v>
       </c>
       <c r="C6" s="18"/>
-      <c r="D6" s="19">
+      <c r="D6" s="36">
         <v>145</v>
       </c>
       <c r="E6" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="37">
         <v>2</v>
       </c>
-      <c r="G6" s="26" t="s">
+      <c r="G6" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="J6" s="26"/>
+      <c r="J6" s="23"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
@@ -2315,19 +2333,19 @@
         <v>10</v>
       </c>
       <c r="C7" s="18"/>
-      <c r="D7" s="19">
+      <c r="D7" s="36">
         <v>237.31</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="F7" s="28">
-        <v>3</v>
-      </c>
-      <c r="G7" s="26" t="s">
+      <c r="F7" s="37">
+        <v>3</v>
+      </c>
+      <c r="G7" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="J7" s="26"/>
+      <c r="J7" s="23"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
@@ -2337,19 +2355,19 @@
         <v>11</v>
       </c>
       <c r="C8" s="18"/>
-      <c r="D8" s="19">
+      <c r="D8" s="36">
         <v>297</v>
       </c>
       <c r="E8" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="28">
-        <v>3</v>
-      </c>
-      <c r="G8" s="26" t="s">
+      <c r="F8" s="37">
+        <v>3</v>
+      </c>
+      <c r="G8" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="J8" s="26"/>
+      <c r="J8" s="23"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
@@ -2365,297 +2383,297 @@
       <c r="E9" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="F9" s="28">
-        <v>3</v>
-      </c>
-      <c r="G9" s="26" t="s">
+      <c r="F9" s="25">
+        <v>1</v>
+      </c>
+      <c r="G9" s="23" t="s">
         <v>315</v>
       </c>
-      <c r="J9" s="26"/>
+      <c r="J9" s="23"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="22">
+      <c r="C10" s="20"/>
+      <c r="D10" s="38">
         <v>156</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="28">
-        <v>3</v>
-      </c>
-      <c r="G10" s="26" t="s">
+      <c r="F10" s="39">
+        <v>3</v>
+      </c>
+      <c r="G10" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="J10" s="26"/>
+      <c r="J10" s="23"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="21"/>
-      <c r="D11" s="22">
+      <c r="C11" s="20"/>
+      <c r="D11" s="38">
         <v>174</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="28">
-        <v>3</v>
-      </c>
-      <c r="G11" s="26" t="s">
+      <c r="F11" s="39">
+        <v>3</v>
+      </c>
+      <c r="G11" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="J11" s="26"/>
+      <c r="J11" s="23"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="21"/>
-      <c r="D12" s="25">
+      <c r="C12" s="20"/>
+      <c r="D12" s="38">
         <v>305.48</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="39">
         <v>0</v>
       </c>
-      <c r="G12" s="26" t="s">
+      <c r="G12" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="J12" s="26"/>
+      <c r="J12" s="23"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="22">
+      <c r="C13" s="20"/>
+      <c r="D13" s="38">
         <v>255</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="28">
+      <c r="F13" s="39">
         <v>2</v>
       </c>
-      <c r="G13" s="26" t="s">
+      <c r="G13" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="J13" s="26"/>
+      <c r="J13" s="23"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="22">
+      <c r="C14" s="20"/>
+      <c r="D14" s="38">
         <v>197</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="F14" s="28">
+      <c r="F14" s="39">
         <v>2</v>
       </c>
-      <c r="G14" s="26" t="s">
+      <c r="G14" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="J14" s="26"/>
+      <c r="J14" s="23"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="22">
+      <c r="C15" s="20"/>
+      <c r="D15" s="38">
         <v>120</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="E15" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="F15" s="28">
-        <v>1</v>
-      </c>
-      <c r="G15" s="26" t="s">
+      <c r="F15" s="39">
+        <v>3</v>
+      </c>
+      <c r="G15" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="J15" s="26"/>
+      <c r="J15" s="23"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="22">
+      <c r="C16" s="20"/>
+      <c r="D16" s="38">
         <v>266.95</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="E16" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="39">
         <v>1</v>
       </c>
-      <c r="G16" s="26" t="s">
+      <c r="G16" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="J16" s="26"/>
+      <c r="J16" s="23"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="22">
+      <c r="C17" s="20"/>
+      <c r="D17" s="38">
         <v>264.11</v>
       </c>
-      <c r="E17" s="20" t="s">
+      <c r="E17" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="28">
-        <v>1</v>
-      </c>
-      <c r="G17" s="26" t="s">
+      <c r="F17" s="39">
+        <v>2</v>
+      </c>
+      <c r="G17" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="J17" s="26"/>
+      <c r="J17" s="23"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="21"/>
-      <c r="D18" s="22">
+      <c r="C18" s="20"/>
+      <c r="D18" s="38">
         <v>228</v>
       </c>
-      <c r="E18" s="20" t="s">
+      <c r="E18" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="39">
         <v>1</v>
       </c>
-      <c r="G18" s="26" t="s">
+      <c r="G18" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="J18" s="26"/>
+      <c r="J18" s="23"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="B19" s="20" t="s">
+      <c r="B19" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="21"/>
-      <c r="D19" s="22">
+      <c r="C19" s="20"/>
+      <c r="D19" s="38">
         <v>299</v>
       </c>
-      <c r="E19" s="20" t="s">
+      <c r="E19" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="28">
+      <c r="F19" s="39">
         <v>1</v>
       </c>
-      <c r="G19" s="26" t="s">
+      <c r="G19" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="J19" s="26"/>
+      <c r="J19" s="23"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="21"/>
-      <c r="D20" s="22">
+      <c r="C20" s="20"/>
+      <c r="D20" s="38">
         <v>308</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="E20" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="F20" s="28">
+      <c r="F20" s="39">
         <v>4</v>
       </c>
-      <c r="G20" s="26" t="s">
+      <c r="G20" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="J20" s="26"/>
+      <c r="J20" s="23"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="B21" s="20" t="s">
+      <c r="B21" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="21"/>
-      <c r="D21" s="22">
+      <c r="C21" s="20"/>
+      <c r="D21" s="38">
         <v>129</v>
       </c>
-      <c r="E21" s="20" t="s">
+      <c r="E21" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="F21" s="28">
-        <v>0</v>
-      </c>
-      <c r="G21" s="26" t="s">
+      <c r="F21" s="39">
+        <v>2</v>
+      </c>
+      <c r="G21" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="J21" s="26"/>
+      <c r="J21" s="23"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
-      <c r="B22" s="30" t="s">
+      <c r="B22" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="21"/>
-      <c r="D22" s="22">
+      <c r="C22" s="20"/>
+      <c r="D22" s="38">
         <v>122.45</v>
       </c>
-      <c r="E22" s="20" t="s">
+      <c r="E22" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="F22" s="28">
+      <c r="F22" s="39">
         <v>2</v>
       </c>
-      <c r="G22" s="26" t="s">
+      <c r="G22" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="J22" s="26"/>
+      <c r="J22" s="23"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
@@ -2671,14 +2689,14 @@
       <c r="E23" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="F23" s="28">
+      <c r="F23" s="25">
         <v>1</v>
       </c>
-      <c r="G23" s="26" t="s">
+      <c r="G23" s="23" t="s">
         <v>95</v>
       </c>
       <c r="I23" s="14"/>
-      <c r="J23" s="26"/>
+      <c r="J23" s="23"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
@@ -2694,14 +2712,14 @@
       <c r="E24" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="F24" s="28">
+      <c r="F24" s="25">
         <v>4</v>
       </c>
-      <c r="G24" s="26" t="s">
+      <c r="G24" s="23" t="s">
         <v>96</v>
       </c>
       <c r="I24" s="14"/>
-      <c r="J24" s="26"/>
+      <c r="J24" s="23"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
@@ -2717,41 +2735,42 @@
       <c r="E25" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="F25" s="28">
-        <v>1</v>
-      </c>
-      <c r="G25" s="26" t="s">
+      <c r="F25" s="25">
+        <v>3</v>
+      </c>
+      <c r="G25" s="23" t="s">
         <v>97</v>
       </c>
       <c r="I25" s="14"/>
-      <c r="J25" s="26"/>
+      <c r="J25" s="23"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="23" t="s">
+      <c r="A26" s="21" t="s">
         <v>75</v>
       </c>
       <c r="B26" s="10"/>
       <c r="D26" s="12"/>
       <c r="E26" s="10"/>
-      <c r="F26" s="28"/>
+      <c r="F26" s="25"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="D27" s="11">
+      <c r="C27" s="40"/>
+      <c r="D27" s="41">
         <v>249.23000000000002</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="F27" s="28">
+      <c r="F27" s="25">
         <v>1</v>
       </c>
-      <c r="G27" s="26" t="s">
+      <c r="G27" s="23" t="s">
         <v>98</v>
       </c>
     </row>
@@ -2768,10 +2787,10 @@
       <c r="E28" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="F28" s="28">
+      <c r="F28" s="25">
         <v>1</v>
       </c>
-      <c r="G28" s="26" t="s">
+      <c r="G28" s="23" t="s">
         <v>99</v>
       </c>
     </row>
@@ -2788,10 +2807,10 @@
       <c r="E29" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F29" s="28">
+      <c r="F29" s="25">
         <v>2</v>
       </c>
-      <c r="G29" s="26" t="s">
+      <c r="G29" s="23" t="s">
         <v>100</v>
       </c>
     </row>
@@ -2808,10 +2827,10 @@
       <c r="E30" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="F30" s="28">
+      <c r="F30" s="25">
         <v>1</v>
       </c>
-      <c r="G30" s="26" t="s">
+      <c r="G30" s="23" t="s">
         <v>103</v>
       </c>
     </row>
@@ -2828,10 +2847,10 @@
       <c r="E31" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F31" s="28">
+      <c r="F31" s="25">
         <v>7</v>
       </c>
-      <c r="G31" s="26" t="s">
+      <c r="G31" s="23" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2848,10 +2867,10 @@
       <c r="E32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F32" s="28">
+      <c r="F32" s="25">
         <v>2</v>
       </c>
-      <c r="G32" s="26" t="s">
+      <c r="G32" s="23" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2868,10 +2887,10 @@
       <c r="E33" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F33" s="28">
-        <v>3</v>
-      </c>
-      <c r="G33" s="26" t="s">
+      <c r="F33" s="25">
+        <v>3</v>
+      </c>
+      <c r="G33" s="23" t="s">
         <v>106</v>
       </c>
     </row>
@@ -2879,17 +2898,17 @@
       <c r="B34" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C34" s="31"/>
+      <c r="C34" s="28"/>
       <c r="D34" s="12">
         <v>134.22999999999999</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F34" s="32">
+      <c r="F34" s="29">
         <v>2</v>
       </c>
-      <c r="G34" s="33" t="s">
+      <c r="G34" s="30" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2906,10 +2925,10 @@
       <c r="E35" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F35" s="28">
+      <c r="F35" s="25">
         <v>2</v>
       </c>
-      <c r="G35" s="26" t="s">
+      <c r="G35" s="23" t="s">
         <v>107</v>
       </c>
     </row>
@@ -2926,10 +2945,10 @@
       <c r="E36" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="F36" s="28">
-        <v>3</v>
-      </c>
-      <c r="G36" s="26" t="s">
+      <c r="F36" s="25">
+        <v>3</v>
+      </c>
+      <c r="G36" s="23" t="s">
         <v>108</v>
       </c>
     </row>
@@ -2946,10 +2965,10 @@
       <c r="E37" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F37" s="28">
-        <v>3</v>
-      </c>
-      <c r="G37" s="26" t="s">
+      <c r="F37" s="25">
+        <v>3</v>
+      </c>
+      <c r="G37" s="23" t="s">
         <v>109</v>
       </c>
     </row>
@@ -2966,10 +2985,10 @@
       <c r="E38" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="F38" s="28">
+      <c r="F38" s="25">
         <v>10</v>
       </c>
-      <c r="G38" s="26" t="s">
+      <c r="G38" s="23" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2986,10 +3005,10 @@
       <c r="E39" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F39" s="28">
+      <c r="F39" s="25">
         <v>1</v>
       </c>
-      <c r="G39" s="26" t="s">
+      <c r="G39" s="23" t="s">
         <v>111</v>
       </c>
     </row>
@@ -2997,17 +3016,17 @@
       <c r="B40" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="C40" s="31"/>
+      <c r="C40" s="28"/>
       <c r="D40" s="12">
         <v>182.9</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="F40" s="32">
+      <c r="F40" s="29">
         <v>0</v>
       </c>
-      <c r="G40" s="33" t="s">
+      <c r="G40" s="30" t="s">
         <v>338</v>
       </c>
     </row>
@@ -3024,7 +3043,7 @@
       <c r="E41" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="F41" s="28">
+      <c r="F41" s="25">
         <v>4</v>
       </c>
       <c r="G41" s="9" t="s">
@@ -3044,7 +3063,7 @@
       <c r="E42" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="F42" s="28">
+      <c r="F42" s="25">
         <v>2</v>
       </c>
       <c r="G42" s="9" t="s">
@@ -3064,7 +3083,7 @@
       <c r="E43" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="F43" s="28">
+      <c r="F43" s="25">
         <v>2</v>
       </c>
       <c r="G43" s="9" t="s">
@@ -3084,7 +3103,7 @@
       <c r="E44" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="F44" s="28">
+      <c r="F44" s="25">
         <v>4</v>
       </c>
       <c r="G44" s="9" t="s">
@@ -3104,7 +3123,7 @@
       <c r="E45" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="F45" s="28">
+      <c r="F45" s="25">
         <v>3</v>
       </c>
       <c r="G45" s="9" t="s">
@@ -3124,7 +3143,7 @@
       <c r="E46" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="F46" s="28">
+      <c r="F46" s="25">
         <v>6</v>
       </c>
       <c r="G46" s="9" t="s">
@@ -3144,7 +3163,7 @@
       <c r="E47" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="F47" s="28">
+      <c r="F47" s="25">
         <v>3</v>
       </c>
       <c r="G47" s="9" t="s">
@@ -3164,7 +3183,7 @@
       <c r="E48" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="F48" s="28">
+      <c r="F48" s="25">
         <v>5</v>
       </c>
       <c r="G48" s="9" t="s">
@@ -3175,20 +3194,20 @@
       <c r="A49" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="B49" s="34" t="s">
+      <c r="B49" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="C49" s="35"/>
-      <c r="D49" s="36">
+      <c r="C49" s="32"/>
+      <c r="D49" s="33">
         <v>550</v>
       </c>
-      <c r="E49" s="34" t="s">
+      <c r="E49" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="F49" s="37">
-        <v>3</v>
-      </c>
-      <c r="G49" s="34" t="s">
+      <c r="F49" s="34">
+        <v>3</v>
+      </c>
+      <c r="G49" s="31" t="s">
         <v>140</v>
       </c>
     </row>
@@ -3196,20 +3215,20 @@
       <c r="A50" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="B50" s="34" t="s">
+      <c r="B50" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="C50" s="35"/>
-      <c r="D50" s="36">
+      <c r="C50" s="32"/>
+      <c r="D50" s="33">
         <v>550</v>
       </c>
-      <c r="E50" s="34" t="s">
+      <c r="E50" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="F50" s="37">
+      <c r="F50" s="34">
         <v>1</v>
       </c>
-      <c r="G50" s="34" t="s">
+      <c r="G50" s="31" t="s">
         <v>143</v>
       </c>
     </row>
@@ -3218,14 +3237,14 @@
       <c r="B51" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="C51" s="31"/>
+      <c r="C51" s="28"/>
       <c r="D51" s="12">
         <v>302.5</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="F51" s="32">
+      <c r="F51" s="29">
         <v>2</v>
       </c>
       <c r="G51" s="10" t="s">
@@ -3233,19 +3252,19 @@
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="27" t="s">
+      <c r="A52" s="24" t="s">
         <v>144</v>
       </c>
       <c r="B52" s="9"/>
       <c r="D52" s="11"/>
       <c r="E52" s="9"/>
-      <c r="F52" s="28"/>
+      <c r="F52" s="25"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="B53" s="29" t="s">
+      <c r="B53" s="26" t="s">
         <v>188</v>
       </c>
       <c r="D53" s="11">
@@ -3254,7 +3273,7 @@
       <c r="E53" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="F53" s="28">
+      <c r="F53" s="25">
         <v>3</v>
       </c>
       <c r="G53" s="9" t="s">
@@ -3265,7 +3284,7 @@
       <c r="A54" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="B54" s="29" t="s">
+      <c r="B54" s="26" t="s">
         <v>189</v>
       </c>
       <c r="D54" s="11">
@@ -3274,7 +3293,7 @@
       <c r="E54" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="F54" s="28">
+      <c r="F54" s="25">
         <v>3</v>
       </c>
       <c r="G54" s="9" t="s">
@@ -3285,7 +3304,7 @@
       <c r="A55" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="B55" s="29" t="s">
+      <c r="B55" s="26" t="s">
         <v>190</v>
       </c>
       <c r="D55" s="11">
@@ -3294,7 +3313,7 @@
       <c r="E55" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="F55" s="28">
+      <c r="F55" s="25">
         <v>3</v>
       </c>
       <c r="G55" s="9" t="s">
@@ -3305,7 +3324,7 @@
       <c r="A56" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="B56" s="29" t="s">
+      <c r="B56" s="26" t="s">
         <v>191</v>
       </c>
       <c r="D56" s="11">
@@ -3314,7 +3333,7 @@
       <c r="E56" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="F56" s="28">
+      <c r="F56" s="25">
         <v>3</v>
       </c>
       <c r="G56" s="9" t="s">
@@ -3325,7 +3344,7 @@
       <c r="A57" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="B57" s="29" t="s">
+      <c r="B57" s="26" t="s">
         <v>192</v>
       </c>
       <c r="D57" s="11">
@@ -3334,7 +3353,7 @@
       <c r="E57" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="F57" s="28">
+      <c r="F57" s="25">
         <v>3</v>
       </c>
       <c r="G57" s="9" t="s">
@@ -3345,7 +3364,7 @@
       <c r="A58" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="B58" s="29" t="s">
+      <c r="B58" s="26" t="s">
         <v>193</v>
       </c>
       <c r="D58" s="11">
@@ -3354,7 +3373,7 @@
       <c r="E58" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="F58" s="28">
+      <c r="F58" s="25">
         <v>3</v>
       </c>
       <c r="G58" s="9" t="s">
@@ -3365,7 +3384,7 @@
       <c r="A59" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="B59" s="29" t="s">
+      <c r="B59" s="26" t="s">
         <v>194</v>
       </c>
       <c r="D59" s="11">
@@ -3374,7 +3393,7 @@
       <c r="E59" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="F59" s="28">
+      <c r="F59" s="25">
         <v>1</v>
       </c>
       <c r="G59" s="9" t="s">
@@ -3385,7 +3404,7 @@
       <c r="A60" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="B60" s="29" t="s">
+      <c r="B60" s="26" t="s">
         <v>195</v>
       </c>
       <c r="C60" s="5"/>
@@ -3395,7 +3414,7 @@
       <c r="E60" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="F60" s="28">
+      <c r="F60" s="25">
         <v>3</v>
       </c>
       <c r="G60" s="9" t="s">
@@ -3406,7 +3425,7 @@
       <c r="A61" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="B61" s="29" t="s">
+      <c r="B61" s="26" t="s">
         <v>196</v>
       </c>
       <c r="C61" s="5"/>
@@ -3416,7 +3435,7 @@
       <c r="E61" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="F61" s="28">
+      <c r="F61" s="25">
         <v>3</v>
       </c>
       <c r="G61" s="9" t="s">
@@ -3427,7 +3446,7 @@
       <c r="A62" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="B62" s="29" t="s">
+      <c r="B62" s="26" t="s">
         <v>197</v>
       </c>
       <c r="C62" s="5"/>
@@ -3437,7 +3456,7 @@
       <c r="E62" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="F62" s="28">
+      <c r="F62" s="25">
         <v>3</v>
       </c>
       <c r="G62" s="9" t="s">
@@ -3448,7 +3467,7 @@
       <c r="A63" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="B63" s="29" t="s">
+      <c r="B63" s="26" t="s">
         <v>198</v>
       </c>
       <c r="D63" s="11">
@@ -3457,7 +3476,7 @@
       <c r="E63" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="F63" s="28">
+      <c r="F63" s="25">
         <v>3</v>
       </c>
       <c r="G63" s="9" t="s">
@@ -3468,7 +3487,7 @@
       <c r="A64" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="B64" s="29" t="s">
+      <c r="B64" s="26" t="s">
         <v>199</v>
       </c>
       <c r="D64" s="11">
@@ -3477,7 +3496,7 @@
       <c r="E64" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="F64" s="28">
+      <c r="F64" s="25">
         <v>3</v>
       </c>
       <c r="G64" s="9" t="s">
@@ -3488,7 +3507,7 @@
       <c r="A65" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="B65" s="29" t="s">
+      <c r="B65" s="26" t="s">
         <v>200</v>
       </c>
       <c r="D65" s="11">
@@ -3497,7 +3516,7 @@
       <c r="E65" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="F65" s="28">
+      <c r="F65" s="25">
         <v>3</v>
       </c>
       <c r="G65" s="9" t="s">
@@ -3508,7 +3527,7 @@
       <c r="A66" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="B66" s="29" t="s">
+      <c r="B66" s="26" t="s">
         <v>201</v>
       </c>
       <c r="D66" s="11">
@@ -3517,7 +3536,7 @@
       <c r="E66" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="F66" s="28">
+      <c r="F66" s="25">
         <v>3</v>
       </c>
       <c r="G66" s="9" t="s">
@@ -3528,7 +3547,7 @@
       <c r="A67" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="B67" s="29" t="s">
+      <c r="B67" s="26" t="s">
         <v>202</v>
       </c>
       <c r="D67" s="11">
@@ -3537,7 +3556,7 @@
       <c r="E67" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="F67" s="28">
+      <c r="F67" s="25">
         <v>3</v>
       </c>
       <c r="G67" s="9" t="s">
@@ -3548,7 +3567,7 @@
       <c r="A68" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="B68" s="29" t="s">
+      <c r="B68" s="26" t="s">
         <v>203</v>
       </c>
       <c r="D68" s="11">
@@ -3557,7 +3576,7 @@
       <c r="E68" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="F68" s="28">
+      <c r="F68" s="25">
         <v>3</v>
       </c>
       <c r="G68" s="9" t="s">
@@ -3568,7 +3587,7 @@
       <c r="A69" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="B69" s="29" t="s">
+      <c r="B69" s="26" t="s">
         <v>204</v>
       </c>
       <c r="D69" s="11">
@@ -3577,7 +3596,7 @@
       <c r="E69" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="F69" s="28">
+      <c r="F69" s="25">
         <v>3</v>
       </c>
       <c r="G69" s="9" t="s">
@@ -3588,7 +3607,7 @@
       <c r="A70" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="B70" s="29" t="s">
+      <c r="B70" s="26" t="s">
         <v>205</v>
       </c>
       <c r="D70" s="11">
@@ -3597,7 +3616,7 @@
       <c r="E70" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="F70" s="28">
+      <c r="F70" s="25">
         <v>3</v>
       </c>
       <c r="G70" s="9" t="s">
@@ -3608,7 +3627,7 @@
       <c r="A71" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="B71" s="29" t="s">
+      <c r="B71" s="26" t="s">
         <v>204</v>
       </c>
       <c r="D71" s="11">
@@ -3617,7 +3636,7 @@
       <c r="E71" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="F71" s="28">
+      <c r="F71" s="25">
         <v>3</v>
       </c>
       <c r="G71" s="9" t="s">
@@ -3628,7 +3647,7 @@
       <c r="A72" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="B72" s="29" t="s">
+      <c r="B72" s="26" t="s">
         <v>205</v>
       </c>
       <c r="D72" s="11">
@@ -3637,7 +3656,7 @@
       <c r="E72" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="F72" s="28">
+      <c r="F72" s="25">
         <v>3</v>
       </c>
       <c r="G72" s="9" t="s">
@@ -3648,7 +3667,7 @@
       <c r="A73" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="B73" s="29" t="s">
+      <c r="B73" s="26" t="s">
         <v>206</v>
       </c>
       <c r="D73" s="11">
@@ -3657,7 +3676,7 @@
       <c r="E73" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="F73" s="28">
+      <c r="F73" s="25">
         <v>3</v>
       </c>
       <c r="G73" s="9" t="s">
@@ -3668,7 +3687,7 @@
       <c r="A74" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="B74" s="29" t="s">
+      <c r="B74" s="26" t="s">
         <v>207</v>
       </c>
       <c r="D74" s="11">
@@ -3677,7 +3696,7 @@
       <c r="E74" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="F74" s="28">
+      <c r="F74" s="25">
         <v>1</v>
       </c>
       <c r="G74" s="9" t="s">
@@ -3688,7 +3707,7 @@
       <c r="A75" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="B75" s="29" t="s">
+      <c r="B75" s="26" t="s">
         <v>208</v>
       </c>
       <c r="D75" s="11">
@@ -3697,7 +3716,7 @@
       <c r="E75" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="F75" s="28">
+      <c r="F75" s="25">
         <v>3</v>
       </c>
       <c r="G75" s="9" t="s">
@@ -3708,7 +3727,7 @@
       <c r="A76" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="B76" s="29" t="s">
+      <c r="B76" s="26" t="s">
         <v>209</v>
       </c>
       <c r="D76" s="11">
@@ -3717,7 +3736,7 @@
       <c r="E76" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="F76" s="28">
+      <c r="F76" s="25">
         <v>3</v>
       </c>
       <c r="G76" s="9" t="s">
@@ -3728,7 +3747,7 @@
       <c r="A77" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="B77" s="29" t="s">
+      <c r="B77" s="26" t="s">
         <v>210</v>
       </c>
       <c r="D77" s="11">
@@ -3737,7 +3756,7 @@
       <c r="E77" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="F77" s="28">
+      <c r="F77" s="25">
         <v>3</v>
       </c>
       <c r="G77" s="9" t="s">
@@ -3748,7 +3767,7 @@
       <c r="A78" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="B78" s="29" t="s">
+      <c r="B78" s="26" t="s">
         <v>211</v>
       </c>
       <c r="D78" s="11">
@@ -3757,7 +3776,7 @@
       <c r="E78" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="F78" s="28">
+      <c r="F78" s="25">
         <v>3</v>
       </c>
       <c r="G78" s="9" t="s">
@@ -3768,7 +3787,7 @@
       <c r="A79" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="B79" s="29" t="s">
+      <c r="B79" s="26" t="s">
         <v>212</v>
       </c>
       <c r="D79" s="11">
@@ -3777,7 +3796,7 @@
       <c r="E79" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="F79" s="28">
+      <c r="F79" s="25">
         <v>3</v>
       </c>
       <c r="G79" s="9" t="s">
@@ -3788,7 +3807,7 @@
       <c r="A80" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="B80" s="29" t="s">
+      <c r="B80" s="26" t="s">
         <v>213</v>
       </c>
       <c r="D80" s="11">
@@ -3797,7 +3816,7 @@
       <c r="E80" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="F80" s="28">
+      <c r="F80" s="25">
         <v>3</v>
       </c>
       <c r="G80" s="9" t="s">
@@ -3808,7 +3827,7 @@
       <c r="A81" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="B81" s="29" t="s">
+      <c r="B81" s="26" t="s">
         <v>214</v>
       </c>
       <c r="D81" s="11">
@@ -3817,7 +3836,7 @@
       <c r="E81" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="F81" s="28">
+      <c r="F81" s="25">
         <v>3</v>
       </c>
       <c r="G81" s="9" t="s">
@@ -3828,7 +3847,7 @@
       <c r="A82" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="B82" s="29" t="s">
+      <c r="B82" s="26" t="s">
         <v>215</v>
       </c>
       <c r="D82" s="11">
@@ -3837,7 +3856,7 @@
       <c r="E82" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="F82" s="28">
+      <c r="F82" s="25">
         <v>3</v>
       </c>
       <c r="G82" s="9" t="s">
@@ -3848,7 +3867,7 @@
       <c r="A83" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="B83" s="29" t="s">
+      <c r="B83" s="26" t="s">
         <v>216</v>
       </c>
       <c r="C83" s="5"/>
@@ -3858,7 +3877,7 @@
       <c r="E83" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="F83" s="28">
+      <c r="F83" s="25">
         <v>3</v>
       </c>
       <c r="G83" s="9" t="s">
@@ -3869,7 +3888,7 @@
       <c r="A84" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="B84" s="29" t="s">
+      <c r="B84" s="26" t="s">
         <v>217</v>
       </c>
       <c r="C84" s="5"/>
@@ -3879,7 +3898,7 @@
       <c r="E84" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="F84" s="28">
+      <c r="F84" s="25">
         <v>3</v>
       </c>
       <c r="G84" s="9" t="s">
@@ -3890,7 +3909,7 @@
       <c r="A85" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="B85" s="29" t="s">
+      <c r="B85" s="26" t="s">
         <v>218</v>
       </c>
       <c r="C85" s="5"/>
@@ -3900,7 +3919,7 @@
       <c r="E85" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="F85" s="28">
+      <c r="F85" s="25">
         <v>3</v>
       </c>
       <c r="G85" s="9" t="s">
@@ -3911,7 +3930,7 @@
       <c r="A86" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="B86" s="29" t="s">
+      <c r="B86" s="26" t="s">
         <v>219</v>
       </c>
       <c r="C86" s="5"/>
@@ -3921,7 +3940,7 @@
       <c r="E86" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="F86" s="28">
+      <c r="F86" s="25">
         <v>3</v>
       </c>
       <c r="G86" s="9" t="s">
@@ -3932,7 +3951,7 @@
       <c r="A87" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="B87" s="29" t="s">
+      <c r="B87" s="26" t="s">
         <v>220</v>
       </c>
       <c r="C87" s="5"/>
@@ -3942,7 +3961,7 @@
       <c r="E87" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="F87" s="28">
+      <c r="F87" s="25">
         <v>3</v>
       </c>
       <c r="G87" s="9" t="s">
@@ -3953,7 +3972,7 @@
       <c r="A88" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="B88" s="29" t="s">
+      <c r="B88" s="26" t="s">
         <v>221</v>
       </c>
       <c r="C88" s="5"/>
@@ -3963,7 +3982,7 @@
       <c r="E88" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="F88" s="28">
+      <c r="F88" s="25">
         <v>3</v>
       </c>
       <c r="G88" s="9" t="s">
@@ -3974,7 +3993,7 @@
       <c r="A89" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="B89" s="29" t="s">
+      <c r="B89" s="26" t="s">
         <v>222</v>
       </c>
       <c r="C89" s="5"/>
@@ -3984,7 +4003,7 @@
       <c r="E89" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F89" s="28">
+      <c r="F89" s="25">
         <v>3</v>
       </c>
       <c r="G89" s="9" t="s">
@@ -3995,7 +4014,7 @@
       <c r="A90" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="B90" s="29" t="s">
+      <c r="B90" s="26" t="s">
         <v>223</v>
       </c>
       <c r="C90" s="5"/>
@@ -4005,7 +4024,7 @@
       <c r="E90" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="F90" s="28">
+      <c r="F90" s="25">
         <v>3</v>
       </c>
       <c r="G90" s="9" t="s">
@@ -4016,7 +4035,7 @@
       <c r="A91" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="B91" s="29" t="s">
+      <c r="B91" s="26" t="s">
         <v>224</v>
       </c>
       <c r="C91" s="5"/>
@@ -4026,7 +4045,7 @@
       <c r="E91" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="F91" s="28">
+      <c r="F91" s="25">
         <v>3</v>
       </c>
       <c r="G91" s="9" t="s">
@@ -4037,7 +4056,7 @@
       <c r="A92" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="B92" s="29" t="s">
+      <c r="B92" s="26" t="s">
         <v>225</v>
       </c>
       <c r="C92" s="5"/>
@@ -4047,7 +4066,7 @@
       <c r="E92" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="F92" s="28">
+      <c r="F92" s="25">
         <v>3</v>
       </c>
       <c r="G92" s="9" t="s">
@@ -4058,7 +4077,7 @@
       <c r="A93" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="B93" s="29" t="s">
+      <c r="B93" s="26" t="s">
         <v>226</v>
       </c>
       <c r="C93" s="5"/>
@@ -4068,7 +4087,7 @@
       <c r="E93" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="F93" s="28">
+      <c r="F93" s="25">
         <v>3</v>
       </c>
       <c r="G93" s="9" t="s">
@@ -4079,7 +4098,7 @@
       <c r="A94" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="B94" s="29" t="s">
+      <c r="B94" s="26" t="s">
         <v>227</v>
       </c>
       <c r="C94" s="5"/>
@@ -4089,7 +4108,7 @@
       <c r="E94" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="F94" s="28">
+      <c r="F94" s="25">
         <v>3</v>
       </c>
       <c r="G94" s="9" t="s">
@@ -4100,7 +4119,7 @@
       <c r="A95" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="B95" s="29" t="s">
+      <c r="B95" s="26" t="s">
         <v>228</v>
       </c>
       <c r="C95" s="5"/>
@@ -4110,7 +4129,7 @@
       <c r="E95" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="F95" s="28">
+      <c r="F95" s="25">
         <v>3</v>
       </c>
       <c r="G95" s="9" t="s">
@@ -4131,7 +4150,7 @@
       <c r="E96" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="F96" s="28">
+      <c r="F96" s="25">
         <v>3</v>
       </c>
       <c r="G96" s="9" t="s">
@@ -4155,7 +4174,7 @@
       <c r="E97" s="9" t="s">
         <v>360</v>
       </c>
-      <c r="F97" s="28">
+      <c r="F97" s="25">
         <v>3</v>
       </c>
       <c r="G97" s="9" t="s">
@@ -4179,7 +4198,7 @@
       <c r="E98" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="F98" s="28">
+      <c r="F98" s="25">
         <v>2</v>
       </c>
       <c r="G98" s="9" t="s">
@@ -4203,7 +4222,7 @@
       <c r="E99" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="F99" s="28">
+      <c r="F99" s="25">
         <v>3</v>
       </c>
       <c r="G99" s="9" t="s">
@@ -4227,7 +4246,7 @@
       <c r="E100" s="9" t="s">
         <v>363</v>
       </c>
-      <c r="F100" s="28">
+      <c r="F100" s="25">
         <v>6</v>
       </c>
       <c r="G100" s="9" t="s">
@@ -4251,7 +4270,7 @@
       <c r="E101" s="9" t="s">
         <v>364</v>
       </c>
-      <c r="F101" s="28">
+      <c r="F101" s="25">
         <v>3</v>
       </c>
       <c r="G101" s="9" t="s">
@@ -4275,7 +4294,7 @@
       <c r="E102" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="F102" s="28">
+      <c r="F102" s="25">
         <v>3</v>
       </c>
       <c r="G102" s="9" t="s">
@@ -4299,7 +4318,7 @@
       <c r="E103" s="9" t="s">
         <v>366</v>
       </c>
-      <c r="F103" s="28">
+      <c r="F103" s="25">
         <v>3</v>
       </c>
       <c r="G103" s="9" t="s">
@@ -4323,7 +4342,7 @@
       <c r="E104" s="9" t="s">
         <v>367</v>
       </c>
-      <c r="F104" s="28">
+      <c r="F104" s="25">
         <v>3</v>
       </c>
       <c r="G104" s="9" t="s">
@@ -4347,7 +4366,7 @@
       <c r="E105" s="9" t="s">
         <v>368</v>
       </c>
-      <c r="F105" s="28">
+      <c r="F105" s="25">
         <v>3</v>
       </c>
       <c r="G105" s="9" t="s">
@@ -4371,7 +4390,7 @@
       <c r="E106" s="9" t="s">
         <v>369</v>
       </c>
-      <c r="F106" s="28">
+      <c r="F106" s="25">
         <v>3</v>
       </c>
       <c r="G106" s="9" t="s">
@@ -4395,7 +4414,7 @@
       <c r="E107" s="9" t="s">
         <v>370</v>
       </c>
-      <c r="F107" s="28">
+      <c r="F107" s="25">
         <v>3</v>
       </c>
       <c r="G107" s="9" t="s">
@@ -4419,7 +4438,7 @@
       <c r="E108" s="9" t="s">
         <v>371</v>
       </c>
-      <c r="F108" s="28">
+      <c r="F108" s="25">
         <v>3</v>
       </c>
       <c r="G108" s="9" t="s">
@@ -4443,7 +4462,7 @@
       <c r="E109" s="9" t="s">
         <v>372</v>
       </c>
-      <c r="F109" s="28">
+      <c r="F109" s="25">
         <v>3</v>
       </c>
       <c r="G109" s="9" t="s">
@@ -4467,7 +4486,7 @@
       <c r="E110" s="9" t="s">
         <v>373</v>
       </c>
-      <c r="F110" s="28">
+      <c r="F110" s="25">
         <v>3</v>
       </c>
       <c r="G110" s="9" t="s">
@@ -4491,7 +4510,7 @@
       <c r="E111" s="9" t="s">
         <v>374</v>
       </c>
-      <c r="F111" s="28">
+      <c r="F111" s="25">
         <v>3</v>
       </c>
       <c r="G111" s="9" t="s">
@@ -4515,7 +4534,7 @@
       <c r="E112" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="F112" s="28">
+      <c r="F112" s="25">
         <v>3</v>
       </c>
       <c r="G112" s="9" t="s">
@@ -4539,7 +4558,7 @@
       <c r="E113" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="F113" s="28">
+      <c r="F113" s="25">
         <v>3</v>
       </c>
       <c r="G113" s="9" t="s">
@@ -4563,7 +4582,7 @@
       <c r="E114" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="F114" s="28">
+      <c r="F114" s="25">
         <v>3</v>
       </c>
       <c r="G114" s="9" t="s">
@@ -4587,7 +4606,7 @@
       <c r="E115" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="F115" s="28">
+      <c r="F115" s="25">
         <v>3</v>
       </c>
       <c r="G115" s="9" t="s">
@@ -4611,7 +4630,7 @@
       <c r="E116" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="F116" s="28">
+      <c r="F116" s="25">
         <v>3</v>
       </c>
       <c r="G116" s="9" t="s">
@@ -4635,7 +4654,7 @@
       <c r="E117" s="9" t="s">
         <v>380</v>
       </c>
-      <c r="F117" s="28">
+      <c r="F117" s="25">
         <v>3</v>
       </c>
       <c r="G117" s="9" t="s">
@@ -4659,7 +4678,7 @@
       <c r="E118" s="9" t="s">
         <v>381</v>
       </c>
-      <c r="F118" s="28">
+      <c r="F118" s="25">
         <v>3</v>
       </c>
       <c r="G118" s="9" t="s">
@@ -4683,7 +4702,7 @@
       <c r="E119" s="9" t="s">
         <v>382</v>
       </c>
-      <c r="F119" s="28">
+      <c r="F119" s="25">
         <v>3</v>
       </c>
       <c r="G119" s="9" t="s">
@@ -4707,7 +4726,7 @@
       <c r="E120" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="F120" s="28">
+      <c r="F120" s="25">
         <v>3</v>
       </c>
       <c r="G120" s="9" t="s">
@@ -4731,7 +4750,7 @@
       <c r="E121" s="9" t="s">
         <v>384</v>
       </c>
-      <c r="F121" s="28">
+      <c r="F121" s="25">
         <v>3</v>
       </c>
       <c r="G121" s="9" t="s">
@@ -4755,7 +4774,7 @@
       <c r="E122" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="F122" s="28">
+      <c r="F122" s="25">
         <v>3</v>
       </c>
       <c r="G122" s="9" t="s">
@@ -4779,7 +4798,7 @@
       <c r="E123" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="F123" s="28">
+      <c r="F123" s="25">
         <v>3</v>
       </c>
       <c r="G123" s="9" t="s">
@@ -4803,7 +4822,7 @@
       <c r="E124" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="F124" s="28">
+      <c r="F124" s="25">
         <v>3</v>
       </c>
       <c r="G124" s="9" t="s">
@@ -4827,7 +4846,7 @@
       <c r="E125" s="9" t="s">
         <v>388</v>
       </c>
-      <c r="F125" s="28">
+      <c r="F125" s="25">
         <v>3</v>
       </c>
       <c r="G125" s="9" t="s">
@@ -4851,7 +4870,7 @@
       <c r="E126" s="9" t="s">
         <v>389</v>
       </c>
-      <c r="F126" s="28">
+      <c r="F126" s="25">
         <v>3</v>
       </c>
       <c r="G126" s="9" t="s">
@@ -4875,7 +4894,7 @@
       <c r="E127" s="9" t="s">
         <v>390</v>
       </c>
-      <c r="F127" s="28">
+      <c r="F127" s="25">
         <v>3</v>
       </c>
       <c r="G127" s="9" t="s">
@@ -4899,7 +4918,7 @@
       <c r="E128" s="9" t="s">
         <v>391</v>
       </c>
-      <c r="F128" s="28">
+      <c r="F128" s="25">
         <v>3</v>
       </c>
       <c r="G128" s="9" t="s">
@@ -4923,7 +4942,7 @@
       <c r="E129" s="9" t="s">
         <v>392</v>
       </c>
-      <c r="F129" s="28">
+      <c r="F129" s="25">
         <v>3</v>
       </c>
       <c r="G129" s="9" t="s">
@@ -4947,7 +4966,7 @@
       <c r="E130" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="F130" s="28">
+      <c r="F130" s="25">
         <v>3</v>
       </c>
       <c r="G130" s="9" t="s">
@@ -4971,7 +4990,7 @@
       <c r="E131" s="9" t="s">
         <v>394</v>
       </c>
-      <c r="F131" s="28">
+      <c r="F131" s="25">
         <v>3</v>
       </c>
       <c r="G131" s="9" t="s">
@@ -4995,7 +5014,7 @@
       <c r="E132" s="9" t="s">
         <v>395</v>
       </c>
-      <c r="F132" s="28">
+      <c r="F132" s="25">
         <v>3</v>
       </c>
       <c r="G132" s="9" t="s">
@@ -5019,7 +5038,7 @@
       <c r="E133" s="9" t="s">
         <v>396</v>
       </c>
-      <c r="F133" s="28">
+      <c r="F133" s="25">
         <v>3</v>
       </c>
       <c r="G133" s="9" t="s">
@@ -5043,7 +5062,7 @@
       <c r="E134" s="9" t="s">
         <v>397</v>
       </c>
-      <c r="F134" s="28">
+      <c r="F134" s="25">
         <v>3</v>
       </c>
       <c r="G134" s="9" t="s">
@@ -5067,7 +5086,7 @@
       <c r="E135" s="9" t="s">
         <v>398</v>
       </c>
-      <c r="F135" s="28">
+      <c r="F135" s="25">
         <v>3</v>
       </c>
       <c r="G135" s="9" t="s">
@@ -5091,7 +5110,7 @@
       <c r="E136" s="9" t="s">
         <v>399</v>
       </c>
-      <c r="F136" s="28">
+      <c r="F136" s="25">
         <v>3</v>
       </c>
       <c r="G136" s="9" t="s">
@@ -5115,7 +5134,7 @@
       <c r="E137" s="9" t="s">
         <v>400</v>
       </c>
-      <c r="F137" s="28">
+      <c r="F137" s="25">
         <v>3</v>
       </c>
       <c r="G137" s="9" t="s">
@@ -5139,7 +5158,7 @@
       <c r="E138" s="9" t="s">
         <v>401</v>
       </c>
-      <c r="F138" s="28">
+      <c r="F138" s="25">
         <v>3</v>
       </c>
       <c r="G138" s="9" t="s">
@@ -5157,7 +5176,7 @@
         <v>8.4700000000000006</v>
       </c>
       <c r="E139" s="10"/>
-      <c r="F139" s="28">
+      <c r="F139" s="25">
         <v>3</v>
       </c>
     </row>
@@ -5167,7 +5186,7 @@
       <c r="C140" s="5"/>
       <c r="D140" s="12"/>
       <c r="E140" s="10"/>
-      <c r="F140" s="28"/>
+      <c r="F140" s="25"/>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" s="5"/>
@@ -5175,7 +5194,7 @@
       <c r="C141" s="5"/>
       <c r="D141" s="12"/>
       <c r="E141" s="10"/>
-      <c r="F141" s="28"/>
+      <c r="F141" s="25"/>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" s="5"/>
@@ -5183,7 +5202,7 @@
       <c r="C142" s="5"/>
       <c r="D142" s="11"/>
       <c r="E142" s="9"/>
-      <c r="F142" s="28"/>
+      <c r="F142" s="25"/>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" s="5"/>
@@ -5191,7 +5210,7 @@
       <c r="C143" s="5"/>
       <c r="D143" s="12"/>
       <c r="E143" s="10"/>
-      <c r="F143" s="28"/>
+      <c r="F143" s="25"/>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" s="5"/>
@@ -5199,7 +5218,7 @@
       <c r="C144" s="5"/>
       <c r="D144" s="11"/>
       <c r="E144" s="9"/>
-      <c r="F144" s="28"/>
+      <c r="F144" s="25"/>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="5"/>
@@ -5207,7 +5226,7 @@
       <c r="C145" s="5"/>
       <c r="D145" s="12"/>
       <c r="E145" s="10"/>
-      <c r="F145" s="28"/>
+      <c r="F145" s="25"/>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="5"/>
@@ -5215,7 +5234,7 @@
       <c r="C146" s="5"/>
       <c r="D146" s="11"/>
       <c r="E146" s="9"/>
-      <c r="F146" s="28"/>
+      <c r="F146" s="25"/>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="5"/>
@@ -5223,7 +5242,7 @@
       <c r="C147" s="5"/>
       <c r="D147" s="11"/>
       <c r="E147" s="9"/>
-      <c r="F147" s="28"/>
+      <c r="F147" s="25"/>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="5"/>
@@ -5231,7 +5250,7 @@
       <c r="C148" s="5"/>
       <c r="D148" s="12"/>
       <c r="E148" s="10"/>
-      <c r="F148" s="28"/>
+      <c r="F148" s="25"/>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="5"/>
@@ -5239,7 +5258,7 @@
       <c r="C149" s="5"/>
       <c r="D149" s="11"/>
       <c r="E149" s="9"/>
-      <c r="F149" s="28"/>
+      <c r="F149" s="25"/>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" s="5"/>
@@ -5247,7 +5266,7 @@
       <c r="C150" s="5"/>
       <c r="D150" s="12"/>
       <c r="E150" s="10"/>
-      <c r="F150" s="28"/>
+      <c r="F150" s="25"/>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="5"/>
@@ -5255,7 +5274,7 @@
       <c r="C151" s="5"/>
       <c r="D151" s="12"/>
       <c r="E151" s="10"/>
-      <c r="F151" s="28"/>
+      <c r="F151" s="25"/>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" s="5"/>
@@ -5263,7 +5282,7 @@
       <c r="C152" s="5"/>
       <c r="D152" s="12"/>
       <c r="E152" s="10"/>
-      <c r="F152" s="28"/>
+      <c r="F152" s="25"/>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" s="5"/>
@@ -5271,7 +5290,7 @@
       <c r="C153" s="5"/>
       <c r="D153" s="12"/>
       <c r="E153" s="10"/>
-      <c r="F153" s="28"/>
+      <c r="F153" s="25"/>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" s="5"/>
@@ -5279,7 +5298,7 @@
       <c r="C154" s="5"/>
       <c r="D154" s="12"/>
       <c r="E154" s="10"/>
-      <c r="F154" s="28"/>
+      <c r="F154" s="25"/>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" s="5"/>
@@ -5287,7 +5306,7 @@
       <c r="C155" s="5"/>
       <c r="D155" s="12"/>
       <c r="E155" s="10"/>
-      <c r="F155" s="28"/>
+      <c r="F155" s="25"/>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" s="5"/>
@@ -5295,7 +5314,7 @@
       <c r="C156" s="5"/>
       <c r="D156" s="11"/>
       <c r="E156" s="9"/>
-      <c r="F156" s="28"/>
+      <c r="F156" s="25"/>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" s="5"/>
@@ -5303,7 +5322,7 @@
       <c r="C157" s="5"/>
       <c r="D157" s="12"/>
       <c r="E157" s="10"/>
-      <c r="F157" s="28"/>
+      <c r="F157" s="25"/>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" s="5"/>
@@ -5311,7 +5330,7 @@
       <c r="C158" s="5"/>
       <c r="D158" s="12"/>
       <c r="E158" s="10"/>
-      <c r="F158" s="28"/>
+      <c r="F158" s="25"/>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" s="5"/>
@@ -5319,7 +5338,7 @@
       <c r="C159" s="5"/>
       <c r="D159" s="12"/>
       <c r="E159" s="10"/>
-      <c r="F159" s="28"/>
+      <c r="F159" s="25"/>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" s="5"/>
@@ -5327,7 +5346,7 @@
       <c r="C160" s="5"/>
       <c r="D160" s="11"/>
       <c r="E160" s="9"/>
-      <c r="F160" s="28"/>
+      <c r="F160" s="25"/>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" s="5"/>
@@ -5335,7 +5354,7 @@
       <c r="C161" s="5"/>
       <c r="D161" s="11"/>
       <c r="E161" s="9"/>
-      <c r="F161" s="28"/>
+      <c r="F161" s="25"/>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" s="5"/>
@@ -5343,7 +5362,7 @@
       <c r="C162" s="5"/>
       <c r="D162" s="11"/>
       <c r="E162" s="9"/>
-      <c r="F162" s="28"/>
+      <c r="F162" s="25"/>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" s="5"/>
@@ -5351,7 +5370,7 @@
       <c r="C163" s="5"/>
       <c r="D163" s="12"/>
       <c r="E163" s="10"/>
-      <c r="F163" s="28"/>
+      <c r="F163" s="25"/>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" s="5"/>
@@ -5359,7 +5378,7 @@
       <c r="C164" s="5"/>
       <c r="D164" s="12"/>
       <c r="E164" s="10"/>
-      <c r="F164" s="28"/>
+      <c r="F164" s="25"/>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" s="5"/>
@@ -5367,7 +5386,7 @@
       <c r="C165" s="5"/>
       <c r="D165" s="12"/>
       <c r="E165" s="10"/>
-      <c r="F165" s="28"/>
+      <c r="F165" s="25"/>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" s="5"/>
@@ -5375,7 +5394,7 @@
       <c r="C166" s="5"/>
       <c r="D166" s="12"/>
       <c r="E166" s="10"/>
-      <c r="F166" s="28"/>
+      <c r="F166" s="25"/>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" s="5"/>
@@ -5383,7 +5402,7 @@
       <c r="C167" s="5"/>
       <c r="D167" s="12"/>
       <c r="E167" s="10"/>
-      <c r="F167" s="28"/>
+      <c r="F167" s="25"/>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" s="5"/>
@@ -5391,7 +5410,7 @@
       <c r="C168" s="5"/>
       <c r="D168" s="12"/>
       <c r="E168" s="10"/>
-      <c r="F168" s="28"/>
+      <c r="F168" s="25"/>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" s="5"/>
@@ -5399,7 +5418,7 @@
       <c r="C169" s="5"/>
       <c r="D169" s="12"/>
       <c r="E169" s="10"/>
-      <c r="F169" s="28"/>
+      <c r="F169" s="25"/>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" s="5"/>
@@ -5407,7 +5426,7 @@
       <c r="C170" s="5"/>
       <c r="D170" s="12"/>
       <c r="E170" s="10"/>
-      <c r="F170" s="28"/>
+      <c r="F170" s="25"/>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" s="5"/>
@@ -5415,7 +5434,7 @@
       <c r="C171" s="5"/>
       <c r="D171" s="12"/>
       <c r="E171" s="10"/>
-      <c r="F171" s="28"/>
+      <c r="F171" s="25"/>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" s="5"/>
@@ -5423,7 +5442,7 @@
       <c r="C172" s="5"/>
       <c r="D172" s="12"/>
       <c r="E172" s="10"/>
-      <c r="F172" s="28"/>
+      <c r="F172" s="25"/>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" s="5"/>
@@ -5431,7 +5450,7 @@
       <c r="C173" s="5"/>
       <c r="D173" s="12"/>
       <c r="E173" s="10"/>
-      <c r="F173" s="28"/>
+      <c r="F173" s="25"/>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" s="5"/>
@@ -5439,7 +5458,7 @@
       <c r="C174" s="5"/>
       <c r="D174" s="11"/>
       <c r="E174" s="9"/>
-      <c r="F174" s="28"/>
+      <c r="F174" s="25"/>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" s="5"/>

--- a/prix/prix.xlsx
+++ b/prix/prix.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\robinetterie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD65C618-4596-4488-ADC2-745945B72FA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAC933DE-AFF1-4998-ACCC-DFA103516828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="538">
   <si>
     <t>path</t>
   </si>
@@ -1632,6 +1632,24 @@
   </si>
   <si>
     <t>ideal-standard/silver.png</t>
+  </si>
+  <si>
+    <t>Set de douche GRAN CANARIA noir</t>
+  </si>
+  <si>
+    <t>Set de douche GRAN CANARIA chome</t>
+  </si>
+  <si>
+    <t>42170609</t>
+  </si>
+  <si>
+    <t>421706090</t>
+  </si>
+  <si>
+    <t>60179</t>
+  </si>
+  <si>
+    <t>60149</t>
   </si>
 </sst>
 </file>
@@ -1684,7 +1702,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1721,6 +1739,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1734,7 +1776,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1839,10 +1881,74 @@
     <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1851,10 +1957,13 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -2191,7 +2300,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{065E4AF0-A4F8-4CE3-9E23-EDCEACB756BD}">
-  <dimension ref="A1:J452"/>
+  <dimension ref="A1:J454"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.88671875" style="4" bestFit="1" customWidth="1"/>
@@ -2245,13 +2354,13 @@
         <v>6</v>
       </c>
       <c r="C3" s="18"/>
-      <c r="D3" s="36">
+      <c r="D3" s="11">
         <v>187</v>
       </c>
       <c r="E3" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="37">
+      <c r="F3" s="25">
         <v>1</v>
       </c>
       <c r="G3" s="23" t="s">
@@ -2267,13 +2376,13 @@
         <v>7</v>
       </c>
       <c r="C4" s="18"/>
-      <c r="D4" s="36">
+      <c r="D4" s="11">
         <v>137.45000000000002</v>
       </c>
       <c r="E4" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="37">
+      <c r="F4" s="25">
         <v>1</v>
       </c>
       <c r="G4" s="23" t="s">
@@ -2289,13 +2398,13 @@
         <v>8</v>
       </c>
       <c r="C5" s="18"/>
-      <c r="D5" s="36">
+      <c r="D5" s="11">
         <v>184.8</v>
       </c>
       <c r="E5" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="37">
+      <c r="F5" s="25">
         <v>3</v>
       </c>
       <c r="G5" s="23" t="s">
@@ -2311,13 +2420,13 @@
         <v>9</v>
       </c>
       <c r="C6" s="18"/>
-      <c r="D6" s="36">
+      <c r="D6" s="11">
         <v>145</v>
       </c>
       <c r="E6" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="37">
+      <c r="F6" s="25">
         <v>2</v>
       </c>
       <c r="G6" s="23" t="s">
@@ -2333,13 +2442,13 @@
         <v>10</v>
       </c>
       <c r="C7" s="18"/>
-      <c r="D7" s="36">
+      <c r="D7" s="11">
         <v>237.31</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="F7" s="37">
+      <c r="F7" s="25">
         <v>3</v>
       </c>
       <c r="G7" s="23" t="s">
@@ -2355,13 +2464,13 @@
         <v>11</v>
       </c>
       <c r="C8" s="18"/>
-      <c r="D8" s="36">
+      <c r="D8" s="11">
         <v>297</v>
       </c>
       <c r="E8" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="37">
+      <c r="F8" s="25">
         <v>3</v>
       </c>
       <c r="G8" s="23" t="s">
@@ -2399,13 +2508,13 @@
         <v>21</v>
       </c>
       <c r="C10" s="20"/>
-      <c r="D10" s="38">
+      <c r="D10" s="11">
         <v>156</v>
       </c>
       <c r="E10" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="39">
+      <c r="F10" s="25">
         <v>3</v>
       </c>
       <c r="G10" s="23" t="s">
@@ -2421,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="C11" s="20"/>
-      <c r="D11" s="38">
+      <c r="D11" s="11">
         <v>174</v>
       </c>
       <c r="E11" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="39">
+      <c r="F11" s="25">
         <v>3</v>
       </c>
       <c r="G11" s="23" t="s">
@@ -2443,13 +2552,13 @@
         <v>23</v>
       </c>
       <c r="C12" s="20"/>
-      <c r="D12" s="38">
+      <c r="D12" s="11">
         <v>305.48</v>
       </c>
       <c r="E12" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="F12" s="39">
+      <c r="F12" s="25">
         <v>0</v>
       </c>
       <c r="G12" s="23" t="s">
@@ -2465,13 +2574,13 @@
         <v>24</v>
       </c>
       <c r="C13" s="20"/>
-      <c r="D13" s="38">
+      <c r="D13" s="11">
         <v>255</v>
       </c>
       <c r="E13" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="39">
+      <c r="F13" s="25">
         <v>2</v>
       </c>
       <c r="G13" s="23" t="s">
@@ -2487,13 +2596,13 @@
         <v>25</v>
       </c>
       <c r="C14" s="20"/>
-      <c r="D14" s="38">
+      <c r="D14" s="11">
         <v>197</v>
       </c>
       <c r="E14" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="F14" s="39">
+      <c r="F14" s="25">
         <v>2</v>
       </c>
       <c r="G14" s="23" t="s">
@@ -2509,13 +2618,13 @@
         <v>26</v>
       </c>
       <c r="C15" s="20"/>
-      <c r="D15" s="38">
+      <c r="D15" s="11">
         <v>120</v>
       </c>
       <c r="E15" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="F15" s="39">
+      <c r="F15" s="25">
         <v>3</v>
       </c>
       <c r="G15" s="23" t="s">
@@ -2531,13 +2640,13 @@
         <v>27</v>
       </c>
       <c r="C16" s="20"/>
-      <c r="D16" s="38">
+      <c r="D16" s="11">
         <v>266.95</v>
       </c>
       <c r="E16" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="F16" s="39">
+      <c r="F16" s="25">
         <v>1</v>
       </c>
       <c r="G16" s="23" t="s">
@@ -2553,13 +2662,13 @@
         <v>28</v>
       </c>
       <c r="C17" s="20"/>
-      <c r="D17" s="38">
+      <c r="D17" s="11">
         <v>264.11</v>
       </c>
       <c r="E17" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="39">
+      <c r="F17" s="25">
         <v>2</v>
       </c>
       <c r="G17" s="23" t="s">
@@ -2575,13 +2684,13 @@
         <v>29</v>
       </c>
       <c r="C18" s="20"/>
-      <c r="D18" s="38">
+      <c r="D18" s="11">
         <v>228</v>
       </c>
       <c r="E18" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="39">
+      <c r="F18" s="25">
         <v>1</v>
       </c>
       <c r="G18" s="23" t="s">
@@ -2597,13 +2706,13 @@
         <v>30</v>
       </c>
       <c r="C19" s="20"/>
-      <c r="D19" s="38">
+      <c r="D19" s="11">
         <v>299</v>
       </c>
       <c r="E19" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="F19" s="39">
+      <c r="F19" s="25">
         <v>1</v>
       </c>
       <c r="G19" s="23" t="s">
@@ -2619,13 +2728,13 @@
         <v>31</v>
       </c>
       <c r="C20" s="20"/>
-      <c r="D20" s="38">
+      <c r="D20" s="11">
         <v>308</v>
       </c>
       <c r="E20" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="F20" s="39">
+      <c r="F20" s="25">
         <v>4</v>
       </c>
       <c r="G20" s="23" t="s">
@@ -2641,13 +2750,13 @@
         <v>32</v>
       </c>
       <c r="C21" s="20"/>
-      <c r="D21" s="38">
+      <c r="D21" s="11">
         <v>129</v>
       </c>
       <c r="E21" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="F21" s="39">
+      <c r="F21" s="25">
         <v>2</v>
       </c>
       <c r="G21" s="23" t="s">
@@ -2661,13 +2770,13 @@
         <v>33</v>
       </c>
       <c r="C22" s="20"/>
-      <c r="D22" s="38">
+      <c r="D22" s="11">
         <v>122.45</v>
       </c>
       <c r="E22" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="F22" s="39">
+      <c r="F22" s="25">
         <v>2</v>
       </c>
       <c r="G22" s="23" t="s">
@@ -2679,14 +2788,14 @@
       <c r="A23" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="38" t="s">
         <v>70</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="16">
         <v>146.41</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" s="38" t="s">
         <v>69</v>
       </c>
       <c r="F23" s="25">
@@ -2760,8 +2869,8 @@
       <c r="B27" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="40"/>
-      <c r="D27" s="41">
+      <c r="C27" s="36"/>
+      <c r="D27" s="37">
         <v>249.23000000000002</v>
       </c>
       <c r="E27" s="35" t="s">
@@ -2778,13 +2887,14 @@
       <c r="A28" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="D28" s="11">
+      <c r="C28" s="40"/>
+      <c r="D28" s="41">
         <v>184.09</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" s="39" t="s">
         <v>66</v>
       </c>
       <c r="F28" s="25">
@@ -2798,13 +2908,14 @@
       <c r="A29" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="D29" s="11">
+      <c r="C29" s="43"/>
+      <c r="D29" s="44">
         <v>68.37</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" s="42" t="s">
         <v>43</v>
       </c>
       <c r="F29" s="25">
@@ -2838,17 +2949,18 @@
       <c r="A31" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="D31" s="11">
+      <c r="C31" s="46"/>
+      <c r="D31" s="47">
         <v>99.93</v>
       </c>
-      <c r="E31" s="9" t="s">
+      <c r="E31" s="45" t="s">
         <v>47</v>
       </c>
       <c r="F31" s="25">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G31" s="23" t="s">
         <v>104</v>
@@ -2878,13 +2990,14 @@
       <c r="A33" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="D33" s="11">
+      <c r="C33" s="49"/>
+      <c r="D33" s="50">
         <v>143.02000000000001</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="E33" s="48" t="s">
         <v>48</v>
       </c>
       <c r="F33" s="25">
@@ -2916,17 +3029,18 @@
       <c r="A35" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="D35" s="11">
+      <c r="C35" s="52"/>
+      <c r="D35" s="53">
         <v>79.55</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="E35" s="51" t="s">
         <v>46</v>
       </c>
       <c r="F35" s="25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G35" s="23" t="s">
         <v>107</v>
@@ -2936,13 +3050,14 @@
       <c r="A36" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="D36" s="11">
+      <c r="C36" s="55"/>
+      <c r="D36" s="56">
         <v>143.12</v>
       </c>
-      <c r="E36" s="9" t="s">
+      <c r="E36" s="54" t="s">
         <v>49</v>
       </c>
       <c r="F36" s="25">
@@ -2956,13 +3071,14 @@
       <c r="A37" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="D37" s="11">
+      <c r="C37" s="55"/>
+      <c r="D37" s="56">
         <v>176.39000000000001</v>
       </c>
-      <c r="E37" s="9" t="s">
+      <c r="E37" s="54" t="s">
         <v>50</v>
       </c>
       <c r="F37" s="25">
@@ -2996,13 +3112,14 @@
       <c r="A39" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="D39" s="11">
+      <c r="C39" s="40"/>
+      <c r="D39" s="41">
         <v>413</v>
       </c>
-      <c r="E39" s="9" t="s">
+      <c r="E39" s="39" t="s">
         <v>65</v>
       </c>
       <c r="F39" s="25">
@@ -3034,7 +3151,7 @@
       <c r="A41" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="39" t="s">
         <v>115</v>
       </c>
       <c r="D41" s="11">
@@ -3074,7 +3191,7 @@
       <c r="A43" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="39" t="s">
         <v>121</v>
       </c>
       <c r="D43" s="11">
@@ -3114,7 +3231,7 @@
       <c r="A45" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="39" t="s">
         <v>127</v>
       </c>
       <c r="D45" s="11">
@@ -3267,13 +3384,13 @@
       <c r="B53" s="26" t="s">
         <v>188</v>
       </c>
-      <c r="D53" s="11">
+      <c r="D53" s="60">
         <v>363</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="F53" s="25">
+      <c r="F53" s="61">
         <v>3</v>
       </c>
       <c r="G53" s="9" t="s">
@@ -3287,13 +3404,13 @@
       <c r="B54" s="26" t="s">
         <v>189</v>
       </c>
-      <c r="D54" s="11">
+      <c r="D54" s="60">
         <v>217.8</v>
       </c>
       <c r="E54" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="F54" s="25">
+      <c r="F54" s="61">
         <v>3</v>
       </c>
       <c r="G54" s="9" t="s">
@@ -3307,14 +3424,14 @@
       <c r="B55" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="D55" s="11">
+      <c r="D55" s="60">
         <v>411.40000000000003</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="F55" s="25">
-        <v>3</v>
+      <c r="F55" s="61">
+        <v>2</v>
       </c>
       <c r="G55" s="9" t="s">
         <v>231</v>
@@ -3327,13 +3444,13 @@
       <c r="B56" s="26" t="s">
         <v>191</v>
       </c>
-      <c r="D56" s="11">
+      <c r="D56" s="60">
         <v>96.8</v>
       </c>
       <c r="E56" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="F56" s="25">
+      <c r="F56" s="61">
         <v>3</v>
       </c>
       <c r="G56" s="9" t="s">
@@ -3347,13 +3464,13 @@
       <c r="B57" s="26" t="s">
         <v>192</v>
       </c>
-      <c r="D57" s="11">
+      <c r="D57" s="60">
         <v>96.8</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="F57" s="25">
+      <c r="F57" s="61">
         <v>3</v>
       </c>
       <c r="G57" s="9" t="s">
@@ -3367,1841 +3484,1773 @@
       <c r="B58" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="D58" s="11">
+      <c r="D58" s="60">
         <v>84.7</v>
       </c>
       <c r="E58" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="F58" s="25">
+      <c r="F58" s="61">
         <v>3</v>
       </c>
       <c r="G58" s="9" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" s="5" t="s">
-        <v>279</v>
-      </c>
+    <row r="59" spans="1:7" s="58" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="5"/>
       <c r="B59" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="D59" s="11">
+        <v>532</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" s="60">
         <v>411.40000000000003</v>
       </c>
-      <c r="E59" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="F59" s="25">
+      <c r="E59" s="59" t="s">
+        <v>534</v>
+      </c>
+      <c r="F59" s="61">
+        <v>2</v>
+      </c>
+      <c r="G59" s="62" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" s="58" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="5"/>
+      <c r="B60" s="26" t="s">
+        <v>533</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" s="60">
+        <v>411.40000000000003</v>
+      </c>
+      <c r="E60" s="59" t="s">
+        <v>535</v>
+      </c>
+      <c r="F60" s="61">
         <v>1</v>
       </c>
-      <c r="G59" s="9" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="B60" s="26" t="s">
-        <v>195</v>
-      </c>
-      <c r="C60" s="5"/>
-      <c r="D60" s="11">
-        <v>53.24</v>
-      </c>
-      <c r="E60" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="F60" s="25">
-        <v>3</v>
-      </c>
-      <c r="G60" s="9" t="s">
-        <v>236</v>
+      <c r="G60" s="62" t="s">
+        <v>537</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B61" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="C61" s="5"/>
-      <c r="D61" s="11">
-        <v>66.55</v>
+        <v>194</v>
+      </c>
+      <c r="D61" s="60">
+        <v>53.24</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="F61" s="25">
+        <v>151</v>
+      </c>
+      <c r="F61" s="61">
         <v>3</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B62" s="26" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C62" s="5"/>
-      <c r="D62" s="11">
-        <v>84.7</v>
+      <c r="D62" s="60">
+        <v>66.55</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="F62" s="25">
-        <v>3</v>
+        <v>152</v>
+      </c>
+      <c r="F62" s="61">
+        <v>2</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B63" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="D63" s="11">
-        <v>96.8</v>
+        <v>196</v>
+      </c>
+      <c r="C63" s="5"/>
+      <c r="D63" s="60">
+        <v>84.7</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="F63" s="25">
+        <v>153</v>
+      </c>
+      <c r="F63" s="61">
         <v>3</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B64" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="D64" s="11">
-        <v>78.650000000000006</v>
+        <v>197</v>
+      </c>
+      <c r="C64" s="5"/>
+      <c r="D64" s="60">
+        <v>96.8</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="F64" s="25">
+        <v>154</v>
+      </c>
+      <c r="F64" s="61">
         <v>3</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B65" s="26" t="s">
-        <v>200</v>
-      </c>
-      <c r="D65" s="11">
-        <v>133.1</v>
+        <v>198</v>
+      </c>
+      <c r="D65" s="60">
+        <v>78.650000000000006</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="F65" s="25">
+        <v>155</v>
+      </c>
+      <c r="F65" s="61">
         <v>3</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B66" s="26" t="s">
-        <v>201</v>
-      </c>
-      <c r="D66" s="11">
-        <v>145.20000000000002</v>
+        <v>199</v>
+      </c>
+      <c r="D66" s="60">
+        <v>133.1</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="F66" s="25">
-        <v>3</v>
+        <v>156</v>
+      </c>
+      <c r="F66" s="61">
+        <v>1</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B67" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="D67" s="11">
-        <v>102.85000000000001</v>
+        <v>200</v>
+      </c>
+      <c r="D67" s="60">
+        <v>145.20000000000002</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="F67" s="25">
+        <v>157</v>
+      </c>
+      <c r="F67" s="61">
         <v>3</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B68" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="D68" s="11">
-        <v>169.4</v>
+        <v>201</v>
+      </c>
+      <c r="D68" s="60">
+        <v>102.85000000000001</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="F68" s="25">
+        <v>158</v>
+      </c>
+      <c r="F68" s="61">
         <v>3</v>
       </c>
       <c r="G68" s="9" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B69" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="D69" s="11">
-        <v>181.5</v>
+        <v>202</v>
+      </c>
+      <c r="D69" s="60">
+        <v>169.4</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="F69" s="25">
+        <v>159</v>
+      </c>
+      <c r="F69" s="61">
         <v>3</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B70" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="D70" s="11">
-        <v>121</v>
+        <v>203</v>
+      </c>
+      <c r="D70" s="60">
+        <v>181.5</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="F70" s="25">
+        <v>160</v>
+      </c>
+      <c r="F70" s="61">
         <v>3</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B71" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="D71" s="11">
-        <v>133.1</v>
+      <c r="D71" s="60">
+        <v>121</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="F71" s="25">
+        <v>161</v>
+      </c>
+      <c r="F71" s="61">
         <v>3</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B72" s="26" t="s">
         <v>205</v>
       </c>
-      <c r="D72" s="11">
-        <v>121</v>
+      <c r="D72" s="60">
+        <v>133.1</v>
       </c>
       <c r="E72" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="F72" s="25">
+        <v>162</v>
+      </c>
+      <c r="F72" s="61">
         <v>3</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B73" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="D73" s="11">
-        <v>133.1</v>
+        <v>204</v>
+      </c>
+      <c r="D73" s="60">
+        <v>121</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="F73" s="25">
+        <v>163</v>
+      </c>
+      <c r="F73" s="61">
         <v>3</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B74" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="D74" s="11">
-        <v>145.20000000000002</v>
+        <v>205</v>
+      </c>
+      <c r="D74" s="60">
+        <v>133.1</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="F74" s="25">
-        <v>1</v>
+        <v>164</v>
+      </c>
+      <c r="F74" s="61">
+        <v>3</v>
       </c>
       <c r="G74" s="9" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B75" s="26" t="s">
-        <v>208</v>
-      </c>
-      <c r="D75" s="11">
-        <v>157.30000000000001</v>
+        <v>206</v>
+      </c>
+      <c r="D75" s="60">
+        <v>145.20000000000002</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="F75" s="25">
-        <v>3</v>
+        <v>165</v>
+      </c>
+      <c r="F75" s="61">
+        <v>1</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B76" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="D76" s="11">
-        <v>53.24</v>
+        <v>207</v>
+      </c>
+      <c r="D76" s="60">
+        <v>157.30000000000001</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="F76" s="25">
+        <v>166</v>
+      </c>
+      <c r="F76" s="61">
         <v>3</v>
       </c>
       <c r="G76" s="9" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B77" s="26" t="s">
-        <v>210</v>
-      </c>
-      <c r="D77" s="11">
-        <v>84.7</v>
+        <v>208</v>
+      </c>
+      <c r="D77" s="60">
+        <v>53.24</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="F77" s="25">
+        <v>167</v>
+      </c>
+      <c r="F77" s="61">
         <v>3</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B78" s="26" t="s">
-        <v>211</v>
-      </c>
-      <c r="D78" s="11">
-        <v>72.600000000000009</v>
+        <v>209</v>
+      </c>
+      <c r="D78" s="60">
+        <v>84.7</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="F78" s="25">
+        <v>168</v>
+      </c>
+      <c r="F78" s="61">
         <v>3</v>
       </c>
       <c r="G78" s="9" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B79" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="D79" s="11">
-        <v>53.24</v>
+        <v>210</v>
+      </c>
+      <c r="D79" s="60">
+        <v>72.600000000000009</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="F79" s="25">
+        <v>169</v>
+      </c>
+      <c r="F79" s="61">
         <v>3</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="B80" s="26" t="s">
+        <v>211</v>
+      </c>
+      <c r="D80" s="60">
+        <v>53.24</v>
+      </c>
+      <c r="E80" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F80" s="61">
+        <v>2</v>
+      </c>
+      <c r="G80" s="9" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="B81" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="D81" s="60">
+        <v>60.5</v>
+      </c>
+      <c r="E81" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="F81" s="61">
+        <v>3</v>
+      </c>
+      <c r="G81" s="9" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="B80" s="26" t="s">
+      <c r="B82" s="26" t="s">
         <v>213</v>
       </c>
-      <c r="D80" s="11">
-        <v>60.5</v>
-      </c>
-      <c r="E80" s="9" t="s">
+      <c r="D82" s="60">
+        <v>66.55</v>
+      </c>
+      <c r="E82" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="F80" s="25">
-        <v>3</v>
-      </c>
-      <c r="G80" s="9" t="s">
+      <c r="F82" s="61">
+        <v>3</v>
+      </c>
+      <c r="G82" s="9" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A81" s="5" t="s">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="B81" s="26" t="s">
+      <c r="B83" s="26" t="s">
         <v>214</v>
       </c>
-      <c r="D81" s="11">
-        <v>66.55</v>
-      </c>
-      <c r="E81" s="9" t="s">
+      <c r="D83" s="60">
+        <v>90.75</v>
+      </c>
+      <c r="E83" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="F81" s="25">
-        <v>3</v>
-      </c>
-      <c r="G81" s="9" t="s">
+      <c r="F83" s="61">
+        <v>2</v>
+      </c>
+      <c r="G83" s="9" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A82" s="5" t="s">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="B82" s="26" t="s">
+      <c r="B84" s="26" t="s">
         <v>215</v>
       </c>
-      <c r="D82" s="11">
+      <c r="D84" s="60">
+        <v>102.85000000000001</v>
+      </c>
+      <c r="E84" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F84" s="61">
+        <v>3</v>
+      </c>
+      <c r="G84" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="B85" s="26" t="s">
+        <v>216</v>
+      </c>
+      <c r="C85" s="5"/>
+      <c r="D85" s="60">
+        <v>133.1</v>
+      </c>
+      <c r="E85" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="F85" s="61">
+        <v>3</v>
+      </c>
+      <c r="G85" s="9" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="B86" s="26" t="s">
+        <v>217</v>
+      </c>
+      <c r="C86" s="5"/>
+      <c r="D86" s="60">
+        <v>133.1</v>
+      </c>
+      <c r="E86" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F86" s="61">
+        <v>3</v>
+      </c>
+      <c r="G86" s="9" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B87" s="26" t="s">
+        <v>218</v>
+      </c>
+      <c r="C87" s="5"/>
+      <c r="D87" s="60">
+        <v>193.6</v>
+      </c>
+      <c r="E87" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="F87" s="61">
+        <v>3</v>
+      </c>
+      <c r="G87" s="9" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="B88" s="26" t="s">
+        <v>219</v>
+      </c>
+      <c r="C88" s="5"/>
+      <c r="D88" s="60">
+        <v>157.30000000000001</v>
+      </c>
+      <c r="E88" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F88" s="61">
+        <v>3</v>
+      </c>
+      <c r="G88" s="9" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="B89" s="26" t="s">
+        <v>220</v>
+      </c>
+      <c r="C89" s="5"/>
+      <c r="D89" s="60">
+        <v>114.95</v>
+      </c>
+      <c r="E89" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="F89" s="61">
+        <v>1</v>
+      </c>
+      <c r="G89" s="9" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="B90" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="C90" s="5"/>
+      <c r="D90" s="60">
         <v>90.75</v>
       </c>
-      <c r="E82" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="F82" s="25">
-        <v>3</v>
-      </c>
-      <c r="G82" s="9" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A83" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="B83" s="26" t="s">
-        <v>216</v>
-      </c>
-      <c r="C83" s="5"/>
-      <c r="D83" s="11">
+      <c r="E90" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F90" s="61">
+        <v>2</v>
+      </c>
+      <c r="G90" s="9" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B91" s="26" t="s">
+        <v>222</v>
+      </c>
+      <c r="C91" s="5"/>
+      <c r="D91" s="60">
+        <v>96.8</v>
+      </c>
+      <c r="E91" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="F91" s="61">
+        <v>3</v>
+      </c>
+      <c r="G91" s="9" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A92" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B92" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="C92" s="5"/>
+      <c r="D92" s="60">
+        <v>133.1</v>
+      </c>
+      <c r="E92" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F92" s="61">
+        <v>3</v>
+      </c>
+      <c r="G92" s="9" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="B93" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="C93" s="5"/>
+      <c r="D93" s="60">
+        <v>84.7</v>
+      </c>
+      <c r="E93" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="F93" s="61">
+        <v>3</v>
+      </c>
+      <c r="G93" s="9" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="B94" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="C94" s="5"/>
+      <c r="D94" s="60">
+        <v>84.7</v>
+      </c>
+      <c r="E94" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F94" s="61">
+        <v>3</v>
+      </c>
+      <c r="G94" s="9" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A95" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="B95" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="C95" s="5"/>
+      <c r="D95" s="60">
         <v>102.85000000000001</v>
       </c>
-      <c r="E83" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="F83" s="25">
-        <v>3</v>
-      </c>
-      <c r="G83" s="9" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A84" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="B84" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="C84" s="5"/>
-      <c r="D84" s="11">
-        <v>133.1</v>
-      </c>
-      <c r="E84" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="F84" s="25">
-        <v>3</v>
-      </c>
-      <c r="G84" s="9" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A85" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="B85" s="26" t="s">
-        <v>218</v>
-      </c>
-      <c r="C85" s="5"/>
-      <c r="D85" s="11">
-        <v>133.1</v>
-      </c>
-      <c r="E85" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="F85" s="25">
-        <v>3</v>
-      </c>
-      <c r="G85" s="9" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="B86" s="26" t="s">
-        <v>219</v>
-      </c>
-      <c r="C86" s="5"/>
-      <c r="D86" s="11">
-        <v>193.6</v>
-      </c>
-      <c r="E86" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="F86" s="25">
-        <v>3</v>
-      </c>
-      <c r="G86" s="9" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A87" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="B87" s="26" t="s">
-        <v>220</v>
-      </c>
-      <c r="C87" s="5"/>
-      <c r="D87" s="11">
-        <v>157.30000000000001</v>
-      </c>
-      <c r="E87" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="F87" s="25">
-        <v>3</v>
-      </c>
-      <c r="G87" s="9" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A88" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="B88" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="C88" s="5"/>
-      <c r="D88" s="11">
-        <v>114.95</v>
-      </c>
-      <c r="E88" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="F88" s="25">
-        <v>3</v>
-      </c>
-      <c r="G88" s="9" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A89" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="B89" s="26" t="s">
-        <v>222</v>
-      </c>
-      <c r="C89" s="5"/>
-      <c r="D89" s="11">
-        <v>90.75</v>
-      </c>
-      <c r="E89" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="F89" s="25">
-        <v>3</v>
-      </c>
-      <c r="G89" s="9" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A90" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="B90" s="26" t="s">
-        <v>223</v>
-      </c>
-      <c r="C90" s="5"/>
-      <c r="D90" s="11">
-        <v>96.8</v>
-      </c>
-      <c r="E90" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="F90" s="25">
-        <v>3</v>
-      </c>
-      <c r="G90" s="9" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A91" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="B91" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="C91" s="5"/>
-      <c r="D91" s="11">
-        <v>133.1</v>
-      </c>
-      <c r="E91" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="F91" s="25">
-        <v>3</v>
-      </c>
-      <c r="G91" s="9" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A92" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="B92" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="C92" s="5"/>
-      <c r="D92" s="11">
-        <v>84.7</v>
-      </c>
-      <c r="E92" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="F92" s="25">
-        <v>3</v>
-      </c>
-      <c r="G92" s="9" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A93" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="B93" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="C93" s="5"/>
-      <c r="D93" s="11">
-        <v>84.7</v>
-      </c>
-      <c r="E93" s="9" t="s">
+      <c r="E95" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="F93" s="25">
-        <v>3</v>
-      </c>
-      <c r="G93" s="9" t="s">
+      <c r="F95" s="61">
+        <v>3</v>
+      </c>
+      <c r="G95" s="9" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A94" s="5" t="s">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="B94" s="26" t="s">
+      <c r="B96" s="26" t="s">
         <v>227</v>
       </c>
-      <c r="C94" s="5"/>
-      <c r="D94" s="11">
+      <c r="C96" s="5"/>
+      <c r="D96" s="60">
         <v>102.85000000000001</v>
       </c>
-      <c r="E94" s="9" t="s">
+      <c r="E96" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="F94" s="25">
-        <v>3</v>
-      </c>
-      <c r="G94" s="9" t="s">
+      <c r="F96" s="61">
+        <v>3</v>
+      </c>
+      <c r="G96" s="9" t="s">
         <v>270</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A95" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="B95" s="26" t="s">
-        <v>228</v>
-      </c>
-      <c r="C95" s="5"/>
-      <c r="D95" s="11">
-        <v>102.85000000000001</v>
-      </c>
-      <c r="E95" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="F95" s="25">
-        <v>3</v>
-      </c>
-      <c r="G95" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A96" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="B96" s="9" t="s">
-        <v>402</v>
-      </c>
-      <c r="C96" s="5"/>
-      <c r="D96" s="11">
-        <v>102.85000000000001</v>
-      </c>
-      <c r="E96" s="9" t="s">
-        <v>359</v>
-      </c>
-      <c r="F96" s="25">
-        <v>3</v>
-      </c>
-      <c r="G96" s="9" t="s">
-        <v>444</v>
-      </c>
-      <c r="H96" s="9" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
-        <v>488</v>
-      </c>
-      <c r="B97" s="9" t="s">
-        <v>403</v>
+        <v>314</v>
+      </c>
+      <c r="B97" s="26" t="s">
+        <v>228</v>
       </c>
       <c r="C97" s="5"/>
-      <c r="D97" s="11">
+      <c r="D97" s="60">
         <v>102.85000000000001</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="F97" s="25">
+        <v>187</v>
+      </c>
+      <c r="F97" s="61">
         <v>3</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>445</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>403</v>
+        <v>271</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C98" s="5"/>
-      <c r="D98" s="11">
-        <v>108.9</v>
+      <c r="D98" s="63">
+        <v>102.85000000000001</v>
       </c>
       <c r="E98" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="F98" s="25">
-        <v>2</v>
+        <v>359</v>
+      </c>
+      <c r="F98" s="64">
+        <v>3</v>
       </c>
       <c r="G98" s="9" t="s">
-        <v>446</v>
-      </c>
-      <c r="H98" s="9" t="s">
-        <v>404</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="H98" s="9"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C99" s="5"/>
-      <c r="D99" s="11">
-        <v>121</v>
+      <c r="D99" s="63">
+        <v>108.9</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="F99" s="25">
-        <v>3</v>
+        <v>360</v>
+      </c>
+      <c r="F99" s="64">
+        <v>2</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="H99" s="9" t="s">
-        <v>405</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="H99" s="9"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C100" s="5"/>
-      <c r="D100" s="11">
-        <v>41.14</v>
+      <c r="D100" s="63">
+        <v>121</v>
       </c>
       <c r="E100" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="F100" s="25">
-        <v>6</v>
+        <v>361</v>
+      </c>
+      <c r="F100" s="64">
+        <v>3</v>
       </c>
       <c r="G100" s="9" t="s">
-        <v>448</v>
-      </c>
-      <c r="H100" s="9" t="s">
-        <v>406</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="H100" s="9"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C101" s="5"/>
-      <c r="D101" s="11">
-        <v>43.56</v>
+      <c r="D101" s="63">
+        <v>41.14</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="F101" s="25">
-        <v>3</v>
+        <v>362</v>
+      </c>
+      <c r="F101" s="64">
+        <v>6</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>449</v>
-      </c>
-      <c r="H101" s="9" t="s">
-        <v>407</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="H101" s="9"/>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C102" s="5"/>
-      <c r="D102" s="11">
+      <c r="D102" s="63">
         <v>43.56</v>
       </c>
       <c r="E102" s="9" t="s">
-        <v>365</v>
-      </c>
-      <c r="F102" s="25">
+        <v>363</v>
+      </c>
+      <c r="F102" s="64">
         <v>3</v>
       </c>
       <c r="G102" s="9" t="s">
-        <v>450</v>
-      </c>
-      <c r="H102" s="9" t="s">
-        <v>408</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="H102" s="9"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C103" s="5"/>
-      <c r="D103" s="11">
+      <c r="D103" s="63">
         <v>43.56</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="F103" s="25">
+        <v>364</v>
+      </c>
+      <c r="F103" s="64">
         <v>3</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="H103" s="9" t="s">
-        <v>409</v>
-      </c>
+        <v>449</v>
+      </c>
+      <c r="H103" s="9"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C104" s="5"/>
-      <c r="D104" s="11">
-        <v>45.980000000000004</v>
+      <c r="D104" s="63">
+        <v>43.56</v>
       </c>
       <c r="E104" s="9" t="s">
-        <v>367</v>
-      </c>
-      <c r="F104" s="25">
+        <v>365</v>
+      </c>
+      <c r="F104" s="64">
         <v>3</v>
       </c>
       <c r="G104" s="9" t="s">
-        <v>452</v>
-      </c>
-      <c r="H104" s="9" t="s">
-        <v>410</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="H104" s="9"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C105" s="5"/>
-      <c r="D105" s="11">
+      <c r="D105" s="63">
         <v>45.980000000000004</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>368</v>
-      </c>
-      <c r="F105" s="25">
+        <v>366</v>
+      </c>
+      <c r="F105" s="64">
         <v>3</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="H105" s="9" t="s">
-        <v>411</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="H105" s="9"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C106" s="5"/>
-      <c r="D106" s="11">
-        <v>38.72</v>
+      <c r="D106" s="63">
+        <v>45.980000000000004</v>
       </c>
       <c r="E106" s="9" t="s">
-        <v>369</v>
-      </c>
-      <c r="F106" s="25">
+        <v>367</v>
+      </c>
+      <c r="F106" s="64">
         <v>3</v>
       </c>
       <c r="G106" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="H106" s="9" t="s">
-        <v>412</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="H106" s="9"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C107" s="5"/>
-      <c r="D107" s="11">
-        <v>11.5</v>
+      <c r="D107" s="63">
+        <v>38.72</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>370</v>
-      </c>
-      <c r="F107" s="25">
+        <v>368</v>
+      </c>
+      <c r="F107" s="64">
         <v>3</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>455</v>
-      </c>
-      <c r="H107" s="9" t="s">
-        <v>413</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="H107" s="9"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C108" s="5"/>
-      <c r="D108" s="11">
-        <v>15.73</v>
+      <c r="D108" s="63">
+        <v>11.5</v>
       </c>
       <c r="E108" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="F108" s="25">
+        <v>369</v>
+      </c>
+      <c r="F108" s="64">
         <v>3</v>
       </c>
       <c r="G108" s="9" t="s">
-        <v>456</v>
-      </c>
-      <c r="H108" s="9" t="s">
-        <v>414</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="H108" s="9"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C109" s="5"/>
-      <c r="D109" s="11">
-        <v>24.2</v>
+      <c r="D109" s="63">
+        <v>15.73</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>372</v>
-      </c>
-      <c r="F109" s="25">
+        <v>370</v>
+      </c>
+      <c r="F109" s="64">
         <v>3</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>457</v>
-      </c>
-      <c r="H109" s="9" t="s">
-        <v>415</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="H109" s="9"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C110" s="5"/>
-      <c r="D110" s="11">
+      <c r="D110" s="63">
         <v>24.2</v>
       </c>
       <c r="E110" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="F110" s="25">
-        <v>3</v>
+        <v>371</v>
+      </c>
+      <c r="F110" s="64">
+        <v>1</v>
       </c>
       <c r="G110" s="9" t="s">
-        <v>458</v>
-      </c>
-      <c r="H110" s="9" t="s">
-        <v>416</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="H110" s="9"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B111" s="9" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C111" s="5"/>
-      <c r="D111" s="11">
-        <v>30.25</v>
+      <c r="D111" s="63">
+        <v>24.2</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="F111" s="25">
+        <v>372</v>
+      </c>
+      <c r="F111" s="64">
         <v>3</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="H111" s="9" t="s">
-        <v>417</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="H111" s="9"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B112" s="9" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C112" s="5"/>
-      <c r="D112" s="11">
-        <v>26.62</v>
+      <c r="D112" s="63">
+        <v>30.25</v>
       </c>
       <c r="E112" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="F112" s="25">
+        <v>373</v>
+      </c>
+      <c r="F112" s="64">
         <v>3</v>
       </c>
       <c r="G112" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="H112" s="9" t="s">
-        <v>418</v>
-      </c>
+        <v>458</v>
+      </c>
+      <c r="H112" s="9"/>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C113" s="5"/>
-      <c r="D113" s="11">
-        <v>12.1</v>
+      <c r="D113" s="63">
+        <v>26.62</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="F113" s="25">
+        <v>374</v>
+      </c>
+      <c r="F113" s="64">
         <v>3</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>461</v>
-      </c>
-      <c r="H113" s="9" t="s">
-        <v>419</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="H113" s="9"/>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C114" s="5"/>
-      <c r="D114" s="11">
-        <v>14.52</v>
+      <c r="D114" s="63">
+        <v>12.1</v>
       </c>
       <c r="E114" s="9" t="s">
-        <v>377</v>
-      </c>
-      <c r="F114" s="25">
+        <v>375</v>
+      </c>
+      <c r="F114" s="64">
         <v>3</v>
       </c>
       <c r="G114" s="9" t="s">
-        <v>462</v>
-      </c>
-      <c r="H114" s="9" t="s">
-        <v>420</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="H114" s="9"/>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C115" s="5"/>
-      <c r="D115" s="11">
-        <v>12.1</v>
+      <c r="D115" s="63">
+        <v>14.52</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="F115" s="25">
+        <v>376</v>
+      </c>
+      <c r="F115" s="64">
         <v>3</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>463</v>
-      </c>
-      <c r="H115" s="9" t="s">
-        <v>421</v>
-      </c>
+        <v>461</v>
+      </c>
+      <c r="H115" s="9"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C116" s="5"/>
-      <c r="D116" s="11">
-        <v>8.4700000000000006</v>
+      <c r="D116" s="63">
+        <v>12.1</v>
       </c>
       <c r="E116" s="9" t="s">
-        <v>379</v>
-      </c>
-      <c r="F116" s="25">
+        <v>377</v>
+      </c>
+      <c r="F116" s="64">
         <v>3</v>
       </c>
       <c r="G116" s="9" t="s">
-        <v>464</v>
-      </c>
-      <c r="H116" s="9" t="s">
-        <v>422</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="H116" s="9"/>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C117" s="5"/>
-      <c r="D117" s="11">
-        <v>4.84</v>
+      <c r="D117" s="63">
+        <v>8.4700000000000006</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="F117" s="25">
+        <v>378</v>
+      </c>
+      <c r="F117" s="64">
         <v>3</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>465</v>
-      </c>
-      <c r="H117" s="9" t="s">
-        <v>422</v>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="H117" s="9"/>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C118" s="5"/>
-      <c r="D118" s="11">
-        <v>8.4700000000000006</v>
+      <c r="D118" s="63">
+        <v>4.84</v>
       </c>
       <c r="E118" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="F118" s="25">
-        <v>3</v>
+        <v>379</v>
+      </c>
+      <c r="F118" s="64">
+        <v>2</v>
       </c>
       <c r="G118" s="9" t="s">
-        <v>466</v>
-      </c>
-      <c r="H118" s="9" t="s">
-        <v>423</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="H118" s="9"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C119" s="5"/>
-      <c r="D119" s="11">
-        <v>12.1</v>
+      <c r="D119" s="63">
+        <v>8.4700000000000006</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="F119" s="25">
+        <v>380</v>
+      </c>
+      <c r="F119" s="64">
         <v>3</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>467</v>
-      </c>
-      <c r="H119" s="9" t="s">
-        <v>424</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="H119" s="9"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C120" s="5"/>
-      <c r="D120" s="11">
-        <v>8.4700000000000006</v>
+      <c r="D120" s="63">
+        <v>12.1</v>
       </c>
       <c r="E120" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="F120" s="25">
-        <v>3</v>
+        <v>381</v>
+      </c>
+      <c r="F120" s="64">
+        <v>2</v>
       </c>
       <c r="G120" s="9" t="s">
-        <v>468</v>
-      </c>
-      <c r="H120" s="9" t="s">
-        <v>425</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="H120" s="9"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="5" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C121" s="5"/>
-      <c r="D121" s="11">
-        <v>18.150000000000002</v>
+      <c r="D121" s="63">
+        <v>8.4700000000000006</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="F121" s="25">
+        <v>382</v>
+      </c>
+      <c r="F121" s="64">
         <v>3</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>469</v>
-      </c>
-      <c r="H121" s="9" t="s">
-        <v>426</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="H121" s="9"/>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C122" s="5"/>
-      <c r="D122" s="11">
-        <v>12.1</v>
+      <c r="D122" s="63">
+        <v>18.150000000000002</v>
       </c>
       <c r="E122" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="F122" s="25">
+        <v>383</v>
+      </c>
+      <c r="F122" s="64">
         <v>3</v>
       </c>
       <c r="G122" s="9" t="s">
-        <v>470</v>
-      </c>
-      <c r="H122" s="9" t="s">
-        <v>427</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="H122" s="9"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B123" s="9" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C123" s="5"/>
-      <c r="D123" s="11">
-        <v>13.31</v>
+      <c r="D123" s="63">
+        <v>12.1</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="F123" s="25">
-        <v>3</v>
+        <v>384</v>
+      </c>
+      <c r="F123" s="64">
+        <v>2</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>471</v>
-      </c>
-      <c r="H123" s="9" t="s">
-        <v>428</v>
-      </c>
+        <v>469</v>
+      </c>
+      <c r="H123" s="9"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B124" s="9" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C124" s="5"/>
-      <c r="D124" s="11">
-        <v>12.1</v>
+      <c r="D124" s="63">
+        <v>13.31</v>
       </c>
       <c r="E124" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="F124" s="25">
+        <v>385</v>
+      </c>
+      <c r="F124" s="64">
         <v>3</v>
       </c>
       <c r="G124" s="9" t="s">
-        <v>472</v>
-      </c>
-      <c r="H124" s="9" t="s">
-        <v>429</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="H124" s="9"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B125" s="9" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C125" s="5"/>
-      <c r="D125" s="11">
-        <v>15.73</v>
+      <c r="D125" s="63">
+        <v>12.1</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="F125" s="25">
-        <v>3</v>
+        <v>386</v>
+      </c>
+      <c r="F125" s="64">
+        <v>2</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>473</v>
-      </c>
-      <c r="H125" s="9" t="s">
-        <v>430</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="H125" s="9"/>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B126" s="9" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C126" s="5"/>
-      <c r="D126" s="11">
+      <c r="D126" s="63">
         <v>15.73</v>
       </c>
       <c r="E126" s="9" t="s">
-        <v>389</v>
-      </c>
-      <c r="F126" s="25">
+        <v>387</v>
+      </c>
+      <c r="F126" s="64">
         <v>3</v>
       </c>
       <c r="G126" s="9" t="s">
-        <v>474</v>
-      </c>
-      <c r="H126" s="9" t="s">
-        <v>431</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="H126" s="9"/>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B127" s="9" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C127" s="5"/>
-      <c r="D127" s="11">
-        <v>14.52</v>
+      <c r="D127" s="63">
+        <v>15.73</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>390</v>
-      </c>
-      <c r="F127" s="25">
+        <v>388</v>
+      </c>
+      <c r="F127" s="64">
         <v>3</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>475</v>
-      </c>
-      <c r="H127" s="9" t="s">
-        <v>432</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="H127" s="9"/>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" s="5" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B128" s="9" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C128" s="5"/>
-      <c r="D128" s="11">
-        <v>15.73</v>
+      <c r="D128" s="63">
+        <v>14.52</v>
       </c>
       <c r="E128" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="F128" s="25">
-        <v>3</v>
+        <v>389</v>
+      </c>
+      <c r="F128" s="64">
+        <v>2</v>
       </c>
       <c r="G128" s="9" t="s">
-        <v>476</v>
-      </c>
-      <c r="H128" s="9" t="s">
-        <v>433</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="H128" s="9"/>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" s="5" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B129" s="9" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C129" s="5"/>
-      <c r="D129" s="11">
-        <v>13.31</v>
+      <c r="D129" s="63">
+        <v>15.73</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>392</v>
-      </c>
-      <c r="F129" s="25">
+        <v>390</v>
+      </c>
+      <c r="F129" s="64">
         <v>3</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>477</v>
-      </c>
-      <c r="H129" s="9" t="s">
-        <v>434</v>
-      </c>
+        <v>475</v>
+      </c>
+      <c r="H129" s="9"/>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" s="5" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B130" s="9" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C130" s="5"/>
-      <c r="D130" s="11">
-        <v>15.73</v>
+      <c r="D130" s="63">
+        <v>13.31</v>
       </c>
       <c r="E130" s="9" t="s">
-        <v>393</v>
-      </c>
-      <c r="F130" s="25">
+        <v>391</v>
+      </c>
+      <c r="F130" s="64">
         <v>3</v>
       </c>
       <c r="G130" s="9" t="s">
-        <v>478</v>
-      </c>
-      <c r="H130" s="9" t="s">
-        <v>435</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="H130" s="9"/>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" s="5" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C131" s="5"/>
-      <c r="D131" s="11">
-        <v>19.36</v>
+      <c r="D131" s="63">
+        <v>15.73</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>394</v>
-      </c>
-      <c r="F131" s="25">
+        <v>392</v>
+      </c>
+      <c r="F131" s="64">
         <v>3</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>479</v>
-      </c>
-      <c r="H131" s="9" t="s">
-        <v>436</v>
-      </c>
+        <v>477</v>
+      </c>
+      <c r="H131" s="9"/>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" s="5" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B132" s="9" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C132" s="5"/>
-      <c r="D132" s="11">
-        <v>18.150000000000002</v>
+      <c r="D132" s="63">
+        <v>19.36</v>
       </c>
       <c r="E132" s="9" t="s">
-        <v>395</v>
-      </c>
-      <c r="F132" s="25">
+        <v>393</v>
+      </c>
+      <c r="F132" s="64">
         <v>3</v>
       </c>
       <c r="G132" s="9" t="s">
-        <v>480</v>
-      </c>
-      <c r="H132" s="9" t="s">
-        <v>437</v>
-      </c>
+        <v>478</v>
+      </c>
+      <c r="H132" s="9"/>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" s="5" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B133" s="9" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C133" s="5"/>
-      <c r="D133" s="11">
-        <v>21.78</v>
+      <c r="D133" s="63">
+        <v>18.150000000000002</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="F133" s="25">
+        <v>394</v>
+      </c>
+      <c r="F133" s="64">
         <v>3</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>481</v>
-      </c>
-      <c r="H133" s="9" t="s">
-        <v>438</v>
-      </c>
+        <v>479</v>
+      </c>
+      <c r="H133" s="9"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" s="5" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B134" s="9" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C134" s="5"/>
-      <c r="D134" s="11">
-        <v>25.41</v>
+      <c r="D134" s="63">
+        <v>21.78</v>
       </c>
       <c r="E134" s="9" t="s">
-        <v>397</v>
-      </c>
-      <c r="F134" s="25">
-        <v>3</v>
+        <v>395</v>
+      </c>
+      <c r="F134" s="64">
+        <v>2</v>
       </c>
       <c r="G134" s="9" t="s">
-        <v>482</v>
-      </c>
-      <c r="H134" s="9" t="s">
-        <v>439</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="H134" s="9"/>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" s="5" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B135" s="9" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C135" s="5"/>
-      <c r="D135" s="11">
-        <v>36.300000000000004</v>
+      <c r="D135" s="63">
+        <v>25.41</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>398</v>
-      </c>
-      <c r="F135" s="25">
+        <v>396</v>
+      </c>
+      <c r="F135" s="64">
         <v>3</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>483</v>
-      </c>
-      <c r="H135" s="9" t="s">
-        <v>440</v>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="H135" s="9"/>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" s="5" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B136" s="9" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C136" s="5"/>
-      <c r="D136" s="11">
-        <v>43.56</v>
+      <c r="D136" s="63">
+        <v>36.300000000000004</v>
       </c>
       <c r="E136" s="9" t="s">
-        <v>399</v>
-      </c>
-      <c r="F136" s="25">
+        <v>397</v>
+      </c>
+      <c r="F136" s="64">
         <v>3</v>
       </c>
       <c r="G136" s="9" t="s">
-        <v>484</v>
-      </c>
-      <c r="H136" s="9" t="s">
-        <v>441</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="H136" s="9"/>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" s="5" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B137" s="9" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C137" s="5"/>
-      <c r="D137" s="11">
-        <v>42.35</v>
+      <c r="D137" s="63">
+        <v>43.56</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>400</v>
-      </c>
-      <c r="F137" s="25">
+        <v>398</v>
+      </c>
+      <c r="F137" s="64">
         <v>3</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>485</v>
-      </c>
-      <c r="H137" s="9" t="s">
-        <v>442</v>
-      </c>
+        <v>483</v>
+      </c>
+      <c r="H137" s="9"/>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="B138" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="C138" s="5"/>
+      <c r="D138" s="63">
+        <v>42.35</v>
+      </c>
+      <c r="E138" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="F138" s="64">
+        <v>2</v>
+      </c>
+      <c r="G138" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="H138" s="9"/>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A139" s="5" t="s">
+        <v>528</v>
+      </c>
+      <c r="B139" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="C139" s="5"/>
+      <c r="D139" s="63">
+        <v>54.45</v>
+      </c>
+      <c r="E139" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="F139" s="64">
+        <v>3</v>
+      </c>
+      <c r="G139" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="H139" s="9"/>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A140" s="5" t="s">
         <v>529</v>
       </c>
-      <c r="B138" s="9" t="s">
+      <c r="B140" s="9" t="s">
         <v>443</v>
       </c>
-      <c r="C138" s="5"/>
-      <c r="D138" s="11">
-        <v>54.45</v>
-      </c>
-      <c r="E138" s="9" t="s">
+      <c r="C140" s="5"/>
+      <c r="D140" s="63">
+        <v>8.4700000000000006</v>
+      </c>
+      <c r="E140" s="9" t="s">
         <v>401</v>
       </c>
-      <c r="F138" s="25">
-        <v>3</v>
-      </c>
-      <c r="G138" s="9" t="s">
+      <c r="F140" s="64">
+        <v>2</v>
+      </c>
+      <c r="G140" s="9" t="s">
         <v>486</v>
       </c>
-      <c r="H138" s="9" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A139" s="5"/>
-      <c r="B139" s="10"/>
-      <c r="C139" s="5"/>
-      <c r="D139" s="11">
-        <v>8.4700000000000006</v>
-      </c>
-      <c r="E139" s="10"/>
-      <c r="F139" s="25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A140" s="5"/>
-      <c r="B140" s="10"/>
-      <c r="C140" s="5"/>
-      <c r="D140" s="12"/>
-      <c r="E140" s="10"/>
-      <c r="F140" s="25"/>
+      <c r="H140" s="9"/>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" s="5"/>
       <c r="B141" s="10"/>
       <c r="C141" s="5"/>
-      <c r="D141" s="12"/>
+      <c r="D141" s="57"/>
       <c r="E141" s="10"/>
       <c r="F141" s="25"/>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" s="5"/>
-      <c r="B142" s="9"/>
+      <c r="B142" s="10"/>
       <c r="C142" s="5"/>
-      <c r="D142" s="11"/>
-      <c r="E142" s="9"/>
+      <c r="D142" s="57"/>
+      <c r="E142" s="10"/>
       <c r="F142" s="25"/>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
@@ -5238,18 +5287,18 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="5"/>
-      <c r="B147" s="9"/>
+      <c r="B147" s="10"/>
       <c r="C147" s="5"/>
-      <c r="D147" s="11"/>
-      <c r="E147" s="9"/>
+      <c r="D147" s="12"/>
+      <c r="E147" s="10"/>
       <c r="F147" s="25"/>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="5"/>
-      <c r="B148" s="10"/>
+      <c r="B148" s="9"/>
       <c r="C148" s="5"/>
-      <c r="D148" s="12"/>
-      <c r="E148" s="10"/>
+      <c r="D148" s="11"/>
+      <c r="E148" s="9"/>
       <c r="F148" s="25"/>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
@@ -5270,10 +5319,10 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="5"/>
-      <c r="B151" s="10"/>
+      <c r="B151" s="9"/>
       <c r="C151" s="5"/>
-      <c r="D151" s="12"/>
-      <c r="E151" s="10"/>
+      <c r="D151" s="11"/>
+      <c r="E151" s="9"/>
       <c r="F151" s="25"/>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
@@ -5310,10 +5359,10 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" s="5"/>
-      <c r="B156" s="9"/>
+      <c r="B156" s="10"/>
       <c r="C156" s="5"/>
-      <c r="D156" s="11"/>
-      <c r="E156" s="9"/>
+      <c r="D156" s="12"/>
+      <c r="E156" s="10"/>
       <c r="F156" s="25"/>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
@@ -5326,10 +5375,10 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" s="5"/>
-      <c r="B158" s="10"/>
+      <c r="B158" s="9"/>
       <c r="C158" s="5"/>
-      <c r="D158" s="12"/>
-      <c r="E158" s="10"/>
+      <c r="D158" s="11"/>
+      <c r="E158" s="9"/>
       <c r="F158" s="25"/>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
@@ -5342,18 +5391,18 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" s="5"/>
-      <c r="B160" s="9"/>
+      <c r="B160" s="10"/>
       <c r="C160" s="5"/>
-      <c r="D160" s="11"/>
-      <c r="E160" s="9"/>
+      <c r="D160" s="12"/>
+      <c r="E160" s="10"/>
       <c r="F160" s="25"/>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" s="5"/>
-      <c r="B161" s="9"/>
+      <c r="B161" s="10"/>
       <c r="C161" s="5"/>
-      <c r="D161" s="11"/>
-      <c r="E161" s="9"/>
+      <c r="D161" s="12"/>
+      <c r="E161" s="10"/>
       <c r="F161" s="25"/>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
@@ -5366,18 +5415,18 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" s="5"/>
-      <c r="B163" s="10"/>
+      <c r="B163" s="9"/>
       <c r="C163" s="5"/>
-      <c r="D163" s="12"/>
-      <c r="E163" s="10"/>
+      <c r="D163" s="11"/>
+      <c r="E163" s="9"/>
       <c r="F163" s="25"/>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" s="5"/>
-      <c r="B164" s="10"/>
+      <c r="B164" s="9"/>
       <c r="C164" s="5"/>
-      <c r="D164" s="12"/>
-      <c r="E164" s="10"/>
+      <c r="D164" s="11"/>
+      <c r="E164" s="9"/>
       <c r="F164" s="25"/>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
@@ -5454,27 +5503,27 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" s="5"/>
-      <c r="B174" s="9"/>
+      <c r="B174" s="10"/>
       <c r="C174" s="5"/>
-      <c r="D174" s="11"/>
-      <c r="E174" s="9"/>
+      <c r="D174" s="12"/>
+      <c r="E174" s="10"/>
       <c r="F174" s="25"/>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" s="5"/>
-      <c r="B175" s="5"/>
+      <c r="B175" s="10"/>
       <c r="C175" s="5"/>
-      <c r="D175" s="5"/>
-      <c r="E175" s="5"/>
-      <c r="F175" s="5"/>
+      <c r="D175" s="12"/>
+      <c r="E175" s="10"/>
+      <c r="F175" s="25"/>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" s="5"/>
-      <c r="B176" s="5"/>
+      <c r="B176" s="9"/>
       <c r="C176" s="5"/>
-      <c r="D176" s="5"/>
-      <c r="E176" s="5"/>
-      <c r="F176" s="5"/>
+      <c r="D176" s="11"/>
+      <c r="E176" s="9"/>
+      <c r="F176" s="25"/>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" s="5"/>
@@ -7661,13 +7710,29 @@
       <c r="F449" s="5"/>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A450" s="2"/>
+      <c r="A450" s="5"/>
+      <c r="B450" s="5"/>
+      <c r="C450" s="5"/>
+      <c r="D450" s="5"/>
+      <c r="E450" s="5"/>
+      <c r="F450" s="5"/>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A451" s="2"/>
+      <c r="A451" s="5"/>
+      <c r="B451" s="5"/>
+      <c r="C451" s="5"/>
+      <c r="D451" s="5"/>
+      <c r="E451" s="5"/>
+      <c r="F451" s="5"/>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A452" s="2"/>
+    </row>
+    <row r="453" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A453" s="2"/>
+    </row>
+    <row r="454" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A454" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
